--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC733A1-5A16-9A43-87C4-342F89D58CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD7734D-2D9D-7E4C-9D44-685866C06F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -175,28 +175,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -206,21 +185,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2502,6 +2472,9 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2511,15 +2484,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2527,6 +2491,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12945,7 +12915,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12964,9 +12934,11 @@
     <v>Powered by Refinitiv</v>
     <v>32.76</v>
     <v>7.77</v>
-    <v>0.82199999999999995</v>
-    <v>0.08</v>
-    <v>7.5399999999999998E-3</v>
+    <v>0.85419999999999996</v>
+    <v>1.0900000000000001</v>
+    <v>9.5447000000000004E-2</v>
+    <v>0.25</v>
+    <v>1.9983999999999998E-2</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12974,49 +12946,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.81</v>
+    <v>13.01</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46234.713113657031</v>
+    <v>46241.937500010936</v>
     <v>0</v>
-    <v>10.425000000000001</v>
-    <v>660769104</v>
+    <v>12.404999999999999</v>
+    <v>773266743</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.62</v>
-    <v>71.841399999999993</v>
-    <v>10.61</v>
-    <v>10.69</v>
+    <v>12.6</v>
+    <v>84.072599999999994</v>
+    <v>11.42</v>
+    <v>12.51</v>
+    <v>12.76</v>
     <v>61811890</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>233186</v>
-    <v>893566</v>
+    <v>1126137</v>
+    <v>748240</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13028,30 +12986,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.14</v>
+    <v>47.47</v>
     <v>39.47</v>
-    <v>0.41</v>
-    <v>8.8710000000000004E-3</v>
+    <v>-0.1</v>
+    <v>-2.1410000000000001E-3</v>
     <v>US</v>
-    <v>46.86</v>
+    <v>46.72</v>
     <v>Index</v>
-    <v>6</v>
-    <v>46.51</v>
+    <v>3</v>
+    <v>46.03</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.69</v>
-    <v>46.22</v>
-    <v>46.63</v>
+    <v>46.64</v>
+    <v>46.7</v>
+    <v>46.6</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13073,6 +13031,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13093,6 +13053,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13102,11 +13063,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13142,7 +13098,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13153,13 +13109,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13253,13 +13212,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13331,6 +13296,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13338,6 +13306,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13839,18 +13810,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="261" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="261"/>
-      <c r="E2" s="260" t="s">
+      <c r="C2" s="262"/>
+      <c r="E2" s="261" t="s">
         <v>306</v>
       </c>
-      <c r="F2" s="261"/>
-      <c r="H2" s="260" t="s">
+      <c r="F2" s="262"/>
+      <c r="H2" s="261" t="s">
         <v>348</v>
       </c>
-      <c r="I2" s="261"/>
+      <c r="I2" s="262"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -13865,15 +13836,15 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>672486.52</v>
+        <v>786979.08</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
       <c r="I3" s="215">
-        <f>'AVG target price'!C5</f>
-        <v>7.1607437568106667</v>
+        <f ca="1">'AVG target price'!C5</f>
+        <v>11.17815549296472</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13889,15 +13860,15 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>688384.52</v>
+        <v>802877.08</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
       <c r="I4" s="215">
-        <f>'AVG target price'!C6</f>
-        <v>14.316056156428232</v>
+        <f ca="1">'AVG target price'!C6</f>
+        <v>16.392704472065507</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13906,7 +13877,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>262</v>
@@ -13920,32 +13891,32 @@
         <v>PS price</v>
       </c>
       <c r="I5" s="215">
-        <f>'AVG target price'!C7</f>
-        <v>15.143111467278782</v>
+        <f ca="1">'AVG target price'!C7</f>
+        <v>16.966930100357011</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="212" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>12.76</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>256</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>-282.34227513432023</v>
+        <v>-330.41177380078074</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
       <c r="I6" s="215">
-        <f>'AVG target price'!C8</f>
-        <v>8.5561967040819642</v>
+        <f ca="1">'AVG target price'!C8</f>
+        <v>9.8346960356092232</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13954,38 +13925,38 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.08</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>215</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>1.3307981194132243</v>
+        <v>1.5573699227183759</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="216">
-        <f>'AVG target price'!C9</f>
-        <v>11.29402702114991</v>
+        <f ca="1">'AVG target price'!C9</f>
+        <v>13.593121525249117</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.25</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>284</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>-6.6915839443146014E-4</v>
+        <v>-5.718068134670111E-4</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -13993,7 +13964,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>5.6503930883995378E-2</v>
+        <v>8.6580457653806342E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14002,23 +13973,23 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>7.5399999999999998E-3</v>
+        <v>9.5447000000000004E-2</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>307</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>-3.5418004601835292E-3</v>
+        <v>-3.0265265323230956E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>1.9983999999999998E-2</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>312</v>
@@ -14031,7 +14002,7 @@
         <v>438</v>
       </c>
       <c r="I10" s="216">
-        <f>DDM!C26</f>
+        <f ca="1">DDM!C26</f>
         <v>0</v>
       </c>
     </row>
@@ -14073,7 +14044,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.82199999999999995</v>
+        <v>0.85419999999999996</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>116</v>
@@ -14089,7 +14060,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>893566</v>
+        <v>748240</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>117</v>
@@ -14105,7 +14076,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3640622565936339E-2</v>
+        <v>-2.0201299378885651E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14118,10 +14089,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="262" t="s">
+      <c r="B17" s="263" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="262"/>
+      <c r="C17" s="263"/>
       <c r="E17" s="188" t="s">
         <v>315</v>
       </c>
@@ -14194,14 +14165,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="262" t="s">
+      <c r="B25" s="263" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="262"/>
-      <c r="E25" s="260" t="s">
+      <c r="C25" s="263"/>
+      <c r="E25" s="261" t="s">
         <v>362</v>
       </c>
-      <c r="F25" s="261"/>
+      <c r="F25" s="262"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -14210,12 +14181,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="5">
+      <c r="E26" s="189" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.63</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14223,14 +14194,14 @@
         <v>186</v>
       </c>
       <c r="C27" s="225">
-        <v>7.0000000000000007E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="E27" s="190" t="s">
         <v>363</v>
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.6600000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14238,7 +14209,7 @@
         <v>367</v>
       </c>
       <c r="C28" s="225">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -14246,19 +14217,19 @@
         <v>437</v>
       </c>
       <c r="C29" s="225">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="263" t="s">
+      <c r="B33" s="260" t="s">
         <v>356</v>
       </c>
-      <c r="C33" s="263"/>
-      <c r="D33" s="263"/>
-      <c r="E33" s="263"/>
-      <c r="F33" s="263"/>
-      <c r="G33" s="263"/>
-      <c r="H33" s="263"/>
+      <c r="C33" s="260"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14277,24 +14248,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="263"/>
-      <c r="C39" s="263"/>
-      <c r="D39" s="263"/>
-      <c r="E39" s="263"/>
-      <c r="F39" s="263"/>
-      <c r="G39" s="263"/>
-      <c r="H39" s="263"/>
+      <c r="B39" s="260"/>
+      <c r="C39" s="260"/>
+      <c r="D39" s="260"/>
+      <c r="E39" s="260"/>
+      <c r="F39" s="260"/>
+      <c r="G39" s="260"/>
+      <c r="H39" s="260"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="263" t="s">
+      <c r="B42" s="260" t="s">
         <v>359</v>
       </c>
-      <c r="C42" s="263"/>
-      <c r="D42" s="263"/>
-      <c r="E42" s="263"/>
-      <c r="F42" s="263"/>
-      <c r="G42" s="263"/>
-      <c r="H42" s="263"/>
+      <c r="C42" s="260"/>
+      <c r="D42" s="260"/>
+      <c r="E42" s="260"/>
+      <c r="F42" s="260"/>
+      <c r="G42" s="260"/>
+      <c r="H42" s="260"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14381,24 +14352,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="263"/>
-      <c r="C55" s="263"/>
-      <c r="D55" s="263"/>
-      <c r="E55" s="263"/>
-      <c r="F55" s="263"/>
-      <c r="G55" s="263"/>
-      <c r="H55" s="263"/>
+      <c r="B55" s="260"/>
+      <c r="C55" s="260"/>
+      <c r="D55" s="260"/>
+      <c r="E55" s="260"/>
+      <c r="F55" s="260"/>
+      <c r="G55" s="260"/>
+      <c r="H55" s="260"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="263" t="s">
+      <c r="B58" s="260" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="263"/>
-      <c r="D58" s="263"/>
-      <c r="E58" s="263"/>
-      <c r="F58" s="263"/>
-      <c r="G58" s="263"/>
-      <c r="H58" s="263"/>
+      <c r="C58" s="260"/>
+      <c r="D58" s="260"/>
+      <c r="E58" s="260"/>
+      <c r="F58" s="260"/>
+      <c r="G58" s="260"/>
+      <c r="H58" s="260"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14447,28 +14418,28 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="263"/>
-      <c r="C68" s="263"/>
-      <c r="D68" s="263"/>
-      <c r="E68" s="263"/>
-      <c r="F68" s="263"/>
-      <c r="G68" s="263"/>
-      <c r="H68" s="263"/>
+      <c r="B68" s="260"/>
+      <c r="C68" s="260"/>
+      <c r="D68" s="260"/>
+      <c r="E68" s="260"/>
+      <c r="F68" s="260"/>
+      <c r="G68" s="260"/>
+      <c r="H68" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B68:H68"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14538,36 +14509,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="263" t="s">
+      <c r="S2" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="T2" s="263"/>
-      <c r="U2" s="263"/>
-      <c r="V2" s="263"/>
-      <c r="W2" s="263"/>
-      <c r="X2" s="263"/>
-      <c r="Y2" s="263"/>
-      <c r="Z2" s="263"/>
-      <c r="AA2" s="263" t="s">
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
+      <c r="AA2" s="260" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="263"/>
-      <c r="AC2" s="263"/>
+      <c r="AB2" s="260"/>
+      <c r="AC2" s="260"/>
       <c r="AE2" s="86" t="s">
         <v>127</v>
       </c>
@@ -16824,35 +16795,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="P2" s="263" t="s">
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
+      <c r="P2" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="Q2" s="263"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="263"/>
-      <c r="V2" s="263"/>
-      <c r="W2" s="263"/>
-      <c r="X2" s="263" t="s">
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260" t="s">
         <v>126</v>
       </c>
-      <c r="Y2" s="263"/>
-      <c r="Z2" s="263"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
       <c r="AB2" s="86" t="s">
         <v>127</v>
       </c>
@@ -18611,20 +18582,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="260"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="260"/>
+      <c r="L3" s="260"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -20022,12 +19993,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20035,6 +20000,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20072,20 +20043,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
       <c r="S2" s="274"/>
       <c r="T2" s="274"/>
       <c r="U2" s="274"/>
@@ -21094,16 +21065,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21166,10 +21137,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="260" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="263"/>
+      <c r="C4" s="260"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21186,7 +21157,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21195,7 +21166,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>672486.52</v>
+        <v>786979.08</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21213,7 +21184,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.6600000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21222,7 +21193,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.82199999999999995</v>
+        <v>0.85419999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21249,15 +21220,15 @@
       </c>
       <c r="C13" s="139">
         <f>Overview!C27</f>
-        <v>7.0000000000000007E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="263" t="s">
+      <c r="B15" s="260" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="263"/>
+      <c r="C15" s="260"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21265,7 +21236,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>0.11873296499607937</v>
+        <v>0.10324264683863323</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21274,7 +21245,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.88126703500392067</v>
+        <v>0.89675735316136673</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21283,7 +21254,7 @@
       </c>
       <c r="C18" s="46">
         <f>C13*(1-C12)</f>
-        <v>5.5300000000000009E-2</v>
+        <v>5.1350000000000007E-2</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21292,7 +21263,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.362E-2</v>
+        <v>8.5039000000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21301,7 +21272,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.0257482431311034E-2</v>
+        <v>8.156085847065328E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21346,20 +21317,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="260"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="260"/>
+      <c r="L3" s="260"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -21551,8 +21522,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="130">
-        <f>L7*(1+C14)/(C15-C14)</f>
-        <v>615792.44390766555</v>
+        <f ca="1">L7*(1+C14)/(C15-C14)</f>
+        <v>900268.79625322053</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21605,24 +21576,24 @@
       <c r="F10" s="141"/>
       <c r="G10" s="142"/>
       <c r="H10" s="130">
-        <f>H7/(1+$C$15)^H9</f>
-        <v>12920.926382196521</v>
+        <f ca="1">H7/(1+$C$15)^H9</f>
+        <v>13260.676153275655</v>
       </c>
       <c r="I10" s="130">
-        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>8364.1534418225347</v>
+        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
+        <v>8809.7995165519278</v>
       </c>
       <c r="J10" s="130">
-        <f t="shared" si="0"/>
-        <v>19970.321218412631</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>21587.437904157301</v>
       </c>
       <c r="K10" s="130">
-        <f t="shared" si="0"/>
-        <v>27422.86677334044</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30422.921833915905</v>
       </c>
       <c r="L10" s="130">
-        <f t="shared" si="0"/>
-        <v>32244.956792243785</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>36713.169900450281</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21640,15 +21611,15 @@
       <c r="J11" s="141"/>
       <c r="K11" s="141"/>
       <c r="L11" s="130">
-        <f>L8/(1+C15)^L9</f>
-        <v>365442.84364542959</v>
+        <f ca="1">L8/(1+C15)^L9</f>
+        <v>608299.40044307348</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="263" t="s">
+      <c r="B13" s="260" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="263"/>
+      <c r="C13" s="260"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21663,23 +21634,23 @@
         <v>179</v>
       </c>
       <c r="C15" s="139">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>8.156085847065328E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="263" t="s">
+      <c r="B18" s="260" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="263"/>
+      <c r="C18" s="260"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>201</v>
       </c>
       <c r="C19" s="64">
-        <f>SUM(H10:L10)</f>
-        <v>100923.22460801591</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>110794.00530835107</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21687,8 +21658,8 @@
         <v>197</v>
       </c>
       <c r="C20" s="64">
-        <f>L11</f>
-        <v>365442.84364542959</v>
+        <f ca="1">L11</f>
+        <v>608299.40044307348</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21696,8 +21667,8 @@
         <v>202</v>
       </c>
       <c r="C21" s="95">
-        <f>C19+C20</f>
-        <v>466366.0682534455</v>
+        <f ca="1">C19+C20</f>
+        <v>719093.40575142461</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21723,8 +21694,8 @@
         <v>205</v>
       </c>
       <c r="C24" s="95">
-        <f>C21+C22-C23</f>
-        <v>450468.06825344544</v>
+        <f ca="1">C21+C22-C23</f>
+        <v>703195.40575142461</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21741,8 +21712,8 @@
         <v>206</v>
       </c>
       <c r="C26" s="146">
-        <f>C24/C25</f>
-        <v>7.1607437568106667</v>
+        <f ca="1">C24/C25</f>
+        <v>11.17815549296472</v>
       </c>
     </row>
   </sheetData>
@@ -21785,20 +21756,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22730,10 +22701,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="263" t="s">
+      <c r="B37" s="260" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="263"/>
+      <c r="C37" s="260"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22750,8 +22721,8 @@
         <v>179</v>
       </c>
       <c r="C39" s="139">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>8.156085847065328E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22776,8 +22747,8 @@
         <v>369</v>
       </c>
       <c r="C42" s="24">
-        <f>C41/(1+C39)^5-G30+G31</f>
-        <v>916492.46068858716</v>
+        <f ca="1">C41/(1+C39)^5-G30+G31</f>
+        <v>1047130.2529286968</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -22803,8 +22774,8 @@
         <v>427</v>
       </c>
       <c r="C45" s="24">
-        <f>C42+C43-C44</f>
-        <v>900594.46068858716</v>
+        <f ca="1">C42+C43-C44</f>
+        <v>1031232.2529286968</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22821,15 +22792,15 @@
         <v>223</v>
       </c>
       <c r="C47" s="146">
-        <f>C45/C46</f>
-        <v>14.316056156428232</v>
+        <f ca="1">C45/C46</f>
+        <v>16.392704472065507</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="263" t="s">
+      <c r="B49" s="260" t="s">
         <v>224</v>
       </c>
-      <c r="C49" s="263"/>
+      <c r="C49" s="260"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22845,8 +22816,8 @@
         <v>368</v>
       </c>
       <c r="C51" s="139">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>8.5039000000000003E-2</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -22880,15 +22851,15 @@
         <v>223</v>
       </c>
       <c r="C55" s="146">
-        <f>C54/(1+C51)^5</f>
-        <v>15.143111467278782</v>
+        <f ca="1">C54/(1+C51)^5</f>
+        <v>16.966930100357011</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="263" t="s">
+      <c r="B57" s="260" t="s">
         <v>342</v>
       </c>
-      <c r="C57" s="263"/>
+      <c r="C57" s="260"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22904,8 +22875,8 @@
         <v>179</v>
       </c>
       <c r="C59" s="139">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>8.156085847065328E-2</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -22930,8 +22901,8 @@
         <v>369</v>
       </c>
       <c r="C62" s="24">
-        <f>C61/(1+C59)^5-G30+G31</f>
-        <v>554151.2222603882</v>
+        <f ca="1">C61/(1+C59)^5-G30+G31</f>
+        <v>634579.05820810504</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -22957,8 +22928,8 @@
         <v>427</v>
       </c>
       <c r="C65" s="24">
-        <f>C62+C63-C64</f>
-        <v>538253.2222603882</v>
+        <f ca="1">C62+C63-C64</f>
+        <v>618681.05820810504</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22975,8 +22946,8 @@
         <v>223</v>
       </c>
       <c r="C67" s="146">
-        <f>C65/C66</f>
-        <v>8.5561967040819642</v>
+        <f ca="1">C65/C66</f>
+        <v>9.8346960356092232</v>
       </c>
     </row>
   </sheetData>
@@ -23028,10 +22999,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="260" t="s">
         <v>229</v>
       </c>
-      <c r="C4" s="263"/>
+      <c r="C4" s="260"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23039,8 +23010,8 @@
         <v>230</v>
       </c>
       <c r="C5" s="137">
-        <f>DCF!C26</f>
-        <v>7.1607437568106667</v>
+        <f ca="1">DCF!C26</f>
+        <v>11.17815549296472</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23048,8 +23019,8 @@
         <v>231</v>
       </c>
       <c r="C6" s="137">
-        <f>Multiples!C47</f>
-        <v>14.316056156428232</v>
+        <f ca="1">Multiples!C47</f>
+        <v>16.392704472065507</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23057,8 +23028,8 @@
         <v>232</v>
       </c>
       <c r="C7" s="137">
-        <f>Multiples!C55</f>
-        <v>15.143111467278782</v>
+        <f ca="1">Multiples!C55</f>
+        <v>16.966930100357011</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23066,8 +23037,8 @@
         <v>343</v>
       </c>
       <c r="C8" s="137">
-        <f>Multiples!C67</f>
-        <v>8.5561967040819642</v>
+        <f ca="1">Multiples!C67</f>
+        <v>9.8346960356092232</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23075,8 +23046,8 @@
         <v>233</v>
       </c>
       <c r="C9" s="146">
-        <f>AVERAGE(C5:C8)</f>
-        <v>11.29402702114991</v>
+        <f ca="1">AVERAGE(C5:C8)</f>
+        <v>13.593121525249117</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23085,7 +23056,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23094,7 +23065,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>5.6503930883995378E-2</v>
+        <v>8.6580457653806342E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23150,20 +23121,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23526,10 +23497,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="263" t="s">
+      <c r="B20" s="260" t="s">
         <v>432</v>
       </c>
-      <c r="C20" s="263"/>
+      <c r="C20" s="260"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23563,8 +23534,8 @@
         <v>368</v>
       </c>
       <c r="C24" s="139">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>8.5039000000000003E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23580,7 +23551,7 @@
         <v>223</v>
       </c>
       <c r="C26" s="146">
-        <f>C23/(C24-C25)</f>
+        <f ca="1">C23/(C24-C25)</f>
         <v>0</v>
       </c>
     </row>
@@ -23630,20 +23601,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="260"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="260"/>
+      <c r="L3" s="260"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -23816,8 +23787,8 @@
       <c r="J8" s="141"/>
       <c r="K8" s="141"/>
       <c r="L8" s="130">
-        <f>L7*(1+C20)/(C21-C20)</f>
-        <v>811159.27833333344</v>
+        <f ca="1">L7*(1+C20)/(C21-C20)</f>
+        <v>1185888.840143481</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -23870,24 +23841,24 @@
       <c r="F10" s="141"/>
       <c r="G10" s="142"/>
       <c r="H10" s="130">
-        <f>H7/(1+$C$21)^H9</f>
-        <v>11171.17117117117</v>
+        <f ca="1">H7/(1+$C$21)^H9</f>
+        <v>11464.911939891968</v>
       </c>
       <c r="I10" s="130">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>15599.383166950733</v>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
+        <v>16430.525723684674</v>
       </c>
       <c r="J10" s="130">
-        <f t="shared" si="1"/>
-        <v>21782.922440336606</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>23546.816318521822</v>
       </c>
       <c r="K10" s="130">
-        <f t="shared" si="1"/>
-        <v>30417.594398668236</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>33745.271944582979</v>
       </c>
       <c r="L10" s="130">
-        <f t="shared" si="1"/>
-        <v>42475.019205347533</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>48360.821404043854</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -23905,8 +23876,8 @@
       <c r="J11" s="141"/>
       <c r="K11" s="141"/>
       <c r="L11" s="130">
-        <f>L8/(1+C21)^L9</f>
-        <v>481383.55099393876</v>
+        <f ca="1">L8/(1+C21)^L9</f>
+        <v>801288.98552706081</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23922,7 +23893,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23930,8 +23901,8 @@
         <v>239</v>
       </c>
       <c r="C16" s="160">
-        <f>C36</f>
-        <v>9.4954319772279341</v>
+        <f ca="1">C36</f>
+        <v>14.866681758522391</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23969,8 +23940,8 @@
         <v>179</v>
       </c>
       <c r="C21" s="226">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>8.156085847065328E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23988,7 +23959,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>660770.27999999991</v>
+        <v>773268.12</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24015,7 +23986,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>676668.27999999991</v>
+        <v>789166.12</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24030,8 +24001,8 @@
         <v>201</v>
       </c>
       <c r="C29" s="165">
-        <f>SUM(H10:L10)</f>
-        <v>121446.09038247429</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>133548.34733072529</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24039,8 +24010,8 @@
         <v>197</v>
       </c>
       <c r="C30" s="165">
-        <f>L11</f>
-        <v>481383.55099393876</v>
+        <f ca="1">L11</f>
+        <v>801288.98552706081</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24048,8 +24019,8 @@
         <v>202</v>
       </c>
       <c r="C31" s="168">
-        <f>C29+C30</f>
-        <v>602829.64137641306</v>
+        <f ca="1">C29+C30</f>
+        <v>934837.3328577861</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24075,8 +24046,8 @@
         <v>205</v>
       </c>
       <c r="C34" s="168">
-        <f>C31+C32-C33</f>
-        <v>586931.64137641306</v>
+        <f ca="1">C31+C32-C33</f>
+        <v>918939.3328577861</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24093,8 +24064,8 @@
         <v>206</v>
       </c>
       <c r="C36" s="171">
-        <f>C34/C35</f>
-        <v>9.4954319772279341</v>
+        <f ca="1">C34/C35</f>
+        <v>14.866681758522391</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -24541,17 +24512,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31507,7 +31478,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31578,7 +31549,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32656,7 +32627,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-282.34227513432023</v>
+        <v>-330.41177380078074</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32693,7 +32664,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3307981194132243</v>
+        <v>1.5573699227183759</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32754,7 +32725,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.8401244256314571</v>
+        <v>2.1534103428109943</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32815,7 +32786,7 @@
       </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>672486.52</v>
+        <v>786979.08</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32876,7 +32847,7 @@
       </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>688384.52</v>
+        <v>802877.08</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32913,7 +32884,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>1.3890201981476624</v>
+        <v>1.6200429387195059</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32950,7 +32921,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC14</f>
-        <v>201.04688084112149</v>
+        <v>234.48512850467287</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33085,7 +33056,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="155">AC153/AC157</f>
-        <v>-1494.4144888888889</v>
+        <v>-1748.8424</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33122,7 +33093,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>513.33670395227443</v>
+        <v>598.7151976137211</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33159,7 +33130,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="158">AC157/AC153</f>
-        <v>-6.6915839443146014E-4</v>
+        <v>-5.718068134670111E-4</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33196,7 +33167,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-3.5418004601835292E-3</v>
+        <v>-3.0265265323230956E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33810,7 +33781,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>-2.3640622565936339E-2</v>
+        <v>-2.0201299378885651E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35408,15 +35379,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="260" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="263"/>
-      <c r="E4" s="263" t="s">
+      <c r="C4" s="260"/>
+      <c r="E4" s="260" t="s">
         <v>259</v>
       </c>
-      <c r="F4" s="263"/>
-      <c r="G4" s="263"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35424,7 +35395,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35440,7 +35411,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>672486.52</v>
+        <v>786979.08</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35460,7 +35431,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>688384.52</v>
+        <v>802877.08</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35480,7 +35451,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-282.34227513432023</v>
+        <v>-330.41177380078074</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>262</v>
@@ -35500,7 +35471,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3307981194132243</v>
+        <v>1.5573699227183759</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>263</v>
@@ -35520,7 +35491,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8401244256314571</v>
+        <v>2.1534103428109943</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35540,7 +35511,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3890201981476624</v>
+        <v>1.6200429387195059</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35549,18 +35520,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>201.04688084112149</v>
+        <v>234.48512850467287</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="263" t="s">
+      <c r="B15" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="263"/>
-      <c r="E15" s="263" t="s">
+      <c r="C15" s="260"/>
+      <c r="E15" s="260" t="s">
         <v>265</v>
       </c>
-      <c r="F15" s="263"/>
+      <c r="F15" s="260"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35611,14 +35582,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="263" t="s">
+      <c r="B21" s="260" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="263"/>
-      <c r="E21" s="263" t="s">
+      <c r="C21" s="260"/>
+      <c r="E21" s="260" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="263"/>
+      <c r="F21" s="260"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35687,14 +35658,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="263" t="s">
+      <c r="B29" s="260" t="s">
         <v>269</v>
       </c>
-      <c r="C29" s="263"/>
-      <c r="E29" s="263" t="s">
+      <c r="C29" s="260"/>
+      <c r="E29" s="260" t="s">
         <v>275</v>
       </c>
-      <c r="F29" s="263"/>
+      <c r="F29" s="260"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35770,14 +35741,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="263" t="s">
+      <c r="B37" s="260" t="s">
         <v>287</v>
       </c>
-      <c r="C37" s="263"/>
-      <c r="E37" s="263" t="s">
+      <c r="C37" s="260"/>
+      <c r="E37" s="260" t="s">
         <v>290</v>
       </c>
-      <c r="F37" s="263"/>
+      <c r="F37" s="260"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35785,7 +35756,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.5418004601835292E-3</v>
+        <v>-3.0265265323230956E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>289</v>
@@ -35801,7 +35772,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>-6.6915839443146014E-4</v>
+        <v>-5.718068134670111E-4</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>291</v>
@@ -35846,14 +35817,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="263" t="s">
+      <c r="B45" s="260" t="s">
         <v>298</v>
       </c>
-      <c r="C45" s="263"/>
-      <c r="E45" s="263" t="s">
+      <c r="C45" s="260"/>
+      <c r="E45" s="260" t="s">
         <v>304</v>
       </c>
-      <c r="F45" s="263"/>
+      <c r="F45" s="260"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35886,18 +35857,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3640622565936339E-2</v>
+        <v>-2.0201299378885651E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="263" t="s">
+      <c r="B51" s="260" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="263"/>
-      <c r="E51" s="263" t="s">
+      <c r="C51" s="260"/>
+      <c r="E51" s="260" t="s">
         <v>322</v>
       </c>
-      <c r="F51" s="263"/>
+      <c r="F51" s="260"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36065,7 +36036,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC120</f>
-        <v>10.69</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36094,7 +36065,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>672486.52</v>
+        <v>786979.08</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36123,7 +36094,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>688384.52</v>
+        <v>802877.08</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36152,7 +36123,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-282.34227513432023</v>
+        <v>-330.41177380078074</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36181,7 +36152,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3307981194132243</v>
+        <v>1.5573699227183759</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36210,7 +36181,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8401244256314571</v>
+        <v>2.1534103428109943</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36239,7 +36210,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3890201981476624</v>
+        <v>1.6200429387195059</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36268,7 +36239,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>201.04688084112149</v>
+        <v>234.48512850467287</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37041,7 +37012,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.5418004601835292E-3</v>
+        <v>-3.0265265323230956E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37070,7 +37041,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>-6.6915839443146014E-4</v>
+        <v>-5.718068134670111E-4</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37393,7 +37364,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3640622565936339E-2</v>
+        <v>-2.0201299378885651E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37882,14 +37853,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="264" t="s">
         <v>332</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="F3" s="268" t="s">
+      <c r="D3" s="265"/>
+      <c r="F3" s="266" t="s">
         <v>333</v>
       </c>
-      <c r="G3" s="267"/>
+      <c r="G3" s="265"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37956,19 +37927,19 @@
       <c r="B7" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="264">
+      <c r="C7" s="267">
         <f>Statement!AA91</f>
         <v>3.0440633681443646E-2</v>
       </c>
-      <c r="D7" s="265"/>
-      <c r="F7" s="264">
+      <c r="D7" s="268"/>
+      <c r="F7" s="267">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12937310240132488</v>
       </c>
-      <c r="G7" s="265"/>
+      <c r="G7" s="268"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -37995,19 +37966,19 @@
       <c r="B9" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="264">
+      <c r="C9" s="267">
         <f>Statement!AA92</f>
         <v>7.2889329041842046E-2</v>
       </c>
-      <c r="D9" s="265"/>
-      <c r="F9" s="264">
+      <c r="D9" s="268"/>
+      <c r="F9" s="267">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13842112176540128</v>
       </c>
-      <c r="G9" s="265"/>
+      <c r="G9" s="268"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -38034,19 +38005,19 @@
       <c r="B11" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C11" s="264">
+      <c r="C11" s="267">
         <f>Statement!AA93</f>
         <v>1.0660267429652618E-2</v>
       </c>
-      <c r="D11" s="265"/>
-      <c r="F11" s="264">
+      <c r="D11" s="268"/>
+      <c r="F11" s="267">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12495023821448292</v>
       </c>
-      <c r="G11" s="265"/>
+      <c r="G11" s="268"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -38073,19 +38044,19 @@
       <c r="B13" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="264">
+      <c r="C13" s="267">
         <f>Statement!AA99</f>
         <v>-0.12340351714118437</v>
       </c>
-      <c r="D13" s="265"/>
-      <c r="F13" s="264">
+      <c r="D13" s="268"/>
+      <c r="F13" s="267">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.7704231252618349E-3</v>
       </c>
-      <c r="G13" s="265"/>
+      <c r="G13" s="268"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -38112,19 +38083,19 @@
       <c r="B15" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C15" s="264">
+      <c r="C15" s="267">
         <f>Statement!AA100</f>
         <v>2.2145042289004859</v>
       </c>
-      <c r="D15" s="265"/>
-      <c r="F15" s="264">
+      <c r="D15" s="268"/>
+      <c r="F15" s="267">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>3.0532400365074537</v>
       </c>
-      <c r="G15" s="265"/>
+      <c r="G15" s="268"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -38151,19 +38122,19 @@
       <c r="B17" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="264">
+      <c r="C17" s="267">
         <f>Statement!AA102</f>
         <v>1.2870289644483193</v>
       </c>
-      <c r="D17" s="265"/>
-      <c r="F17" s="264">
+      <c r="D17" s="268"/>
+      <c r="F17" s="267">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.7570260602963721</v>
       </c>
-      <c r="G17" s="265"/>
+      <c r="G17" s="268"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -38190,22 +38161,22 @@
       <c r="B19" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="264">
+      <c r="C19" s="267">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>8.8459599655267736E-3</v>
       </c>
-      <c r="D19" s="265"/>
-      <c r="F19" s="264">
+      <c r="D19" s="268"/>
+      <c r="F19" s="267">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>5.2952258108314526E-2</v>
       </c>
-      <c r="G19" s="265"/>
+      <c r="G19" s="268"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -38232,22 +38203,22 @@
       <c r="B21" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="264">
+      <c r="C21" s="267">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.2978639930252833</v>
       </c>
-      <c r="D21" s="265"/>
-      <c r="F21" s="264">
+      <c r="D21" s="268"/>
+      <c r="F21" s="267">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="G21" s="265"/>
+      <c r="G21" s="268"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38296,22 +38267,22 @@
       <c r="B25" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C25" s="264">
+      <c r="C25" s="267">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.7274157785566125E-2</v>
       </c>
-      <c r="D25" s="265"/>
-      <c r="F25" s="264">
+      <c r="D25" s="268"/>
+      <c r="F25" s="267">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-3.0061631864593874E-2</v>
       </c>
-      <c r="G25" s="265"/>
+      <c r="G25" s="268"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38339,22 +38310,22 @@
       <c r="B27" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C27" s="264">
+      <c r="C27" s="267">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.17416013437849945</v>
       </c>
-      <c r="D27" s="265"/>
-      <c r="F27" s="264">
+      <c r="D27" s="268"/>
+      <c r="F27" s="267">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.40153717627401836</v>
       </c>
-      <c r="G27" s="265"/>
+      <c r="G27" s="268"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38382,22 +38353,22 @@
       <c r="B29" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C29" s="264">
+      <c r="C29" s="267">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.3995709002625414E-2</v>
       </c>
-      <c r="D29" s="265"/>
-      <c r="F29" s="264">
+      <c r="D29" s="268"/>
+      <c r="F29" s="267">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.14584912812736922</v>
       </c>
-      <c r="G29" s="265"/>
+      <c r="G29" s="268"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38446,22 +38417,22 @@
       <c r="B33" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="264">
+      <c r="C33" s="267">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.0734220695577501E-2</v>
       </c>
-      <c r="D33" s="265"/>
-      <c r="F33" s="264">
+      <c r="D33" s="268"/>
+      <c r="F33" s="267">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.7331670822942641E-2</v>
       </c>
-      <c r="G33" s="265"/>
+      <c r="G33" s="268"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="239" t="str">
@@ -38489,43 +38460,25 @@
       <c r="B35" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C35" s="264">
+      <c r="C35" s="267">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-6.7286114478582681E-2</v>
       </c>
-      <c r="D35" s="265"/>
-      <c r="F35" s="264">
+      <c r="D35" s="268"/>
+      <c r="F35" s="267">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-9.1249332658182622E-2</v>
       </c>
-      <c r="G35" s="265"/>
+      <c r="G35" s="268"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38536,6 +38489,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3CAE4A-6692-964E-A946-2EFCAF4869CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53751FBE-4C3F-D54B-B2F4-D78F63C4F710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2472,6 +2472,9 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2481,15 +2484,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2497,6 +2491,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12707,7 +12707,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -12932,13 +12932,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>31.38</v>
+    <v>25</v>
     <v>7.77</v>
-    <v>0.82920000000000005</v>
-    <v>-0.16</v>
-    <v>-1.4414E-2</v>
-    <v>0.28610000000000002</v>
-    <v>2.6152000000000002E-2</v>
+    <v>0.85060000000000002</v>
+    <v>0.14000000000000001</v>
+    <v>1.3766E-2</v>
+    <v>-0.06</v>
+    <v>-5.8199999999999997E-3</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12946,25 +12946,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>11.145</v>
+    <v>10.34</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46269.845740543751</v>
+    <v>46276.979267025003</v>
     <v>0</v>
-    <v>10.7203</v>
-    <v>678723945</v>
+    <v>10.02</v>
+    <v>639951391</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>11.08</v>
-    <v>64.772099999999995</v>
-    <v>11.1</v>
-    <v>10.94</v>
-    <v>11.226100000000001</v>
-    <v>62040580</v>
+    <v>10.119999999999999</v>
+    <v>60.209600000000002</v>
+    <v>10.17</v>
+    <v>10.31</v>
+    <v>10.25</v>
+    <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>807901</v>
-    <v>792142</v>
+    <v>526878</v>
+    <v>792150</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -12986,19 +12986,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>48.12</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>0.22</v>
+    <v>4.62E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>48.12</v>
     <v>Index</v>
     <v>3</v>
-    <v>47.32</v>
+    <v>47.48</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
+    <v>47.54</v>
     <v>47.62</v>
+    <v>47.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13810,18 +13810,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="261" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="261"/>
-      <c r="E2" s="260" t="s">
+      <c r="C2" s="262"/>
+      <c r="E2" s="261" t="s">
         <v>304</v>
       </c>
-      <c r="F2" s="261"/>
-      <c r="H2" s="260" t="s">
+      <c r="F2" s="262"/>
+      <c r="H2" s="261" t="s">
         <v>346</v>
       </c>
-      <c r="I2" s="261"/>
+      <c r="I2" s="262"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>708102.44</v>
+        <v>667325.06000000006</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -13844,7 +13844,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>11.111693361692478</v>
+        <v>11.083518153090505</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>701603.44</v>
+        <v>660826.06000000006</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>16.24062631079282</v>
+        <v>16.229759126541744</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>260</v>
@@ -13892,7 +13892,7 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.975141994014567</v>
+        <v>16.949161820774108</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13901,14 +13901,14 @@
       </c>
       <c r="C6" s="212" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>11.226100000000001</v>
+        <v>10.25</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>254</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>-612.47865628840634</v>
+        <v>-577.20794756247437</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>9.8812965238991417</v>
+        <v>9.8746060854190354</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13925,14 +13925,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>1.3333766613561036</v>
+        <v>1.2565917165065292</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>13.552189547599752</v>
+        <v>13.534261296456346</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13949,14 +13949,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.28610000000000002</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>282</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.1433373962106388E-2</v>
+        <v>1.2132018539810267E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.23877418168187872</v>
+        <v>0.31273145455444673</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13973,14 +13973,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.4414E-2</v>
+        <v>1.3766E-2</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>305</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6327099560659892E-3</v>
+        <v>-1.7324778777266653E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.6152000000000002E-2</v>
+        <v>-5.8199999999999997E-3</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>310</v>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="C11" s="213" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>31.38</v>
+        <v>25</v>
       </c>
       <c r="E11" s="190" t="s">
         <v>306</v>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.82920000000000005</v>
+        <v>0.85060000000000002</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>114</v>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>792142</v>
+        <v>792150</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>115</v>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.178050565678041E-3</v>
+        <v>9.7388819775477923E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14089,10 +14089,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="262" t="s">
+      <c r="B17" s="263" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="262"/>
+      <c r="C17" s="263"/>
       <c r="E17" s="188" t="s">
         <v>313</v>
       </c>
@@ -14165,14 +14165,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="262" t="s">
+      <c r="B25" s="263" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="262"/>
-      <c r="E25" s="260" t="s">
+      <c r="C25" s="263"/>
+      <c r="E25" s="261" t="s">
         <v>360</v>
       </c>
-      <c r="F25" s="261"/>
+      <c r="F25" s="262"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14221,15 +14221,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="263" t="s">
+      <c r="B33" s="260" t="s">
         <v>354</v>
       </c>
-      <c r="C33" s="263"/>
-      <c r="D33" s="263"/>
-      <c r="E33" s="263"/>
-      <c r="F33" s="263"/>
-      <c r="G33" s="263"/>
-      <c r="H33" s="263"/>
+      <c r="C33" s="260"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14248,24 +14248,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="263"/>
-      <c r="C39" s="263"/>
-      <c r="D39" s="263"/>
-      <c r="E39" s="263"/>
-      <c r="F39" s="263"/>
-      <c r="G39" s="263"/>
-      <c r="H39" s="263"/>
+      <c r="B39" s="260"/>
+      <c r="C39" s="260"/>
+      <c r="D39" s="260"/>
+      <c r="E39" s="260"/>
+      <c r="F39" s="260"/>
+      <c r="G39" s="260"/>
+      <c r="H39" s="260"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="263" t="s">
+      <c r="B42" s="260" t="s">
         <v>357</v>
       </c>
-      <c r="C42" s="263"/>
-      <c r="D42" s="263"/>
-      <c r="E42" s="263"/>
-      <c r="F42" s="263"/>
-      <c r="G42" s="263"/>
-      <c r="H42" s="263"/>
+      <c r="C42" s="260"/>
+      <c r="D42" s="260"/>
+      <c r="E42" s="260"/>
+      <c r="F42" s="260"/>
+      <c r="G42" s="260"/>
+      <c r="H42" s="260"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14352,24 +14352,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="263"/>
-      <c r="C55" s="263"/>
-      <c r="D55" s="263"/>
-      <c r="E55" s="263"/>
-      <c r="F55" s="263"/>
-      <c r="G55" s="263"/>
-      <c r="H55" s="263"/>
+      <c r="B55" s="260"/>
+      <c r="C55" s="260"/>
+      <c r="D55" s="260"/>
+      <c r="E55" s="260"/>
+      <c r="F55" s="260"/>
+      <c r="G55" s="260"/>
+      <c r="H55" s="260"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="263" t="s">
+      <c r="B58" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="263"/>
-      <c r="D58" s="263"/>
-      <c r="E58" s="263"/>
-      <c r="F58" s="263"/>
-      <c r="G58" s="263"/>
-      <c r="H58" s="263"/>
+      <c r="C58" s="260"/>
+      <c r="D58" s="260"/>
+      <c r="E58" s="260"/>
+      <c r="F58" s="260"/>
+      <c r="G58" s="260"/>
+      <c r="H58" s="260"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14418,28 +14418,28 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="263"/>
-      <c r="C68" s="263"/>
-      <c r="D68" s="263"/>
-      <c r="E68" s="263"/>
-      <c r="F68" s="263"/>
-      <c r="G68" s="263"/>
-      <c r="H68" s="263"/>
+      <c r="B68" s="260"/>
+      <c r="C68" s="260"/>
+      <c r="D68" s="260"/>
+      <c r="E68" s="260"/>
+      <c r="F68" s="260"/>
+      <c r="G68" s="260"/>
+      <c r="H68" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B68:H68"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14509,36 +14509,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="263" t="s">
+      <c r="S2" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="263"/>
-      <c r="U2" s="263"/>
-      <c r="V2" s="263"/>
-      <c r="W2" s="263"/>
-      <c r="X2" s="263"/>
-      <c r="Y2" s="263"/>
-      <c r="Z2" s="263"/>
-      <c r="AA2" s="263" t="s">
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
+      <c r="AA2" s="260" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="263"/>
-      <c r="AC2" s="263"/>
+      <c r="AB2" s="260"/>
+      <c r="AC2" s="260"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -16795,35 +16795,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="P2" s="263" t="s">
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
+      <c r="P2" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="263"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="263"/>
-      <c r="V2" s="263"/>
-      <c r="W2" s="263"/>
-      <c r="X2" s="263" t="s">
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="263"/>
-      <c r="Z2" s="263"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -18582,20 +18582,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="260"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="260"/>
+      <c r="L3" s="260"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -19993,12 +19993,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20006,6 +20000,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20043,20 +20043,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
       <c r="S2" s="274"/>
       <c r="T2" s="274"/>
       <c r="U2" s="274"/>
@@ -21065,16 +21065,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21137,10 +21137,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="260" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="263"/>
+      <c r="C4" s="260"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>708102.44</v>
+        <v>667325.06000000006</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21184,7 +21184,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.82920000000000005</v>
+        <v>0.85060000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C11" s="139">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21225,10 +21225,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="263" t="s">
+      <c r="B15" s="260" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="263"/>
+      <c r="C15" s="260"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.5786758540240565E-2</v>
+        <v>9.0554130057950225E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.91421324145975946</v>
+        <v>0.90944586994204979</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.4933999999999996E-2</v>
+        <v>8.5266399999999992E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.2052937501184559E-2</v>
+        <v>8.2195129903302522E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21317,20 +21317,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="260"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="260"/>
+      <c r="L3" s="260"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>893129.67578097223</v>
+        <v>891087.77548749943</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21577,23 +21577,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13254.645671365261</v>
+        <v>13252.904109372274</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8801.7885741539376</v>
+        <v>8799.4757468205044</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21557.99970836208</v>
+        <v>21549.50314172354</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30367.618539969961</v>
+        <v>30351.661367206689</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36629.766600327544</v>
+        <v>36605.708526935137</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21612,14 +21612,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>602104.64543472847</v>
+        <v>600333.54308487789</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="263" t="s">
+      <c r="B13" s="260" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="263"/>
+      <c r="C13" s="260"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21635,14 +21635,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2052937501184559E-2</v>
+        <v>8.2195129903302522E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="263" t="s">
+      <c r="B18" s="260" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="263"/>
+      <c r="C18" s="260"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>110611.81909417879</v>
+        <v>110559.25289205814</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>602104.64543472847</v>
+        <v>600333.54308487789</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>712716.46452890732</v>
+        <v>710892.795976936</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21695,7 +21695,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>719215.46452890732</v>
+        <v>717391.795976936</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21713,7 +21713,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>11.111693361692478</v>
+        <v>11.083518153090505</v>
       </c>
     </row>
   </sheetData>
@@ -21756,20 +21756,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22701,10 +22701,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="263" t="s">
+      <c r="B37" s="260" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="263"/>
+      <c r="C37" s="260"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2052937501184559E-2</v>
+        <v>8.2195129903302522E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>1044691.778592376</v>
+        <v>1043988.3892245409</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>1051190.778592376</v>
+        <v>1050487.3892245409</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22793,14 +22793,14 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>16.24062631079282</v>
+        <v>16.229759126541744</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="263" t="s">
+      <c r="B49" s="260" t="s">
         <v>222</v>
       </c>
-      <c r="C49" s="263"/>
+      <c r="C49" s="260"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.4933999999999996E-2</v>
+        <v>8.5266399999999992E-2</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -22852,14 +22852,14 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>16.975141994014567</v>
+        <v>16.949161820774108</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="263" t="s">
+      <c r="B57" s="260" t="s">
         <v>340</v>
       </c>
-      <c r="C57" s="263"/>
+      <c r="C57" s="260"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2052937501184559E-2</v>
+        <v>8.2195129903302522E-2</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -22902,7 +22902,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>633077.79880589584</v>
+        <v>632644.75348483247</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>639576.79880589584</v>
+        <v>639143.75348483247</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>9.8812965238991417</v>
+        <v>9.8746060854190354</v>
       </c>
     </row>
   </sheetData>
@@ -22999,10 +22999,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="260" t="s">
         <v>227</v>
       </c>
-      <c r="C4" s="263"/>
+      <c r="C4" s="260"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>11.111693361692478</v>
+        <v>11.083518153090505</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23020,7 +23020,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>16.24062631079282</v>
+        <v>16.229759126541744</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>16.975141994014567</v>
+        <v>16.949161820774108</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>9.8812965238991417</v>
+        <v>9.8746060854190354</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>13.552189547599752</v>
+        <v>13.534261296456346</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23056,7 +23056,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.23877418168187872</v>
+        <v>0.31273145455444673</v>
       </c>
     </row>
   </sheetData>
@@ -23121,20 +23121,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23497,10 +23497,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="263" t="s">
+      <c r="B20" s="260" t="s">
         <v>430</v>
       </c>
-      <c r="C20" s="263"/>
+      <c r="C20" s="260"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.4933999999999996E-2</v>
+        <v>8.5266399999999992E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23601,20 +23601,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="260"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="260"/>
+      <c r="L3" s="260"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -23788,7 +23788,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1176484.7562390806</v>
+        <v>1173795.0409220632</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -23842,23 +23842,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11459.698107410226</v>
+        <v>11458.192388195257</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>16415.585089122691</v>
+        <v>16411.27160061197</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>23514.706172231356</v>
+        <v>23505.438416842135</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>33683.929227278408</v>
+        <v>33666.229443631622</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48250.957501997793</v>
+        <v>48219.266743781867</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -23877,7 +23877,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>793128.87727673247</v>
+        <v>790795.87348921818</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23893,7 +23893,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>15.030412807507096</v>
+        <v>14.991787986052763</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23941,7 +23941,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2052937501184559E-2</v>
+        <v>8.2195129903302522E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23959,7 +23959,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>679056.74</v>
+        <v>639952.01</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>672557.74</v>
+        <v>633453.01</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>133324.87609804049</v>
+        <v>133260.39859306286</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>793128.87727673247</v>
+        <v>790795.87348921818</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>926453.75337477296</v>
+        <v>924056.27208228107</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>932952.75337477296</v>
+        <v>930555.27208228107</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>15.030412807507096</v>
+        <v>14.991787986052763</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -24512,17 +24512,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -24897,7 +24897,7 @@
         <v>87601</v>
       </c>
       <c r="AA7" s="22">
-        <f t="shared" ref="Z7:AA7" si="3">AA5-AA6</f>
+        <f t="shared" ref="AA7" si="3">AA5-AA6</f>
         <v>86273</v>
       </c>
       <c r="AB7" s="16"/>
@@ -25263,19 +25263,19 @@
         <v>333080</v>
       </c>
       <c r="T13" s="24">
-        <f t="shared" ref="T13:U13" si="5">SUM(T8:T12)</f>
+        <f t="shared" ref="T13" si="5">SUM(T8:T12)</f>
         <v>86106</v>
       </c>
       <c r="U13" s="24">
-        <f t="shared" ref="U13:V13" si="6">SUM(U8:U12)</f>
+        <f t="shared" ref="U13" si="6">SUM(U8:U12)</f>
         <v>83727</v>
       </c>
       <c r="V13" s="24">
-        <f t="shared" ref="V13:W13" si="7">SUM(V8:V12)</f>
+        <f t="shared" ref="V13" si="7">SUM(V8:V12)</f>
         <v>81158</v>
       </c>
       <c r="W13" s="24">
-        <f t="shared" ref="W13:X13" si="8">SUM(W8:W12)</f>
+        <f t="shared" ref="W13" si="8">SUM(W8:W12)</f>
         <v>81121</v>
       </c>
       <c r="X13" s="24">
@@ -25291,7 +25291,7 @@
         <v>80852</v>
       </c>
       <c r="AA13" s="24">
-        <f t="shared" ref="Z13:AA13" si="10">SUM(AA8:AA12)</f>
+        <f t="shared" ref="AA13" si="10">SUM(AA8:AA12)</f>
         <v>78665</v>
       </c>
       <c r="AC13" s="24">
@@ -25855,7 +25855,7 @@
         <v>59738</v>
       </c>
       <c r="T22" s="25">
-        <f t="shared" ref="T22:Z22" si="12">T21*T$87</f>
+        <f t="shared" ref="T22:Y22" si="12">T21*T$87</f>
         <v>57892</v>
       </c>
       <c r="U22" s="25">
@@ -26014,7 +26014,7 @@
         <v>61495</v>
       </c>
       <c r="T24" s="25">
-        <f t="shared" ref="T24:Z24" si="15">T23*T$87</f>
+        <f t="shared" ref="T24:Y24" si="15">T23*T$87</f>
         <v>57892</v>
       </c>
       <c r="U24" s="25">
@@ -26143,7 +26143,7 @@
         <v>-0.16</v>
       </c>
       <c r="T26" s="65">
-        <f t="shared" ref="T26:Z26" si="17">T25/T$87</f>
+        <f t="shared" ref="T26:Y26" si="17">T25/T$87</f>
         <v>-0.25</v>
       </c>
       <c r="U26" s="65">
@@ -26275,7 +26275,7 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="66">
-        <f t="shared" ref="T28:Z28" si="19">T27/T$87</f>
+        <f t="shared" ref="T28:Y28" si="19">T27/T$87</f>
         <v>-0.25</v>
       </c>
       <c r="U28" s="66">
@@ -26832,7 +26832,7 @@
         <v>398890</v>
       </c>
       <c r="AA38" s="35">
-        <f t="shared" ref="Z38:AA38" si="24">AA39-AA34</f>
+        <f t="shared" ref="AA38" si="24">AA39-AA34</f>
         <v>393474</v>
       </c>
       <c r="AB38" s="1"/>
@@ -27211,7 +27211,7 @@
         <v>154942</v>
       </c>
       <c r="AA44" s="35">
-        <f t="shared" ref="Z44:AA44" si="27">AA45-AA42</f>
+        <f t="shared" ref="AA44" si="27">AA45-AA42</f>
         <v>131291</v>
       </c>
       <c r="AB44" s="1"/>
@@ -28629,7 +28629,7 @@
         <v>-9312</v>
       </c>
       <c r="T71" s="64">
-        <f t="shared" ref="T71:Z71" si="31">T5-T6-T13+T15+T16+T18-T19</f>
+        <f t="shared" ref="T71:Y71" si="31">T5-T6-T13+T15+T16+T18-T19</f>
         <v>-14403</v>
       </c>
       <c r="U71" s="64">
@@ -28761,7 +28761,7 @@
         <v>0</v>
       </c>
       <c r="AA72" s="40">
-        <f t="shared" ref="Z72:AA72" si="35">AA20-AA71</f>
+        <f t="shared" ref="AA72" si="35">AA20-AA71</f>
         <v>0</v>
       </c>
       <c r="AB72" s="16"/>
@@ -28840,7 +28840,7 @@
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
       <c r="T73" s="42">
-        <f t="shared" ref="T73:Z73" si="37">T39-(T45+T116)</f>
+        <f t="shared" ref="T73:Y73" si="37">T39-(T45+T116)</f>
         <v>0</v>
       </c>
       <c r="U73" s="42">
@@ -28993,11 +28993,11 @@
         <v>60763</v>
       </c>
       <c r="T77" s="25">
-        <f t="shared" ref="T77:U77" si="40">T76*T87</f>
+        <f t="shared" ref="T77" si="40">T76*T87</f>
         <v>58124</v>
       </c>
       <c r="U77" s="25">
-        <f t="shared" ref="U77:V77" si="41">U76*U87</f>
+        <f t="shared" ref="U77" si="41">U76*U87</f>
         <v>58772</v>
       </c>
       <c r="V77" s="25">
@@ -29154,7 +29154,7 @@
         <v>1096</v>
       </c>
       <c r="AA79" s="25">
-        <f t="shared" ref="Z79:AA79" si="46">AA78*AA87</f>
+        <f t="shared" ref="AA79" si="46">AA78*AA87</f>
         <v>2655</v>
       </c>
       <c r="AC79" s="24">
@@ -29225,7 +29225,7 @@
         <v>62908</v>
       </c>
       <c r="AA80" s="25">
-        <f t="shared" ref="Z80:AA80" si="49">AA77+AA79</f>
+        <f t="shared" ref="AA80" si="49">AA77+AA79</f>
         <v>64726</v>
       </c>
       <c r="AC80" s="24">
@@ -29415,11 +29415,11 @@
         <v>0</v>
       </c>
       <c r="T84" s="45">
-        <f t="shared" ref="T84:U84" si="52">T83/T87</f>
+        <f t="shared" ref="T84" si="52">T83/T87</f>
         <v>0</v>
       </c>
       <c r="U84" s="45">
-        <f t="shared" ref="U84:V84" si="53">U83/U87</f>
+        <f t="shared" ref="U84" si="53">U83/U87</f>
         <v>0</v>
       </c>
       <c r="V84" s="45">
@@ -29516,7 +29516,7 @@
         <v>0</v>
       </c>
       <c r="T85" s="46">
-        <f t="shared" ref="T85:Z85" si="57">IF(AND(T17&gt;0,T18&lt;0),-(T18)/T17,0)</f>
+        <f t="shared" ref="T85:Y85" si="57">IF(AND(T17&gt;0,T18&lt;0),-(T18)/T17,0)</f>
         <v>0</v>
       </c>
       <c r="U85" s="46">
@@ -30680,7 +30680,7 @@
         <v>0.67930527205045454</v>
       </c>
       <c r="T105" s="50">
-        <f t="shared" ref="T105:Z105" si="89">T7/T5</f>
+        <f t="shared" ref="T105:Y105" si="89">T7/T5</f>
         <v>0.67661985018726589</v>
       </c>
       <c r="U105" s="50">
@@ -30751,7 +30751,7 @@
         <v>-1.3758060388147093E-2</v>
       </c>
       <c r="T106" s="50">
-        <f t="shared" ref="T106:Z106" si="91">T14/T5</f>
+        <f t="shared" ref="T106:Y106" si="91">T14/T5</f>
         <v>-0.12961610486891387</v>
       </c>
       <c r="U106" s="50">
@@ -30825,7 +30825,7 @@
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
       <c r="T107" s="55">
-        <f t="shared" ref="T107:Z107" si="93">T115/T5</f>
+        <f t="shared" ref="T107:Y107" si="93">T115/T5</f>
         <v>-0.13485955056179774</v>
       </c>
       <c r="U107" s="55">
@@ -30943,7 +30943,7 @@
         <v>0</v>
       </c>
       <c r="T110" s="81">
-        <f t="shared" ref="T110:Z110" si="96">IF(AND(T85&gt;=0,T14&gt;=0),T85,0)</f>
+        <f t="shared" ref="T110:Y110" si="96">IF(AND(T85&gt;=0,T14&gt;=0),T85,0)</f>
         <v>0</v>
       </c>
       <c r="U110" s="81">
@@ -31014,7 +31014,7 @@
         <v>73830</v>
       </c>
       <c r="T111" s="25">
-        <f t="shared" ref="T111:Z111" si="99">T31+T36</f>
+        <f t="shared" ref="T111:Y111" si="99">T31+T36</f>
         <v>81740</v>
       </c>
       <c r="U111" s="25">
@@ -31105,7 +31105,7 @@
         <v>100088</v>
       </c>
       <c r="T112" s="25">
-        <f t="shared" ref="T112:Z112" si="101">T41+T43</f>
+        <f t="shared" ref="T112:Y112" si="101">T41+T43</f>
         <v>19158</v>
       </c>
       <c r="U112" s="25">
@@ -31223,7 +31223,7 @@
         <v>-24397</v>
       </c>
       <c r="T114" s="130">
-        <f t="shared" ref="T114:Z114" si="103">T62+T63</f>
+        <f t="shared" ref="T114:Y114" si="103">T62+T63</f>
         <v>-4182</v>
       </c>
       <c r="U114" s="130">
@@ -31294,7 +31294,7 @@
         <v>-9312</v>
       </c>
       <c r="T115" s="130">
-        <f t="shared" ref="T115:Z115" si="105">T19+T20</f>
+        <f t="shared" ref="T115:Y115" si="105">T19+T20</f>
         <v>-14403</v>
       </c>
       <c r="U115" s="130">
@@ -31365,7 +31365,7 @@
         <v>337207</v>
       </c>
       <c r="T116" s="130">
-        <f t="shared" ref="T116:Z116" si="107">T51+T50</f>
+        <f t="shared" ref="T116:Y116" si="107">T51+T50</f>
         <v>254592</v>
       </c>
       <c r="U116" s="130">
@@ -31481,7 +31481,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31547,12 +31547,12 @@
         <v>9.2100000000000009</v>
       </c>
       <c r="AA121" s="65">
-        <f t="shared" ref="T121:AA121" si="110">AA120/AA87</f>
+        <f t="shared" ref="AA121" si="110">AA120/AA87</f>
         <v>10.73</v>
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -31935,7 +31935,7 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="229" t="str">
-        <f t="shared" ref="T136:Y136" si="121">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:X136" si="121">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U136" s="229" t="str">
@@ -32072,7 +32072,7 @@
         <v>74.013755979616761</v>
       </c>
       <c r="T141" s="122">
-        <f t="shared" ref="T141:Z141" si="123">T32/T5*90</f>
+        <f t="shared" ref="T141:Y141" si="123">T32/T5*90</f>
         <v>60.175280898876402</v>
       </c>
       <c r="U141" s="122">
@@ -32133,7 +32133,7 @@
         <v>0</v>
       </c>
       <c r="T142" s="122">
-        <f t="shared" ref="T142:Z142" si="125">T33/T6*365</f>
+        <f t="shared" ref="T142:Y142" si="125">T33/T6*365</f>
         <v>0</v>
       </c>
       <c r="U142" s="122">
@@ -32194,7 +32194,7 @@
         <v>27.180271601253548</v>
       </c>
       <c r="T143" s="122">
-        <f t="shared" ref="T143:Z143" si="127">T40/T6*90</f>
+        <f t="shared" ref="T143:Y143" si="127">T40/T6*90</f>
         <v>41.355647566378089</v>
       </c>
       <c r="U143" s="122">
@@ -32255,11 +32255,11 @@
         <v>46.83348437836321</v>
       </c>
       <c r="T144" s="122">
-        <f t="shared" ref="T144:U144" si="130">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="130">T141+T142-T143</f>
         <v>18.819633332498313</v>
       </c>
       <c r="U144" s="122">
-        <f t="shared" ref="U144:V144" si="131">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="131">U141+U142-U143</f>
         <v>45.333089789697915</v>
       </c>
       <c r="V144" s="122">
@@ -32316,7 +32316,7 @@
         <v>0.29681471618323463</v>
       </c>
       <c r="T145" s="122">
-        <f t="shared" ref="T145:Z145" si="135">T112/T51</f>
+        <f t="shared" ref="T145:Y145" si="135">T112/T51</f>
         <v>7.5249811463046754E-2</v>
       </c>
       <c r="U145" s="122">
@@ -32377,7 +32377,7 @@
         <v>7.7869083382017576E-2</v>
       </c>
       <c r="T146" s="183">
-        <f t="shared" ref="T146:Z146" si="137">(T112-T111)/T51</f>
+        <f t="shared" ref="T146:Y146" si="137">(T112-T111)/T51</f>
         <v>-0.24581290849673201</v>
       </c>
       <c r="U146" s="183">
@@ -32438,7 +32438,7 @@
         <v>0.93474167899105554</v>
       </c>
       <c r="T147" s="122">
-        <f t="shared" ref="T147:Z147" si="139">(T111+T32)/T42</f>
+        <f t="shared" ref="T147:Y147" si="139">(T111+T32)/T42</f>
         <v>1.4024413695845277</v>
       </c>
       <c r="U147" s="122">
@@ -32499,7 +32499,7 @@
         <v>1.527185509793114</v>
       </c>
       <c r="T148" s="122">
-        <f t="shared" ref="T148:Z148" si="141">T34/T42</f>
+        <f t="shared" ref="T148:Y148" si="141">T34/T42</f>
         <v>1.736000586075219</v>
       </c>
       <c r="U148" s="122">
@@ -32560,7 +32560,7 @@
         <v>N/A</v>
       </c>
       <c r="T149" s="185" t="str">
-        <f t="shared" ref="T149:Z149" si="143">IF(T15&gt;=0,"N/A",IF(T14&lt;=0,"N/A",T14/-T15))</f>
+        <f t="shared" ref="T149:Y149" si="143">IF(T15&gt;=0,"N/A",IF(T14&lt;=0,"N/A",T14/-T15))</f>
         <v>N/A</v>
       </c>
       <c r="U149" s="185" t="str">
@@ -32630,7 +32630,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-612.47865628840634</v>
+        <v>-577.20794756247437</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32667,7 +32667,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3333766613561036</v>
+        <v>1.2565917165065292</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32728,7 +32728,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.8261527870033964</v>
+        <v>1.7209904235836397</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32789,7 +32789,7 @@
       </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>708102.44</v>
+        <v>667325.06000000006</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32845,12 +32845,12 @@
         <v>595280.68000000005</v>
       </c>
       <c r="AA154" s="147">
-        <f t="shared" ref="T154:AA154" si="146">AA153+AA112-AA111+AA50+AA47</f>
+        <f t="shared" ref="AA154" si="146">AA153+AA112-AA111+AA50+AA47</f>
         <v>688010.98</v>
       </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>701603.44</v>
+        <v>660826.06000000006</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32887,7 +32887,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>1.3816721380562551</v>
+        <v>1.3013689830304869</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32924,7 +32924,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC14</f>
-        <v>55.95369965706994</v>
+        <v>52.701655634420611</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32952,7 +32952,7 @@
         <v>-13035</v>
       </c>
       <c r="T157" s="64">
-        <f t="shared" ref="T157:Z157" si="147">T61-T56+T114+T67</f>
+        <f t="shared" ref="T157:Y157" si="147">T61-T56+T114+T67</f>
         <v>-14922</v>
       </c>
       <c r="U157" s="64">
@@ -33059,7 +33059,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>87.463246047430829</v>
+        <v>82.426514328063249</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33096,7 +33096,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-116.65607472122143</v>
+        <v>-109.87599238836452</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33133,7 +33133,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.1433373962106388E-2</v>
+        <v>1.2132018539810267E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33170,7 +33170,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.6327099560659892E-3</v>
+        <v>-1.7324778777266653E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33531,7 +33531,7 @@
         <v>1.2150486315685531</v>
       </c>
       <c r="T172" s="72">
-        <f t="shared" ref="T172:Z172" si="154">T111/T77</f>
+        <f t="shared" ref="T172:Y172" si="154">T111/T77</f>
         <v>1.4063037643658385</v>
       </c>
       <c r="U172" s="72">
@@ -33592,7 +33592,7 @@
         <v>0.85583779531555304</v>
       </c>
       <c r="T173" s="158">
-        <f t="shared" ref="T173:Z173" si="156">T56/T61</f>
+        <f t="shared" ref="T173:Y173" si="156">T56/T61</f>
         <v>2.856525496974935</v>
       </c>
       <c r="U173" s="158">
@@ -33653,7 +33653,7 @@
         <v>0.14035219136438259</v>
       </c>
       <c r="T174" s="158">
-        <f t="shared" ref="T174:Z174" si="158">T56/T5</f>
+        <f t="shared" ref="T174:Y174" si="158">T56/T5</f>
         <v>0.15472846441947566</v>
       </c>
       <c r="U174" s="158">
@@ -33714,7 +33714,7 @@
         <v>-0.43213797870414561</v>
       </c>
       <c r="T175" s="72">
-        <f t="shared" ref="T175:Z175" si="160">(T111-T112)/T77</f>
+        <f t="shared" ref="T175:Y175" si="160">(T111-T112)/T77</f>
         <v>1.0766980937306447</v>
       </c>
       <c r="U175" s="72">
@@ -33784,7 +33784,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.178050565678041E-3</v>
+        <v>9.7388819775477923E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33812,7 +33812,7 @@
         <v>5.0764579444891808E-2</v>
       </c>
       <c r="T177" s="158">
-        <f t="shared" ref="T177:Z177" si="162">-T114/T5</f>
+        <f t="shared" ref="T177:Y177" si="162">-T114/T5</f>
         <v>3.9157303370786517E-2</v>
       </c>
       <c r="U177" s="158">
@@ -33873,7 +33873,7 @@
         <v>0.30955160250716879</v>
       </c>
       <c r="T178" s="158">
-        <f t="shared" ref="T178:Z178" si="164">-(T114/T61)</f>
+        <f t="shared" ref="T178:Y178" si="164">-(T114/T61)</f>
         <v>0.72290406222990489</v>
       </c>
       <c r="U178" s="158">
@@ -33934,7 +33934,7 @@
         <v>0.77566527835182653</v>
       </c>
       <c r="T179" s="158">
-        <f t="shared" ref="T179:Z179" si="166">-T114/T55</f>
+        <f t="shared" ref="T179:Y179" si="166">-T114/T55</f>
         <v>0.59009453929730493</v>
       </c>
       <c r="U179" s="158">
@@ -34894,19 +34894,19 @@
         <v>48.61785556047851</v>
       </c>
       <c r="T210" s="234">
-        <f t="shared" ref="T210:U210" si="183">T187/T209</f>
+        <f t="shared" ref="T210" si="183">T187/T209</f>
         <v>11.650460231295728</v>
       </c>
       <c r="U210" s="234">
-        <f t="shared" ref="U210:V210" si="184">U187/U209</f>
+        <f t="shared" ref="U210" si="184">U187/U209</f>
         <v>11.931121861322277</v>
       </c>
       <c r="V210" s="234">
-        <f t="shared" ref="V210:W210" si="185">V187/V209</f>
+        <f t="shared" ref="V210" si="185">V187/V209</f>
         <v>12.322602584447971</v>
       </c>
       <c r="W210" s="234">
-        <f t="shared" ref="W210:X210" si="186">W187/W209</f>
+        <f t="shared" ref="W210" si="186">W187/W209</f>
         <v>12.021938661293934</v>
       </c>
       <c r="X210" s="234">
@@ -34922,7 +34922,7 @@
         <v>11.198173322005097</v>
       </c>
       <c r="AA210" s="234">
-        <f t="shared" ref="Z210:AA210" si="188">AA187/AA209</f>
+        <f t="shared" ref="AA210" si="188">AA187/AA209</f>
         <v>11.107715008431704</v>
       </c>
       <c r="AC210" s="235">
@@ -35203,7 +35203,7 @@
         <v>30.941736818785998</v>
       </c>
       <c r="T217" s="234">
-        <f t="shared" ref="T217:Z217" si="192">T189/T209</f>
+        <f t="shared" ref="T217:Y217" si="192">T189/T209</f>
         <v>7.7255133349067737</v>
       </c>
       <c r="U217" s="234">
@@ -35302,7 +35302,7 @@
         <v>27.811172472387426</v>
       </c>
       <c r="AA218" s="234">
-        <f t="shared" ref="T218:AC218" si="196">AA5/AA209</f>
+        <f t="shared" ref="AA218:AC218" si="196">AA5/AA209</f>
         <v>27.288785834738619</v>
       </c>
       <c r="AC218" s="234">
@@ -35380,15 +35380,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="260" t="s">
         <v>250</v>
       </c>
-      <c r="C4" s="263"/>
-      <c r="E4" s="263" t="s">
+      <c r="C4" s="260"/>
+      <c r="E4" s="260" t="s">
         <v>257</v>
       </c>
-      <c r="F4" s="263"/>
-      <c r="G4" s="263"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35396,7 +35396,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35412,7 +35412,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>708102.44</v>
+        <v>667325.06000000006</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35432,7 +35432,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>701603.44</v>
+        <v>660826.06000000006</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35452,7 +35452,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-612.47865628840634</v>
+        <v>-577.20794756247437</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>260</v>
@@ -35472,7 +35472,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3333766613561036</v>
+        <v>1.2565917165065292</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>261</v>
@@ -35492,7 +35492,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8261527870033964</v>
+        <v>1.7209904235836397</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35512,7 +35512,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3816721380562551</v>
+        <v>1.3013689830304869</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35521,18 +35521,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>55.95369965706994</v>
+        <v>52.701655634420611</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="263" t="s">
+      <c r="B15" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="263"/>
-      <c r="E15" s="263" t="s">
+      <c r="C15" s="260"/>
+      <c r="E15" s="260" t="s">
         <v>263</v>
       </c>
-      <c r="F15" s="263"/>
+      <c r="F15" s="260"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35583,14 +35583,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="263" t="s">
+      <c r="B21" s="260" t="s">
         <v>262</v>
       </c>
-      <c r="C21" s="263"/>
-      <c r="E21" s="263" t="s">
+      <c r="C21" s="260"/>
+      <c r="E21" s="260" t="s">
         <v>266</v>
       </c>
-      <c r="F21" s="263"/>
+      <c r="F21" s="260"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35659,14 +35659,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="263" t="s">
+      <c r="B29" s="260" t="s">
         <v>267</v>
       </c>
-      <c r="C29" s="263"/>
-      <c r="E29" s="263" t="s">
+      <c r="C29" s="260"/>
+      <c r="E29" s="260" t="s">
         <v>273</v>
       </c>
-      <c r="F29" s="263"/>
+      <c r="F29" s="260"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35742,14 +35742,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="263" t="s">
+      <c r="B37" s="260" t="s">
         <v>285</v>
       </c>
-      <c r="C37" s="263"/>
-      <c r="E37" s="263" t="s">
+      <c r="C37" s="260"/>
+      <c r="E37" s="260" t="s">
         <v>288</v>
       </c>
-      <c r="F37" s="263"/>
+      <c r="F37" s="260"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6327099560659892E-3</v>
+        <v>-1.7324778777266653E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>287</v>
@@ -35773,7 +35773,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>1.1433373962106388E-2</v>
+        <v>1.2132018539810267E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>289</v>
@@ -35818,14 +35818,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="263" t="s">
+      <c r="B45" s="260" t="s">
         <v>296</v>
       </c>
-      <c r="C45" s="263"/>
-      <c r="E45" s="263" t="s">
+      <c r="C45" s="260"/>
+      <c r="E45" s="260" t="s">
         <v>302</v>
       </c>
-      <c r="F45" s="263"/>
+      <c r="F45" s="260"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35858,18 +35858,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>9.178050565678041E-3</v>
+        <v>9.7388819775477923E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="263" t="s">
+      <c r="B51" s="260" t="s">
         <v>299</v>
       </c>
-      <c r="C51" s="263"/>
-      <c r="E51" s="263" t="s">
+      <c r="C51" s="260"/>
+      <c r="E51" s="260" t="s">
         <v>320</v>
       </c>
-      <c r="F51" s="263"/>
+      <c r="F51" s="260"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36037,7 +36037,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC120</f>
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>708102.44</v>
+        <v>667325.06000000006</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36095,7 +36095,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>701603.44</v>
+        <v>660826.06000000006</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-612.47865628840634</v>
+        <v>-577.20794756247437</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36153,7 +36153,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3333766613561036</v>
+        <v>1.2565917165065292</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36182,7 +36182,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8261527870033964</v>
+        <v>1.7209904235836397</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3816721380562551</v>
+        <v>1.3013689830304869</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36240,7 +36240,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>55.95369965706994</v>
+        <v>52.701655634420611</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37013,7 +37013,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6327099560659892E-3</v>
+        <v>-1.7324778777266653E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37042,7 +37042,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>1.1433373962106388E-2</v>
+        <v>1.2132018539810267E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37365,7 +37365,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>9.178050565678041E-3</v>
+        <v>9.7388819775477923E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37854,14 +37854,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="264" t="s">
         <v>330</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="F3" s="268" t="s">
+      <c r="D3" s="265"/>
+      <c r="F3" s="266" t="s">
         <v>331</v>
       </c>
-      <c r="G3" s="267"/>
+      <c r="G3" s="265"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37928,19 +37928,19 @@
       <c r="B7" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C7" s="264">
+      <c r="C7" s="267">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="265"/>
-      <c r="F7" s="264">
+      <c r="D7" s="268"/>
+      <c r="F7" s="267">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="265"/>
+      <c r="G7" s="268"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -37967,19 +37967,19 @@
       <c r="B9" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="264">
+      <c r="C9" s="267">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="265"/>
-      <c r="F9" s="264">
+      <c r="D9" s="268"/>
+      <c r="F9" s="267">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="265"/>
+      <c r="G9" s="268"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -38006,19 +38006,19 @@
       <c r="B11" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C11" s="264">
+      <c r="C11" s="267">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="265"/>
-      <c r="F11" s="264">
+      <c r="D11" s="268"/>
+      <c r="F11" s="267">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="265"/>
+      <c r="G11" s="268"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -38045,19 +38045,19 @@
       <c r="B13" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C13" s="264">
+      <c r="C13" s="267">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="265"/>
-      <c r="F13" s="264">
+      <c r="D13" s="268"/>
+      <c r="F13" s="267">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="265"/>
+      <c r="G13" s="268"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -38084,19 +38084,19 @@
       <c r="B15" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="264">
+      <c r="C15" s="267">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="265"/>
-      <c r="F15" s="264">
+      <c r="D15" s="268"/>
+      <c r="F15" s="267">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="265"/>
+      <c r="G15" s="268"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -38123,19 +38123,19 @@
       <c r="B17" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C17" s="264">
+      <c r="C17" s="267">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="265"/>
-      <c r="F17" s="264">
+      <c r="D17" s="268"/>
+      <c r="F17" s="267">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="265"/>
+      <c r="G17" s="268"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -38162,22 +38162,22 @@
       <c r="B19" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C19" s="264">
+      <c r="C19" s="267">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="265"/>
-      <c r="F19" s="264">
+      <c r="D19" s="268"/>
+      <c r="F19" s="267">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="265"/>
+      <c r="G19" s="268"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -38204,22 +38204,22 @@
       <c r="B21" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C21" s="264">
+      <c r="C21" s="267">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="265"/>
-      <c r="F21" s="264">
+      <c r="D21" s="268"/>
+      <c r="F21" s="267">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="265"/>
+      <c r="G21" s="268"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38268,22 +38268,22 @@
       <c r="B25" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C25" s="264">
+      <c r="C25" s="267">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="265"/>
-      <c r="F25" s="264">
+      <c r="D25" s="268"/>
+      <c r="F25" s="267">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="265"/>
+      <c r="G25" s="268"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38311,22 +38311,22 @@
       <c r="B27" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C27" s="264">
+      <c r="C27" s="267">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="265"/>
-      <c r="F27" s="264">
+      <c r="D27" s="268"/>
+      <c r="F27" s="267">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="265"/>
+      <c r="G27" s="268"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38354,22 +38354,22 @@
       <c r="B29" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C29" s="264">
+      <c r="C29" s="267">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="265"/>
-      <c r="F29" s="264">
+      <c r="D29" s="268"/>
+      <c r="F29" s="267">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="265"/>
+      <c r="G29" s="268"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38418,22 +38418,22 @@
       <c r="B33" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C33" s="264">
+      <c r="C33" s="267">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="265"/>
-      <c r="F33" s="264">
+      <c r="D33" s="268"/>
+      <c r="F33" s="267">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="265"/>
+      <c r="G33" s="268"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="239" t="str">
@@ -38461,43 +38461,25 @@
       <c r="B35" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C35" s="264">
+      <c r="C35" s="267">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="265"/>
-      <c r="F35" s="264">
+      <c r="D35" s="268"/>
+      <c r="F35" s="267">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="265"/>
+      <c r="G35" s="268"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38508,6 +38490,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53751FBE-4C3F-D54B-B2F4-D78F63C4F710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D38F486-5B9C-CB44-B4AC-847C26EADD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -175,7 +175,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -185,12 +206,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2472,9 +2502,6 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2484,6 +2511,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2491,12 +2527,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12915,7 +12945,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12934,11 +12964,9 @@
     <v>Powered by Refinitiv</v>
     <v>25</v>
     <v>7.77</v>
-    <v>0.85060000000000002</v>
-    <v>0.14000000000000001</v>
-    <v>1.3766E-2</v>
-    <v>-0.06</v>
-    <v>-5.8199999999999997E-3</v>
+    <v>0.82830000000000004</v>
+    <v>0.1</v>
+    <v>9.9699999999999997E-3</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12946,35 +12974,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.34</v>
+    <v>10.23</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46276.979267025003</v>
+    <v>46287.766462904685</v>
     <v>0</v>
-    <v>10.02</v>
-    <v>639951391</v>
+    <v>9.9949999999999992</v>
+    <v>628778622</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.119999999999999</v>
-    <v>60.209600000000002</v>
-    <v>10.17</v>
-    <v>10.31</v>
-    <v>10.25</v>
+    <v>10.130000000000001</v>
+    <v>59.976300000000002</v>
+    <v>10.029999999999999</v>
+    <v>10.130000000000001</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>526878</v>
-    <v>792150</v>
+    <v>225971</v>
+    <v>827802</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12986,30 +13028,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.12</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.62E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>48.12</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>3</v>
-    <v>47.48</v>
+    <v>6</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.54</v>
-    <v>47.62</v>
-    <v>47.84</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13031,8 +13073,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13053,7 +13093,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13063,6 +13102,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13098,7 +13142,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13109,16 +13153,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13212,19 +13253,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13296,9 +13331,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13306,9 +13338,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13810,18 +13839,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="261" t="s">
+      <c r="B2" s="260" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="262"/>
-      <c r="E2" s="261" t="s">
+      <c r="C2" s="261"/>
+      <c r="E2" s="260" t="s">
         <v>304</v>
       </c>
-      <c r="F2" s="262"/>
-      <c r="H2" s="261" t="s">
+      <c r="F2" s="261"/>
+      <c r="H2" s="260" t="s">
         <v>346</v>
       </c>
-      <c r="I2" s="262"/>
+      <c r="I2" s="261"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -13836,7 +13865,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>667325.06000000006</v>
+        <v>655674.38</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -13844,7 +13873,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>11.083518153090505</v>
+        <v>10.949628242320637</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13860,7 +13889,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>660826.06000000006</v>
+        <v>649175.38</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -13868,7 +13897,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>16.229759126541744</v>
+        <v>16.177540452666161</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13877,7 +13906,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>260</v>
@@ -13892,23 +13921,23 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.949161820774108</v>
+        <v>16.886145558770821</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.25</v>
+      <c r="C6" s="212" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>254</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>-577.20794756247437</v>
+        <v>-567.13060221220815</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -13916,7 +13945,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>9.8746060854190354</v>
+        <v>9.842457387374953</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13925,14 +13954,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>1.2565917165065292</v>
+        <v>1.2346531608352223</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -13940,23 +13969,23 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>13.534261296456346</v>
+        <v>13.463942910283144</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.06</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>282</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.2132018539810267E-2</v>
+        <v>1.2347592413173136E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -13964,7 +13993,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.31273145455444673</v>
+        <v>0.32911578581274858</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13973,23 +14002,23 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.3766E-2</v>
+        <v>9.9699999999999997E-3</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>305</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7324778777266653E-3</v>
+        <v>-1.7632622822667246E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.8199999999999997E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>310</v>
@@ -14044,7 +14073,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.85060000000000002</v>
+        <v>0.82830000000000004</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>114</v>
@@ -14060,7 +14089,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>792150</v>
+        <v>827802</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>115</v>
@@ -14076,7 +14105,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.7388819775477923E-3</v>
+        <v>9.9119322002485435E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14089,10 +14118,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="263" t="s">
+      <c r="B17" s="262" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="263"/>
+      <c r="C17" s="262"/>
       <c r="E17" s="188" t="s">
         <v>313</v>
       </c>
@@ -14165,14 +14194,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="263" t="s">
+      <c r="B25" s="262" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="263"/>
-      <c r="E25" s="261" t="s">
+      <c r="C25" s="262"/>
+      <c r="E25" s="260" t="s">
         <v>360</v>
       </c>
-      <c r="F25" s="262"/>
+      <c r="F25" s="261"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -14181,12 +14210,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="2">
+      <c r="E26" s="189" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.84</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14201,7 +14230,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14221,15 +14250,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="260" t="s">
+      <c r="B33" s="263" t="s">
         <v>354</v>
       </c>
-      <c r="C33" s="260"/>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
+      <c r="C33" s="263"/>
+      <c r="D33" s="263"/>
+      <c r="E33" s="263"/>
+      <c r="F33" s="263"/>
+      <c r="G33" s="263"/>
+      <c r="H33" s="263"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14248,24 +14277,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="260"/>
-      <c r="C39" s="260"/>
-      <c r="D39" s="260"/>
-      <c r="E39" s="260"/>
-      <c r="F39" s="260"/>
-      <c r="G39" s="260"/>
-      <c r="H39" s="260"/>
+      <c r="B39" s="263"/>
+      <c r="C39" s="263"/>
+      <c r="D39" s="263"/>
+      <c r="E39" s="263"/>
+      <c r="F39" s="263"/>
+      <c r="G39" s="263"/>
+      <c r="H39" s="263"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="260" t="s">
+      <c r="B42" s="263" t="s">
         <v>357</v>
       </c>
-      <c r="C42" s="260"/>
-      <c r="D42" s="260"/>
-      <c r="E42" s="260"/>
-      <c r="F42" s="260"/>
-      <c r="G42" s="260"/>
-      <c r="H42" s="260"/>
+      <c r="C42" s="263"/>
+      <c r="D42" s="263"/>
+      <c r="E42" s="263"/>
+      <c r="F42" s="263"/>
+      <c r="G42" s="263"/>
+      <c r="H42" s="263"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14352,24 +14381,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="260"/>
-      <c r="C55" s="260"/>
-      <c r="D55" s="260"/>
-      <c r="E55" s="260"/>
-      <c r="F55" s="260"/>
-      <c r="G55" s="260"/>
-      <c r="H55" s="260"/>
+      <c r="B55" s="263"/>
+      <c r="C55" s="263"/>
+      <c r="D55" s="263"/>
+      <c r="E55" s="263"/>
+      <c r="F55" s="263"/>
+      <c r="G55" s="263"/>
+      <c r="H55" s="263"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="260" t="s">
+      <c r="B58" s="263" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="260"/>
-      <c r="D58" s="260"/>
-      <c r="E58" s="260"/>
-      <c r="F58" s="260"/>
-      <c r="G58" s="260"/>
-      <c r="H58" s="260"/>
+      <c r="C58" s="263"/>
+      <c r="D58" s="263"/>
+      <c r="E58" s="263"/>
+      <c r="F58" s="263"/>
+      <c r="G58" s="263"/>
+      <c r="H58" s="263"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14418,28 +14447,28 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="260"/>
-      <c r="C68" s="260"/>
-      <c r="D68" s="260"/>
-      <c r="E68" s="260"/>
-      <c r="F68" s="260"/>
-      <c r="G68" s="260"/>
-      <c r="H68" s="260"/>
+      <c r="B68" s="263"/>
+      <c r="C68" s="263"/>
+      <c r="D68" s="263"/>
+      <c r="E68" s="263"/>
+      <c r="F68" s="263"/>
+      <c r="G68" s="263"/>
+      <c r="H68" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14509,36 +14538,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="260" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="260"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="260"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="260"/>
-      <c r="L2" s="260"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="260" t="s">
+      <c r="S2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="260"/>
-      <c r="X2" s="260"/>
-      <c r="Y2" s="260"/>
-      <c r="Z2" s="260"/>
-      <c r="AA2" s="260" t="s">
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="260"/>
-      <c r="AC2" s="260"/>
+      <c r="AB2" s="263"/>
+      <c r="AC2" s="263"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -16795,35 +16824,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="260" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="260"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="260"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="260"/>
-      <c r="L2" s="260"/>
-      <c r="P2" s="260" t="s">
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
+      <c r="P2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="260"/>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="260"/>
-      <c r="X2" s="260" t="s">
+      <c r="Q2" s="263"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="260"/>
-      <c r="Z2" s="260"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -18582,20 +18611,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="260"/>
-      <c r="E3" s="260"/>
-      <c r="F3" s="260"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="260"/>
-      <c r="J3" s="260"/>
-      <c r="K3" s="260"/>
-      <c r="L3" s="260"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -19993,6 +20022,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20000,12 +20035,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20043,20 +20072,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="260" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="260"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="260"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="260"/>
-      <c r="L2" s="260"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
       <c r="S2" s="274"/>
       <c r="T2" s="274"/>
       <c r="U2" s="274"/>
@@ -20519,23 +20548,23 @@
         <v>74</v>
       </c>
       <c r="C15" s="133">
-        <f>-Statement!M85</f>
+        <f>Statement!M85</f>
         <v>0</v>
       </c>
       <c r="D15" s="133">
-        <f>-Statement!N85</f>
+        <f>Statement!N85</f>
         <v>0</v>
       </c>
       <c r="E15" s="133">
-        <f>-Statement!O85</f>
+        <f>Statement!O85</f>
         <v>0</v>
       </c>
       <c r="F15" s="133">
-        <f>-Statement!P85</f>
+        <f>Statement!P85</f>
         <v>0</v>
       </c>
       <c r="G15" s="134">
-        <f>-Statement!Q85</f>
+        <f>Statement!Q85</f>
         <v>0</v>
       </c>
       <c r="H15" s="133">
@@ -21065,16 +21094,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21137,10 +21166,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="260" t="s">
+      <c r="B4" s="263" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="260"/>
+      <c r="C4" s="263"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21157,7 +21186,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21166,7 +21195,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>667325.06000000006</v>
+        <v>655674.38</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21184,7 +21213,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21193,7 +21222,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.85060000000000002</v>
+        <v>0.82830000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21225,10 +21254,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="260" t="s">
+      <c r="B15" s="263" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="260"/>
+      <c r="C15" s="263"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21236,7 +21265,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.0554130057950225E-2</v>
+        <v>9.2015129111852514E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21245,7 +21274,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.90944586994204979</v>
+        <v>0.9079848708881475</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21263,7 +21292,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.5266399999999992E-2</v>
+        <v>8.6075199999999991E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21272,7 +21301,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.2195129903302522E-2</v>
+        <v>8.2879956238565089E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21317,20 +21346,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="260"/>
-      <c r="E3" s="260"/>
-      <c r="F3" s="260"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="260"/>
-      <c r="J3" s="260"/>
-      <c r="K3" s="260"/>
-      <c r="L3" s="260"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -21523,7 +21552,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>891087.77548749943</v>
+        <v>881382.92815317342</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21577,23 +21606,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13252.904109372274</v>
+        <v>13244.522813088672</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8799.4757468205044</v>
+        <v>8788.3494770986144</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21549.50314172354</v>
+        <v>21508.644495612978</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30351.661367206689</v>
+        <v>30274.955144681029</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36605.708526935137</v>
+        <v>36490.105380846187</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21612,14 +21641,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>600333.54308487789</v>
+        <v>591920.06030111806</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="260" t="s">
+      <c r="B13" s="263" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="260"/>
+      <c r="C13" s="263"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21635,14 +21664,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2195129903302522E-2</v>
+        <v>8.2879956238565089E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="260" t="s">
+      <c r="B18" s="263" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="260"/>
+      <c r="C18" s="263"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21650,7 +21679,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>110559.25289205814</v>
+        <v>110306.57731132748</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21659,7 +21688,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>600333.54308487789</v>
+        <v>591920.06030111806</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21668,7 +21697,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>710892.795976936</v>
+        <v>702226.63761244551</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21695,7 +21724,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>717391.795976936</v>
+        <v>708725.63761244551</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21713,7 +21742,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>11.083518153090505</v>
+        <v>10.949628242320637</v>
       </c>
     </row>
   </sheetData>
@@ -21756,20 +21785,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="260" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="260"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="260"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="260"/>
-      <c r="L2" s="260"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22701,10 +22730,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="260" t="s">
+      <c r="B37" s="263" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="260"/>
+      <c r="C37" s="263"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22722,7 +22751,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2195129903302522E-2</v>
+        <v>8.2879956238565089E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22748,7 +22777,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>1043988.3892245409</v>
+        <v>1040608.4833392699</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -22775,7 +22804,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>1050487.3892245409</v>
+        <v>1047107.4833392699</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22793,14 +22822,14 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>16.229759126541744</v>
+        <v>16.177540452666161</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="260" t="s">
+      <c r="B49" s="263" t="s">
         <v>222</v>
       </c>
-      <c r="C49" s="260"/>
+      <c r="C49" s="263"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22817,7 +22846,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.5266399999999992E-2</v>
+        <v>8.6075199999999991E-2</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -22852,14 +22881,14 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>16.949161820774108</v>
+        <v>16.886145558770821</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="260" t="s">
+      <c r="B57" s="263" t="s">
         <v>340</v>
       </c>
-      <c r="C57" s="260"/>
+      <c r="C57" s="263"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22876,7 +22905,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2195129903302522E-2</v>
+        <v>8.2879956238565089E-2</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -22902,7 +22931,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>632644.75348483247</v>
+        <v>630563.89685523126</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -22929,7 +22958,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>639143.75348483247</v>
+        <v>637062.89685523126</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22947,7 +22976,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>9.8746060854190354</v>
+        <v>9.842457387374953</v>
       </c>
     </row>
   </sheetData>
@@ -22999,10 +23028,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="260" t="s">
+      <c r="B4" s="263" t="s">
         <v>227</v>
       </c>
-      <c r="C4" s="260"/>
+      <c r="C4" s="263"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23011,7 +23040,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>11.083518153090505</v>
+        <v>10.949628242320637</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23020,7 +23049,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>16.229759126541744</v>
+        <v>16.177540452666161</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23029,7 +23058,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>16.949161820774108</v>
+        <v>16.886145558770821</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23038,7 +23067,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>9.8746060854190354</v>
+        <v>9.842457387374953</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23047,7 +23076,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>13.534261296456346</v>
+        <v>13.463942910283144</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23056,7 +23085,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23065,7 +23094,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.31273145455444673</v>
+        <v>0.32911578581274858</v>
       </c>
     </row>
   </sheetData>
@@ -23121,20 +23150,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="260" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="260"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
       <c r="G2" s="272"/>
       <c r="H2" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="260"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="260"/>
-      <c r="L2" s="260"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23497,10 +23526,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="260" t="s">
+      <c r="B20" s="263" t="s">
         <v>430</v>
       </c>
-      <c r="C20" s="260"/>
+      <c r="C20" s="263"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23535,7 +23564,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.5266399999999992E-2</v>
+        <v>8.6075199999999991E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23601,20 +23630,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="260"/>
-      <c r="E3" s="260"/>
-      <c r="F3" s="260"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
       <c r="G3" s="272"/>
       <c r="H3" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="260"/>
-      <c r="J3" s="260"/>
-      <c r="K3" s="260"/>
-      <c r="L3" s="260"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
       <c r="P3" s="274"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="274"/>
@@ -23788,7 +23817,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1173795.0409220632</v>
+        <v>1161011.2254694209</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -23842,23 +23871,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11458.192388195257</v>
+        <v>11450.946089234109</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>16411.27160061197</v>
+        <v>16390.520792318239</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>23505.438416842135</v>
+        <v>23460.87124591336</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>33666.229443631622</v>
+        <v>33581.146480427065</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48219.266743781867</v>
+        <v>48066.987245255506</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -23877,7 +23906,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>790795.87348921818</v>
+        <v>779713.12200263457</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23893,7 +23922,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23902,7 +23931,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>14.991787986052763</v>
+        <v>14.808245297413976</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23941,7 +23970,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.2195129903302522E-2</v>
+        <v>8.2879956238565089E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23959,7 +23988,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>639952.01</v>
+        <v>628779.2300000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23986,7 +24015,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>633453.01</v>
+        <v>622280.2300000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24002,7 +24031,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>133260.39859306286</v>
+        <v>132950.47185314828</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24011,7 +24040,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>790795.87348921818</v>
+        <v>779713.12200263457</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24020,7 +24049,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>924056.27208228107</v>
+        <v>912663.59385578288</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24047,7 +24076,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>930555.27208228107</v>
+        <v>919162.59385578288</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24065,7 +24094,7 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>14.991787986052763</v>
+        <v>14.808245297413976</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -24512,17 +24541,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31481,7 +31510,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31552,7 +31581,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32630,7 +32659,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-577.20794756247437</v>
+        <v>-567.13060221220815</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32667,7 +32696,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.2565917165065292</v>
+        <v>1.2346531608352223</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32728,7 +32757,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.7209904235836397</v>
+        <v>1.6909440340351378</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32789,7 +32818,7 @@
       </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>667325.06000000006</v>
+        <v>655674.38</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32850,7 +32879,7 @@
       </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>660826.06000000006</v>
+        <v>649175.38</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32887,7 +32916,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>1.3013689830304869</v>
+        <v>1.2784252244516958</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32924,7 +32953,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC14</f>
-        <v>52.701655634420611</v>
+        <v>51.772500199377944</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33059,7 +33088,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>82.426514328063249</v>
+        <v>80.987448122529642</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33096,7 +33125,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-109.87599238836452</v>
+        <v>-107.93882600754826</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33133,7 +33162,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.2132018539810267E-2</v>
+        <v>1.2347592413173136E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33170,7 +33199,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.7324778777266653E-3</v>
+        <v>-1.7632622822667246E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33784,7 +33813,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.7388819775477923E-3</v>
+        <v>9.9119322002485435E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35380,15 +35409,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="260" t="s">
+      <c r="B4" s="263" t="s">
         <v>250</v>
       </c>
-      <c r="C4" s="260"/>
-      <c r="E4" s="260" t="s">
+      <c r="C4" s="263"/>
+      <c r="E4" s="263" t="s">
         <v>257</v>
       </c>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
+      <c r="F4" s="263"/>
+      <c r="G4" s="263"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35396,7 +35425,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35412,7 +35441,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>667325.06000000006</v>
+        <v>655674.38</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35432,7 +35461,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>660826.06000000006</v>
+        <v>649175.38</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35452,7 +35481,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-577.20794756247437</v>
+        <v>-567.13060221220815</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>260</v>
@@ -35472,7 +35501,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.2565917165065292</v>
+        <v>1.2346531608352223</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>261</v>
@@ -35492,7 +35521,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.7209904235836397</v>
+        <v>1.6909440340351378</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35512,7 +35541,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3013689830304869</v>
+        <v>1.2784252244516958</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35521,18 +35550,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>52.701655634420611</v>
+        <v>51.772500199377944</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="260" t="s">
+      <c r="B15" s="263" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="260"/>
-      <c r="E15" s="260" t="s">
+      <c r="C15" s="263"/>
+      <c r="E15" s="263" t="s">
         <v>263</v>
       </c>
-      <c r="F15" s="260"/>
+      <c r="F15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35583,14 +35612,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="260" t="s">
+      <c r="B21" s="263" t="s">
         <v>262</v>
       </c>
-      <c r="C21" s="260"/>
-      <c r="E21" s="260" t="s">
+      <c r="C21" s="263"/>
+      <c r="E21" s="263" t="s">
         <v>266</v>
       </c>
-      <c r="F21" s="260"/>
+      <c r="F21" s="263"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35659,14 +35688,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="260" t="s">
+      <c r="B29" s="263" t="s">
         <v>267</v>
       </c>
-      <c r="C29" s="260"/>
-      <c r="E29" s="260" t="s">
+      <c r="C29" s="263"/>
+      <c r="E29" s="263" t="s">
         <v>273</v>
       </c>
-      <c r="F29" s="260"/>
+      <c r="F29" s="263"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35742,14 +35771,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="260" t="s">
+      <c r="B37" s="263" t="s">
         <v>285</v>
       </c>
-      <c r="C37" s="260"/>
-      <c r="E37" s="260" t="s">
+      <c r="C37" s="263"/>
+      <c r="E37" s="263" t="s">
         <v>288</v>
       </c>
-      <c r="F37" s="260"/>
+      <c r="F37" s="263"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35757,7 +35786,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7324778777266653E-3</v>
+        <v>-1.7632622822667246E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>287</v>
@@ -35773,7 +35802,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>1.2132018539810267E-2</v>
+        <v>1.2347592413173136E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>289</v>
@@ -35818,14 +35847,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="260" t="s">
+      <c r="B45" s="263" t="s">
         <v>296</v>
       </c>
-      <c r="C45" s="260"/>
-      <c r="E45" s="260" t="s">
+      <c r="C45" s="263"/>
+      <c r="E45" s="263" t="s">
         <v>302</v>
       </c>
-      <c r="F45" s="260"/>
+      <c r="F45" s="263"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35858,18 +35887,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>9.7388819775477923E-3</v>
+        <v>9.9119322002485435E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="260" t="s">
+      <c r="B51" s="263" t="s">
         <v>299</v>
       </c>
-      <c r="C51" s="260"/>
-      <c r="E51" s="260" t="s">
+      <c r="C51" s="263"/>
+      <c r="E51" s="263" t="s">
         <v>320</v>
       </c>
-      <c r="F51" s="260"/>
+      <c r="F51" s="263"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36037,7 +36066,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC120</f>
-        <v>10.31</v>
+        <v>10.130000000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36066,7 +36095,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>667325.06000000006</v>
+        <v>655674.38</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36095,7 +36124,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>660826.06000000006</v>
+        <v>649175.38</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36124,7 +36153,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-577.20794756247437</v>
+        <v>-567.13060221220815</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36153,7 +36182,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.2565917165065292</v>
+        <v>1.2346531608352223</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36182,7 +36211,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.7209904235836397</v>
+        <v>1.6909440340351378</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36211,7 +36240,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3013689830304869</v>
+        <v>1.2784252244516958</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36240,7 +36269,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>52.701655634420611</v>
+        <v>51.772500199377944</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37013,7 +37042,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7324778777266653E-3</v>
+        <v>-1.7632622822667246E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37042,7 +37071,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>1.2132018539810267E-2</v>
+        <v>1.2347592413173136E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37365,7 +37394,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>9.7388819775477923E-3</v>
+        <v>9.9119322002485435E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37854,14 +37883,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="266" t="s">
         <v>330</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="267"/>
+      <c r="F3" s="268" t="s">
         <v>331</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="267"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37928,19 +37957,19 @@
       <c r="B7" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C7" s="267">
+      <c r="C7" s="264">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="268"/>
-      <c r="F7" s="267">
+      <c r="D7" s="265"/>
+      <c r="F7" s="264">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="268"/>
+      <c r="G7" s="265"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -37967,19 +37996,19 @@
       <c r="B9" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="267">
+      <c r="C9" s="264">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="268"/>
-      <c r="F9" s="267">
+      <c r="D9" s="265"/>
+      <c r="F9" s="264">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="268"/>
+      <c r="G9" s="265"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -38006,19 +38035,19 @@
       <c r="B11" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C11" s="267">
+      <c r="C11" s="264">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="268"/>
-      <c r="F11" s="267">
+      <c r="D11" s="265"/>
+      <c r="F11" s="264">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="268"/>
+      <c r="G11" s="265"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -38045,19 +38074,19 @@
       <c r="B13" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C13" s="267">
+      <c r="C13" s="264">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="268"/>
-      <c r="F13" s="267">
+      <c r="D13" s="265"/>
+      <c r="F13" s="264">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="268"/>
+      <c r="G13" s="265"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -38084,19 +38113,19 @@
       <c r="B15" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="267">
+      <c r="C15" s="264">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="268"/>
-      <c r="F15" s="267">
+      <c r="D15" s="265"/>
+      <c r="F15" s="264">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="268"/>
+      <c r="G15" s="265"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -38123,19 +38152,19 @@
       <c r="B17" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C17" s="267">
+      <c r="C17" s="264">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="268"/>
-      <c r="F17" s="267">
+      <c r="D17" s="265"/>
+      <c r="F17" s="264">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="268"/>
+      <c r="G17" s="265"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -38162,22 +38191,22 @@
       <c r="B19" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C19" s="267">
+      <c r="C19" s="264">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="268"/>
-      <c r="F19" s="267">
+      <c r="D19" s="265"/>
+      <c r="F19" s="264">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="268"/>
+      <c r="G19" s="265"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -38204,22 +38233,22 @@
       <c r="B21" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C21" s="267">
+      <c r="C21" s="264">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="268"/>
-      <c r="F21" s="267">
+      <c r="D21" s="265"/>
+      <c r="F21" s="264">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="268"/>
+      <c r="G21" s="265"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38268,22 +38297,22 @@
       <c r="B25" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C25" s="267">
+      <c r="C25" s="264">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="268"/>
-      <c r="F25" s="267">
+      <c r="D25" s="265"/>
+      <c r="F25" s="264">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="268"/>
+      <c r="G25" s="265"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38311,22 +38340,22 @@
       <c r="B27" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C27" s="267">
+      <c r="C27" s="264">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="268"/>
-      <c r="F27" s="267">
+      <c r="D27" s="265"/>
+      <c r="F27" s="264">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="268"/>
+      <c r="G27" s="265"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38354,22 +38383,22 @@
       <c r="B29" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C29" s="267">
+      <c r="C29" s="264">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="268"/>
-      <c r="F29" s="267">
+      <c r="D29" s="265"/>
+      <c r="F29" s="264">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="268"/>
+      <c r="G29" s="265"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38418,22 +38447,22 @@
       <c r="B33" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C33" s="267">
+      <c r="C33" s="264">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="268"/>
-      <c r="F33" s="267">
+      <c r="D33" s="265"/>
+      <c r="F33" s="264">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="268"/>
+      <c r="G33" s="265"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="239" t="str">
@@ -38461,25 +38490,43 @@
       <c r="B35" s="210" t="s">
         <v>332</v>
       </c>
-      <c r="C35" s="267">
+      <c r="C35" s="264">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="268"/>
-      <c r="F35" s="267">
+      <c r="D35" s="265"/>
+      <c r="F35" s="264">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="268"/>
+      <c r="G35" s="265"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38490,24 +38537,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47126648-52DB-E24D-AF4A-37D7F46DB7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5590149E-93EE-6747-BA84-D5F7EF6BB258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -164,7 +164,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -175,28 +175,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -206,21 +185,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2485,7 +2455,16 @@
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2497,12 +2476,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2512,19 +2485,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12928,7 +12898,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12948,8 +12918,10 @@
     <v>24.245000000000001</v>
     <v>7.77</v>
     <v>0.83860000000000001</v>
-    <v>0.08</v>
-    <v>8.0000000000000002E-3</v>
+    <v>0.15</v>
+    <v>1.4999999999999999E-2</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12957,49 +12929,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.199999999999999</v>
+    <v>10.244999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.719201885935</v>
+    <v>46290.836163055472</v>
     <v>0</v>
     <v>9.9749999999999996</v>
-    <v>625675075</v>
+    <v>630020041</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
     <v>10.07</v>
-    <v>59.680300000000003</v>
+    <v>60.094700000000003</v>
     <v>10</v>
-    <v>10.08</v>
+    <v>10.15</v>
+    <v>10.15</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>216569</v>
+    <v>756630</v>
     <v>748802</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13018,7 +12976,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -13028,13 +12986,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13056,6 +13014,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13076,6 +13036,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13085,11 +13046,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13125,7 +13081,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13136,13 +13092,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13236,13 +13195,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13314,6 +13279,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13321,6 +13289,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13822,18 +13793,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="259" t="s">
+      <c r="B2" s="262" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="260"/>
-      <c r="E2" s="259" t="s">
+      <c r="C2" s="263"/>
+      <c r="E2" s="262" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="260"/>
-      <c r="H2" s="259" t="s">
+      <c r="F2" s="263"/>
+      <c r="H2" s="262" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="260"/>
+      <c r="I2" s="263"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13848,7 +13819,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>652438.07999999996</v>
+        <v>656968.9</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13856,7 +13827,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.402648144878828</v>
+        <v>10.398774522093143</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13872,7 +13843,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>645939.07999999996</v>
+        <v>650469.9</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13880,7 +13851,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.085142031856485</v>
+        <v>17.489107063427593</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13889,7 +13860,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13911,16 +13882,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>10.15</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-564.33133961491194</v>
+        <v>-568.25030725112663</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13928,7 +13899,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>10.836054101895284</v>
+        <v>11.240652209271225</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13937,14 +13908,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.2285591175931925</v>
+        <v>1.2370907781320342</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13952,23 +13923,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>13.739290381291442</v>
+        <v>13.940462760331782</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.2408840391413083E-2</v>
+        <v>1.2323262181817131E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13976,7 +13947,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.36302483941383346</v>
+        <v>0.37344460692923953</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13985,23 +13956,23 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>8.0000000000000002E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7720086229525715E-3</v>
+        <v>-1.7597878738287605E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14088,7 +14059,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>9.9610985306069211E-3</v>
+        <v>9.8924012993613537E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14101,10 +14072,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="261" t="s">
+      <c r="B17" s="264" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="261"/>
+      <c r="C17" s="264"/>
       <c r="E17" s="184" t="s">
         <v>308</v>
       </c>
@@ -14177,14 +14148,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="261" t="s">
+      <c r="B25" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="261"/>
-      <c r="E25" s="259" t="s">
+      <c r="C25" s="264"/>
+      <c r="E25" s="262" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="260"/>
+      <c r="F25" s="263"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14193,7 +14164,7 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
@@ -14233,15 +14204,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="258" t="s">
+      <c r="B33" s="259" t="s">
         <v>346</v>
       </c>
-      <c r="C33" s="258"/>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
+      <c r="C33" s="259"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="259"/>
+      <c r="G33" s="259"/>
+      <c r="H33" s="259"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14260,24 +14231,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="258"/>
-      <c r="C39" s="258"/>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
+      <c r="B39" s="259"/>
+      <c r="C39" s="259"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="259"/>
+      <c r="F39" s="259"/>
+      <c r="G39" s="259"/>
+      <c r="H39" s="259"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="258" t="s">
+      <c r="B42" s="259" t="s">
         <v>349</v>
       </c>
-      <c r="C42" s="258"/>
-      <c r="D42" s="258"/>
-      <c r="E42" s="258"/>
-      <c r="F42" s="258"/>
-      <c r="G42" s="258"/>
-      <c r="H42" s="258"/>
+      <c r="C42" s="259"/>
+      <c r="D42" s="259"/>
+      <c r="E42" s="259"/>
+      <c r="F42" s="259"/>
+      <c r="G42" s="259"/>
+      <c r="H42" s="259"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14364,24 +14335,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="258"/>
-      <c r="C55" s="258"/>
-      <c r="D55" s="258"/>
-      <c r="E55" s="258"/>
-      <c r="F55" s="258"/>
-      <c r="G55" s="258"/>
-      <c r="H55" s="258"/>
+      <c r="B55" s="259"/>
+      <c r="C55" s="259"/>
+      <c r="D55" s="259"/>
+      <c r="E55" s="259"/>
+      <c r="F55" s="259"/>
+      <c r="G55" s="259"/>
+      <c r="H55" s="259"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="258" t="s">
+      <c r="B58" s="259" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="258"/>
-      <c r="D58" s="258"/>
-      <c r="E58" s="258"/>
-      <c r="F58" s="258"/>
-      <c r="G58" s="258"/>
-      <c r="H58" s="258"/>
+      <c r="C58" s="259"/>
+      <c r="D58" s="259"/>
+      <c r="E58" s="259"/>
+      <c r="F58" s="259"/>
+      <c r="G58" s="259"/>
+      <c r="H58" s="259"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14430,28 +14401,28 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="258"/>
-      <c r="C68" s="258"/>
-      <c r="D68" s="258"/>
-      <c r="E68" s="258"/>
-      <c r="F68" s="258"/>
-      <c r="G68" s="258"/>
-      <c r="H68" s="258"/>
+      <c r="B68" s="259"/>
+      <c r="C68" s="259"/>
+      <c r="D68" s="259"/>
+      <c r="E68" s="259"/>
+      <c r="F68" s="259"/>
+      <c r="G68" s="259"/>
+      <c r="H68" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B68:H68"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14521,36 +14492,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="258" t="s">
+      <c r="S2" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
-      <c r="AA2" s="258" t="s">
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
+      <c r="AA2" s="259" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="258"/>
-      <c r="AC2" s="258"/>
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="259"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -14561,32 +14532,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="268" t="s">
+      <c r="S4" s="270" t="s">
         <v>126</v>
       </c>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
-      <c r="AA4" s="269"/>
-      <c r="AB4" s="269"/>
-      <c r="AC4" s="269"/>
+      <c r="T4" s="271"/>
+      <c r="U4" s="271"/>
+      <c r="V4" s="271"/>
+      <c r="W4" s="271"/>
+      <c r="X4" s="271"/>
+      <c r="Y4" s="271"/>
+      <c r="Z4" s="271"/>
+      <c r="AA4" s="271"/>
+      <c r="AB4" s="271"/>
+      <c r="AC4" s="271"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15077,33 +15048,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="258" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="268" t="s">
+      <c r="S11" s="270" t="s">
         <v>132</v>
       </c>
-      <c r="T11" s="269"/>
-      <c r="U11" s="269"/>
-      <c r="V11" s="269"/>
-      <c r="W11" s="269"/>
-      <c r="X11" s="269"/>
-      <c r="Y11" s="269"/>
-      <c r="Z11" s="269"/>
-      <c r="AA11" s="269"/>
-      <c r="AB11" s="269"/>
-      <c r="AC11" s="269"/>
+      <c r="T11" s="271"/>
+      <c r="U11" s="271"/>
+      <c r="V11" s="271"/>
+      <c r="W11" s="271"/>
+      <c r="X11" s="271"/>
+      <c r="Y11" s="271"/>
+      <c r="Z11" s="271"/>
+      <c r="AA11" s="271"/>
+      <c r="AB11" s="271"/>
+      <c r="AC11" s="271"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15544,33 +15515,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="267" t="s">
+      <c r="C19" s="258" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="267"/>
-      <c r="E19" s="267"/>
-      <c r="F19" s="267"/>
-      <c r="G19" s="267"/>
-      <c r="H19" s="267"/>
-      <c r="I19" s="267"/>
-      <c r="J19" s="267"/>
-      <c r="K19" s="267"/>
-      <c r="L19" s="267"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="258"/>
+      <c r="F19" s="258"/>
+      <c r="G19" s="258"/>
+      <c r="H19" s="258"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="268" t="s">
+      <c r="S19" s="270" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="269"/>
-      <c r="U19" s="269"/>
-      <c r="V19" s="269"/>
-      <c r="W19" s="269"/>
-      <c r="X19" s="269"/>
-      <c r="Y19" s="269"/>
-      <c r="Z19" s="269"/>
-      <c r="AA19" s="269"/>
-      <c r="AB19" s="269"/>
-      <c r="AC19" s="269"/>
+      <c r="T19" s="271"/>
+      <c r="U19" s="271"/>
+      <c r="V19" s="271"/>
+      <c r="W19" s="271"/>
+      <c r="X19" s="271"/>
+      <c r="Y19" s="271"/>
+      <c r="Z19" s="271"/>
+      <c r="AA19" s="271"/>
+      <c r="AB19" s="271"/>
+      <c r="AC19" s="271"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16807,35 +16778,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="P2" s="258" t="s">
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
+      <c r="P2" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="258"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258" t="s">
+      <c r="Q2" s="259"/>
+      <c r="R2" s="259"/>
+      <c r="S2" s="259"/>
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -16844,31 +16815,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="P4" s="269" t="s">
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="P4" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="Q4" s="269"/>
-      <c r="R4" s="269"/>
-      <c r="S4" s="269"/>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
+      <c r="Q4" s="271"/>
+      <c r="R4" s="271"/>
+      <c r="S4" s="271"/>
+      <c r="T4" s="271"/>
+      <c r="U4" s="271"/>
+      <c r="V4" s="271"/>
+      <c r="W4" s="271"/>
+      <c r="X4" s="271"/>
+      <c r="Y4" s="271"/>
+      <c r="Z4" s="271"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17063,32 +17034,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="258" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="269" t="s">
+      <c r="P9" s="271" t="s">
         <v>138</v>
       </c>
-      <c r="Q9" s="269"/>
-      <c r="R9" s="269"/>
-      <c r="S9" s="269"/>
-      <c r="T9" s="269"/>
-      <c r="U9" s="269"/>
-      <c r="V9" s="269"/>
-      <c r="W9" s="269"/>
-      <c r="X9" s="269"/>
-      <c r="Y9" s="269"/>
-      <c r="Z9" s="269"/>
+      <c r="Q9" s="271"/>
+      <c r="R9" s="271"/>
+      <c r="S9" s="271"/>
+      <c r="T9" s="271"/>
+      <c r="U9" s="271"/>
+      <c r="V9" s="271"/>
+      <c r="W9" s="271"/>
+      <c r="X9" s="271"/>
+      <c r="Y9" s="271"/>
+      <c r="Z9" s="271"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -17846,31 +17817,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="267" t="s">
+      <c r="C20" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="267"/>
-      <c r="E20" s="267"/>
-      <c r="F20" s="267"/>
-      <c r="G20" s="267"/>
-      <c r="H20" s="267"/>
-      <c r="I20" s="267"/>
-      <c r="J20" s="267"/>
-      <c r="K20" s="267"/>
-      <c r="L20" s="267"/>
-      <c r="P20" s="269" t="s">
+      <c r="D20" s="258"/>
+      <c r="E20" s="258"/>
+      <c r="F20" s="258"/>
+      <c r="G20" s="258"/>
+      <c r="H20" s="258"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="258"/>
+      <c r="L20" s="258"/>
+      <c r="P20" s="271" t="s">
         <v>140</v>
       </c>
-      <c r="Q20" s="269"/>
-      <c r="R20" s="269"/>
-      <c r="S20" s="269"/>
-      <c r="T20" s="269"/>
-      <c r="U20" s="269"/>
-      <c r="V20" s="269"/>
-      <c r="W20" s="269"/>
-      <c r="X20" s="269"/>
-      <c r="Y20" s="269"/>
-      <c r="Z20" s="269"/>
+      <c r="Q20" s="271"/>
+      <c r="R20" s="271"/>
+      <c r="S20" s="271"/>
+      <c r="T20" s="271"/>
+      <c r="U20" s="271"/>
+      <c r="V20" s="271"/>
+      <c r="W20" s="271"/>
+      <c r="X20" s="271"/>
+      <c r="Y20" s="271"/>
+      <c r="Z20" s="271"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18594,20 +18565,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -18625,18 +18596,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -18833,18 +18804,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="258" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="92"/>
       <c r="P11" s="272"/>
       <c r="Q11" s="272"/>
@@ -19098,18 +19069,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="258" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19327,18 +19298,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="267" t="s">
+      <c r="C26" s="258" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="267"/>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="267"/>
-      <c r="J26" s="267"/>
-      <c r="K26" s="267"/>
-      <c r="L26" s="267"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19530,18 +19501,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="267" t="s">
+      <c r="C33" s="258" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="E33" s="267"/>
-      <c r="F33" s="267"/>
-      <c r="G33" s="267"/>
-      <c r="H33" s="267"/>
-      <c r="I33" s="267"/>
-      <c r="J33" s="267"/>
-      <c r="K33" s="267"/>
-      <c r="L33" s="267"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19725,18 +19696,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="267" t="s">
+      <c r="C40" s="258" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="267"/>
-      <c r="E40" s="267"/>
-      <c r="F40" s="267"/>
-      <c r="G40" s="267"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="267"/>
-      <c r="J40" s="267"/>
-      <c r="K40" s="267"/>
-      <c r="L40" s="267"/>
+      <c r="D40" s="258"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="258"/>
+      <c r="G40" s="258"/>
+      <c r="H40" s="258"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20005,12 +19976,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20018,6 +19983,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20055,20 +20026,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="S2" s="272"/>
       <c r="T2" s="272"/>
       <c r="U2" s="272"/>
@@ -20086,18 +20057,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="S4" s="272"/>
       <c r="T4" s="272"/>
       <c r="U4" s="272"/>
@@ -20471,18 +20442,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="267" t="s">
+      <c r="C13" s="258" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="E13" s="267"/>
-      <c r="F13" s="267"/>
-      <c r="G13" s="267"/>
-      <c r="H13" s="267"/>
-      <c r="I13" s="267"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20575,18 +20546,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="258" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20778,18 +20749,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="267" t="s">
+      <c r="C25" s="258" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="E25" s="267"/>
-      <c r="F25" s="267"/>
-      <c r="G25" s="267"/>
-      <c r="H25" s="267"/>
-      <c r="I25" s="267"/>
-      <c r="J25" s="267"/>
-      <c r="K25" s="267"/>
-      <c r="L25" s="267"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20927,18 +20898,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="267" t="s">
+      <c r="C31" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="267"/>
-      <c r="E31" s="267"/>
-      <c r="F31" s="267"/>
-      <c r="G31" s="267"/>
-      <c r="H31" s="267"/>
-      <c r="I31" s="267"/>
-      <c r="J31" s="267"/>
-      <c r="K31" s="267"/>
-      <c r="L31" s="267"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="258"/>
+      <c r="G31" s="258"/>
+      <c r="H31" s="258"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21077,16 +21048,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21149,10 +21120,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="259" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="259"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21169,7 +21140,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21178,7 +21149,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>652438.07999999996</v>
+        <v>656968.9</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21237,10 +21208,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="259" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="258"/>
+      <c r="C15" s="259"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21248,7 +21219,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.2429366359038034E-2</v>
+        <v>9.1850471976731463E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21257,7 +21228,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.90757063364096202</v>
+        <v>0.90814952802326854</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21284,7 +21255,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.5844037072792034E-2</v>
+        <v>8.5866039111580361E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21329,20 +21300,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -21360,18 +21331,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="258" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -21535,7 +21506,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>841705.98304020159</v>
+        <v>841424.81769403827</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21589,23 +21560,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13208.368600431588</v>
+        <v>13208.100969777519</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8740.4350009135323</v>
+        <v>8740.0808035545488</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21332.985322255779</v>
+        <v>21331.688588653553</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>29945.734230247104</v>
+        <v>29943.30723775459</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>35994.773035857004</v>
+        <v>35991.126516530501</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21624,14 +21595,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>557600.50763572205</v>
+        <v>557357.77560073009</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="258" t="s">
+      <c r="B13" s="259" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="258"/>
+      <c r="C13" s="259"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21647,14 +21618,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5844037072792034E-2</v>
+        <v>8.5866039111580361E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="258" t="s">
+      <c r="B18" s="259" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="258"/>
+      <c r="C18" s="259"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21662,7 +21633,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109222.296189705</v>
+        <v>109214.30411627071</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21671,7 +21642,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>557600.50763572205</v>
+        <v>557357.77560073009</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21680,7 +21651,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>666822.80382542708</v>
+        <v>666572.07971700083</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21707,7 +21678,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>673321.80382542708</v>
+        <v>673071.07971700083</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21725,7 +21696,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.402648144878828</v>
+        <v>10.398774522093143</v>
       </c>
     </row>
   </sheetData>
@@ -21768,37 +21739,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="258" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21994,23 +21965,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13208.368600431588</v>
+        <v>13208.100969777519</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8740.4350009135323</v>
+        <v>8740.0808035545488</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21332.985322255779</v>
+        <v>21331.688588653553</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>29945.734230247104</v>
+        <v>29943.30723775459</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>35994.773035857004</v>
+        <v>35991.126516530501</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22018,18 +21989,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="258" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22223,18 +22194,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="267" t="s">
+      <c r="C17" s="258" t="s">
         <v>208</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="E17" s="267"/>
-      <c r="F17" s="267"/>
-      <c r="G17" s="267"/>
-      <c r="H17" s="267"/>
-      <c r="I17" s="267"/>
-      <c r="J17" s="267"/>
-      <c r="K17" s="267"/>
-      <c r="L17" s="267"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22368,18 +22339,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="267" t="s">
+      <c r="C22" s="258" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="267"/>
-      <c r="E22" s="267"/>
-      <c r="F22" s="267"/>
-      <c r="G22" s="267"/>
-      <c r="H22" s="267"/>
-      <c r="I22" s="267"/>
-      <c r="J22" s="267"/>
-      <c r="K22" s="267"/>
-      <c r="L22" s="267"/>
+      <c r="D22" s="258"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="258"/>
+      <c r="G22" s="258"/>
+      <c r="H22" s="258"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="258"/>
+      <c r="K22" s="258"/>
+      <c r="L22" s="258"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22463,18 +22434,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="267" t="s">
+      <c r="C27" s="258" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="267"/>
-      <c r="E27" s="267"/>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="267"/>
-      <c r="K27" s="267"/>
-      <c r="L27" s="267"/>
+      <c r="D27" s="258"/>
+      <c r="E27" s="258"/>
+      <c r="F27" s="258"/>
+      <c r="G27" s="258"/>
+      <c r="H27" s="258"/>
+      <c r="I27" s="258"/>
+      <c r="J27" s="258"/>
+      <c r="K27" s="258"/>
+      <c r="L27" s="258"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22744,10 +22715,10 @@
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="258" t="s">
+      <c r="B38" s="259" t="s">
         <v>217</v>
       </c>
-      <c r="C38" s="258"/>
+      <c r="C38" s="259"/>
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -22765,7 +22736,7 @@
       </c>
       <c r="C40" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5844037072792034E-2</v>
+        <v>8.5866039111580361E-2</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -22790,8 +22761,8 @@
         <v>432</v>
       </c>
       <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5-G31+G32</f>
-        <v>1026126.3800000949</v>
+        <f ca="1">C42/(1+C40)^5</f>
+        <v>1052277.7661876741</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -22800,7 +22771,7 @@
       </c>
       <c r="C44" s="112">
         <f ca="1">SUM(H9:K9)+C43</f>
-        <v>1099353.9031539429</v>
+        <v>1125500.9437874143</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22827,7 +22798,7 @@
       </c>
       <c r="C47" s="112">
         <f ca="1">C44+C45-C46</f>
-        <v>1105852.9031539429</v>
+        <v>1131999.9437874143</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -22845,14 +22816,14 @@
       </c>
       <c r="C49" s="257">
         <f ca="1">C47/C48</f>
-        <v>17.085142031856485</v>
+        <v>17.489107063427593</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="258" t="s">
+      <c r="B51" s="259" t="s">
         <v>222</v>
       </c>
-      <c r="C51" s="258"/>
+      <c r="C51" s="259"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -22908,10 +22879,10 @@
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="258" t="s">
+      <c r="B59" s="259" t="s">
         <v>335</v>
       </c>
-      <c r="C59" s="258"/>
+      <c r="C59" s="259"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -22928,7 +22899,7 @@
       </c>
       <c r="C61" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5844037072792034E-2</v>
+        <v>8.5866039111580361E-2</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -22953,8 +22924,8 @@
         <v>432</v>
       </c>
       <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5-G31+G32</f>
-        <v>621647.91464542609</v>
+        <f ca="1">C63/(1+C61)^5</f>
+        <v>647840.27729754907</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -22963,7 +22934,7 @@
       </c>
       <c r="C65" s="112">
         <f ca="1">SUM(H9:K9)+C64</f>
-        <v>694875.43779927411</v>
+        <v>721063.45489728928</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22990,7 +22961,7 @@
       </c>
       <c r="C68" s="112">
         <f ca="1">C65+C66-C67</f>
-        <v>701374.43779927411</v>
+        <v>727562.45489728928</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -23008,7 +22979,7 @@
       </c>
       <c r="C70" s="257">
         <f ca="1">C68/C69</f>
-        <v>10.836054101895284</v>
+        <v>11.240652209271225</v>
       </c>
     </row>
   </sheetData>
@@ -23060,10 +23031,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="259" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="259"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23072,7 +23043,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.402648144878828</v>
+        <v>10.398774522093143</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23081,7 +23052,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C49</f>
-        <v>17.085142031856485</v>
+        <v>17.489107063427593</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23099,7 +23070,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C70</f>
-        <v>10.836054101895284</v>
+        <v>11.240652209271225</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23108,7 +23079,7 @@
       </c>
       <c r="C9" s="257">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>13.739290381291442</v>
+        <v>13.940462760331782</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23117,7 +23088,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23126,7 +23097,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.36302483941383346</v>
+        <v>0.37344460692923953</v>
       </c>
     </row>
   </sheetData>
@@ -23182,37 +23153,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="258" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23325,18 +23296,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="258" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23457,18 +23428,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="267" t="s">
+      <c r="C14" s="258" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="267"/>
-      <c r="E14" s="267"/>
-      <c r="F14" s="267"/>
-      <c r="G14" s="267"/>
-      <c r="H14" s="267"/>
-      <c r="I14" s="267"/>
-      <c r="J14" s="267"/>
-      <c r="K14" s="267"/>
-      <c r="L14" s="267"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="258"/>
+      <c r="F14" s="258"/>
+      <c r="G14" s="258"/>
+      <c r="H14" s="258"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="258"/>
+      <c r="K14" s="258"/>
+      <c r="L14" s="258"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23558,10 +23529,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="258" t="s">
+      <c r="B20" s="259" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="258"/>
+      <c r="C20" s="259"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23662,20 +23633,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="259" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -23693,18 +23664,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="258" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -23849,7 +23820,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>822125.24995348987</v>
+        <v>821850.62539913203</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -23903,23 +23874,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10756.609237811752</v>
+        <v>10756.391285205114</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14463.080286872137</v>
+        <v>14462.494185054566</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19446.712877622733</v>
+        <v>19445.530801806326</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>26147.58642306368</v>
+        <v>26145.467256592146</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>35157.42120810099</v>
+        <v>35153.859518302932</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -23938,7 +23909,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>544628.96302391612</v>
+        <v>544391.87770082173</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23954,7 +23925,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23963,7 +23934,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.586254016487368</v>
+        <v>10.582310914078761</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24002,7 +23973,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5844037072792034E-2</v>
+        <v>8.5866039111580361E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24020,7 +23991,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>625675.68000000005</v>
+        <v>630020.65</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24047,7 +24018,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>619176.68000000005</v>
+        <v>623521.65</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24063,7 +24034,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>105971.41003347129</v>
+        <v>105963.74304696108</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24072,7 +24043,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>544628.96302391612</v>
+        <v>544391.87770082173</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24081,7 +24052,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>650600.37305738742</v>
+        <v>650355.62074778276</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24108,7 +24079,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>657099.37305738742</v>
+        <v>656854.62074778276</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24126,21 +24097,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.586254016487368</v>
+        <v>10.582310914078761</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31099,7 +31070,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31170,7 +31141,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32248,7 +32219,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-564.33133961491194</v>
+        <v>-568.25030725112663</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32285,7 +32256,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.2285591175931925</v>
+        <v>1.2370907781320342</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32346,7 +32317,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.6825978147161094</v>
+        <v>1.6942825217627491</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32407,7 +32378,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>652438.07999999996</v>
+        <v>656968.9</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32468,7 +32439,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>645939.07999999996</v>
+        <v>650469.9</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32505,7 +32476,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.2720519581798093</v>
+        <v>1.2809745309604506</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32542,7 +32513,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>51.514401467421642</v>
+        <v>51.875739692160458</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32677,7 +32648,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>80.587707509881412</v>
+        <v>81.147344367588943</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32714,7 +32685,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-107.40072423509928</v>
+        <v>-108.15406671652784</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32751,7 +32722,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.2408840391413083E-2</v>
+        <v>1.2323262181817131E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32788,7 +32759,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.7720086229525715E-3</v>
+        <v>-1.7597878738287605E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33402,7 +33373,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.9610985306069211E-3</v>
+        <v>9.8924012993613537E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34998,15 +34969,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="259" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="258"/>
-      <c r="E4" s="258" t="s">
+      <c r="C4" s="259"/>
+      <c r="E4" s="259" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35014,7 +34985,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35030,7 +35001,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>652438.07999999996</v>
+        <v>656968.9</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35050,7 +35021,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>645939.07999999996</v>
+        <v>650469.9</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35070,7 +35041,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-564.33133961491194</v>
+        <v>-568.25030725112663</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35090,7 +35061,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2285591175931925</v>
+        <v>1.2370907781320342</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35110,7 +35081,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.6825978147161094</v>
+        <v>1.6942825217627491</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35130,7 +35101,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.2720519581798093</v>
+        <v>1.2809745309604506</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35139,18 +35110,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>51.514401467421642</v>
+        <v>51.875739692160458</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="258"/>
-      <c r="E15" s="258" t="s">
+      <c r="C15" s="259"/>
+      <c r="E15" s="259" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="258"/>
+      <c r="F15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35201,14 +35172,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="258" t="s">
+      <c r="B21" s="259" t="s">
         <v>257</v>
       </c>
-      <c r="C21" s="258"/>
-      <c r="E21" s="258" t="s">
+      <c r="C21" s="259"/>
+      <c r="E21" s="259" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="258"/>
+      <c r="F21" s="259"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35277,14 +35248,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="258" t="s">
+      <c r="B29" s="259" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="258"/>
-      <c r="E29" s="258" t="s">
+      <c r="C29" s="259"/>
+      <c r="E29" s="259" t="s">
         <v>268</v>
       </c>
-      <c r="F29" s="258"/>
+      <c r="F29" s="259"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35360,14 +35331,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="259" t="s">
         <v>280</v>
       </c>
-      <c r="C37" s="258"/>
-      <c r="E37" s="258" t="s">
+      <c r="C37" s="259"/>
+      <c r="E37" s="259" t="s">
         <v>283</v>
       </c>
-      <c r="F37" s="258"/>
+      <c r="F37" s="259"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35375,7 +35346,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7720086229525715E-3</v>
+        <v>-1.7597878738287605E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35391,7 +35362,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.2408840391413083E-2</v>
+        <v>1.2323262181817131E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35436,14 +35407,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="258" t="s">
+      <c r="B45" s="259" t="s">
         <v>291</v>
       </c>
-      <c r="C45" s="258"/>
-      <c r="E45" s="258" t="s">
+      <c r="C45" s="259"/>
+      <c r="E45" s="259" t="s">
         <v>297</v>
       </c>
-      <c r="F45" s="258"/>
+      <c r="F45" s="259"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35476,18 +35447,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>9.9610985306069211E-3</v>
+        <v>9.8924012993613537E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="258" t="s">
+      <c r="B51" s="259" t="s">
         <v>294</v>
       </c>
-      <c r="C51" s="258"/>
-      <c r="E51" s="258" t="s">
+      <c r="C51" s="259"/>
+      <c r="E51" s="259" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="258"/>
+      <c r="F51" s="259"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35655,7 +35626,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35684,7 +35655,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>652438.07999999996</v>
+        <v>656968.9</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35713,7 +35684,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>645939.07999999996</v>
+        <v>650469.9</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35742,7 +35713,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-564.33133961491194</v>
+        <v>-568.25030725112663</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35771,7 +35742,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2285591175931925</v>
+        <v>1.2370907781320342</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35800,7 +35771,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.6825978147161094</v>
+        <v>1.6942825217627491</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35829,7 +35800,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.2720519581798093</v>
+        <v>1.2809745309604506</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35858,7 +35829,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>51.514401467421642</v>
+        <v>51.875739692160458</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36631,7 +36602,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7720086229525715E-3</v>
+        <v>-1.7597878738287605E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36660,7 +36631,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.2408840391413083E-2</v>
+        <v>1.2323262181817131E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36983,7 +36954,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.9610985306069211E-3</v>
+        <v>9.8924012993613537E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37472,14 +37443,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="265" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="266"/>
+      <c r="F3" s="267" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="266"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37546,19 +37517,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="268">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="269"/>
+      <c r="F7" s="268">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="269"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37585,19 +37556,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="268">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="269"/>
+      <c r="F9" s="268">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="269"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -37624,19 +37595,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="268">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="269"/>
+      <c r="F11" s="268">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="269"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -37663,19 +37634,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="268">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="269"/>
+      <c r="F13" s="268">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="269"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -37702,19 +37673,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="268">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="269"/>
+      <c r="F15" s="268">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="269"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -37741,19 +37712,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="268">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="269"/>
+      <c r="F17" s="268">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="269"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -37780,22 +37751,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="268">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="269"/>
+      <c r="F19" s="268">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="269"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -37822,22 +37793,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="268">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="269"/>
+      <c r="F21" s="268">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="269"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37886,22 +37857,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="268">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="269"/>
+      <c r="F25" s="268">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="269"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37929,22 +37900,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="268">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="269"/>
+      <c r="F27" s="268">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="269"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37972,22 +37943,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="268">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="269"/>
+      <c r="F29" s="268">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="269"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38036,22 +38007,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="268">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="269"/>
+      <c r="F33" s="268">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="269"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38079,43 +38050,25 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="262">
+      <c r="C35" s="268">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="263"/>
-      <c r="F35" s="262">
+      <c r="D35" s="269"/>
+      <c r="F35" s="268">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="263"/>
+      <c r="G35" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38126,6 +38079,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5590149E-93EE-6747-BA84-D5F7EF6BB258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E1BD86-C050-9D45-A700-86E0FFD98798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="440">
   <si>
     <t>Ticker</t>
   </si>
@@ -1502,6 +1502,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>EV/Sales price</t>
   </si>
 </sst>
 </file>
@@ -2476,6 +2491,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2483,12 +2504,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2500,14 +2515,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12917,7 +12932,7 @@
     <v>Powered by Refinitiv</v>
     <v>24.245000000000001</v>
     <v>7.77</v>
-    <v>0.83860000000000001</v>
+    <v>0.83169999999999999</v>
     <v>0.15</v>
     <v>1.4999999999999999E-2</v>
     <v>0</v>
@@ -12929,24 +12944,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.244999999999999</v>
+    <v>10.25</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.836163055472</v>
+    <v>46290.979243992966</v>
     <v>0</v>
-    <v>9.9749999999999996</v>
+    <v>9.9700000000000006</v>
     <v>630020041</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.07</v>
-    <v>60.094700000000003</v>
+    <v>9.9700000000000006</v>
+    <v>59.203099999999999</v>
     <v>10</v>
     <v>10.15</v>
     <v>10.15</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>756630</v>
+    <v>757838</v>
     <v>748802</v>
     <v>2005</v>
   </rv>
@@ -12969,19 +12984,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13203,9 +13218,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13827,7 +13842,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.398774522093143</v>
+        <v>10.413257673494117</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13851,7 +13866,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.489107063427593</v>
+        <v>17.495511776203944</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13875,7 +13890,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.633317246535167</v>
+        <v>16.640228160278969</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13899,7 +13914,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>11.240652209271225</v>
+        <v>14.026012208255541</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13918,12 +13933,12 @@
         <v>1.2370907781320342</v>
       </c>
       <c r="H7" s="184" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="212">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>13.940462760331782</v>
+        <f ca="1">'AVG target price'!C10</f>
+        <v>16.792154061860721</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13942,12 +13957,12 @@
         <v>1.2323262181817131E-2</v>
       </c>
       <c r="H8" s="184" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="213">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>0.37344460692923953</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.65439941496164733</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14027,7 +14042,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.83860000000000001</v>
+        <v>0.83169999999999999</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14169,7 +14184,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14184,7 +14199,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14411,18 +14426,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -19976,6 +19991,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19983,12 +20004,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21048,16 +21063,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21167,7 +21182,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21176,7 +21191,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.83860000000000001</v>
+        <v>0.83169999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21246,7 +21261,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.9356999999999992E-2</v>
+        <v>8.9266499999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21255,7 +21270,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.5866039111580361E-2</v>
+        <v>8.578385157929426E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21506,7 +21521,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>841424.81769403827</v>
+        <v>842476.05789524782</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21560,23 +21575,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13208.100969777519</v>
+        <v>13209.100746319888</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8740.0808035545488</v>
+        <v>8741.4040003560513</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21331.688588653553</v>
+        <v>21336.533010181007</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>29943.30723775459</v>
+        <v>29952.374405081457</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>35991.126516530501</v>
+        <v>36004.750175200425</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21595,7 +21610,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>557357.77560073009</v>
+        <v>558265.3538374413</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21618,7 +21633,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5866039111580361E-2</v>
+        <v>8.578385157929426E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21633,7 +21648,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109214.30411627071</v>
+        <v>109244.16233713884</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21642,7 +21657,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>557357.77560073009</v>
+        <v>558265.3538374413</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21651,7 +21666,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>666572.07971700083</v>
+        <v>667509.5161745802</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21678,7 +21693,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>673071.07971700083</v>
+        <v>674008.5161745802</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21696,7 +21711,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.398774522093143</v>
+        <v>10.413257673494117</v>
       </c>
     </row>
   </sheetData>
@@ -21717,7 +21732,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="84" customWidth="1"/>
@@ -21965,23 +21980,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13208.100969777519</v>
+        <v>13209.100746319888</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8740.0808035545488</v>
+        <v>8741.4040003560513</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21331.688588653553</v>
+        <v>21336.533010181007</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>29943.30723775459</v>
+        <v>29952.374405081457</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>35991.126516530501</v>
+        <v>36004.750175200425</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22686,7 +22701,7 @@
         <v>-7.7178480374902509</v>
       </c>
       <c r="D35" s="151">
-        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
         <v>-9.5360928339390991</v>
       </c>
       <c r="E35" s="151">
@@ -22709,285 +22724,421 @@
       <c r="N35" s="92"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="C36" s="151">
+        <f>C33/C6</f>
+        <v>5.2442479353570972</v>
+      </c>
+      <c r="D36" s="151">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>6.1550589156669391</v>
+      </c>
+      <c r="E36" s="151">
+        <f t="shared" si="14"/>
+        <v>3.7082428241448895</v>
+      </c>
+      <c r="F36" s="151">
+        <f t="shared" si="14"/>
+        <v>3.8161824431353959</v>
+      </c>
+      <c r="G36" s="152">
+        <f t="shared" si="14"/>
+        <v>1.7730998915918108</v>
+      </c>
+      <c r="H36" s="141"/>
+      <c r="I36" s="141"/>
+      <c r="J36" s="141"/>
+      <c r="K36" s="141"/>
+      <c r="L36" s="141"/>
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="259" t="s">
+      <c r="N38" s="92"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="259" t="s">
         <v>217</v>
       </c>
-      <c r="C38" s="259"/>
-      <c r="N38" s="92"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="259"/>
+      <c r="N39" s="92"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>79429.467600379314</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="139">
+      <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5866039111580361E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+        <v>8.578385157929426E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="C41" s="107">
+      <c r="C42" s="107">
         <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>1588589.3520075863</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>1588589.3520075863</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5</f>
-        <v>1052277.7661876741</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="24">
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>1052676.0830646381</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="C44" s="112">
-        <f ca="1">SUM(H9:K9)+C43</f>
-        <v>1125500.9437874143</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="112">
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>1125915.4952265765</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C45" s="89">
+      <c r="C46" s="89">
         <f>Statement!AC111</f>
         <v>72945</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="89">
+      <c r="C47" s="89">
         <f>Statement!AC112</f>
         <v>66446</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="C47" s="112">
-        <f ca="1">C44+C45-C46</f>
-        <v>1131999.9437874143</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="112">
+        <f ca="1">C45+C46-C47</f>
+        <v>1132414.4952265765</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="89">
+      <c r="C49" s="89">
         <f>Statement!AC80</f>
         <v>64726</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="256" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="C49" s="257">
-        <f ca="1">C47/C48</f>
-        <v>17.489107063427593</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="259" t="s">
+      <c r="C50" s="257">
+        <f ca="1">C48/C49</f>
+        <v>17.495511776203944</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="259" t="s">
         <v>222</v>
       </c>
-      <c r="C51" s="259"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="259"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>786430.37228098325</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C53" s="139">
+      <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.9356999999999992E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+        <v>8.9266499999999999E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="107">
+      <c r="C55" s="107">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>92459.495500155026</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>25.517023471526446</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="256" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="C57" s="257">
-        <f ca="1">C56/(1+C53)^5</f>
-        <v>16.633317246535167</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="259" t="s">
+      <c r="C58" s="257">
+        <f ca="1">C57/(1+C54)^5</f>
+        <v>16.640228160278969</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="259" t="s">
         <v>335</v>
       </c>
-      <c r="C59" s="259"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="259"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>54334.627403617545</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C61" s="139">
+      <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5866039111580361E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+        <v>8.578385157929426E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="C62" s="107">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>978023.29326511582</v>
+      <c r="C63" s="107">
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>1249696.4302832035</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5</f>
-        <v>647840.27729754907</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="24">
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>828109.25402960973</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="C65" s="112">
-        <f ca="1">SUM(H9:K9)+C64</f>
-        <v>721063.45489728928</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="112">
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>901348.66619154811</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C66" s="89">
+      <c r="C67" s="89">
         <f>Statement!AC111</f>
         <v>72945</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C67" s="89">
+      <c r="C68" s="89">
         <f>Statement!AC112</f>
         <v>66446</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="C68" s="112">
-        <f ca="1">C65+C66-C67</f>
-        <v>727562.45489728928</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="112">
+        <f ca="1">C66+C67-C68</f>
+        <v>907847.66619154811</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C69" s="89">
+      <c r="C70" s="89">
         <f>Statement!AC80</f>
         <v>64726</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="256" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="C70" s="257">
-        <f ca="1">C68/C69</f>
-        <v>11.240652209271225</v>
+      <c r="C71" s="257">
+        <f ca="1">C69/C70</f>
+        <v>14.026012208255541</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="259" t="s">
+        <v>436</v>
+      </c>
+      <c r="C73" s="259"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>786430.37228098325</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C75" s="139">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>8.578385157929426E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>438</v>
+      </c>
+      <c r="C76" s="107">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>2359291.1168429498</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C78" s="24">
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>1563380.3213831258</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="112">
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>1636619.7335450642</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C80" s="89">
+        <f>Statement!AC111</f>
+        <v>72945</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C81" s="89">
+        <f>Statement!AC112</f>
+        <v>66446</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C82" s="112">
+        <f ca="1">C79+C80-C81</f>
+        <v>1643118.7335450642</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C83" s="89">
+        <f>Statement!AC80</f>
+        <v>64726</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="256" t="s">
+        <v>221</v>
+      </c>
+      <c r="C84" s="257">
+        <f ca="1">C82/C83</f>
+        <v>25.385760491071043</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -23004,7 +23155,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="84" customWidth="1"/>
@@ -23043,7 +23194,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.398774522093143</v>
+        <v>10.413257673494117</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23051,8 +23202,8 @@
         <v>228</v>
       </c>
       <c r="C6" s="137">
-        <f ca="1">Multiples!C49</f>
-        <v>17.489107063427593</v>
+        <f ca="1">Multiples!C50</f>
+        <v>17.495511776203944</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23060,8 +23211,8 @@
         <v>229</v>
       </c>
       <c r="C7" s="137">
-        <f ca="1">Multiples!C57</f>
-        <v>16.633317246535167</v>
+        <f ca="1">Multiples!C58</f>
+        <v>16.640228160278969</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23069,35 +23220,44 @@
         <v>336</v>
       </c>
       <c r="C8" s="137">
-        <f ca="1">Multiples!C70</f>
-        <v>11.240652209271225</v>
+        <f ca="1">Multiples!C71</f>
+        <v>14.026012208255541</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="256" t="s">
+      <c r="B9" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="137">
+        <f ca="1">Multiples!C84</f>
+        <v>25.385760491071043</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="256" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="257">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>13.940462760331782</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="257">
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>16.792154061860721</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="137">
+      <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
         <v>10.15</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C11" s="156">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>0.37344460692923953</v>
+      <c r="C12" s="156">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>0.65439941496164733</v>
       </c>
     </row>
   </sheetData>
@@ -23567,7 +23727,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.9356999999999992E-2</v>
+        <v>8.9266499999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23820,7 +23980,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>821850.62539913203</v>
+        <v>822877.41044117115</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -23874,23 +24034,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10756.391285205114</v>
+        <v>10757.205481561736</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14462.494185054566</v>
+        <v>14464.683721567733</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19445.530801806326</v>
+        <v>19449.946877338156</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>26145.467256592146</v>
+        <v>26153.384395623329</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>35153.859518302932</v>
+        <v>35167.166247748799</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -23909,15 +24069,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>544391.87770082173</v>
+        <v>545278.34280828538</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="273" t="s">
+      <c r="B14" s="274" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="274"/>
+      <c r="C14" s="275"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -23934,7 +24094,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.582310914078761</v>
+        <v>10.597053850141373</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23944,20 +24104,20 @@
       <c r="C17" s="160">
         <v>0.46</v>
       </c>
-      <c r="E17" s="275" t="s">
+      <c r="E17" s="273" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="275"/>
-      <c r="G17" s="275"/>
-      <c r="H17" s="275"/>
-      <c r="I17" s="275"/>
+      <c r="F17" s="273"/>
+      <c r="G17" s="273"/>
+      <c r="H17" s="273"/>
+      <c r="I17" s="273"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="273" t="s">
+      <c r="B19" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="274"/>
+      <c r="C19" s="275"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -23973,7 +24133,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.5866039111580361E-2</v>
+        <v>8.578385157929426E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24023,10 +24183,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="273" t="s">
+      <c r="B28" s="274" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="274"/>
+      <c r="C28" s="275"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24034,7 +24194,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>105963.74304696108</v>
+        <v>105992.38672383975</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24043,7 +24203,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>544391.87770082173</v>
+        <v>545278.34280828538</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24052,7 +24212,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>650355.62074778276</v>
+        <v>651270.72953212517</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24079,7 +24239,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>656854.62074778276</v>
+        <v>657769.72953212517</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24097,21 +24257,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.582310914078761</v>
+        <v>10.597053850141373</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -37443,14 +37603,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="265" t="s">
+      <c r="C3" s="267" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="266"/>
-      <c r="F3" s="267" t="s">
+      <c r="D3" s="268"/>
+      <c r="F3" s="269" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="266"/>
+      <c r="G3" s="268"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37517,19 +37677,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="268">
+      <c r="C7" s="265">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="269"/>
-      <c r="F7" s="268">
+      <c r="D7" s="266"/>
+      <c r="F7" s="265">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="269"/>
+      <c r="G7" s="266"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37556,19 +37716,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="268">
+      <c r="C9" s="265">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="269"/>
-      <c r="F9" s="268">
+      <c r="D9" s="266"/>
+      <c r="F9" s="265">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="269"/>
+      <c r="G9" s="266"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -37595,19 +37755,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="268">
+      <c r="C11" s="265">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="269"/>
-      <c r="F11" s="268">
+      <c r="D11" s="266"/>
+      <c r="F11" s="265">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="269"/>
+      <c r="G11" s="266"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -37634,19 +37794,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="268">
+      <c r="C13" s="265">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="269"/>
-      <c r="F13" s="268">
+      <c r="D13" s="266"/>
+      <c r="F13" s="265">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="269"/>
+      <c r="G13" s="266"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -37673,19 +37833,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="268">
+      <c r="C15" s="265">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="269"/>
-      <c r="F15" s="268">
+      <c r="D15" s="266"/>
+      <c r="F15" s="265">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="269"/>
+      <c r="G15" s="266"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -37712,19 +37872,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="268">
+      <c r="C17" s="265">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="269"/>
-      <c r="F17" s="268">
+      <c r="D17" s="266"/>
+      <c r="F17" s="265">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="269"/>
+      <c r="G17" s="266"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -37751,22 +37911,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="268">
+      <c r="C19" s="265">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="269"/>
-      <c r="F19" s="268">
+      <c r="D19" s="266"/>
+      <c r="F19" s="265">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="269"/>
+      <c r="G19" s="266"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -37793,22 +37953,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="268">
+      <c r="C21" s="265">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="269"/>
-      <c r="F21" s="268">
+      <c r="D21" s="266"/>
+      <c r="F21" s="265">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="269"/>
+      <c r="G21" s="266"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37857,22 +38017,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="268">
+      <c r="C25" s="265">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="269"/>
-      <c r="F25" s="268">
+      <c r="D25" s="266"/>
+      <c r="F25" s="265">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="269"/>
+      <c r="G25" s="266"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37900,22 +38060,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="268">
+      <c r="C27" s="265">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="269"/>
-      <c r="F27" s="268">
+      <c r="D27" s="266"/>
+      <c r="F27" s="265">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="269"/>
+      <c r="G27" s="266"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37943,22 +38103,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="268">
+      <c r="C29" s="265">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="269"/>
-      <c r="F29" s="268">
+      <c r="D29" s="266"/>
+      <c r="F29" s="265">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="269"/>
+      <c r="G29" s="266"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38007,22 +38167,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="268">
+      <c r="C33" s="265">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="269"/>
-      <c r="F33" s="268">
+      <c r="D33" s="266"/>
+      <c r="F33" s="265">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="269"/>
+      <c r="G33" s="266"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38050,25 +38210,43 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="268">
+      <c r="C35" s="265">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="269"/>
-      <c r="F35" s="268">
+      <c r="D35" s="266"/>
+      <c r="F35" s="265">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="269"/>
+      <c r="G35" s="266"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38079,24 +38257,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E1BD86-C050-9D45-A700-86E0FFD98798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4FBED4-325C-8748-8566-3E3814D5C072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="441">
   <si>
     <t>Ticker</t>
   </si>
@@ -1517,6 +1517,9 @@
   </si>
   <si>
     <t>EV/Sales price</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2470,18 +2473,6 @@
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2489,6 +2480,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2506,10 +2500,19 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12932,9 +12935,9 @@
     <v>Powered by Refinitiv</v>
     <v>24.245000000000001</v>
     <v>7.77</v>
-    <v>0.83169999999999999</v>
-    <v>0.15</v>
-    <v>1.4999999999999999E-2</v>
+    <v>0.84109999999999996</v>
+    <v>-0.09</v>
+    <v>-8.9110000000000005E-3</v>
     <v>0</v>
     <v>0</v>
     <v>USD</v>
@@ -12944,25 +12947,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.25</v>
+    <v>10.15</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.979243992966</v>
+    <v>46294.937500010936</v>
     <v>0</v>
-    <v>9.9700000000000006</v>
-    <v>630020041</v>
+    <v>9.75</v>
+    <v>621330109</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>9.9700000000000006</v>
-    <v>59.203099999999999</v>
-    <v>10</v>
-    <v>10.15</v>
-    <v>10.15</v>
+    <v>10.07</v>
+    <v>59.265799999999999</v>
+    <v>10.1</v>
+    <v>10.01</v>
+    <v>10.01</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>757838</v>
-    <v>748802</v>
+    <v>570646</v>
+    <v>733676</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -12984,19 +12987,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.15</v>
+    <v>2.8630000000000001E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>52.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.13</v>
+    <v>52.4</v>
+    <v>52.55</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13808,18 +13811,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="262" t="s">
+      <c r="B2" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="263"/>
-      <c r="E2" s="262" t="s">
+      <c r="C2" s="259"/>
+      <c r="E2" s="258" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="263"/>
-      <c r="H2" s="262" t="s">
+      <c r="F2" s="259"/>
+      <c r="H2" s="258" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="263"/>
+      <c r="I2" s="259"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13834,7 +13837,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>656968.9</v>
+        <v>647907.26</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13842,7 +13845,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.413257673494117</v>
+        <v>10.242327948114355</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13858,7 +13861,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>650469.9</v>
+        <v>641408.26</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13866,7 +13869,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.495511776203944</v>
+        <v>17.41906297434867</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13875,7 +13878,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13890,7 +13893,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.640228160278969</v>
+        <v>16.553955930312938</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13899,14 +13902,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-568.25030725112663</v>
+        <v>-560.41237197869725</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13914,7 +13917,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.026012208255541</v>
+        <v>13.965233089151369</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13923,22 +13926,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.15</v>
+        <v>-0.09</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.2370907781320342</v>
-      </c>
-      <c r="H7" s="184" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="212">
-        <f ca="1">'AVG target price'!C10</f>
-        <v>16.792154061860721</v>
+        <v>1.2200274570543508</v>
+      </c>
+      <c r="H7" s="185" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales price</v>
+      </c>
+      <c r="I7" s="211">
+        <f ca="1">'AVG target price'!C9</f>
+        <v>25.273676090545717</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13954,15 +13957,15 @@
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.2323262181817131E-2</v>
+        <v>1.2495615499045341E-2</v>
       </c>
       <c r="H8" s="184" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="213">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>0.65439941496164733</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="212">
+        <f ca="1">'AVG target price'!C10</f>
+        <v>16.69085120649461</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13971,14 +13974,22 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>-8.9110000000000005E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7597878738287605E-3</v>
+        <v>-1.7844002916445475E-3</v>
+      </c>
+      <c r="H9" s="184" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="213">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.66741770294651459</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13996,13 +14007,6 @@
         <f ca="1">Statement!AC164</f>
         <v>0</v>
       </c>
-      <c r="H10" s="184" t="s">
-        <v>427</v>
-      </c>
-      <c r="I10" s="212">
-        <f ca="1">DDM!C26</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="185" t="s">
@@ -14019,6 +14023,13 @@
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
+      <c r="H11" s="184" t="s">
+        <v>427</v>
+      </c>
+      <c r="I11" s="212">
+        <f ca="1">DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="185" t="s">
@@ -14042,7 +14053,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.83169999999999999</v>
+        <v>0.84109999999999996</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14051,6 +14062,13 @@
         <f>Statement!AC129</f>
         <v>-3.1491107997558164E-3</v>
       </c>
+      <c r="H13" s="184" t="s">
+        <v>440</v>
+      </c>
+      <c r="I13" s="213">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.45</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="186" t="s">
@@ -14058,7 +14076,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>748802</v>
+        <v>733676</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14074,7 +14092,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>9.8924012993613537E-3</v>
+        <v>1.0030756562289486E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14087,10 +14105,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="264" t="s">
+      <c r="B17" s="260" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="264"/>
+      <c r="C17" s="260"/>
       <c r="E17" s="184" t="s">
         <v>308</v>
       </c>
@@ -14163,14 +14181,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="264" t="s">
+      <c r="B25" s="260" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="264"/>
-      <c r="E25" s="262" t="s">
+      <c r="C25" s="260"/>
+      <c r="E25" s="258" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="263"/>
+      <c r="F25" s="259"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14184,7 +14202,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14199,7 +14217,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14219,15 +14237,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="259" t="s">
+      <c r="B33" s="136" t="s">
         <v>346</v>
       </c>
-      <c r="C33" s="259"/>
-      <c r="D33" s="259"/>
-      <c r="E33" s="259"/>
-      <c r="F33" s="259"/>
-      <c r="G33" s="259"/>
-      <c r="H33" s="259"/>
+      <c r="C33" s="136"/>
+      <c r="D33" s="136"/>
+      <c r="E33" s="136"/>
+      <c r="F33" s="136"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="136"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14246,24 +14264,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="259"/>
-      <c r="C39" s="259"/>
-      <c r="D39" s="259"/>
-      <c r="E39" s="259"/>
-      <c r="F39" s="259"/>
-      <c r="G39" s="259"/>
-      <c r="H39" s="259"/>
+      <c r="B39" s="136"/>
+      <c r="C39" s="136"/>
+      <c r="D39" s="136"/>
+      <c r="E39" s="136"/>
+      <c r="F39" s="136"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="136"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="259" t="s">
+      <c r="B42" s="136" t="s">
         <v>349</v>
       </c>
-      <c r="C42" s="259"/>
-      <c r="D42" s="259"/>
-      <c r="E42" s="259"/>
-      <c r="F42" s="259"/>
-      <c r="G42" s="259"/>
-      <c r="H42" s="259"/>
+      <c r="C42" s="136"/>
+      <c r="D42" s="136"/>
+      <c r="E42" s="136"/>
+      <c r="F42" s="136"/>
+      <c r="G42" s="136"/>
+      <c r="H42" s="136"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14350,24 +14368,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="259"/>
-      <c r="C55" s="259"/>
-      <c r="D55" s="259"/>
-      <c r="E55" s="259"/>
-      <c r="F55" s="259"/>
-      <c r="G55" s="259"/>
-      <c r="H55" s="259"/>
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
+      <c r="D55" s="136"/>
+      <c r="E55" s="136"/>
+      <c r="F55" s="136"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="259" t="s">
+      <c r="B58" s="136" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="259"/>
-      <c r="D58" s="259"/>
-      <c r="E58" s="259"/>
-      <c r="F58" s="259"/>
-      <c r="G58" s="259"/>
-      <c r="H58" s="259"/>
+      <c r="C58" s="136"/>
+      <c r="D58" s="136"/>
+      <c r="E58" s="136"/>
+      <c r="F58" s="136"/>
+      <c r="G58" s="136"/>
+      <c r="H58" s="136"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14416,22 +14434,16 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="259"/>
-      <c r="C68" s="259"/>
-      <c r="D68" s="259"/>
-      <c r="E68" s="259"/>
-      <c r="F68" s="259"/>
-      <c r="G68" s="259"/>
-      <c r="H68" s="259"/>
+      <c r="B68" s="136"/>
+      <c r="C68" s="136"/>
+      <c r="D68" s="136"/>
+      <c r="E68" s="136"/>
+      <c r="F68" s="136"/>
+      <c r="G68" s="136"/>
+      <c r="H68" s="136"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -14507,36 +14519,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="259" t="s">
+      <c r="S2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="259"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="259"/>
-      <c r="X2" s="259"/>
-      <c r="Y2" s="259"/>
-      <c r="Z2" s="259"/>
-      <c r="AA2" s="259" t="s">
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
+      <c r="AA2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="259"/>
-      <c r="AC2" s="259"/>
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="261"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -14547,32 +14559,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="270" t="s">
+      <c r="S4" s="268" t="s">
         <v>126</v>
       </c>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
-      <c r="AA4" s="271"/>
-      <c r="AB4" s="271"/>
-      <c r="AC4" s="271"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15063,33 +15075,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="270" t="s">
+      <c r="S11" s="268" t="s">
         <v>132</v>
       </c>
-      <c r="T11" s="271"/>
-      <c r="U11" s="271"/>
-      <c r="V11" s="271"/>
-      <c r="W11" s="271"/>
-      <c r="X11" s="271"/>
-      <c r="Y11" s="271"/>
-      <c r="Z11" s="271"/>
-      <c r="AA11" s="271"/>
-      <c r="AB11" s="271"/>
-      <c r="AC11" s="271"/>
+      <c r="T11" s="269"/>
+      <c r="U11" s="269"/>
+      <c r="V11" s="269"/>
+      <c r="W11" s="269"/>
+      <c r="X11" s="269"/>
+      <c r="Y11" s="269"/>
+      <c r="Z11" s="269"/>
+      <c r="AA11" s="269"/>
+      <c r="AB11" s="269"/>
+      <c r="AC11" s="269"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15530,33 +15542,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="258" t="s">
+      <c r="C19" s="267" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="258"/>
-      <c r="E19" s="258"/>
-      <c r="F19" s="258"/>
-      <c r="G19" s="258"/>
-      <c r="H19" s="258"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
+      <c r="D19" s="267"/>
+      <c r="E19" s="267"/>
+      <c r="F19" s="267"/>
+      <c r="G19" s="267"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="267"/>
+      <c r="J19" s="267"/>
+      <c r="K19" s="267"/>
+      <c r="L19" s="267"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="270" t="s">
+      <c r="S19" s="268" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="271"/>
-      <c r="U19" s="271"/>
-      <c r="V19" s="271"/>
-      <c r="W19" s="271"/>
-      <c r="X19" s="271"/>
-      <c r="Y19" s="271"/>
-      <c r="Z19" s="271"/>
-      <c r="AA19" s="271"/>
-      <c r="AB19" s="271"/>
-      <c r="AC19" s="271"/>
+      <c r="T19" s="269"/>
+      <c r="U19" s="269"/>
+      <c r="V19" s="269"/>
+      <c r="W19" s="269"/>
+      <c r="X19" s="269"/>
+      <c r="Y19" s="269"/>
+      <c r="Z19" s="269"/>
+      <c r="AA19" s="269"/>
+      <c r="AB19" s="269"/>
+      <c r="AC19" s="269"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16793,35 +16805,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
-      <c r="P2" s="259" t="s">
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="P2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="259"/>
-      <c r="R2" s="259"/>
-      <c r="S2" s="259"/>
-      <c r="T2" s="259"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="259"/>
-      <c r="X2" s="259" t="s">
+      <c r="Q2" s="261"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="261"/>
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="259"/>
-      <c r="Z2" s="259"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -16830,31 +16842,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="P4" s="271" t="s">
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="P4" s="269" t="s">
         <v>126</v>
       </c>
-      <c r="Q4" s="271"/>
-      <c r="R4" s="271"/>
-      <c r="S4" s="271"/>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17049,32 +17061,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="267" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="271" t="s">
+      <c r="P9" s="269" t="s">
         <v>138</v>
       </c>
-      <c r="Q9" s="271"/>
-      <c r="R9" s="271"/>
-      <c r="S9" s="271"/>
-      <c r="T9" s="271"/>
-      <c r="U9" s="271"/>
-      <c r="V9" s="271"/>
-      <c r="W9" s="271"/>
-      <c r="X9" s="271"/>
-      <c r="Y9" s="271"/>
-      <c r="Z9" s="271"/>
+      <c r="Q9" s="269"/>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="269"/>
+      <c r="U9" s="269"/>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="269"/>
+      <c r="Y9" s="269"/>
+      <c r="Z9" s="269"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -17832,31 +17844,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="258" t="s">
+      <c r="C20" s="267" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="258"/>
-      <c r="E20" s="258"/>
-      <c r="F20" s="258"/>
-      <c r="G20" s="258"/>
-      <c r="H20" s="258"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="258"/>
-      <c r="K20" s="258"/>
-      <c r="L20" s="258"/>
-      <c r="P20" s="271" t="s">
+      <c r="D20" s="267"/>
+      <c r="E20" s="267"/>
+      <c r="F20" s="267"/>
+      <c r="G20" s="267"/>
+      <c r="H20" s="267"/>
+      <c r="I20" s="267"/>
+      <c r="J20" s="267"/>
+      <c r="K20" s="267"/>
+      <c r="L20" s="267"/>
+      <c r="P20" s="269" t="s">
         <v>140</v>
       </c>
-      <c r="Q20" s="271"/>
-      <c r="R20" s="271"/>
-      <c r="S20" s="271"/>
-      <c r="T20" s="271"/>
-      <c r="U20" s="271"/>
-      <c r="V20" s="271"/>
-      <c r="W20" s="271"/>
-      <c r="X20" s="271"/>
-      <c r="Y20" s="271"/>
-      <c r="Z20" s="271"/>
+      <c r="Q20" s="269"/>
+      <c r="R20" s="269"/>
+      <c r="S20" s="269"/>
+      <c r="T20" s="269"/>
+      <c r="U20" s="269"/>
+      <c r="V20" s="269"/>
+      <c r="W20" s="269"/>
+      <c r="X20" s="269"/>
+      <c r="Y20" s="269"/>
+      <c r="Z20" s="269"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18580,20 +18592,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -18611,18 +18623,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -18819,18 +18831,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="267" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
       <c r="P11" s="272"/>
       <c r="Q11" s="272"/>
@@ -19084,18 +19096,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="267" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19313,18 +19325,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="267" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19516,18 +19528,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="258" t="s">
+      <c r="C33" s="267" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
+      <c r="D33" s="267"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="267"/>
+      <c r="G33" s="267"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+      <c r="J33" s="267"/>
+      <c r="K33" s="267"/>
+      <c r="L33" s="267"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19711,18 +19723,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="258" t="s">
+      <c r="C40" s="267" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="258"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="258"/>
-      <c r="H40" s="258"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20041,20 +20053,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
       <c r="S2" s="272"/>
       <c r="T2" s="272"/>
       <c r="U2" s="272"/>
@@ -20072,18 +20084,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="S4" s="272"/>
       <c r="T4" s="272"/>
       <c r="U4" s="272"/>
@@ -20457,18 +20469,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="258" t="s">
+      <c r="C13" s="267" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
-      <c r="H13" s="258"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20561,18 +20573,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="267" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20764,18 +20776,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="267" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="258"/>
-      <c r="E25" s="258"/>
-      <c r="F25" s="258"/>
-      <c r="G25" s="258"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
+      <c r="D25" s="267"/>
+      <c r="E25" s="267"/>
+      <c r="F25" s="267"/>
+      <c r="G25" s="267"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="267"/>
+      <c r="J25" s="267"/>
+      <c r="K25" s="267"/>
+      <c r="L25" s="267"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20913,18 +20925,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="258" t="s">
+      <c r="C31" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="258"/>
-      <c r="E31" s="258"/>
-      <c r="F31" s="258"/>
-      <c r="G31" s="258"/>
-      <c r="H31" s="258"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="267"/>
+      <c r="G31" s="267"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="267"/>
+      <c r="J31" s="267"/>
+      <c r="K31" s="267"/>
+      <c r="L31" s="267"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21135,10 +21147,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="261" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="259"/>
+      <c r="C4" s="261"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21155,7 +21167,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21164,7 +21176,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>656968.9</v>
+        <v>647907.26</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21182,7 +21194,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21191,7 +21203,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.83169999999999999</v>
+        <v>0.84109999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21223,10 +21235,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="259" t="s">
+      <c r="B15" s="261" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="259"/>
+      <c r="C15" s="261"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21234,7 +21246,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.1850471976731463E-2</v>
+        <v>9.3015604072416491E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21243,7 +21255,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.90814952802326854</v>
+        <v>0.90698439592758351</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21261,7 +21273,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.9266499999999999E-2</v>
+        <v>9.0399499999999994E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21270,7 +21282,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.578385157929426E-2</v>
+        <v>8.676728716877416E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21315,20 +21327,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -21346,18 +21358,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="267" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -21521,7 +21533,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>842476.05789524782</v>
+        <v>830066.97294134542</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21575,23 +21587,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13209.100746319888</v>
+        <v>13197.147589528799</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8741.4040003560513</v>
+        <v>8725.590645862163</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21336.533010181007</v>
+        <v>21278.661953799889</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>29952.374405081457</v>
+        <v>29844.10367511287</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36004.750175200425</v>
+        <v>35842.137959309039</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21610,14 +21622,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>558265.3538374413</v>
+        <v>547558.27694603696</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="259" t="s">
+      <c r="B13" s="261" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="259"/>
+      <c r="C13" s="261"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21633,14 +21645,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.578385157929426E-2</v>
+        <v>8.676728716877416E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="259" t="s">
+      <c r="B18" s="261" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="259"/>
+      <c r="C18" s="261"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21648,7 +21660,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109244.16233713884</v>
+        <v>108887.64182361276</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21657,7 +21669,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>558265.3538374413</v>
+        <v>547558.27694603696</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21666,7 +21678,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>667509.5161745802</v>
+        <v>656445.9187696497</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21693,7 +21705,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>674008.5161745802</v>
+        <v>662944.9187696497</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21723,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.413257673494117</v>
+        <v>10.242327948114355</v>
       </c>
     </row>
   </sheetData>
@@ -21754,37 +21766,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21980,23 +21992,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13209.100746319888</v>
+        <v>13197.147589528799</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8741.4040003560513</v>
+        <v>8725.590645862163</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21336.533010181007</v>
+        <v>21278.661953799889</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>29952.374405081457</v>
+        <v>29844.10367511287</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36004.750175200425</v>
+        <v>35842.137959309039</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22004,18 +22016,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22209,18 +22221,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="258" t="s">
+      <c r="C17" s="267" t="s">
         <v>208</v>
       </c>
-      <c r="D17" s="258"/>
-      <c r="E17" s="258"/>
-      <c r="F17" s="258"/>
-      <c r="G17" s="258"/>
-      <c r="H17" s="258"/>
-      <c r="I17" s="258"/>
-      <c r="J17" s="258"/>
-      <c r="K17" s="258"/>
-      <c r="L17" s="258"/>
+      <c r="D17" s="267"/>
+      <c r="E17" s="267"/>
+      <c r="F17" s="267"/>
+      <c r="G17" s="267"/>
+      <c r="H17" s="267"/>
+      <c r="I17" s="267"/>
+      <c r="J17" s="267"/>
+      <c r="K17" s="267"/>
+      <c r="L17" s="267"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22354,18 +22366,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="258" t="s">
+      <c r="C22" s="267" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="258"/>
-      <c r="E22" s="258"/>
-      <c r="F22" s="258"/>
-      <c r="G22" s="258"/>
-      <c r="H22" s="258"/>
-      <c r="I22" s="258"/>
-      <c r="J22" s="258"/>
-      <c r="K22" s="258"/>
-      <c r="L22" s="258"/>
+      <c r="D22" s="267"/>
+      <c r="E22" s="267"/>
+      <c r="F22" s="267"/>
+      <c r="G22" s="267"/>
+      <c r="H22" s="267"/>
+      <c r="I22" s="267"/>
+      <c r="J22" s="267"/>
+      <c r="K22" s="267"/>
+      <c r="L22" s="267"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22449,18 +22461,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="258" t="s">
+      <c r="C27" s="267" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="258"/>
-      <c r="E27" s="258"/>
-      <c r="F27" s="258"/>
-      <c r="G27" s="258"/>
-      <c r="H27" s="258"/>
-      <c r="I27" s="258"/>
-      <c r="J27" s="258"/>
-      <c r="K27" s="258"/>
-      <c r="L27" s="258"/>
+      <c r="D27" s="267"/>
+      <c r="E27" s="267"/>
+      <c r="F27" s="267"/>
+      <c r="G27" s="267"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="267"/>
+      <c r="J27" s="267"/>
+      <c r="K27" s="267"/>
+      <c r="L27" s="267"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22701,7 +22713,7 @@
         <v>-7.7178480374902509</v>
       </c>
       <c r="D35" s="151">
-        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
         <v>-9.5360928339390991</v>
       </c>
       <c r="E35" s="151">
@@ -22761,10 +22773,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="259" t="s">
+      <c r="B39" s="261" t="s">
         <v>217</v>
       </c>
-      <c r="C39" s="259"/>
+      <c r="C39" s="261"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22782,7 +22794,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.578385157929426E-2</v>
+        <v>8.676728716877416E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22808,7 +22820,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1052676.0830646381</v>
+        <v>1047921.7662133881</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22817,7 +22829,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1125915.4952265765</v>
+        <v>1120967.2700776919</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22844,7 +22856,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1132414.4952265765</v>
+        <v>1127466.2700776919</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -22862,14 +22874,14 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.495511776203944</v>
+        <v>17.41906297434867</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="259" t="s">
+      <c r="B52" s="261" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="259"/>
+      <c r="C52" s="261"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22886,7 +22898,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.9266499999999999E-2</v>
+        <v>9.0399499999999994E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -22921,14 +22933,14 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>16.640228160278969</v>
+        <v>16.553955930312938</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="259" t="s">
+      <c r="B60" s="261" t="s">
         <v>335</v>
       </c>
-      <c r="C60" s="259"/>
+      <c r="C60" s="261"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -22945,7 +22957,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.578385157929426E-2</v>
+        <v>8.676728716877416E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -22971,7 +22983,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>828109.25402960973</v>
+        <v>824369.17306410777</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22980,7 +22992,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>901348.66619154811</v>
+        <v>897414.67692841147</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23007,7 +23019,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>907847.66619154811</v>
+        <v>903913.67692841147</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23025,14 +23037,14 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.026012208255541</v>
+        <v>13.965233089151369</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="259" t="s">
+      <c r="B73" s="261" t="s">
         <v>436</v>
       </c>
-      <c r="C73" s="259"/>
+      <c r="C73" s="261"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23049,7 +23061,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.578385157929426E-2</v>
+        <v>8.676728716877416E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23075,7 +23087,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1563380.3213831258</v>
+        <v>1556319.4547723583</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23084,7 +23096,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1636619.7335450642</v>
+        <v>1629364.958636662</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23111,7 +23123,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1643118.7335450642</v>
+        <v>1635863.958636662</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23129,7 +23141,7 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.385760491071043</v>
+        <v>25.273676090545717</v>
       </c>
     </row>
   </sheetData>
@@ -23139,12 +23151,12 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23182,10 +23194,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="261" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="259"/>
+      <c r="C4" s="261"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23194,7 +23206,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.413257673494117</v>
+        <v>10.242327948114355</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23203,7 +23215,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.495511776203944</v>
+        <v>17.41906297434867</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23212,7 +23224,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>16.640228160278969</v>
+        <v>16.553955930312938</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23221,7 +23233,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.026012208255541</v>
+        <v>13.965233089151369</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23230,7 +23242,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.385760491071043</v>
+        <v>25.273676090545717</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23239,7 +23251,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>16.792154061860721</v>
+        <v>16.69085120649461</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23248,7 +23260,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23257,7 +23269,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.65439941496164733</v>
+        <v>0.66741770294651459</v>
       </c>
     </row>
   </sheetData>
@@ -23313,37 +23325,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23456,18 +23468,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23588,18 +23600,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="258" t="s">
+      <c r="C14" s="267" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="258"/>
-      <c r="E14" s="258"/>
-      <c r="F14" s="258"/>
-      <c r="G14" s="258"/>
-      <c r="H14" s="258"/>
-      <c r="I14" s="258"/>
-      <c r="J14" s="258"/>
-      <c r="K14" s="258"/>
-      <c r="L14" s="258"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23689,10 +23701,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="259" t="s">
+      <c r="B20" s="261" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="259"/>
+      <c r="C20" s="261"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23727,7 +23739,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.9266499999999999E-2</v>
+        <v>9.0399499999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23793,20 +23805,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -23824,18 +23836,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="267" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -23932,23 +23944,23 @@
       </c>
       <c r="H7" s="130">
         <f>G7*(1+$C$17)</f>
-        <v>11680</v>
+        <v>11600</v>
       </c>
       <c r="I7" s="130">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>17052.8</v>
+        <v>16820</v>
       </c>
       <c r="J7" s="130">
         <f t="shared" si="0"/>
-        <v>24897.088</v>
+        <v>24389</v>
       </c>
       <c r="K7" s="130">
         <f t="shared" si="0"/>
-        <v>36349.748480000002</v>
+        <v>35364.049999999996</v>
       </c>
       <c r="L7" s="130">
         <f t="shared" si="0"/>
-        <v>53070.632780799999</v>
+        <v>51277.87249999999</v>
       </c>
       <c r="N7" s="92"/>
       <c r="O7" s="16"/>
@@ -23980,7 +23992,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>822877.41044117115</v>
+        <v>783369.10436075577</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24034,23 +24046,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10757.205481561736</v>
+        <v>10673.858273945752</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14464.683721567733</v>
+        <v>14241.406306535027</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19449.946877338156</v>
+        <v>19001.344067204016</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>26153.384395623329</v>
+        <v>25352.206698476952</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>35167.166247748799</v>
+        <v>33825.732653915147</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24069,7 +24081,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>545278.34280828538</v>
+        <v>516753.76924898516</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24085,7 +24097,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24094,7 +24106,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.597053850141373</v>
+        <v>10.090820467675114</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24102,7 +24114,7 @@
         <v>337</v>
       </c>
       <c r="C17" s="160">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="E17" s="273" t="s">
         <v>237</v>
@@ -24133,7 +24145,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.578385157929426E-2</v>
+        <v>8.676728716877416E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24151,7 +24163,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>630020.65</v>
+        <v>621330.71</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24178,7 +24190,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>623521.65</v>
+        <v>614831.71</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24194,7 +24206,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>105992.38672383975</v>
+        <v>103094.5480000769</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24203,7 +24215,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>545278.34280828538</v>
+        <v>516753.76924898516</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24212,7 +24224,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>651270.72953212517</v>
+        <v>619848.31724906201</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24239,7 +24251,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>657769.72953212517</v>
+        <v>626347.31724906201</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24257,7 +24269,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.597053850141373</v>
+        <v>10.090820467675114</v>
       </c>
     </row>
   </sheetData>
@@ -31230,7 +31242,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31301,7 +31313,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32379,7 +32391,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-568.25030725112663</v>
+        <v>-560.41237197869725</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32416,7 +32428,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.2370907781320342</v>
+        <v>1.2200274570543508</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32477,7 +32489,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.6942825217627491</v>
+        <v>1.6709131076694697</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32538,7 +32550,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>656968.9</v>
+        <v>647907.26</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32599,7 +32611,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>650469.9</v>
+        <v>641408.26</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32636,7 +32648,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.2809745309604506</v>
+        <v>1.2631293853991685</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32673,7 +32685,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>51.875739692160458</v>
+        <v>51.153063242682833</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32808,7 +32820,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>81.147344367588943</v>
+        <v>80.028070652173909</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32845,7 +32857,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-108.15406671652784</v>
+        <v>-106.64738175367074</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32882,7 +32894,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.2323262181817131E-2</v>
+        <v>1.2495615499045341E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32919,7 +32931,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.7597878738287605E-3</v>
+        <v>-1.7844002916445475E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33533,7 +33545,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.8924012993613537E-3</v>
+        <v>1.0030756562289486E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35129,15 +35141,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="261" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="259"/>
-      <c r="E4" s="259" t="s">
+      <c r="C4" s="261"/>
+      <c r="E4" s="261" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35145,7 +35157,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35161,7 +35173,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>656968.9</v>
+        <v>647907.26</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35181,7 +35193,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>650469.9</v>
+        <v>641408.26</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35201,7 +35213,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-568.25030725112663</v>
+        <v>-560.41237197869725</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35221,7 +35233,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2370907781320342</v>
+        <v>1.2200274570543508</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35241,7 +35253,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.6942825217627491</v>
+        <v>1.6709131076694697</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35261,7 +35273,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.2809745309604506</v>
+        <v>1.2631293853991685</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35270,18 +35282,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>51.875739692160458</v>
+        <v>51.153063242682833</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="259" t="s">
+      <c r="B15" s="261" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="259"/>
-      <c r="E15" s="259" t="s">
+      <c r="C15" s="261"/>
+      <c r="E15" s="261" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="259"/>
+      <c r="F15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35332,14 +35344,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="259" t="s">
+      <c r="B21" s="261" t="s">
         <v>257</v>
       </c>
-      <c r="C21" s="259"/>
-      <c r="E21" s="259" t="s">
+      <c r="C21" s="261"/>
+      <c r="E21" s="261" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="259"/>
+      <c r="F21" s="261"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35408,14 +35420,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="259" t="s">
+      <c r="B29" s="261" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="259"/>
-      <c r="E29" s="259" t="s">
+      <c r="C29" s="261"/>
+      <c r="E29" s="261" t="s">
         <v>268</v>
       </c>
-      <c r="F29" s="259"/>
+      <c r="F29" s="261"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35491,14 +35503,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="259" t="s">
+      <c r="B37" s="261" t="s">
         <v>280</v>
       </c>
-      <c r="C37" s="259"/>
-      <c r="E37" s="259" t="s">
+      <c r="C37" s="261"/>
+      <c r="E37" s="261" t="s">
         <v>283</v>
       </c>
-      <c r="F37" s="259"/>
+      <c r="F37" s="261"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35506,7 +35518,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7597878738287605E-3</v>
+        <v>-1.7844002916445475E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35522,7 +35534,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.2323262181817131E-2</v>
+        <v>1.2495615499045341E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35567,14 +35579,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="259" t="s">
+      <c r="B45" s="261" t="s">
         <v>291</v>
       </c>
-      <c r="C45" s="259"/>
-      <c r="E45" s="259" t="s">
+      <c r="C45" s="261"/>
+      <c r="E45" s="261" t="s">
         <v>297</v>
       </c>
-      <c r="F45" s="259"/>
+      <c r="F45" s="261"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35607,18 +35619,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>9.8924012993613537E-3</v>
+        <v>1.0030756562289486E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="259" t="s">
+      <c r="B51" s="261" t="s">
         <v>294</v>
       </c>
-      <c r="C51" s="259"/>
-      <c r="E51" s="259" t="s">
+      <c r="C51" s="261"/>
+      <c r="E51" s="261" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="259"/>
+      <c r="F51" s="261"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35786,7 +35798,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>10.15</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35815,7 +35827,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>656968.9</v>
+        <v>647907.26</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35844,7 +35856,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>650469.9</v>
+        <v>641408.26</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35873,7 +35885,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-568.25030725112663</v>
+        <v>-560.41237197869725</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35902,7 +35914,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2370907781320342</v>
+        <v>1.2200274570543508</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35931,7 +35943,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.6942825217627491</v>
+        <v>1.6709131076694697</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35960,7 +35972,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.2809745309604506</v>
+        <v>1.2631293853991685</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35989,7 +36001,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>51.875739692160458</v>
+        <v>51.153063242682833</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36762,7 +36774,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7597878738287605E-3</v>
+        <v>-1.7844002916445475E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36791,7 +36803,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.2323262181817131E-2</v>
+        <v>1.2495615499045341E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37114,7 +37126,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.8924012993613537E-3</v>
+        <v>1.0030756562289486E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37603,14 +37615,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="267" t="s">
+      <c r="C3" s="264" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="268"/>
-      <c r="F3" s="269" t="s">
+      <c r="D3" s="265"/>
+      <c r="F3" s="266" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="268"/>
+      <c r="G3" s="265"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37677,19 +37689,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="265">
+      <c r="C7" s="262">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="266"/>
-      <c r="F7" s="265">
+      <c r="D7" s="263"/>
+      <c r="F7" s="262">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="266"/>
+      <c r="G7" s="263"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37716,19 +37728,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="265">
+      <c r="C9" s="262">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="F9" s="265">
+      <c r="D9" s="263"/>
+      <c r="F9" s="262">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="266"/>
+      <c r="G9" s="263"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -37755,19 +37767,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="265">
+      <c r="C11" s="262">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="F11" s="265">
+      <c r="D11" s="263"/>
+      <c r="F11" s="262">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="266"/>
+      <c r="G11" s="263"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -37794,19 +37806,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="265">
+      <c r="C13" s="262">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="F13" s="265">
+      <c r="D13" s="263"/>
+      <c r="F13" s="262">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="266"/>
+      <c r="G13" s="263"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -37833,19 +37845,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="265">
+      <c r="C15" s="262">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="266"/>
-      <c r="F15" s="265">
+      <c r="D15" s="263"/>
+      <c r="F15" s="262">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="266"/>
+      <c r="G15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -37872,19 +37884,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="265">
+      <c r="C17" s="262">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="266"/>
-      <c r="F17" s="265">
+      <c r="D17" s="263"/>
+      <c r="F17" s="262">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="266"/>
+      <c r="G17" s="263"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -37911,22 +37923,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="265">
+      <c r="C19" s="262">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="266"/>
-      <c r="F19" s="265">
+      <c r="D19" s="263"/>
+      <c r="F19" s="262">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="266"/>
+      <c r="G19" s="263"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -37953,22 +37965,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="265">
+      <c r="C21" s="262">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="266"/>
-      <c r="F21" s="265">
+      <c r="D21" s="263"/>
+      <c r="F21" s="262">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="266"/>
+      <c r="G21" s="263"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38017,22 +38029,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="265">
+      <c r="C25" s="262">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="266"/>
-      <c r="F25" s="265">
+      <c r="D25" s="263"/>
+      <c r="F25" s="262">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="266"/>
+      <c r="G25" s="263"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38060,22 +38072,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="265">
+      <c r="C27" s="262">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="F27" s="265">
+      <c r="D27" s="263"/>
+      <c r="F27" s="262">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="266"/>
+      <c r="G27" s="263"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38103,22 +38115,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="265">
+      <c r="C29" s="262">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="266"/>
-      <c r="F29" s="265">
+      <c r="D29" s="263"/>
+      <c r="F29" s="262">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="266"/>
+      <c r="G29" s="263"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38167,22 +38179,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="265">
+      <c r="C33" s="262">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="F33" s="265">
+      <c r="D33" s="263"/>
+      <c r="F33" s="262">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="266"/>
+      <c r="G33" s="263"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38210,22 +38222,22 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="265">
+      <c r="C35" s="262">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="266"/>
-      <c r="F35" s="265">
+      <c r="D35" s="263"/>
+      <c r="F35" s="262">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="266"/>
+      <c r="G35" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4FBED4-325C-8748-8566-3E3814D5C072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C66123E-0AEE-1B42-ABEE-299F998218F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2473,6 +2473,30 @@
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2480,15 +2504,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2500,31 +2515,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -12935,11 +12935,11 @@
     <v>Powered by Refinitiv</v>
     <v>24.245000000000001</v>
     <v>7.77</v>
-    <v>0.84109999999999996</v>
-    <v>-0.09</v>
-    <v>-8.9110000000000005E-3</v>
-    <v>0</v>
-    <v>0</v>
+    <v>0.7873</v>
+    <v>0.3</v>
+    <v>2.9790999999999998E-2</v>
+    <v>-0.11</v>
+    <v>-1.0607999999999999E-2</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12947,25 +12947,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.15</v>
+    <v>10.49</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46294.937500010936</v>
+    <v>46300.863038680465</v>
     <v>0</v>
-    <v>9.75</v>
-    <v>621330109</v>
+    <v>10.09</v>
+    <v>643675647</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
+    <v>10.119999999999999</v>
+    <v>61.397300000000001</v>
     <v>10.07</v>
-    <v>59.265799999999999</v>
-    <v>10.1</v>
-    <v>10.01</v>
-    <v>10.01</v>
+    <v>10.37</v>
+    <v>10.26</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>570646</v>
-    <v>733676</v>
+    <v>504067</v>
+    <v>725761</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -12987,19 +12987,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.93</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.15</v>
-    <v>2.8630000000000001E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.93</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.13</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.13</v>
-    <v>52.4</v>
-    <v>52.55</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13811,18 +13811,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="259"/>
-      <c r="E2" s="258" t="s">
+      <c r="C2" s="267"/>
+      <c r="E2" s="266" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="259"/>
-      <c r="H2" s="258" t="s">
+      <c r="F2" s="267"/>
+      <c r="H2" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="259"/>
+      <c r="I2" s="267"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>647907.26</v>
+        <v>671208.62</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.242327948114355</v>
+        <v>10.575119841953303</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>641408.26</v>
+        <v>664709.62</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.41906297434867</v>
+        <v>17.566193491504745</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13893,7 +13893,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.553955930312938</v>
+        <v>16.722045410153854</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13902,14 +13902,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.01</v>
+        <v>10.26</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-560.41237197869725</v>
+        <v>-580.56706267922971</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>13.965233089151369</v>
+        <v>14.082205506481209</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13926,14 +13926,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.09</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.2200274570543508</v>
+        <v>1.2639045683969647</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.273676090545717</v>
+        <v>25.489391400331563</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13950,14 +13950,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.2495615499045341E-2</v>
+        <v>1.2061823639869226E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>16.69085120649461</v>
+        <v>16.886991130084933</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13974,14 +13974,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-8.9110000000000005E-3</v>
+        <v>2.9790999999999998E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7844002916445475E-3</v>
+        <v>-1.7224538977205326E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.66741770294651459</v>
+        <v>0.62844658920780472</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-1.0607999999999999E-2</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.84109999999999996</v>
+        <v>0.7873</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>733676</v>
+        <v>725761</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>1.0030756562289486E-2</v>
+        <v>9.6825335765205155E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14105,10 +14105,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="260" t="s">
+      <c r="B17" s="268" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="260"/>
+      <c r="C17" s="268"/>
       <c r="E17" s="184" t="s">
         <v>308</v>
       </c>
@@ -14181,14 +14181,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="260" t="s">
+      <c r="B25" s="268" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="260"/>
-      <c r="E25" s="258" t="s">
+      <c r="C25" s="268"/>
+      <c r="E25" s="266" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="259"/>
+      <c r="F25" s="267"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.55</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14519,36 +14519,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="261" t="s">
+      <c r="S2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261"/>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
-      <c r="AA2" s="261" t="s">
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="261"/>
-      <c r="AC2" s="261"/>
+      <c r="AB2" s="263"/>
+      <c r="AC2" s="263"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -14559,32 +14559,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="259" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="268" t="s">
+      <c r="S4" s="274" t="s">
         <v>126</v>
       </c>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
-      <c r="AA4" s="269"/>
-      <c r="AB4" s="269"/>
-      <c r="AC4" s="269"/>
+      <c r="T4" s="275"/>
+      <c r="U4" s="275"/>
+      <c r="V4" s="275"/>
+      <c r="W4" s="275"/>
+      <c r="X4" s="275"/>
+      <c r="Y4" s="275"/>
+      <c r="Z4" s="275"/>
+      <c r="AA4" s="275"/>
+      <c r="AB4" s="275"/>
+      <c r="AC4" s="275"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15075,33 +15075,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="259" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="259"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="259"/>
+      <c r="G11" s="259"/>
+      <c r="H11" s="259"/>
+      <c r="I11" s="259"/>
+      <c r="J11" s="259"/>
+      <c r="K11" s="259"/>
+      <c r="L11" s="259"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="268" t="s">
+      <c r="S11" s="274" t="s">
         <v>132</v>
       </c>
-      <c r="T11" s="269"/>
-      <c r="U11" s="269"/>
-      <c r="V11" s="269"/>
-      <c r="W11" s="269"/>
-      <c r="X11" s="269"/>
-      <c r="Y11" s="269"/>
-      <c r="Z11" s="269"/>
-      <c r="AA11" s="269"/>
-      <c r="AB11" s="269"/>
-      <c r="AC11" s="269"/>
+      <c r="T11" s="275"/>
+      <c r="U11" s="275"/>
+      <c r="V11" s="275"/>
+      <c r="W11" s="275"/>
+      <c r="X11" s="275"/>
+      <c r="Y11" s="275"/>
+      <c r="Z11" s="275"/>
+      <c r="AA11" s="275"/>
+      <c r="AB11" s="275"/>
+      <c r="AC11" s="275"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15542,33 +15542,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="267" t="s">
+      <c r="C19" s="259" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="267"/>
-      <c r="E19" s="267"/>
-      <c r="F19" s="267"/>
-      <c r="G19" s="267"/>
-      <c r="H19" s="267"/>
-      <c r="I19" s="267"/>
-      <c r="J19" s="267"/>
-      <c r="K19" s="267"/>
-      <c r="L19" s="267"/>
+      <c r="D19" s="259"/>
+      <c r="E19" s="259"/>
+      <c r="F19" s="259"/>
+      <c r="G19" s="259"/>
+      <c r="H19" s="259"/>
+      <c r="I19" s="259"/>
+      <c r="J19" s="259"/>
+      <c r="K19" s="259"/>
+      <c r="L19" s="259"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="268" t="s">
+      <c r="S19" s="274" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="269"/>
-      <c r="U19" s="269"/>
-      <c r="V19" s="269"/>
-      <c r="W19" s="269"/>
-      <c r="X19" s="269"/>
-      <c r="Y19" s="269"/>
-      <c r="Z19" s="269"/>
-      <c r="AA19" s="269"/>
-      <c r="AB19" s="269"/>
-      <c r="AC19" s="269"/>
+      <c r="T19" s="275"/>
+      <c r="U19" s="275"/>
+      <c r="V19" s="275"/>
+      <c r="W19" s="275"/>
+      <c r="X19" s="275"/>
+      <c r="Y19" s="275"/>
+      <c r="Z19" s="275"/>
+      <c r="AA19" s="275"/>
+      <c r="AB19" s="275"/>
+      <c r="AC19" s="275"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16805,35 +16805,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="P2" s="261" t="s">
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
+      <c r="P2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="261"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261" t="s">
+      <c r="Q2" s="263"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -16842,31 +16842,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="259" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="P4" s="269" t="s">
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
+      <c r="P4" s="275" t="s">
         <v>126</v>
       </c>
-      <c r="Q4" s="269"/>
-      <c r="R4" s="269"/>
-      <c r="S4" s="269"/>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
+      <c r="Q4" s="275"/>
+      <c r="R4" s="275"/>
+      <c r="S4" s="275"/>
+      <c r="T4" s="275"/>
+      <c r="U4" s="275"/>
+      <c r="V4" s="275"/>
+      <c r="W4" s="275"/>
+      <c r="X4" s="275"/>
+      <c r="Y4" s="275"/>
+      <c r="Z4" s="275"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17061,32 +17061,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="259" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="259"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="259"/>
+      <c r="I9" s="259"/>
+      <c r="J9" s="259"/>
+      <c r="K9" s="259"/>
+      <c r="L9" s="259"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="269" t="s">
+      <c r="P9" s="275" t="s">
         <v>138</v>
       </c>
-      <c r="Q9" s="269"/>
-      <c r="R9" s="269"/>
-      <c r="S9" s="269"/>
-      <c r="T9" s="269"/>
-      <c r="U9" s="269"/>
-      <c r="V9" s="269"/>
-      <c r="W9" s="269"/>
-      <c r="X9" s="269"/>
-      <c r="Y9" s="269"/>
-      <c r="Z9" s="269"/>
+      <c r="Q9" s="275"/>
+      <c r="R9" s="275"/>
+      <c r="S9" s="275"/>
+      <c r="T9" s="275"/>
+      <c r="U9" s="275"/>
+      <c r="V9" s="275"/>
+      <c r="W9" s="275"/>
+      <c r="X9" s="275"/>
+      <c r="Y9" s="275"/>
+      <c r="Z9" s="275"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -17844,31 +17844,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="267" t="s">
+      <c r="C20" s="259" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="267"/>
-      <c r="E20" s="267"/>
-      <c r="F20" s="267"/>
-      <c r="G20" s="267"/>
-      <c r="H20" s="267"/>
-      <c r="I20" s="267"/>
-      <c r="J20" s="267"/>
-      <c r="K20" s="267"/>
-      <c r="L20" s="267"/>
-      <c r="P20" s="269" t="s">
+      <c r="D20" s="259"/>
+      <c r="E20" s="259"/>
+      <c r="F20" s="259"/>
+      <c r="G20" s="259"/>
+      <c r="H20" s="259"/>
+      <c r="I20" s="259"/>
+      <c r="J20" s="259"/>
+      <c r="K20" s="259"/>
+      <c r="L20" s="259"/>
+      <c r="P20" s="275" t="s">
         <v>140</v>
       </c>
-      <c r="Q20" s="269"/>
-      <c r="R20" s="269"/>
-      <c r="S20" s="269"/>
-      <c r="T20" s="269"/>
-      <c r="U20" s="269"/>
-      <c r="V20" s="269"/>
-      <c r="W20" s="269"/>
-      <c r="X20" s="269"/>
-      <c r="Y20" s="269"/>
-      <c r="Z20" s="269"/>
+      <c r="Q20" s="275"/>
+      <c r="R20" s="275"/>
+      <c r="S20" s="275"/>
+      <c r="T20" s="275"/>
+      <c r="U20" s="275"/>
+      <c r="V20" s="275"/>
+      <c r="W20" s="275"/>
+      <c r="X20" s="275"/>
+      <c r="Y20" s="275"/>
+      <c r="Z20" s="275"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18592,60 +18592,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="259" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="259"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="259"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="259"/>
+      <c r="L5" s="259"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18831,30 +18831,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="259" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="259"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="259"/>
+      <c r="G11" s="259"/>
+      <c r="H11" s="259"/>
+      <c r="I11" s="259"/>
+      <c r="J11" s="259"/>
+      <c r="K11" s="259"/>
+      <c r="L11" s="259"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="272"/>
-      <c r="Q11" s="272"/>
-      <c r="R11" s="272"/>
-      <c r="S11" s="272"/>
-      <c r="T11" s="272"/>
-      <c r="U11" s="272"/>
-      <c r="V11" s="272"/>
-      <c r="W11" s="272"/>
-      <c r="X11" s="272"/>
-      <c r="Y11" s="272"/>
-      <c r="Z11" s="272"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="258"/>
+      <c r="S11" s="258"/>
+      <c r="T11" s="258"/>
+      <c r="U11" s="258"/>
+      <c r="V11" s="258"/>
+      <c r="W11" s="258"/>
+      <c r="X11" s="258"/>
+      <c r="Y11" s="258"/>
+      <c r="Z11" s="258"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19096,18 +19096,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="259" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="259"/>
+      <c r="E18" s="259"/>
+      <c r="F18" s="259"/>
+      <c r="G18" s="259"/>
+      <c r="H18" s="259"/>
+      <c r="I18" s="259"/>
+      <c r="J18" s="259"/>
+      <c r="K18" s="259"/>
+      <c r="L18" s="259"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19320,23 +19320,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="272"/>
-      <c r="C25" s="272"/>
+      <c r="B25" s="258"/>
+      <c r="C25" s="258"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="267" t="s">
+      <c r="C26" s="259" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="267"/>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="267"/>
-      <c r="J26" s="267"/>
-      <c r="K26" s="267"/>
-      <c r="L26" s="267"/>
+      <c r="D26" s="259"/>
+      <c r="E26" s="259"/>
+      <c r="F26" s="259"/>
+      <c r="G26" s="259"/>
+      <c r="H26" s="259"/>
+      <c r="I26" s="259"/>
+      <c r="J26" s="259"/>
+      <c r="K26" s="259"/>
+      <c r="L26" s="259"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19528,18 +19528,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="267" t="s">
+      <c r="C33" s="259" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="E33" s="267"/>
-      <c r="F33" s="267"/>
-      <c r="G33" s="267"/>
-      <c r="H33" s="267"/>
-      <c r="I33" s="267"/>
-      <c r="J33" s="267"/>
-      <c r="K33" s="267"/>
-      <c r="L33" s="267"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="259"/>
+      <c r="G33" s="259"/>
+      <c r="H33" s="259"/>
+      <c r="I33" s="259"/>
+      <c r="J33" s="259"/>
+      <c r="K33" s="259"/>
+      <c r="L33" s="259"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19723,18 +19723,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="267" t="s">
+      <c r="C40" s="259" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="267"/>
-      <c r="E40" s="267"/>
-      <c r="F40" s="267"/>
-      <c r="G40" s="267"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="267"/>
-      <c r="J40" s="267"/>
-      <c r="K40" s="267"/>
-      <c r="L40" s="267"/>
+      <c r="D40" s="259"/>
+      <c r="E40" s="259"/>
+      <c r="F40" s="259"/>
+      <c r="G40" s="259"/>
+      <c r="H40" s="259"/>
+      <c r="I40" s="259"/>
+      <c r="J40" s="259"/>
+      <c r="K40" s="259"/>
+      <c r="L40" s="259"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20003,12 +20003,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20016,6 +20010,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20053,60 +20053,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="S2" s="272"/>
-      <c r="T2" s="272"/>
-      <c r="U2" s="272"/>
-      <c r="V2" s="272"/>
-      <c r="W2" s="272"/>
-      <c r="X2" s="272"/>
-      <c r="Y2" s="272"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="272"/>
-      <c r="AB2" s="272"/>
-      <c r="AC2" s="272"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
+      <c r="S2" s="258"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
+      <c r="AA2" s="258"/>
+      <c r="AB2" s="258"/>
+      <c r="AC2" s="258"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="259" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="S4" s="272"/>
-      <c r="T4" s="272"/>
-      <c r="U4" s="272"/>
-      <c r="V4" s="272"/>
-      <c r="W4" s="272"/>
-      <c r="X4" s="272"/>
-      <c r="Y4" s="272"/>
-      <c r="Z4" s="272"/>
-      <c r="AA4" s="272"/>
-      <c r="AB4" s="272"/>
-      <c r="AC4" s="272"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
+      <c r="S4" s="258"/>
+      <c r="T4" s="258"/>
+      <c r="U4" s="258"/>
+      <c r="V4" s="258"/>
+      <c r="W4" s="258"/>
+      <c r="X4" s="258"/>
+      <c r="Y4" s="258"/>
+      <c r="Z4" s="258"/>
+      <c r="AA4" s="258"/>
+      <c r="AB4" s="258"/>
+      <c r="AC4" s="258"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20469,18 +20469,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="267" t="s">
+      <c r="C13" s="259" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="E13" s="267"/>
-      <c r="F13" s="267"/>
-      <c r="G13" s="267"/>
-      <c r="H13" s="267"/>
-      <c r="I13" s="267"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
+      <c r="D13" s="259"/>
+      <c r="E13" s="259"/>
+      <c r="F13" s="259"/>
+      <c r="G13" s="259"/>
+      <c r="H13" s="259"/>
+      <c r="I13" s="259"/>
+      <c r="J13" s="259"/>
+      <c r="K13" s="259"/>
+      <c r="L13" s="259"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20573,18 +20573,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="259" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="259"/>
+      <c r="E18" s="259"/>
+      <c r="F18" s="259"/>
+      <c r="G18" s="259"/>
+      <c r="H18" s="259"/>
+      <c r="I18" s="259"/>
+      <c r="J18" s="259"/>
+      <c r="K18" s="259"/>
+      <c r="L18" s="259"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20776,18 +20776,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="267" t="s">
+      <c r="C25" s="259" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="E25" s="267"/>
-      <c r="F25" s="267"/>
-      <c r="G25" s="267"/>
-      <c r="H25" s="267"/>
-      <c r="I25" s="267"/>
-      <c r="J25" s="267"/>
-      <c r="K25" s="267"/>
-      <c r="L25" s="267"/>
+      <c r="D25" s="259"/>
+      <c r="E25" s="259"/>
+      <c r="F25" s="259"/>
+      <c r="G25" s="259"/>
+      <c r="H25" s="259"/>
+      <c r="I25" s="259"/>
+      <c r="J25" s="259"/>
+      <c r="K25" s="259"/>
+      <c r="L25" s="259"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20925,18 +20925,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="267" t="s">
+      <c r="C31" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="267"/>
-      <c r="E31" s="267"/>
-      <c r="F31" s="267"/>
-      <c r="G31" s="267"/>
-      <c r="H31" s="267"/>
-      <c r="I31" s="267"/>
-      <c r="J31" s="267"/>
-      <c r="K31" s="267"/>
-      <c r="L31" s="267"/>
+      <c r="D31" s="259"/>
+      <c r="E31" s="259"/>
+      <c r="F31" s="259"/>
+      <c r="G31" s="259"/>
+      <c r="H31" s="259"/>
+      <c r="I31" s="259"/>
+      <c r="J31" s="259"/>
+      <c r="K31" s="259"/>
+      <c r="L31" s="259"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21075,16 +21075,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21147,10 +21147,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="263" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="263"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>647907.26</v>
+        <v>671208.62</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.84109999999999996</v>
+        <v>0.7873</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21235,10 +21235,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="263" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="261"/>
+      <c r="C15" s="263"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.3015604072416491E-2</v>
+        <v>9.0077386080765001E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.90698439592758351</v>
+        <v>0.90992261391923501</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.0399499999999994E-2</v>
+        <v>8.8198500000000013E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.676728716877416E-2</v>
+        <v>8.4879283439002945E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21327,60 +21327,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="259" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="259"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="259"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="259"/>
+      <c r="L5" s="259"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>830066.97294134542</v>
+        <v>854222.13400052325</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21587,23 +21587,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13197.147589528799</v>
+        <v>13220.114443308501</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8725.590645862163</v>
+        <v>8755.9871750472721</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21278.661953799889</v>
+        <v>21389.948478541719</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>29844.10367511287</v>
+        <v>30052.396109357069</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>35842.137959309039</v>
+        <v>36155.10380027166</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21622,14 +21622,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>547558.27694603696</v>
+        <v>568412.65688374313</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="261" t="s">
+      <c r="B13" s="263" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="261"/>
+      <c r="C13" s="263"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21645,14 +21645,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.676728716877416E-2</v>
+        <v>8.4879283439002945E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="261" t="s">
+      <c r="B18" s="263" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="261"/>
+      <c r="C18" s="263"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>108887.64182361276</v>
+        <v>109573.55000652623</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>547558.27694603696</v>
+        <v>568412.65688374313</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>656445.9187696497</v>
+        <v>677986.20689026942</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21705,7 +21705,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>662944.9187696497</v>
+        <v>684485.20689026942</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.242327948114355</v>
+        <v>10.575119841953303</v>
       </c>
     </row>
   </sheetData>
@@ -21766,37 +21766,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="259" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21992,23 +21992,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13197.147589528799</v>
+        <v>13220.114443308501</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8725.590645862163</v>
+        <v>8755.9871750472721</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21278.661953799889</v>
+        <v>21389.948478541719</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>29844.10367511287</v>
+        <v>30052.396109357069</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>35842.137959309039</v>
+        <v>36155.10380027166</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22016,18 +22016,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="259" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="259"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="259"/>
+      <c r="G11" s="259"/>
+      <c r="H11" s="259"/>
+      <c r="I11" s="259"/>
+      <c r="J11" s="259"/>
+      <c r="K11" s="259"/>
+      <c r="L11" s="259"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22221,18 +22221,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="267" t="s">
+      <c r="C17" s="259" t="s">
         <v>208</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="E17" s="267"/>
-      <c r="F17" s="267"/>
-      <c r="G17" s="267"/>
-      <c r="H17" s="267"/>
-      <c r="I17" s="267"/>
-      <c r="J17" s="267"/>
-      <c r="K17" s="267"/>
-      <c r="L17" s="267"/>
+      <c r="D17" s="259"/>
+      <c r="E17" s="259"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
+      <c r="J17" s="259"/>
+      <c r="K17" s="259"/>
+      <c r="L17" s="259"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22366,18 +22366,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="267" t="s">
+      <c r="C22" s="259" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="267"/>
-      <c r="E22" s="267"/>
-      <c r="F22" s="267"/>
-      <c r="G22" s="267"/>
-      <c r="H22" s="267"/>
-      <c r="I22" s="267"/>
-      <c r="J22" s="267"/>
-      <c r="K22" s="267"/>
-      <c r="L22" s="267"/>
+      <c r="D22" s="259"/>
+      <c r="E22" s="259"/>
+      <c r="F22" s="259"/>
+      <c r="G22" s="259"/>
+      <c r="H22" s="259"/>
+      <c r="I22" s="259"/>
+      <c r="J22" s="259"/>
+      <c r="K22" s="259"/>
+      <c r="L22" s="259"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22461,18 +22461,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="267" t="s">
+      <c r="C27" s="259" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="267"/>
-      <c r="E27" s="267"/>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="267"/>
-      <c r="K27" s="267"/>
-      <c r="L27" s="267"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="259"/>
+      <c r="F27" s="259"/>
+      <c r="G27" s="259"/>
+      <c r="H27" s="259"/>
+      <c r="I27" s="259"/>
+      <c r="J27" s="259"/>
+      <c r="K27" s="259"/>
+      <c r="L27" s="259"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22773,10 +22773,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="261" t="s">
+      <c r="B39" s="263" t="s">
         <v>217</v>
       </c>
-      <c r="C39" s="261"/>
+      <c r="C39" s="263"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.676728716877416E-2</v>
+        <v>8.4879283439002945E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1047921.7662133881</v>
+        <v>1057071.9937248814</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1120967.2700776919</v>
+        <v>1130490.4399311361</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1127466.2700776919</v>
+        <v>1136989.4399311361</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -22874,14 +22874,14 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.41906297434867</v>
+        <v>17.566193491504745</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="261" t="s">
+      <c r="B52" s="263" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="261"/>
+      <c r="C52" s="263"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.0399499999999994E-2</v>
+        <v>8.8198500000000013E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -22933,14 +22933,14 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>16.553955930312938</v>
+        <v>16.722045410153854</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="261" t="s">
+      <c r="B60" s="263" t="s">
         <v>335</v>
       </c>
-      <c r="C60" s="261"/>
+      <c r="C60" s="263"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.676728716877416E-2</v>
+        <v>8.4879283439002945E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>824369.17306410777</v>
+        <v>831567.38740624825</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>897414.67692841147</v>
+        <v>904985.83361250279</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>903913.67692841147</v>
+        <v>911484.83361250279</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23037,14 +23037,14 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>13.965233089151369</v>
+        <v>14.082205506481209</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="261" t="s">
+      <c r="B73" s="263" t="s">
         <v>436</v>
       </c>
-      <c r="C73" s="261"/>
+      <c r="C73" s="263"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.676728716877416E-2</v>
+        <v>8.4879283439002945E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1556319.4547723583</v>
+        <v>1569908.9015716061</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1629364.958636662</v>
+        <v>1643327.3477778607</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1635863.958636662</v>
+        <v>1649826.3477778607</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23141,22 +23141,22 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.273676090545717</v>
+        <v>25.489391400331563</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23194,10 +23194,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="263" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="263"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.242327948114355</v>
+        <v>10.575119841953303</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.41906297434867</v>
+        <v>17.566193491504745</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>16.553955930312938</v>
+        <v>16.722045410153854</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>13.965233089151369</v>
+        <v>14.082205506481209</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.273676090545717</v>
+        <v>25.489391400331563</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>16.69085120649461</v>
+        <v>16.886991130084933</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.66741770294651459</v>
+        <v>0.62844658920780472</v>
       </c>
     </row>
   </sheetData>
@@ -23325,37 +23325,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="259" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23468,18 +23468,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="259" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="259"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="259"/>
+      <c r="I9" s="259"/>
+      <c r="J9" s="259"/>
+      <c r="K9" s="259"/>
+      <c r="L9" s="259"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23600,18 +23600,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="267" t="s">
+      <c r="C14" s="259" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="267"/>
-      <c r="E14" s="267"/>
-      <c r="F14" s="267"/>
-      <c r="G14" s="267"/>
-      <c r="H14" s="267"/>
-      <c r="I14" s="267"/>
-      <c r="J14" s="267"/>
-      <c r="K14" s="267"/>
-      <c r="L14" s="267"/>
+      <c r="D14" s="259"/>
+      <c r="E14" s="259"/>
+      <c r="F14" s="259"/>
+      <c r="G14" s="259"/>
+      <c r="H14" s="259"/>
+      <c r="I14" s="259"/>
+      <c r="J14" s="259"/>
+      <c r="K14" s="259"/>
+      <c r="L14" s="259"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23701,10 +23701,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="261" t="s">
+      <c r="B20" s="263" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="261"/>
+      <c r="C20" s="263"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.0399499999999994E-2</v>
+        <v>8.8198500000000013E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23805,60 +23805,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="259" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="259"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="259"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="259"/>
+      <c r="L5" s="259"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23992,7 +23992,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>783369.10436075577</v>
+        <v>806165.34550930583</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24046,23 +24046,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10673.858273945752</v>
+        <v>10692.433874512461</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14241.406306535027</v>
+        <v>14291.017770102695</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19001.344067204016</v>
+        <v>19100.720313288199</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25352.206698476952</v>
+        <v>25529.148613173871</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>33825.732653915147</v>
+        <v>34121.091677370387</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24081,15 +24081,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>516753.76924898516</v>
+        <v>536434.9244645827</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="274" t="s">
+      <c r="B14" s="260" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="275"/>
+      <c r="C14" s="261"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.090820467675114</v>
+        <v>10.41820393924748</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24116,20 +24116,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="273" t="s">
+      <c r="E17" s="262" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="273"/>
-      <c r="G17" s="273"/>
-      <c r="H17" s="273"/>
-      <c r="I17" s="273"/>
+      <c r="F17" s="262"/>
+      <c r="G17" s="262"/>
+      <c r="H17" s="262"/>
+      <c r="I17" s="262"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="274" t="s">
+      <c r="B19" s="260" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="275"/>
+      <c r="C19" s="261"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.676728716877416E-2</v>
+        <v>8.4879283439002945E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>621330.71</v>
+        <v>643676.2699999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24190,15 +24190,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>614831.71</v>
+        <v>637177.2699999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="274" t="s">
+      <c r="B28" s="260" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="275"/>
+      <c r="C28" s="261"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>103094.5480000769</v>
+        <v>103734.41224844762</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24215,7 +24215,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>516753.76924898516</v>
+        <v>536434.9244645827</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>619848.31724906201</v>
+        <v>640169.33671303035</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>626347.31724906201</v>
+        <v>646668.33671303035</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24269,21 +24269,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.090820467675114</v>
+        <v>10.41820393924748</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31242,7 +31242,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31313,7 +31313,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32391,7 +32391,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-560.41237197869725</v>
+        <v>-580.56706267922971</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32428,7 +32428,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.2200274570543508</v>
+        <v>1.2639045683969647</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.6709131076694697</v>
+        <v>1.7310058867664735</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32550,7 +32550,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>647907.26</v>
+        <v>671208.62</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32611,7 +32611,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>641408.26</v>
+        <v>664709.62</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32648,7 +32648,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.2631293853991685</v>
+        <v>1.3090169025567504</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32685,7 +32685,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>51.153063242682833</v>
+        <v>53.011374112768166</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32782,7 +32782,7 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="64">
-        <f>AC113+AC55+AC114+AC57+AC59+AC60</f>
+        <f>AC113+AC55+AC114+AC57+AC59+AC60+AC58</f>
         <v>-6014.2897973950785</v>
       </c>
     </row>
@@ -32820,7 +32820,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>80.028070652173909</v>
+        <v>82.906203063241108</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32857,7 +32857,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-106.64738175367074</v>
+        <v>-110.52171451530327</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32894,7 +32894,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.2495615499045341E-2</v>
+        <v>1.2061823639869226E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32931,7 +32931,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.7844002916445475E-3</v>
+        <v>-1.7224538977205326E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33545,7 +33545,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>1.0030756562289486E-2</v>
+        <v>9.6825335765205155E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35141,15 +35141,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="263" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="261"/>
-      <c r="E4" s="261" t="s">
+      <c r="C4" s="263"/>
+      <c r="E4" s="263" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
+      <c r="F4" s="263"/>
+      <c r="G4" s="263"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35157,7 +35157,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35173,7 +35173,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>647907.26</v>
+        <v>671208.62</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>641408.26</v>
+        <v>664709.62</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-560.41237197869725</v>
+        <v>-580.56706267922971</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35233,7 +35233,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2200274570543508</v>
+        <v>1.2639045683969647</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35253,7 +35253,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.6709131076694697</v>
+        <v>1.7310058867664735</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35273,7 +35273,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.2631293853991685</v>
+        <v>1.3090169025567504</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35282,18 +35282,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>51.153063242682833</v>
+        <v>53.011374112768166</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="263" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="261"/>
-      <c r="E15" s="261" t="s">
+      <c r="C15" s="263"/>
+      <c r="E15" s="263" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="261"/>
+      <c r="F15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35344,14 +35344,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="261" t="s">
+      <c r="B21" s="263" t="s">
         <v>257</v>
       </c>
-      <c r="C21" s="261"/>
-      <c r="E21" s="261" t="s">
+      <c r="C21" s="263"/>
+      <c r="E21" s="263" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="261"/>
+      <c r="F21" s="263"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35420,14 +35420,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="261" t="s">
+      <c r="B29" s="263" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="261"/>
-      <c r="E29" s="261" t="s">
+      <c r="C29" s="263"/>
+      <c r="E29" s="263" t="s">
         <v>268</v>
       </c>
-      <c r="F29" s="261"/>
+      <c r="F29" s="263"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35503,14 +35503,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="261" t="s">
+      <c r="B37" s="263" t="s">
         <v>280</v>
       </c>
-      <c r="C37" s="261"/>
-      <c r="E37" s="261" t="s">
+      <c r="C37" s="263"/>
+      <c r="E37" s="263" t="s">
         <v>283</v>
       </c>
-      <c r="F37" s="261"/>
+      <c r="F37" s="263"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35518,7 +35518,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7844002916445475E-3</v>
+        <v>-1.7224538977205326E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35534,7 +35534,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.2495615499045341E-2</v>
+        <v>1.2061823639869226E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35579,14 +35579,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="261" t="s">
+      <c r="B45" s="263" t="s">
         <v>291</v>
       </c>
-      <c r="C45" s="261"/>
-      <c r="E45" s="261" t="s">
+      <c r="C45" s="263"/>
+      <c r="E45" s="263" t="s">
         <v>297</v>
       </c>
-      <c r="F45" s="261"/>
+      <c r="F45" s="263"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35619,18 +35619,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>1.0030756562289486E-2</v>
+        <v>9.6825335765205155E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="261" t="s">
+      <c r="B51" s="263" t="s">
         <v>294</v>
       </c>
-      <c r="C51" s="261"/>
-      <c r="E51" s="261" t="s">
+      <c r="C51" s="263"/>
+      <c r="E51" s="263" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="261"/>
+      <c r="F51" s="263"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35798,7 +35798,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>10.01</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35827,7 +35827,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>647907.26</v>
+        <v>671208.62</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35856,7 +35856,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>641408.26</v>
+        <v>664709.62</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-560.41237197869725</v>
+        <v>-580.56706267922971</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35914,7 +35914,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2200274570543508</v>
+        <v>1.2639045683969647</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35943,7 +35943,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.6709131076694697</v>
+        <v>1.7310058867664735</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35972,7 +35972,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.2631293853991685</v>
+        <v>1.3090169025567504</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>51.153063242682833</v>
+        <v>53.011374112768166</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7844002916445475E-3</v>
+        <v>-1.7224538977205326E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.2495615499045341E-2</v>
+        <v>1.2061823639869226E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37126,7 +37126,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>1.0030756562289486E-2</v>
+        <v>9.6825335765205155E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37615,14 +37615,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="269" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="270"/>
+      <c r="F3" s="271" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="270"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37689,19 +37689,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="272">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="273"/>
+      <c r="F7" s="272">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="273"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37728,19 +37728,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="272">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="273"/>
+      <c r="F9" s="272">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="273"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -37767,19 +37767,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="272">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="273"/>
+      <c r="F11" s="272">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="273"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -37806,19 +37806,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="272">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="273"/>
+      <c r="F13" s="272">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="273"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -37845,19 +37845,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="272">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="273"/>
+      <c r="F15" s="272">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="273"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -37884,19 +37884,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="272">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="273"/>
+      <c r="F17" s="272">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="273"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -37923,22 +37923,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="272">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="273"/>
+      <c r="F19" s="272">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="273"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -37965,22 +37965,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="272">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="273"/>
+      <c r="F21" s="272">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="273"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38029,22 +38029,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="272">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="273"/>
+      <c r="F25" s="272">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="273"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38072,22 +38072,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="272">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="273"/>
+      <c r="F27" s="272">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="273"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38115,22 +38115,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="272">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="273"/>
+      <c r="F29" s="272">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="273"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38179,22 +38179,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="272">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="273"/>
+      <c r="F33" s="272">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="273"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38222,43 +38222,25 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="262">
+      <c r="C35" s="272">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="263"/>
-      <c r="F35" s="262">
+      <c r="D35" s="273"/>
+      <c r="F35" s="272">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="263"/>
+      <c r="G35" s="273"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38269,6 +38251,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C66123E-0AEE-1B42-ABEE-299F998218F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9DDBF9-62CD-354D-98C3-A8876F9CE944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2473,30 +2473,6 @@
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2504,6 +2480,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2515,16 +2500,31 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -12933,13 +12933,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>24.245000000000001</v>
+    <v>24.07</v>
     <v>7.77</v>
-    <v>0.7873</v>
-    <v>0.3</v>
-    <v>2.9790999999999998E-2</v>
-    <v>-0.11</v>
-    <v>-1.0607999999999999E-2</v>
+    <v>0.79259999999999997</v>
+    <v>0.15</v>
+    <v>1.4071E-2</v>
+    <v>1.12E-2</v>
+    <v>1.036E-3</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12947,25 +12947,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.49</v>
+    <v>10.82</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46300.863038680465</v>
+    <v>46304.979243541406</v>
     <v>0</v>
-    <v>10.09</v>
-    <v>643675647</v>
+    <v>10.56</v>
+    <v>670986861</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.119999999999999</v>
-    <v>61.397300000000001</v>
-    <v>10.07</v>
-    <v>10.37</v>
-    <v>10.26</v>
+    <v>10.7</v>
+    <v>63.110500000000002</v>
+    <v>10.66</v>
+    <v>10.81</v>
+    <v>10.821199999999999</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>504067</v>
-    <v>725761</v>
+    <v>537070</v>
+    <v>726273</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -12987,19 +12987,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13811,18 +13811,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="266" t="s">
+      <c r="B2" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="267"/>
-      <c r="E2" s="266" t="s">
+      <c r="C2" s="259"/>
+      <c r="E2" s="258" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="267"/>
-      <c r="H2" s="266" t="s">
+      <c r="F2" s="259"/>
+      <c r="H2" s="258" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="267"/>
+      <c r="I2" s="259"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>671208.62</v>
+        <v>699688.06</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.575119841953303</v>
+        <v>10.567898156985528</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>664709.62</v>
+        <v>693189.06</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.566193491504745</v>
+        <v>17.563074594846377</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13893,7 +13893,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.722045410153854</v>
+        <v>16.729077459880621</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13902,14 +13902,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.26</v>
+        <v>10.821199999999999</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-580.56706267922971</v>
+        <v>-605.20057353543632</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.082205506481209</v>
+        <v>14.079725941136617</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13926,14 +13926,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.2639045683969647</v>
+        <v>1.3175321489268266</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.489391400331563</v>
+        <v>25.48481855246839</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13950,14 +13950,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.11</v>
+        <v>1.12E-2</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.2061823639869226E-2</v>
+        <v>1.1570870596248275E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>16.886991130084933</v>
+        <v>16.884918941063507</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13974,14 +13974,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.9790999999999998E-2</v>
+        <v>1.4071E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7224538977205326E-3</v>
+        <v>-1.65234476589842E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.62844658920780472</v>
+        <v>0.5619721499596213</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.0607999999999999E-2</v>
+        <v>1.036E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14014,7 +14014,7 @@
       </c>
       <c r="C11" s="209" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>24.245000000000001</v>
+        <v>24.07</v>
       </c>
       <c r="E11" s="186" t="s">
         <v>301</v>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.7873</v>
+        <v>0.79259999999999997</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>725761</v>
+        <v>726273</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>9.6825335765205155E-3</v>
+        <v>9.2884249018055261E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14105,10 +14105,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="268" t="s">
+      <c r="B17" s="260" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="268"/>
+      <c r="C17" s="260"/>
       <c r="E17" s="184" t="s">
         <v>308</v>
       </c>
@@ -14181,14 +14181,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="268" t="s">
+      <c r="B25" s="260" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="268"/>
-      <c r="E25" s="266" t="s">
+      <c r="C25" s="260"/>
+      <c r="E25" s="258" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="267"/>
+      <c r="F25" s="259"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14519,36 +14519,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="263" t="s">
+      <c r="S2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="263"/>
-      <c r="U2" s="263"/>
-      <c r="V2" s="263"/>
-      <c r="W2" s="263"/>
-      <c r="X2" s="263"/>
-      <c r="Y2" s="263"/>
-      <c r="Z2" s="263"/>
-      <c r="AA2" s="263" t="s">
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
+      <c r="AA2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="263"/>
-      <c r="AC2" s="263"/>
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="261"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -14559,32 +14559,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="274" t="s">
+      <c r="S4" s="268" t="s">
         <v>126</v>
       </c>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
-      <c r="AA4" s="275"/>
-      <c r="AB4" s="275"/>
-      <c r="AC4" s="275"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15075,33 +15075,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="259" t="s">
+      <c r="C11" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="259"/>
-      <c r="G11" s="259"/>
-      <c r="H11" s="259"/>
-      <c r="I11" s="259"/>
-      <c r="J11" s="259"/>
-      <c r="K11" s="259"/>
-      <c r="L11" s="259"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="274" t="s">
+      <c r="S11" s="268" t="s">
         <v>132</v>
       </c>
-      <c r="T11" s="275"/>
-      <c r="U11" s="275"/>
-      <c r="V11" s="275"/>
-      <c r="W11" s="275"/>
-      <c r="X11" s="275"/>
-      <c r="Y11" s="275"/>
-      <c r="Z11" s="275"/>
-      <c r="AA11" s="275"/>
-      <c r="AB11" s="275"/>
-      <c r="AC11" s="275"/>
+      <c r="T11" s="269"/>
+      <c r="U11" s="269"/>
+      <c r="V11" s="269"/>
+      <c r="W11" s="269"/>
+      <c r="X11" s="269"/>
+      <c r="Y11" s="269"/>
+      <c r="Z11" s="269"/>
+      <c r="AA11" s="269"/>
+      <c r="AB11" s="269"/>
+      <c r="AC11" s="269"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15542,33 +15542,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="259" t="s">
+      <c r="C19" s="267" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="259"/>
-      <c r="E19" s="259"/>
-      <c r="F19" s="259"/>
-      <c r="G19" s="259"/>
-      <c r="H19" s="259"/>
-      <c r="I19" s="259"/>
-      <c r="J19" s="259"/>
-      <c r="K19" s="259"/>
-      <c r="L19" s="259"/>
+      <c r="D19" s="267"/>
+      <c r="E19" s="267"/>
+      <c r="F19" s="267"/>
+      <c r="G19" s="267"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="267"/>
+      <c r="J19" s="267"/>
+      <c r="K19" s="267"/>
+      <c r="L19" s="267"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="274" t="s">
+      <c r="S19" s="268" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="275"/>
-      <c r="U19" s="275"/>
-      <c r="V19" s="275"/>
-      <c r="W19" s="275"/>
-      <c r="X19" s="275"/>
-      <c r="Y19" s="275"/>
-      <c r="Z19" s="275"/>
-      <c r="AA19" s="275"/>
-      <c r="AB19" s="275"/>
-      <c r="AC19" s="275"/>
+      <c r="T19" s="269"/>
+      <c r="U19" s="269"/>
+      <c r="V19" s="269"/>
+      <c r="W19" s="269"/>
+      <c r="X19" s="269"/>
+      <c r="Y19" s="269"/>
+      <c r="Z19" s="269"/>
+      <c r="AA19" s="269"/>
+      <c r="AB19" s="269"/>
+      <c r="AC19" s="269"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16805,35 +16805,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="P2" s="263" t="s">
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="P2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="263"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="263"/>
-      <c r="V2" s="263"/>
-      <c r="W2" s="263"/>
-      <c r="X2" s="263" t="s">
+      <c r="Q2" s="261"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="261"/>
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="263"/>
-      <c r="Z2" s="263"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -16842,31 +16842,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="P4" s="275" t="s">
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="P4" s="269" t="s">
         <v>126</v>
       </c>
-      <c r="Q4" s="275"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="275"/>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17061,32 +17061,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="259" t="s">
+      <c r="C9" s="267" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="259"/>
-      <c r="E9" s="259"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="259"/>
-      <c r="H9" s="259"/>
-      <c r="I9" s="259"/>
-      <c r="J9" s="259"/>
-      <c r="K9" s="259"/>
-      <c r="L9" s="259"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="275" t="s">
+      <c r="P9" s="269" t="s">
         <v>138</v>
       </c>
-      <c r="Q9" s="275"/>
-      <c r="R9" s="275"/>
-      <c r="S9" s="275"/>
-      <c r="T9" s="275"/>
-      <c r="U9" s="275"/>
-      <c r="V9" s="275"/>
-      <c r="W9" s="275"/>
-      <c r="X9" s="275"/>
-      <c r="Y9" s="275"/>
-      <c r="Z9" s="275"/>
+      <c r="Q9" s="269"/>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="269"/>
+      <c r="U9" s="269"/>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="269"/>
+      <c r="Y9" s="269"/>
+      <c r="Z9" s="269"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -17844,31 +17844,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="259" t="s">
+      <c r="C20" s="267" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="259"/>
-      <c r="E20" s="259"/>
-      <c r="F20" s="259"/>
-      <c r="G20" s="259"/>
-      <c r="H20" s="259"/>
-      <c r="I20" s="259"/>
-      <c r="J20" s="259"/>
-      <c r="K20" s="259"/>
-      <c r="L20" s="259"/>
-      <c r="P20" s="275" t="s">
+      <c r="D20" s="267"/>
+      <c r="E20" s="267"/>
+      <c r="F20" s="267"/>
+      <c r="G20" s="267"/>
+      <c r="H20" s="267"/>
+      <c r="I20" s="267"/>
+      <c r="J20" s="267"/>
+      <c r="K20" s="267"/>
+      <c r="L20" s="267"/>
+      <c r="P20" s="269" t="s">
         <v>140</v>
       </c>
-      <c r="Q20" s="275"/>
-      <c r="R20" s="275"/>
-      <c r="S20" s="275"/>
-      <c r="T20" s="275"/>
-      <c r="U20" s="275"/>
-      <c r="V20" s="275"/>
-      <c r="W20" s="275"/>
-      <c r="X20" s="275"/>
-      <c r="Y20" s="275"/>
-      <c r="Z20" s="275"/>
+      <c r="Q20" s="269"/>
+      <c r="R20" s="269"/>
+      <c r="S20" s="269"/>
+      <c r="T20" s="269"/>
+      <c r="U20" s="269"/>
+      <c r="V20" s="269"/>
+      <c r="W20" s="269"/>
+      <c r="X20" s="269"/>
+      <c r="Y20" s="269"/>
+      <c r="Z20" s="269"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18592,60 +18592,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="P3" s="258"/>
-      <c r="Q3" s="258"/>
-      <c r="R3" s="258"/>
-      <c r="S3" s="258"/>
-      <c r="T3" s="258"/>
-      <c r="U3" s="258"/>
-      <c r="V3" s="258"/>
-      <c r="W3" s="258"/>
-      <c r="X3" s="258"/>
-      <c r="Y3" s="258"/>
-      <c r="Z3" s="258"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="272"/>
+      <c r="S3" s="272"/>
+      <c r="T3" s="272"/>
+      <c r="U3" s="272"/>
+      <c r="V3" s="272"/>
+      <c r="W3" s="272"/>
+      <c r="X3" s="272"/>
+      <c r="Y3" s="272"/>
+      <c r="Z3" s="272"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="259"/>
-      <c r="G5" s="259"/>
-      <c r="H5" s="259"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="259"/>
-      <c r="K5" s="259"/>
-      <c r="L5" s="259"/>
-      <c r="P5" s="258"/>
-      <c r="Q5" s="258"/>
-      <c r="R5" s="258"/>
-      <c r="S5" s="258"/>
-      <c r="T5" s="258"/>
-      <c r="U5" s="258"/>
-      <c r="V5" s="258"/>
-      <c r="W5" s="258"/>
-      <c r="X5" s="258"/>
-      <c r="Y5" s="258"/>
-      <c r="Z5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="P5" s="272"/>
+      <c r="Q5" s="272"/>
+      <c r="R5" s="272"/>
+      <c r="S5" s="272"/>
+      <c r="T5" s="272"/>
+      <c r="U5" s="272"/>
+      <c r="V5" s="272"/>
+      <c r="W5" s="272"/>
+      <c r="X5" s="272"/>
+      <c r="Y5" s="272"/>
+      <c r="Z5" s="272"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18831,30 +18831,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="259" t="s">
+      <c r="C11" s="267" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="259"/>
-      <c r="G11" s="259"/>
-      <c r="H11" s="259"/>
-      <c r="I11" s="259"/>
-      <c r="J11" s="259"/>
-      <c r="K11" s="259"/>
-      <c r="L11" s="259"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="258"/>
-      <c r="Q11" s="258"/>
-      <c r="R11" s="258"/>
-      <c r="S11" s="258"/>
-      <c r="T11" s="258"/>
-      <c r="U11" s="258"/>
-      <c r="V11" s="258"/>
-      <c r="W11" s="258"/>
-      <c r="X11" s="258"/>
-      <c r="Y11" s="258"/>
-      <c r="Z11" s="258"/>
+      <c r="P11" s="272"/>
+      <c r="Q11" s="272"/>
+      <c r="R11" s="272"/>
+      <c r="S11" s="272"/>
+      <c r="T11" s="272"/>
+      <c r="U11" s="272"/>
+      <c r="V11" s="272"/>
+      <c r="W11" s="272"/>
+      <c r="X11" s="272"/>
+      <c r="Y11" s="272"/>
+      <c r="Z11" s="272"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19096,18 +19096,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="259" t="s">
+      <c r="C18" s="267" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="259"/>
-      <c r="E18" s="259"/>
-      <c r="F18" s="259"/>
-      <c r="G18" s="259"/>
-      <c r="H18" s="259"/>
-      <c r="I18" s="259"/>
-      <c r="J18" s="259"/>
-      <c r="K18" s="259"/>
-      <c r="L18" s="259"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19320,23 +19320,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="258"/>
-      <c r="C25" s="258"/>
+      <c r="B25" s="272"/>
+      <c r="C25" s="272"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="259" t="s">
+      <c r="C26" s="267" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="259"/>
-      <c r="E26" s="259"/>
-      <c r="F26" s="259"/>
-      <c r="G26" s="259"/>
-      <c r="H26" s="259"/>
-      <c r="I26" s="259"/>
-      <c r="J26" s="259"/>
-      <c r="K26" s="259"/>
-      <c r="L26" s="259"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19528,18 +19528,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="259" t="s">
+      <c r="C33" s="267" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="259"/>
-      <c r="E33" s="259"/>
-      <c r="F33" s="259"/>
-      <c r="G33" s="259"/>
-      <c r="H33" s="259"/>
-      <c r="I33" s="259"/>
-      <c r="J33" s="259"/>
-      <c r="K33" s="259"/>
-      <c r="L33" s="259"/>
+      <c r="D33" s="267"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="267"/>
+      <c r="G33" s="267"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+      <c r="J33" s="267"/>
+      <c r="K33" s="267"/>
+      <c r="L33" s="267"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19723,18 +19723,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="259" t="s">
+      <c r="C40" s="267" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="259"/>
-      <c r="E40" s="259"/>
-      <c r="F40" s="259"/>
-      <c r="G40" s="259"/>
-      <c r="H40" s="259"/>
-      <c r="I40" s="259"/>
-      <c r="J40" s="259"/>
-      <c r="K40" s="259"/>
-      <c r="L40" s="259"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20003,6 +20003,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20010,12 +20016,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20053,60 +20053,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
-      <c r="AA2" s="258"/>
-      <c r="AB2" s="258"/>
-      <c r="AC2" s="258"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="S2" s="272"/>
+      <c r="T2" s="272"/>
+      <c r="U2" s="272"/>
+      <c r="V2" s="272"/>
+      <c r="W2" s="272"/>
+      <c r="X2" s="272"/>
+      <c r="Y2" s="272"/>
+      <c r="Z2" s="272"/>
+      <c r="AA2" s="272"/>
+      <c r="AB2" s="272"/>
+      <c r="AC2" s="272"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="S4" s="258"/>
-      <c r="T4" s="258"/>
-      <c r="U4" s="258"/>
-      <c r="V4" s="258"/>
-      <c r="W4" s="258"/>
-      <c r="X4" s="258"/>
-      <c r="Y4" s="258"/>
-      <c r="Z4" s="258"/>
-      <c r="AA4" s="258"/>
-      <c r="AB4" s="258"/>
-      <c r="AC4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="S4" s="272"/>
+      <c r="T4" s="272"/>
+      <c r="U4" s="272"/>
+      <c r="V4" s="272"/>
+      <c r="W4" s="272"/>
+      <c r="X4" s="272"/>
+      <c r="Y4" s="272"/>
+      <c r="Z4" s="272"/>
+      <c r="AA4" s="272"/>
+      <c r="AB4" s="272"/>
+      <c r="AC4" s="272"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20469,18 +20469,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="259" t="s">
+      <c r="C13" s="267" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="259"/>
-      <c r="E13" s="259"/>
-      <c r="F13" s="259"/>
-      <c r="G13" s="259"/>
-      <c r="H13" s="259"/>
-      <c r="I13" s="259"/>
-      <c r="J13" s="259"/>
-      <c r="K13" s="259"/>
-      <c r="L13" s="259"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20573,18 +20573,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="259" t="s">
+      <c r="C18" s="267" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="259"/>
-      <c r="E18" s="259"/>
-      <c r="F18" s="259"/>
-      <c r="G18" s="259"/>
-      <c r="H18" s="259"/>
-      <c r="I18" s="259"/>
-      <c r="J18" s="259"/>
-      <c r="K18" s="259"/>
-      <c r="L18" s="259"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20776,18 +20776,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="259" t="s">
+      <c r="C25" s="267" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="259"/>
-      <c r="E25" s="259"/>
-      <c r="F25" s="259"/>
-      <c r="G25" s="259"/>
-      <c r="H25" s="259"/>
-      <c r="I25" s="259"/>
-      <c r="J25" s="259"/>
-      <c r="K25" s="259"/>
-      <c r="L25" s="259"/>
+      <c r="D25" s="267"/>
+      <c r="E25" s="267"/>
+      <c r="F25" s="267"/>
+      <c r="G25" s="267"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="267"/>
+      <c r="J25" s="267"/>
+      <c r="K25" s="267"/>
+      <c r="L25" s="267"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20925,18 +20925,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="259" t="s">
+      <c r="C31" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="259"/>
-      <c r="E31" s="259"/>
-      <c r="F31" s="259"/>
-      <c r="G31" s="259"/>
-      <c r="H31" s="259"/>
-      <c r="I31" s="259"/>
-      <c r="J31" s="259"/>
-      <c r="K31" s="259"/>
-      <c r="L31" s="259"/>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="267"/>
+      <c r="G31" s="267"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="267"/>
+      <c r="J31" s="267"/>
+      <c r="K31" s="267"/>
+      <c r="L31" s="267"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21075,16 +21075,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21147,10 +21147,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="261" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="263"/>
+      <c r="C4" s="261"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>671208.62</v>
+        <v>699688.06</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.7873</v>
+        <v>0.79259999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21235,10 +21235,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="263" t="s">
+      <c r="B15" s="261" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="263"/>
+      <c r="C15" s="261"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.0077386080765001E-2</v>
+        <v>8.6728946628479089E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.90992261391923501</v>
+        <v>0.91327105337152092</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.8198500000000013E-2</v>
+        <v>8.8106999999999991E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.4879283439002945E-2</v>
+        <v>8.4919104108776997E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21327,60 +21327,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="P3" s="258"/>
-      <c r="Q3" s="258"/>
-      <c r="R3" s="258"/>
-      <c r="S3" s="258"/>
-      <c r="T3" s="258"/>
-      <c r="U3" s="258"/>
-      <c r="V3" s="258"/>
-      <c r="W3" s="258"/>
-      <c r="X3" s="258"/>
-      <c r="Y3" s="258"/>
-      <c r="Z3" s="258"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="272"/>
+      <c r="S3" s="272"/>
+      <c r="T3" s="272"/>
+      <c r="U3" s="272"/>
+      <c r="V3" s="272"/>
+      <c r="W3" s="272"/>
+      <c r="X3" s="272"/>
+      <c r="Y3" s="272"/>
+      <c r="Z3" s="272"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="267" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="259"/>
-      <c r="G5" s="259"/>
-      <c r="H5" s="259"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="259"/>
-      <c r="K5" s="259"/>
-      <c r="L5" s="259"/>
-      <c r="P5" s="258"/>
-      <c r="Q5" s="258"/>
-      <c r="R5" s="258"/>
-      <c r="S5" s="258"/>
-      <c r="T5" s="258"/>
-      <c r="U5" s="258"/>
-      <c r="V5" s="258"/>
-      <c r="W5" s="258"/>
-      <c r="X5" s="258"/>
-      <c r="Y5" s="258"/>
-      <c r="Z5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="P5" s="272"/>
+      <c r="Q5" s="272"/>
+      <c r="R5" s="272"/>
+      <c r="S5" s="272"/>
+      <c r="T5" s="272"/>
+      <c r="U5" s="272"/>
+      <c r="V5" s="272"/>
+      <c r="W5" s="272"/>
+      <c r="X5" s="272"/>
+      <c r="Y5" s="272"/>
+      <c r="Z5" s="272"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>854222.13400052325</v>
+        <v>853698.16346860211</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21587,23 +21587,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13220.114443308501</v>
+        <v>13219.62921467751</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8755.9871750472721</v>
+        <v>8755.3444305812991</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21389.948478541719</v>
+        <v>21387.59328687143</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30052.396109357069</v>
+        <v>30047.984201951531</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36155.10380027166</v>
+        <v>36148.469136170737</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21622,14 +21622,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>568412.65688374313</v>
+        <v>567959.75583879277</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="263" t="s">
+      <c r="B13" s="261" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="263"/>
+      <c r="C13" s="261"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21645,14 +21645,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4879283439002945E-2</v>
+        <v>8.4919104108776997E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="263" t="s">
+      <c r="B18" s="261" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="263"/>
+      <c r="C18" s="261"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109573.55000652623</v>
+        <v>109559.02027025251</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>568412.65688374313</v>
+        <v>567959.75583879277</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>677986.20689026942</v>
+        <v>677518.77610904525</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21705,7 +21705,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>684485.20689026942</v>
+        <v>684017.77610904525</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.575119841953303</v>
+        <v>10.567898156985528</v>
       </c>
     </row>
   </sheetData>
@@ -21766,37 +21766,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="267" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21992,23 +21992,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13220.114443308501</v>
+        <v>13219.62921467751</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8755.9871750472721</v>
+        <v>8755.3444305812991</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21389.948478541719</v>
+        <v>21387.59328687143</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>30052.396109357069</v>
+        <v>30047.984201951531</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36155.10380027166</v>
+        <v>36148.469136170737</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22016,18 +22016,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="259" t="s">
+      <c r="C11" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="259"/>
-      <c r="G11" s="259"/>
-      <c r="H11" s="259"/>
-      <c r="I11" s="259"/>
-      <c r="J11" s="259"/>
-      <c r="K11" s="259"/>
-      <c r="L11" s="259"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22221,18 +22221,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="259" t="s">
+      <c r="C17" s="267" t="s">
         <v>208</v>
       </c>
-      <c r="D17" s="259"/>
-      <c r="E17" s="259"/>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
-      <c r="J17" s="259"/>
-      <c r="K17" s="259"/>
-      <c r="L17" s="259"/>
+      <c r="D17" s="267"/>
+      <c r="E17" s="267"/>
+      <c r="F17" s="267"/>
+      <c r="G17" s="267"/>
+      <c r="H17" s="267"/>
+      <c r="I17" s="267"/>
+      <c r="J17" s="267"/>
+      <c r="K17" s="267"/>
+      <c r="L17" s="267"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22366,18 +22366,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="259" t="s">
+      <c r="C22" s="267" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="259"/>
-      <c r="E22" s="259"/>
-      <c r="F22" s="259"/>
-      <c r="G22" s="259"/>
-      <c r="H22" s="259"/>
-      <c r="I22" s="259"/>
-      <c r="J22" s="259"/>
-      <c r="K22" s="259"/>
-      <c r="L22" s="259"/>
+      <c r="D22" s="267"/>
+      <c r="E22" s="267"/>
+      <c r="F22" s="267"/>
+      <c r="G22" s="267"/>
+      <c r="H22" s="267"/>
+      <c r="I22" s="267"/>
+      <c r="J22" s="267"/>
+      <c r="K22" s="267"/>
+      <c r="L22" s="267"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22461,18 +22461,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="259" t="s">
+      <c r="C27" s="267" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="259"/>
-      <c r="E27" s="259"/>
-      <c r="F27" s="259"/>
-      <c r="G27" s="259"/>
-      <c r="H27" s="259"/>
-      <c r="I27" s="259"/>
-      <c r="J27" s="259"/>
-      <c r="K27" s="259"/>
-      <c r="L27" s="259"/>
+      <c r="D27" s="267"/>
+      <c r="E27" s="267"/>
+      <c r="F27" s="267"/>
+      <c r="G27" s="267"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="267"/>
+      <c r="J27" s="267"/>
+      <c r="K27" s="267"/>
+      <c r="L27" s="267"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22773,10 +22773,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="263" t="s">
+      <c r="B39" s="261" t="s">
         <v>217</v>
       </c>
-      <c r="C39" s="263"/>
+      <c r="C39" s="261"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4879283439002945E-2</v>
+        <v>8.4919104108776997E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1057071.9937248814</v>
+        <v>1056878.0150919447</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1130490.4399311361</v>
+        <v>1130288.5662260265</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1136989.4399311361</v>
+        <v>1136787.5662260265</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -22874,14 +22874,14 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.566193491504745</v>
+        <v>17.563074594846377</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="263" t="s">
+      <c r="B52" s="261" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="263"/>
+      <c r="C52" s="261"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.8198500000000013E-2</v>
+        <v>8.8106999999999991E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -22933,14 +22933,14 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>16.722045410153854</v>
+        <v>16.729077459880621</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="263" t="s">
+      <c r="B60" s="261" t="s">
         <v>335</v>
       </c>
-      <c r="C60" s="263"/>
+      <c r="C60" s="261"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4879283439002945E-2</v>
+        <v>8.4919104108776997E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>831567.38740624825</v>
+        <v>831414.79013192689</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>904985.83361250279</v>
+        <v>904825.34126600868</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>911484.83361250279</v>
+        <v>911324.34126600868</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23037,14 +23037,14 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.082205506481209</v>
+        <v>14.079725941136617</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="263" t="s">
+      <c r="B73" s="261" t="s">
         <v>436</v>
       </c>
-      <c r="C73" s="263"/>
+      <c r="C73" s="261"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4879283439002945E-2</v>
+        <v>8.4919104108776997E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1569908.9015716061</v>
+        <v>1569620.8144929872</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1643327.3477778607</v>
+        <v>1643031.365627069</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1649826.3477778607</v>
+        <v>1649530.365627069</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23141,22 +23141,22 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.489391400331563</v>
+        <v>25.48481855246839</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23194,10 +23194,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="261" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="263"/>
+      <c r="C4" s="261"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.575119841953303</v>
+        <v>10.567898156985528</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.566193491504745</v>
+        <v>17.563074594846377</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>16.722045410153854</v>
+        <v>16.729077459880621</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.082205506481209</v>
+        <v>14.079725941136617</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.489391400331563</v>
+        <v>25.48481855246839</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>16.886991130084933</v>
+        <v>16.884918941063507</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.62844658920780472</v>
+        <v>0.5619721499596213</v>
       </c>
     </row>
   </sheetData>
@@ -23325,37 +23325,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="267" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23468,18 +23468,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="259" t="s">
+      <c r="C9" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="259"/>
-      <c r="E9" s="259"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="259"/>
-      <c r="H9" s="259"/>
-      <c r="I9" s="259"/>
-      <c r="J9" s="259"/>
-      <c r="K9" s="259"/>
-      <c r="L9" s="259"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23600,18 +23600,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="259" t="s">
+      <c r="C14" s="267" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="259"/>
-      <c r="E14" s="259"/>
-      <c r="F14" s="259"/>
-      <c r="G14" s="259"/>
-      <c r="H14" s="259"/>
-      <c r="I14" s="259"/>
-      <c r="J14" s="259"/>
-      <c r="K14" s="259"/>
-      <c r="L14" s="259"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23701,10 +23701,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="263" t="s">
+      <c r="B20" s="261" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="263"/>
+      <c r="C20" s="261"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.8198500000000013E-2</v>
+        <v>8.8106999999999991E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23805,60 +23805,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="P3" s="258"/>
-      <c r="Q3" s="258"/>
-      <c r="R3" s="258"/>
-      <c r="S3" s="258"/>
-      <c r="T3" s="258"/>
-      <c r="U3" s="258"/>
-      <c r="V3" s="258"/>
-      <c r="W3" s="258"/>
-      <c r="X3" s="258"/>
-      <c r="Y3" s="258"/>
-      <c r="Z3" s="258"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="272"/>
+      <c r="S3" s="272"/>
+      <c r="T3" s="272"/>
+      <c r="U3" s="272"/>
+      <c r="V3" s="272"/>
+      <c r="W3" s="272"/>
+      <c r="X3" s="272"/>
+      <c r="Y3" s="272"/>
+      <c r="Z3" s="272"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="267" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="259"/>
-      <c r="G5" s="259"/>
-      <c r="H5" s="259"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="259"/>
-      <c r="K5" s="259"/>
-      <c r="L5" s="259"/>
-      <c r="P5" s="258"/>
-      <c r="Q5" s="258"/>
-      <c r="R5" s="258"/>
-      <c r="S5" s="258"/>
-      <c r="T5" s="258"/>
-      <c r="U5" s="258"/>
-      <c r="V5" s="258"/>
-      <c r="W5" s="258"/>
-      <c r="X5" s="258"/>
-      <c r="Y5" s="258"/>
-      <c r="Z5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="P5" s="272"/>
+      <c r="Q5" s="272"/>
+      <c r="R5" s="272"/>
+      <c r="S5" s="272"/>
+      <c r="T5" s="272"/>
+      <c r="U5" s="272"/>
+      <c r="V5" s="272"/>
+      <c r="W5" s="272"/>
+      <c r="X5" s="272"/>
+      <c r="Y5" s="272"/>
+      <c r="Z5" s="272"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23992,7 +23992,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>806165.34550930583</v>
+        <v>805670.85248683556</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24046,23 +24046,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10692.433874512461</v>
+        <v>10692.041421400718</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14291.017770102695</v>
+        <v>14289.968719618586</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19100.720313288199</v>
+        <v>19098.617182585313</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25529.148613173871</v>
+        <v>25525.4007509597</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>34121.091677370387</v>
+        <v>34114.830265889257</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24081,15 +24081,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>536434.9244645827</v>
+        <v>536007.50270524004</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="260" t="s">
+      <c r="B14" s="274" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="261"/>
+      <c r="C14" s="275"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.41820393924748</v>
+        <v>10.41109956413935</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24116,20 +24116,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="262" t="s">
+      <c r="E17" s="273" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="262"/>
-      <c r="G17" s="262"/>
-      <c r="H17" s="262"/>
-      <c r="I17" s="262"/>
+      <c r="F17" s="273"/>
+      <c r="G17" s="273"/>
+      <c r="H17" s="273"/>
+      <c r="I17" s="273"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="260" t="s">
+      <c r="B19" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="261"/>
+      <c r="C19" s="275"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4879283439002945E-2</v>
+        <v>8.4919104108776997E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>643676.2699999999</v>
+        <v>670987.51</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24190,15 +24190,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>637177.2699999999</v>
+        <v>664488.51</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="260" t="s">
+      <c r="B28" s="274" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="261"/>
+      <c r="C28" s="275"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>103734.41224844762</v>
+        <v>103720.85834045356</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24215,7 +24215,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>536434.9244645827</v>
+        <v>536007.50270524004</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>640169.33671303035</v>
+        <v>639728.36104569363</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>646668.33671303035</v>
+        <v>646227.36104569363</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24269,21 +24269,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.41820393924748</v>
+        <v>10.41109956413935</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31242,7 +31242,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31313,7 +31313,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32391,7 +32391,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-580.56706267922971</v>
+        <v>-605.20057353543632</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32428,7 +32428,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.2639045683969647</v>
+        <v>1.3175321489268266</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.7310058867664735</v>
+        <v>1.804452616773923</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32550,7 +32550,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>671208.62</v>
+        <v>699688.06</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32611,7 +32611,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>664709.62</v>
+        <v>693189.06</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32648,7 +32648,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.3090169025567504</v>
+        <v>1.3651016457493508</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32685,7 +32685,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>53.011374112768166</v>
+        <v>55.282642953983576</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32820,7 +32820,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>82.906203063241108</v>
+        <v>86.423920454545467</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32857,7 +32857,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-110.52171451530327</v>
+        <v>-115.25701011285415</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32894,7 +32894,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.2061823639869226E-2</v>
+        <v>1.1570870596248275E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32931,7 +32931,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.7224538977205326E-3</v>
+        <v>-1.65234476589842E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33545,7 +33545,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.6825335765205155E-3</v>
+        <v>9.2884249018055261E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35141,15 +35141,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="261" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="263"/>
-      <c r="E4" s="263" t="s">
+      <c r="C4" s="261"/>
+      <c r="E4" s="261" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="263"/>
-      <c r="G4" s="263"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35157,7 +35157,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35173,7 +35173,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>671208.62</v>
+        <v>699688.06</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>664709.62</v>
+        <v>693189.06</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-580.56706267922971</v>
+        <v>-605.20057353543632</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35233,7 +35233,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2639045683969647</v>
+        <v>1.3175321489268266</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35253,7 +35253,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.7310058867664735</v>
+        <v>1.804452616773923</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35273,7 +35273,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.3090169025567504</v>
+        <v>1.3651016457493508</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35282,18 +35282,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>53.011374112768166</v>
+        <v>55.282642953983576</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="263" t="s">
+      <c r="B15" s="261" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="263"/>
-      <c r="E15" s="263" t="s">
+      <c r="C15" s="261"/>
+      <c r="E15" s="261" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="263"/>
+      <c r="F15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35344,14 +35344,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="263" t="s">
+      <c r="B21" s="261" t="s">
         <v>257</v>
       </c>
-      <c r="C21" s="263"/>
-      <c r="E21" s="263" t="s">
+      <c r="C21" s="261"/>
+      <c r="E21" s="261" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="263"/>
+      <c r="F21" s="261"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35420,14 +35420,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="263" t="s">
+      <c r="B29" s="261" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="263"/>
-      <c r="E29" s="263" t="s">
+      <c r="C29" s="261"/>
+      <c r="E29" s="261" t="s">
         <v>268</v>
       </c>
-      <c r="F29" s="263"/>
+      <c r="F29" s="261"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35503,14 +35503,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="263" t="s">
+      <c r="B37" s="261" t="s">
         <v>280</v>
       </c>
-      <c r="C37" s="263"/>
-      <c r="E37" s="263" t="s">
+      <c r="C37" s="261"/>
+      <c r="E37" s="261" t="s">
         <v>283</v>
       </c>
-      <c r="F37" s="263"/>
+      <c r="F37" s="261"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35518,7 +35518,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7224538977205326E-3</v>
+        <v>-1.65234476589842E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35534,7 +35534,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.2061823639869226E-2</v>
+        <v>1.1570870596248275E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35579,14 +35579,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="263" t="s">
+      <c r="B45" s="261" t="s">
         <v>291</v>
       </c>
-      <c r="C45" s="263"/>
-      <c r="E45" s="263" t="s">
+      <c r="C45" s="261"/>
+      <c r="E45" s="261" t="s">
         <v>297</v>
       </c>
-      <c r="F45" s="263"/>
+      <c r="F45" s="261"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35619,18 +35619,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>9.6825335765205155E-3</v>
+        <v>9.2884249018055261E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="263" t="s">
+      <c r="B51" s="261" t="s">
         <v>294</v>
       </c>
-      <c r="C51" s="263"/>
-      <c r="E51" s="263" t="s">
+      <c r="C51" s="261"/>
+      <c r="E51" s="261" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="263"/>
+      <c r="F51" s="261"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35798,7 +35798,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35827,7 +35827,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>671208.62</v>
+        <v>699688.06</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35856,7 +35856,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>664709.62</v>
+        <v>693189.06</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-580.56706267922971</v>
+        <v>-605.20057353543632</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35914,7 +35914,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.2639045683969647</v>
+        <v>1.3175321489268266</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35943,7 +35943,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.7310058867664735</v>
+        <v>1.804452616773923</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35972,7 +35972,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.3090169025567504</v>
+        <v>1.3651016457493508</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>53.011374112768166</v>
+        <v>55.282642953983576</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7224538977205326E-3</v>
+        <v>-1.65234476589842E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.2061823639869226E-2</v>
+        <v>1.1570870596248275E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37126,7 +37126,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.6825335765205155E-3</v>
+        <v>9.2884249018055261E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37615,14 +37615,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="269" t="s">
+      <c r="C3" s="264" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="270"/>
-      <c r="F3" s="271" t="s">
+      <c r="D3" s="265"/>
+      <c r="F3" s="266" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="270"/>
+      <c r="G3" s="265"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37689,19 +37689,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="272">
+      <c r="C7" s="262">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="273"/>
-      <c r="F7" s="272">
+      <c r="D7" s="263"/>
+      <c r="F7" s="262">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="273"/>
+      <c r="G7" s="263"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37728,19 +37728,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="272">
+      <c r="C9" s="262">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="273"/>
-      <c r="F9" s="272">
+      <c r="D9" s="263"/>
+      <c r="F9" s="262">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="273"/>
+      <c r="G9" s="263"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -37767,19 +37767,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="272">
+      <c r="C11" s="262">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="273"/>
-      <c r="F11" s="272">
+      <c r="D11" s="263"/>
+      <c r="F11" s="262">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="273"/>
+      <c r="G11" s="263"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -37806,19 +37806,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="272">
+      <c r="C13" s="262">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="273"/>
-      <c r="F13" s="272">
+      <c r="D13" s="263"/>
+      <c r="F13" s="262">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="273"/>
+      <c r="G13" s="263"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -37845,19 +37845,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="272">
+      <c r="C15" s="262">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="273"/>
-      <c r="F15" s="272">
+      <c r="D15" s="263"/>
+      <c r="F15" s="262">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="273"/>
+      <c r="G15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -37884,19 +37884,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="272">
+      <c r="C17" s="262">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="273"/>
-      <c r="F17" s="272">
+      <c r="D17" s="263"/>
+      <c r="F17" s="262">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="273"/>
+      <c r="G17" s="263"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -37923,22 +37923,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="272">
+      <c r="C19" s="262">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="273"/>
-      <c r="F19" s="272">
+      <c r="D19" s="263"/>
+      <c r="F19" s="262">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="273"/>
+      <c r="G19" s="263"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -37965,22 +37965,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="272">
+      <c r="C21" s="262">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="273"/>
-      <c r="F21" s="272">
+      <c r="D21" s="263"/>
+      <c r="F21" s="262">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="273"/>
+      <c r="G21" s="263"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38029,22 +38029,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="272">
+      <c r="C25" s="262">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="273"/>
-      <c r="F25" s="272">
+      <c r="D25" s="263"/>
+      <c r="F25" s="262">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="273"/>
+      <c r="G25" s="263"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38072,22 +38072,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="272">
+      <c r="C27" s="262">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="273"/>
-      <c r="F27" s="272">
+      <c r="D27" s="263"/>
+      <c r="F27" s="262">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="273"/>
+      <c r="G27" s="263"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38115,22 +38115,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="272">
+      <c r="C29" s="262">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="273"/>
-      <c r="F29" s="272">
+      <c r="D29" s="263"/>
+      <c r="F29" s="262">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="273"/>
+      <c r="G29" s="263"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38179,22 +38179,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="272">
+      <c r="C33" s="262">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="273"/>
-      <c r="F33" s="272">
+      <c r="D33" s="263"/>
+      <c r="F33" s="262">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="273"/>
+      <c r="G33" s="263"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38222,25 +38222,43 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="272">
+      <c r="C35" s="262">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="273"/>
-      <c r="F35" s="272">
+      <c r="D35" s="263"/>
+      <c r="F35" s="262">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="273"/>
+      <c r="G35" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38251,24 +38269,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9DDBF9-62CD-354D-98C3-A8876F9CE944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA857D3A-213F-3146-A575-8FE0D4BD3715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="449">
   <si>
     <t>Ticker</t>
   </si>
@@ -1520,6 +1520,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1560,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1709,6 +1733,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2132,11 +2164,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2473,6 +2506,14 @@
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2485,12 +2526,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2498,6 +2533,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2518,17 +2559,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12936,10 +12978,10 @@
     <v>24.07</v>
     <v>7.77</v>
     <v>0.79259999999999997</v>
-    <v>0.15</v>
-    <v>1.4071E-2</v>
-    <v>1.12E-2</v>
-    <v>1.036E-3</v>
+    <v>0.01</v>
+    <v>9.2509999999999999E-4</v>
+    <v>-0.02</v>
+    <v>-1.8479999999999998E-3</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12947,25 +12989,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>10.82</v>
+    <v>11.02</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46304.979243541406</v>
+    <v>46307.851047742966</v>
     <v>0</v>
-    <v>10.56</v>
-    <v>670986861</v>
+    <v>10.49</v>
+    <v>671607570</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.7</v>
-    <v>63.110500000000002</v>
-    <v>10.66</v>
+    <v>10.49</v>
+    <v>64.061599999999999</v>
     <v>10.81</v>
-    <v>10.821199999999999</v>
+    <v>10.82</v>
+    <v>10.8</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>537070</v>
-    <v>726273</v>
+    <v>533230</v>
+    <v>697289</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -13794,7 +13836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I68"/>
+  <dimension ref="B1:K68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13806,25 +13848,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="258" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="262" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="259"/>
-      <c r="E2" s="258" t="s">
+      <c r="C2" s="263"/>
+      <c r="E2" s="262" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="259"/>
-      <c r="H2" s="258" t="s">
+      <c r="F2" s="263"/>
+      <c r="H2" s="262" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="259"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="263"/>
+      <c r="K2" s="136" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
         <v>11</v>
       </c>
@@ -13837,7 +13884,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>699688.06</v>
+        <v>700335.32000000007</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13845,10 +13892,13 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.567898156985528</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+        <v>10.567410456732686</v>
+      </c>
+      <c r="K3" s="260" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="185" t="s">
         <v>0</v>
       </c>
@@ -13861,7 +13911,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>693189.06</v>
+        <v>693836.32000000007</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13869,16 +13919,19 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.563074594846377</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+        <v>17.562863851780918</v>
+      </c>
+      <c r="K4" s="260" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="185" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13895,21 +13948,24 @@
         <f ca="1">'AVG target price'!C7</f>
         <v>16.729077459880621</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="260" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.821199999999999</v>
+        <v>10.8</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-605.20057353543632</v>
+        <v>-605.76042605489556</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13917,23 +13973,26 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.079725941136617</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+        <v>14.079558397473312</v>
+      </c>
+      <c r="K6" s="261" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="185" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.3175321489268266</v>
+        <v>1.3187509575752323</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13941,23 +14000,23 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.48481855246839</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+        <v>25.484509566408331</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>1.12E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.1570870596248275E-2</v>
+        <v>1.1560176630817362E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -13965,23 +14024,23 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>16.884918941063507</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+        <v>16.884683946455176</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="185" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.4071E-2</v>
+        <v>9.2509999999999999E-4</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.65234476589842E-3</v>
+        <v>-1.6508176450426913E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -13989,16 +14048,16 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.5619721499596213</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.56050683423800152</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.036E-3</v>
+        <v>-1.8479999999999998E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14008,7 +14067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="185" t="s">
         <v>7</v>
       </c>
@@ -14031,7 +14090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="185" t="s">
         <v>8</v>
       </c>
@@ -14047,7 +14106,7 @@
         <v>-1.8099561499095023E-3</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="185" t="s">
         <v>9</v>
       </c>
@@ -14070,13 +14129,13 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="186" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>726273</v>
+        <v>697289</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14086,16 +14145,16 @@
         <v>-1.4540196296708597E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="185" t="s">
         <v>302</v>
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>9.2884249018055261E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>9.2798404055931365E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="186" t="s">
         <v>307</v>
       </c>
@@ -14103,12 +14162,16 @@
         <f>Statement!AC175</f>
         <v>0.10470267918995989</v>
       </c>
+      <c r="H16" s="262" t="s">
+        <v>441</v>
+      </c>
+      <c r="I16" s="263"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="260" t="s">
+      <c r="B17" s="264" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="260"/>
+      <c r="C17" s="264"/>
       <c r="E17" s="184" t="s">
         <v>308</v>
       </c>
@@ -14116,6 +14179,13 @@
         <f>Statement!AC171</f>
         <v>5.0026264561381824E-2</v>
       </c>
+      <c r="H17" s="185" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="258">
+        <f ca="1">DCF!C15</f>
+        <v>8.4921795094382302E-2</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="184" t="s">
@@ -14131,7 +14201,13 @@
         <f>Statement!AC144</f>
         <v>37.184518492589405</v>
       </c>
-      <c r="I18" s="50"/>
+      <c r="H18" s="186" t="s">
+        <v>442</v>
+      </c>
+      <c r="I18" s="259">
+        <f ca="1">Multiples!C54</f>
+        <v>8.8106999999999991E-2</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="184" t="s">
@@ -14181,14 +14257,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="260" t="s">
+      <c r="B25" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="260"/>
-      <c r="E25" s="258" t="s">
+      <c r="C25" s="264"/>
+      <c r="E25" s="262" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="259"/>
+      <c r="F25" s="263"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14443,13 +14519,14 @@
       <c r="H68" s="136"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14462,6 +14539,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{E408AF42-F5FB-7443-88AB-0DF109BF0CF5}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{07364BB6-8036-5D4B-B404-C4AC7ACB15AC}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{E62C4688-86EB-9642-B23D-66F9D6FE8A6B}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{135A1967-42BC-E545-BC4E-C3CE29C5586D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14471,18 +14554,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="21" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="260" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="260" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="260" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="260" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="261" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>121</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{BBA00E0F-1BD9-9C42-98C2-07BCDFC4AC57}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{13C161E0-B9F1-F947-94E5-CC9E17A8DEF7}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{2E444A28-14E6-8546-95CF-0DC745980C0A}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{667C2DD7-2AD6-8A40-83E8-5E681275FB39}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{696FB99B-A30D-C948-ADFD-0194F4E14885}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14519,36 +14641,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="261" t="s">
+      <c r="S2" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261"/>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
-      <c r="AA2" s="261" t="s">
+      <c r="T2" s="265"/>
+      <c r="U2" s="265"/>
+      <c r="V2" s="265"/>
+      <c r="W2" s="265"/>
+      <c r="X2" s="265"/>
+      <c r="Y2" s="265"/>
+      <c r="Z2" s="265"/>
+      <c r="AA2" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="261"/>
-      <c r="AC2" s="261"/>
+      <c r="AB2" s="265"/>
+      <c r="AC2" s="265"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -14559,32 +14681,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="268" t="s">
+      <c r="S4" s="272" t="s">
         <v>126</v>
       </c>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
-      <c r="AA4" s="269"/>
-      <c r="AB4" s="269"/>
-      <c r="AC4" s="269"/>
+      <c r="T4" s="273"/>
+      <c r="U4" s="273"/>
+      <c r="V4" s="273"/>
+      <c r="W4" s="273"/>
+      <c r="X4" s="273"/>
+      <c r="Y4" s="273"/>
+      <c r="Z4" s="273"/>
+      <c r="AA4" s="273"/>
+      <c r="AB4" s="273"/>
+      <c r="AC4" s="273"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15075,33 +15197,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="271" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="268" t="s">
+      <c r="S11" s="272" t="s">
         <v>132</v>
       </c>
-      <c r="T11" s="269"/>
-      <c r="U11" s="269"/>
-      <c r="V11" s="269"/>
-      <c r="W11" s="269"/>
-      <c r="X11" s="269"/>
-      <c r="Y11" s="269"/>
-      <c r="Z11" s="269"/>
-      <c r="AA11" s="269"/>
-      <c r="AB11" s="269"/>
-      <c r="AC11" s="269"/>
+      <c r="T11" s="273"/>
+      <c r="U11" s="273"/>
+      <c r="V11" s="273"/>
+      <c r="W11" s="273"/>
+      <c r="X11" s="273"/>
+      <c r="Y11" s="273"/>
+      <c r="Z11" s="273"/>
+      <c r="AA11" s="273"/>
+      <c r="AB11" s="273"/>
+      <c r="AC11" s="273"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15542,33 +15664,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="267" t="s">
+      <c r="C19" s="271" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="267"/>
-      <c r="E19" s="267"/>
-      <c r="F19" s="267"/>
-      <c r="G19" s="267"/>
-      <c r="H19" s="267"/>
-      <c r="I19" s="267"/>
-      <c r="J19" s="267"/>
-      <c r="K19" s="267"/>
-      <c r="L19" s="267"/>
+      <c r="D19" s="271"/>
+      <c r="E19" s="271"/>
+      <c r="F19" s="271"/>
+      <c r="G19" s="271"/>
+      <c r="H19" s="271"/>
+      <c r="I19" s="271"/>
+      <c r="J19" s="271"/>
+      <c r="K19" s="271"/>
+      <c r="L19" s="271"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="268" t="s">
+      <c r="S19" s="272" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="269"/>
-      <c r="U19" s="269"/>
-      <c r="V19" s="269"/>
-      <c r="W19" s="269"/>
-      <c r="X19" s="269"/>
-      <c r="Y19" s="269"/>
-      <c r="Z19" s="269"/>
-      <c r="AA19" s="269"/>
-      <c r="AB19" s="269"/>
-      <c r="AC19" s="269"/>
+      <c r="T19" s="273"/>
+      <c r="U19" s="273"/>
+      <c r="V19" s="273"/>
+      <c r="W19" s="273"/>
+      <c r="X19" s="273"/>
+      <c r="Y19" s="273"/>
+      <c r="Z19" s="273"/>
+      <c r="AA19" s="273"/>
+      <c r="AB19" s="273"/>
+      <c r="AC19" s="273"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16805,35 +16927,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="P2" s="261" t="s">
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
+      <c r="P2" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="261"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261" t="s">
+      <c r="Q2" s="265"/>
+      <c r="R2" s="265"/>
+      <c r="S2" s="265"/>
+      <c r="T2" s="265"/>
+      <c r="U2" s="265"/>
+      <c r="V2" s="265"/>
+      <c r="W2" s="265"/>
+      <c r="X2" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
+      <c r="Y2" s="265"/>
+      <c r="Z2" s="265"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -16842,31 +16964,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="P4" s="269" t="s">
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="P4" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="Q4" s="269"/>
-      <c r="R4" s="269"/>
-      <c r="S4" s="269"/>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
+      <c r="Q4" s="273"/>
+      <c r="R4" s="273"/>
+      <c r="S4" s="273"/>
+      <c r="T4" s="273"/>
+      <c r="U4" s="273"/>
+      <c r="V4" s="273"/>
+      <c r="W4" s="273"/>
+      <c r="X4" s="273"/>
+      <c r="Y4" s="273"/>
+      <c r="Z4" s="273"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17061,32 +17183,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="271" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="269" t="s">
+      <c r="P9" s="273" t="s">
         <v>138</v>
       </c>
-      <c r="Q9" s="269"/>
-      <c r="R9" s="269"/>
-      <c r="S9" s="269"/>
-      <c r="T9" s="269"/>
-      <c r="U9" s="269"/>
-      <c r="V9" s="269"/>
-      <c r="W9" s="269"/>
-      <c r="X9" s="269"/>
-      <c r="Y9" s="269"/>
-      <c r="Z9" s="269"/>
+      <c r="Q9" s="273"/>
+      <c r="R9" s="273"/>
+      <c r="S9" s="273"/>
+      <c r="T9" s="273"/>
+      <c r="U9" s="273"/>
+      <c r="V9" s="273"/>
+      <c r="W9" s="273"/>
+      <c r="X9" s="273"/>
+      <c r="Y9" s="273"/>
+      <c r="Z9" s="273"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -17844,31 +17966,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="267" t="s">
+      <c r="C20" s="271" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="267"/>
-      <c r="E20" s="267"/>
-      <c r="F20" s="267"/>
-      <c r="G20" s="267"/>
-      <c r="H20" s="267"/>
-      <c r="I20" s="267"/>
-      <c r="J20" s="267"/>
-      <c r="K20" s="267"/>
-      <c r="L20" s="267"/>
-      <c r="P20" s="269" t="s">
+      <c r="D20" s="271"/>
+      <c r="E20" s="271"/>
+      <c r="F20" s="271"/>
+      <c r="G20" s="271"/>
+      <c r="H20" s="271"/>
+      <c r="I20" s="271"/>
+      <c r="J20" s="271"/>
+      <c r="K20" s="271"/>
+      <c r="L20" s="271"/>
+      <c r="P20" s="273" t="s">
         <v>140</v>
       </c>
-      <c r="Q20" s="269"/>
-      <c r="R20" s="269"/>
-      <c r="S20" s="269"/>
-      <c r="T20" s="269"/>
-      <c r="U20" s="269"/>
-      <c r="V20" s="269"/>
-      <c r="W20" s="269"/>
-      <c r="X20" s="269"/>
-      <c r="Y20" s="269"/>
-      <c r="Z20" s="269"/>
+      <c r="Q20" s="273"/>
+      <c r="R20" s="273"/>
+      <c r="S20" s="273"/>
+      <c r="T20" s="273"/>
+      <c r="U20" s="273"/>
+      <c r="V20" s="273"/>
+      <c r="W20" s="273"/>
+      <c r="X20" s="273"/>
+      <c r="Y20" s="273"/>
+      <c r="Z20" s="273"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18592,60 +18714,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="P3" s="276"/>
+      <c r="Q3" s="276"/>
+      <c r="R3" s="276"/>
+      <c r="S3" s="276"/>
+      <c r="T3" s="276"/>
+      <c r="U3" s="276"/>
+      <c r="V3" s="276"/>
+      <c r="W3" s="276"/>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="276"/>
+      <c r="Z3" s="276"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="276"/>
+      <c r="T5" s="276"/>
+      <c r="U5" s="276"/>
+      <c r="V5" s="276"/>
+      <c r="W5" s="276"/>
+      <c r="X5" s="276"/>
+      <c r="Y5" s="276"/>
+      <c r="Z5" s="276"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18831,30 +18953,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="271" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="272"/>
-      <c r="Q11" s="272"/>
-      <c r="R11" s="272"/>
-      <c r="S11" s="272"/>
-      <c r="T11" s="272"/>
-      <c r="U11" s="272"/>
-      <c r="V11" s="272"/>
-      <c r="W11" s="272"/>
-      <c r="X11" s="272"/>
-      <c r="Y11" s="272"/>
-      <c r="Z11" s="272"/>
+      <c r="P11" s="276"/>
+      <c r="Q11" s="276"/>
+      <c r="R11" s="276"/>
+      <c r="S11" s="276"/>
+      <c r="T11" s="276"/>
+      <c r="U11" s="276"/>
+      <c r="V11" s="276"/>
+      <c r="W11" s="276"/>
+      <c r="X11" s="276"/>
+      <c r="Y11" s="276"/>
+      <c r="Z11" s="276"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19096,18 +19218,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="271" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19320,23 +19442,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="272"/>
-      <c r="C25" s="272"/>
+      <c r="B25" s="276"/>
+      <c r="C25" s="276"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="267" t="s">
+      <c r="C26" s="271" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="267"/>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="267"/>
-      <c r="J26" s="267"/>
-      <c r="K26" s="267"/>
-      <c r="L26" s="267"/>
+      <c r="D26" s="271"/>
+      <c r="E26" s="271"/>
+      <c r="F26" s="271"/>
+      <c r="G26" s="271"/>
+      <c r="H26" s="271"/>
+      <c r="I26" s="271"/>
+      <c r="J26" s="271"/>
+      <c r="K26" s="271"/>
+      <c r="L26" s="271"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19528,18 +19650,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="267" t="s">
+      <c r="C33" s="271" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="E33" s="267"/>
-      <c r="F33" s="267"/>
-      <c r="G33" s="267"/>
-      <c r="H33" s="267"/>
-      <c r="I33" s="267"/>
-      <c r="J33" s="267"/>
-      <c r="K33" s="267"/>
-      <c r="L33" s="267"/>
+      <c r="D33" s="271"/>
+      <c r="E33" s="271"/>
+      <c r="F33" s="271"/>
+      <c r="G33" s="271"/>
+      <c r="H33" s="271"/>
+      <c r="I33" s="271"/>
+      <c r="J33" s="271"/>
+      <c r="K33" s="271"/>
+      <c r="L33" s="271"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19723,18 +19845,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="267" t="s">
+      <c r="C40" s="271" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="267"/>
-      <c r="E40" s="267"/>
-      <c r="F40" s="267"/>
-      <c r="G40" s="267"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="267"/>
-      <c r="J40" s="267"/>
-      <c r="K40" s="267"/>
-      <c r="L40" s="267"/>
+      <c r="D40" s="271"/>
+      <c r="E40" s="271"/>
+      <c r="F40" s="271"/>
+      <c r="G40" s="271"/>
+      <c r="H40" s="271"/>
+      <c r="I40" s="271"/>
+      <c r="J40" s="271"/>
+      <c r="K40" s="271"/>
+      <c r="L40" s="271"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20003,12 +20125,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20016,6 +20132,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20053,60 +20175,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="S2" s="272"/>
-      <c r="T2" s="272"/>
-      <c r="U2" s="272"/>
-      <c r="V2" s="272"/>
-      <c r="W2" s="272"/>
-      <c r="X2" s="272"/>
-      <c r="Y2" s="272"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="272"/>
-      <c r="AB2" s="272"/>
-      <c r="AC2" s="272"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
+      <c r="S2" s="276"/>
+      <c r="T2" s="276"/>
+      <c r="U2" s="276"/>
+      <c r="V2" s="276"/>
+      <c r="W2" s="276"/>
+      <c r="X2" s="276"/>
+      <c r="Y2" s="276"/>
+      <c r="Z2" s="276"/>
+      <c r="AA2" s="276"/>
+      <c r="AB2" s="276"/>
+      <c r="AC2" s="276"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="271" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="S4" s="272"/>
-      <c r="T4" s="272"/>
-      <c r="U4" s="272"/>
-      <c r="V4" s="272"/>
-      <c r="W4" s="272"/>
-      <c r="X4" s="272"/>
-      <c r="Y4" s="272"/>
-      <c r="Z4" s="272"/>
-      <c r="AA4" s="272"/>
-      <c r="AB4" s="272"/>
-      <c r="AC4" s="272"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="S4" s="276"/>
+      <c r="T4" s="276"/>
+      <c r="U4" s="276"/>
+      <c r="V4" s="276"/>
+      <c r="W4" s="276"/>
+      <c r="X4" s="276"/>
+      <c r="Y4" s="276"/>
+      <c r="Z4" s="276"/>
+      <c r="AA4" s="276"/>
+      <c r="AB4" s="276"/>
+      <c r="AC4" s="276"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20469,18 +20591,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="267" t="s">
+      <c r="C13" s="271" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="E13" s="267"/>
-      <c r="F13" s="267"/>
-      <c r="G13" s="267"/>
-      <c r="H13" s="267"/>
-      <c r="I13" s="267"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
+      <c r="D13" s="271"/>
+      <c r="E13" s="271"/>
+      <c r="F13" s="271"/>
+      <c r="G13" s="271"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="271"/>
+      <c r="L13" s="271"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20573,18 +20695,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="271" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20776,18 +20898,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="267" t="s">
+      <c r="C25" s="271" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="E25" s="267"/>
-      <c r="F25" s="267"/>
-      <c r="G25" s="267"/>
-      <c r="H25" s="267"/>
-      <c r="I25" s="267"/>
-      <c r="J25" s="267"/>
-      <c r="K25" s="267"/>
-      <c r="L25" s="267"/>
+      <c r="D25" s="271"/>
+      <c r="E25" s="271"/>
+      <c r="F25" s="271"/>
+      <c r="G25" s="271"/>
+      <c r="H25" s="271"/>
+      <c r="I25" s="271"/>
+      <c r="J25" s="271"/>
+      <c r="K25" s="271"/>
+      <c r="L25" s="271"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20925,18 +21047,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="267" t="s">
+      <c r="C31" s="271" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="267"/>
-      <c r="E31" s="267"/>
-      <c r="F31" s="267"/>
-      <c r="G31" s="267"/>
-      <c r="H31" s="267"/>
-      <c r="I31" s="267"/>
-      <c r="J31" s="267"/>
-      <c r="K31" s="267"/>
-      <c r="L31" s="267"/>
+      <c r="D31" s="271"/>
+      <c r="E31" s="271"/>
+      <c r="F31" s="271"/>
+      <c r="G31" s="271"/>
+      <c r="H31" s="271"/>
+      <c r="I31" s="271"/>
+      <c r="J31" s="271"/>
+      <c r="K31" s="271"/>
+      <c r="L31" s="271"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21075,16 +21197,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21098,18 +21220,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="260" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="260" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="260" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="260" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="261" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>176</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{BF5FA49C-A360-2C46-9AC4-087B9A82BD62}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{E1B31D47-80A1-5640-A51B-BFBFEC3F7165}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{A545C11B-5F75-214F-AA44-B65738F09815}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{0E82C950-DB55-C84F-9FE3-AE3ABCC4D70E}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{ED292B1E-744B-4542-9A0B-87AC248E4C0B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21147,10 +21308,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="265" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="265"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21167,7 +21328,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21176,7 +21337,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>699688.06</v>
+        <v>700335.32000000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21235,10 +21396,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="265" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="261"/>
+      <c r="C15" s="265"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21246,7 +21407,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.6728946628479089E-2</v>
+        <v>8.6655736475166084E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21255,7 +21416,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.91327105337152092</v>
+        <v>0.91334426352483389</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21282,7 +21443,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.4919104108776997E-2</v>
+        <v>8.4921795094382302E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21327,60 +21488,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="P3" s="276"/>
+      <c r="Q3" s="276"/>
+      <c r="R3" s="276"/>
+      <c r="S3" s="276"/>
+      <c r="T3" s="276"/>
+      <c r="U3" s="276"/>
+      <c r="V3" s="276"/>
+      <c r="W3" s="276"/>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="276"/>
+      <c r="Z3" s="276"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="271" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="276"/>
+      <c r="T5" s="276"/>
+      <c r="U5" s="276"/>
+      <c r="V5" s="276"/>
+      <c r="W5" s="276"/>
+      <c r="X5" s="276"/>
+      <c r="Y5" s="276"/>
+      <c r="Z5" s="276"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21533,7 +21694,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>853698.16346860211</v>
+        <v>853662.77797955589</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21587,23 +21748,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13219.62921467751</v>
+        <v>13219.596425372247</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8755.3444305812991</v>
+        <v>8755.3009980007737</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21387.59328687143</v>
+        <v>21387.434141125133</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30047.984201951531</v>
+        <v>30047.686085008943</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36148.469136170737</v>
+        <v>36148.020834145675</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21622,14 +21783,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>567959.75583879277</v>
+        <v>567929.17073882709</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="261" t="s">
+      <c r="B13" s="265" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="261"/>
+      <c r="C13" s="265"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21645,14 +21806,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4919104108776997E-2</v>
+        <v>8.4921795094382302E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="261" t="s">
+      <c r="B18" s="265" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="261"/>
+      <c r="C18" s="265"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21660,7 +21821,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109559.02027025251</v>
+        <v>109558.03848365277</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21669,7 +21830,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>567959.75583879277</v>
+        <v>567929.17073882709</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21678,7 +21839,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>677518.77610904525</v>
+        <v>677487.20922247984</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21705,7 +21866,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>684017.77610904525</v>
+        <v>683986.20922247984</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21723,7 +21884,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.567898156985528</v>
+        <v>10.567410456732686</v>
       </c>
     </row>
   </sheetData>
@@ -21766,37 +21927,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="271" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21992,23 +22153,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13219.62921467751</v>
+        <v>13219.596425372247</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8755.3444305812991</v>
+        <v>8755.3009980007737</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21387.59328687143</v>
+        <v>21387.434141125133</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>30047.984201951531</v>
+        <v>30047.686085008943</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36148.469136170737</v>
+        <v>36148.020834145675</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22016,18 +22177,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="271" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22221,18 +22382,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="267" t="s">
+      <c r="C17" s="271" t="s">
         <v>208</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="E17" s="267"/>
-      <c r="F17" s="267"/>
-      <c r="G17" s="267"/>
-      <c r="H17" s="267"/>
-      <c r="I17" s="267"/>
-      <c r="J17" s="267"/>
-      <c r="K17" s="267"/>
-      <c r="L17" s="267"/>
+      <c r="D17" s="271"/>
+      <c r="E17" s="271"/>
+      <c r="F17" s="271"/>
+      <c r="G17" s="271"/>
+      <c r="H17" s="271"/>
+      <c r="I17" s="271"/>
+      <c r="J17" s="271"/>
+      <c r="K17" s="271"/>
+      <c r="L17" s="271"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22366,18 +22527,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="267" t="s">
+      <c r="C22" s="271" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="267"/>
-      <c r="E22" s="267"/>
-      <c r="F22" s="267"/>
-      <c r="G22" s="267"/>
-      <c r="H22" s="267"/>
-      <c r="I22" s="267"/>
-      <c r="J22" s="267"/>
-      <c r="K22" s="267"/>
-      <c r="L22" s="267"/>
+      <c r="D22" s="271"/>
+      <c r="E22" s="271"/>
+      <c r="F22" s="271"/>
+      <c r="G22" s="271"/>
+      <c r="H22" s="271"/>
+      <c r="I22" s="271"/>
+      <c r="J22" s="271"/>
+      <c r="K22" s="271"/>
+      <c r="L22" s="271"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22461,18 +22622,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="267" t="s">
+      <c r="C27" s="271" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="267"/>
-      <c r="E27" s="267"/>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="267"/>
-      <c r="K27" s="267"/>
-      <c r="L27" s="267"/>
+      <c r="D27" s="271"/>
+      <c r="E27" s="271"/>
+      <c r="F27" s="271"/>
+      <c r="G27" s="271"/>
+      <c r="H27" s="271"/>
+      <c r="I27" s="271"/>
+      <c r="J27" s="271"/>
+      <c r="K27" s="271"/>
+      <c r="L27" s="271"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22773,10 +22934,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="261" t="s">
+      <c r="B39" s="265" t="s">
         <v>217</v>
       </c>
-      <c r="C39" s="261"/>
+      <c r="C39" s="265"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22794,7 +22955,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4919104108776997E-2</v>
+        <v>8.4921795094382302E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22820,7 +22981,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1056878.0150919447</v>
+        <v>1056864.9080208645</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22829,7 +22990,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1130288.5662260265</v>
+        <v>1130274.9256703716</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22856,7 +23017,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1136787.5662260265</v>
+        <v>1136773.9256703716</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -22874,14 +23035,14 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.563074594846377</v>
+        <v>17.562863851780918</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="261" t="s">
+      <c r="B52" s="265" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="261"/>
+      <c r="C52" s="265"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22937,10 +23098,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="261" t="s">
+      <c r="B60" s="265" t="s">
         <v>335</v>
       </c>
-      <c r="C60" s="261"/>
+      <c r="C60" s="265"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -22957,7 +23118,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4919104108776997E-2</v>
+        <v>8.4921795094382302E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -22983,7 +23144,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>831414.79013192689</v>
+        <v>831404.47918535047</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22992,7 +23153,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>904825.34126600868</v>
+        <v>904814.49683485762</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23019,7 +23180,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>911324.34126600868</v>
+        <v>911313.49683485762</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23037,14 +23198,14 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.079725941136617</v>
+        <v>14.079558397473312</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="261" t="s">
+      <c r="B73" s="265" t="s">
         <v>436</v>
       </c>
-      <c r="C73" s="261"/>
+      <c r="C73" s="265"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23061,7 +23222,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4919104108776997E-2</v>
+        <v>8.4921795094382302E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23087,7 +23248,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1569620.8144929872</v>
+        <v>1569601.3485458384</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,7 +23257,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1643031.365627069</v>
+        <v>1643011.3661953455</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23123,7 +23284,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1649530.365627069</v>
+        <v>1649510.3661953455</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23141,22 +23302,22 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.48481855246839</v>
+        <v>25.484509566408331</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23194,10 +23355,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="265" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="265"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23206,7 +23367,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.567898156985528</v>
+        <v>10.567410456732686</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23215,7 +23376,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.563074594846377</v>
+        <v>17.562863851780918</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23233,7 +23394,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.079725941136617</v>
+        <v>14.079558397473312</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23242,7 +23403,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.48481855246839</v>
+        <v>25.484509566408331</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23251,7 +23412,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>16.884918941063507</v>
+        <v>16.884683946455176</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23260,7 +23421,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23269,7 +23430,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.5619721499596213</v>
+        <v>0.56050683423800152</v>
       </c>
     </row>
   </sheetData>
@@ -23285,18 +23446,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="260" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="260" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="260" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="260" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="261" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{863A7BEB-FD2C-B043-8721-5908661C55DE}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{733756E3-5812-AA41-A85C-6AA8941813B1}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{3B1AE0AD-58C8-9247-B3DC-FB2F2F72A726}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{86638A7D-42ED-6B41-9FA7-A6BCAF75C46B}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{CD7B5495-9110-C04A-B821-DDA21F557B53}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23325,37 +23525,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="271" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23468,18 +23668,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="271" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23600,18 +23800,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="267" t="s">
+      <c r="C14" s="271" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="267"/>
-      <c r="E14" s="267"/>
-      <c r="F14" s="267"/>
-      <c r="G14" s="267"/>
-      <c r="H14" s="267"/>
-      <c r="I14" s="267"/>
-      <c r="J14" s="267"/>
-      <c r="K14" s="267"/>
-      <c r="L14" s="267"/>
+      <c r="D14" s="271"/>
+      <c r="E14" s="271"/>
+      <c r="F14" s="271"/>
+      <c r="G14" s="271"/>
+      <c r="H14" s="271"/>
+      <c r="I14" s="271"/>
+      <c r="J14" s="271"/>
+      <c r="K14" s="271"/>
+      <c r="L14" s="271"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23701,10 +23901,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="261" t="s">
+      <c r="B20" s="265" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="261"/>
+      <c r="C20" s="265"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23805,60 +24005,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="265" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="P3" s="276"/>
+      <c r="Q3" s="276"/>
+      <c r="R3" s="276"/>
+      <c r="S3" s="276"/>
+      <c r="T3" s="276"/>
+      <c r="U3" s="276"/>
+      <c r="V3" s="276"/>
+      <c r="W3" s="276"/>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="276"/>
+      <c r="Z3" s="276"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="271" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="276"/>
+      <c r="T5" s="276"/>
+      <c r="U5" s="276"/>
+      <c r="V5" s="276"/>
+      <c r="W5" s="276"/>
+      <c r="X5" s="276"/>
+      <c r="Y5" s="276"/>
+      <c r="Z5" s="276"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23992,7 +24192,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>805670.85248683556</v>
+        <v>805637.45771296183</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24046,23 +24246,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10692.041421400718</v>
+        <v>10692.014901397444</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14289.968719618586</v>
+        <v>14289.897831463124</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19098.617182585313</v>
+        <v>19098.475069181339</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25525.4007509597</v>
+        <v>25525.147504206805</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>34114.830265889257</v>
+        <v>34114.407184418364</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24081,15 +24281,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>536007.50270524004</v>
+        <v>535978.63826038444</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="274" t="s">
+      <c r="B14" s="277" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="275"/>
+      <c r="C14" s="278"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24097,7 +24297,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24106,7 +24306,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.41109956413935</v>
+        <v>10.410619786229503</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24116,20 +24316,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="273" t="s">
+      <c r="E17" s="279" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="273"/>
-      <c r="G17" s="273"/>
-      <c r="H17" s="273"/>
-      <c r="I17" s="273"/>
+      <c r="F17" s="279"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="279"/>
+      <c r="I17" s="279"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="274" t="s">
+      <c r="B19" s="277" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="275"/>
+      <c r="C19" s="278"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24145,7 +24345,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4919104108776997E-2</v>
+        <v>8.4921795094382302E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24163,7 +24363,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>670987.51</v>
+        <v>671608.22</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24190,15 +24390,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>664488.51</v>
+        <v>665109.22</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="274" t="s">
+      <c r="B28" s="277" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="275"/>
+      <c r="C28" s="278"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24206,7 +24406,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>103720.85834045356</v>
+        <v>103719.94249066708</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24215,7 +24415,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>536007.50270524004</v>
+        <v>535978.63826038444</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24224,7 +24424,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>639728.36104569363</v>
+        <v>639698.58075105154</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24251,7 +24451,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>646227.36104569363</v>
+        <v>646197.58075105154</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24269,21 +24469,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.41109956413935</v>
+        <v>10.410619786229503</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31242,7 +31442,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31313,7 +31513,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32391,7 +32591,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-605.20057353543632</v>
+        <v>-605.76042605489556</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32428,7 +32628,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3175321489268266</v>
+        <v>1.3187509575752323</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32489,7 +32689,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.804452616773923</v>
+        <v>1.8061218606377287</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32550,7 +32750,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>699688.06</v>
+        <v>700335.32000000007</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32611,7 +32811,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>693189.06</v>
+        <v>693836.32000000007</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32648,7 +32848,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.3651016457493508</v>
+        <v>1.366376299003728</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32685,7 +32885,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>55.282642953983576</v>
+        <v>55.334262700374836</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32820,7 +33020,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>86.423920454545467</v>
+        <v>86.50386857707511</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32857,7 +33057,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-115.25701011285415</v>
+        <v>-115.36463046734394</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32894,7 +33094,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.1570870596248275E-2</v>
+        <v>1.1560176630817362E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32931,7 +33131,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.65234476589842E-3</v>
+        <v>-1.6508176450426913E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33545,7 +33745,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.2884249018055261E-3</v>
+        <v>9.2798404055931365E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35106,18 +35306,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="260" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="260" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="260" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="260" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="261" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>244</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{CDB7A626-333F-8342-BD4B-A3B9160B7157}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{3AF10922-796E-8E40-8D44-E5A7B05EBBF9}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{966D1CAF-4424-8C4F-BF25-B68FCF9B9AB5}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{06FDE9BB-1407-9A49-A17E-63D96A84C01F}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{980564A1-B3B5-C042-B75F-FABE4DFE62B9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -35141,15 +35380,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="265" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="261"/>
-      <c r="E4" s="261" t="s">
+      <c r="C4" s="265"/>
+      <c r="E4" s="265" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35157,7 +35396,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35173,7 +35412,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>699688.06</v>
+        <v>700335.32000000007</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35193,7 +35432,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>693189.06</v>
+        <v>693836.32000000007</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35213,7 +35452,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-605.20057353543632</v>
+        <v>-605.76042605489556</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35233,7 +35472,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.3175321489268266</v>
+        <v>1.3187509575752323</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35253,7 +35492,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.804452616773923</v>
+        <v>1.8061218606377287</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35273,7 +35512,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.3651016457493508</v>
+        <v>1.366376299003728</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35282,18 +35521,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>55.282642953983576</v>
+        <v>55.334262700374836</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="265" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="261"/>
-      <c r="E15" s="261" t="s">
+      <c r="C15" s="265"/>
+      <c r="E15" s="265" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="261"/>
+      <c r="F15" s="265"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35344,14 +35583,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="261" t="s">
+      <c r="B21" s="265" t="s">
         <v>257</v>
       </c>
-      <c r="C21" s="261"/>
-      <c r="E21" s="261" t="s">
+      <c r="C21" s="265"/>
+      <c r="E21" s="265" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="261"/>
+      <c r="F21" s="265"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35420,14 +35659,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="261" t="s">
+      <c r="B29" s="265" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="261"/>
-      <c r="E29" s="261" t="s">
+      <c r="C29" s="265"/>
+      <c r="E29" s="265" t="s">
         <v>268</v>
       </c>
-      <c r="F29" s="261"/>
+      <c r="F29" s="265"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35503,14 +35742,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="261" t="s">
+      <c r="B37" s="265" t="s">
         <v>280</v>
       </c>
-      <c r="C37" s="261"/>
-      <c r="E37" s="261" t="s">
+      <c r="C37" s="265"/>
+      <c r="E37" s="265" t="s">
         <v>283</v>
       </c>
-      <c r="F37" s="261"/>
+      <c r="F37" s="265"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35518,7 +35757,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.65234476589842E-3</v>
+        <v>-1.6508176450426913E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35534,7 +35773,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.1570870596248275E-2</v>
+        <v>1.1560176630817362E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35579,14 +35818,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="261" t="s">
+      <c r="B45" s="265" t="s">
         <v>291</v>
       </c>
-      <c r="C45" s="261"/>
-      <c r="E45" s="261" t="s">
+      <c r="C45" s="265"/>
+      <c r="E45" s="265" t="s">
         <v>297</v>
       </c>
-      <c r="F45" s="261"/>
+      <c r="F45" s="265"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35619,18 +35858,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>9.2884249018055261E-3</v>
+        <v>9.2798404055931365E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="261" t="s">
+      <c r="B51" s="265" t="s">
         <v>294</v>
       </c>
-      <c r="C51" s="261"/>
-      <c r="E51" s="261" t="s">
+      <c r="C51" s="265"/>
+      <c r="E51" s="265" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="261"/>
+      <c r="F51" s="265"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35798,7 +36037,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35827,7 +36066,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>699688.06</v>
+        <v>700335.32000000007</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35856,7 +36095,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>693189.06</v>
+        <v>693836.32000000007</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35885,7 +36124,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-605.20057353543632</v>
+        <v>-605.76042605489556</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35914,7 +36153,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.3175321489268266</v>
+        <v>1.3187509575752323</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35943,7 +36182,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.804452616773923</v>
+        <v>1.8061218606377287</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35972,7 +36211,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.3651016457493508</v>
+        <v>1.366376299003728</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36001,7 +36240,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>55.282642953983576</v>
+        <v>55.334262700374836</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36774,7 +37013,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.65234476589842E-3</v>
+        <v>-1.6508176450426913E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36803,7 +37042,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.1570870596248275E-2</v>
+        <v>1.1560176630817362E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37126,7 +37365,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.2884249018055261E-3</v>
+        <v>9.2798404055931365E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37615,14 +37854,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="266" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="267"/>
+      <c r="F3" s="268" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="267"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37689,19 +37928,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="269">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="270"/>
+      <c r="F7" s="269">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="270"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37728,19 +37967,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="269">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="270"/>
+      <c r="F9" s="269">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="270"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -37767,19 +38006,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="269">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="270"/>
+      <c r="F11" s="269">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="270"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -37806,19 +38045,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="269">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="270"/>
+      <c r="F13" s="269">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="270"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -37845,19 +38084,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="269">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="270"/>
+      <c r="F15" s="269">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="270"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -37884,19 +38123,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="269">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="270"/>
+      <c r="F17" s="269">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="270"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -37923,22 +38162,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="269">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="270"/>
+      <c r="F19" s="269">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="270"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -37965,22 +38204,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="269">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="270"/>
+      <c r="F21" s="269">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="270"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38029,22 +38268,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="269">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="270"/>
+      <c r="F25" s="269">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="270"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38072,22 +38311,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="269">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="270"/>
+      <c r="F27" s="269">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="270"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38115,22 +38354,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="269">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="270"/>
+      <c r="F29" s="269">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="270"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38179,22 +38418,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="269">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="270"/>
+      <c r="F33" s="269">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="270"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38222,43 +38461,25 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="262">
+      <c r="C35" s="269">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="263"/>
-      <c r="F35" s="262">
+      <c r="D35" s="270"/>
+      <c r="F35" s="269">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="263"/>
+      <c r="G35" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38269,6 +38490,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA857D3A-213F-3146-A575-8FE0D4BD3715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E296D1-D11E-4744-82CC-47C6A26200B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2526,6 +2526,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2533,12 +2539,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2559,14 +2559,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12977,11 +12977,11 @@
     <v>Powered by Refinitiv</v>
     <v>24.07</v>
     <v>7.77</v>
-    <v>0.79259999999999997</v>
-    <v>0.01</v>
-    <v>9.2509999999999999E-4</v>
-    <v>-0.02</v>
-    <v>-1.8479999999999998E-3</v>
+    <v>0.78690000000000004</v>
+    <v>0.40500000000000003</v>
+    <v>3.8100000000000002E-2</v>
+    <v>0.26979999999999998</v>
+    <v>2.4438000000000001E-2</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12989,25 +12989,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>11.02</v>
+    <v>11.055</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46307.851047742966</v>
+    <v>46310.908268726562</v>
     <v>0</v>
-    <v>10.49</v>
-    <v>671607570</v>
+    <v>10.62</v>
+    <v>684952822</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.49</v>
-    <v>64.061599999999999</v>
-    <v>10.81</v>
-    <v>10.82</v>
-    <v>10.8</v>
+    <v>10.69</v>
+    <v>62.932899999999997</v>
+    <v>10.63</v>
+    <v>11.035</v>
+    <v>11.309799999999999</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>533230</v>
-    <v>697289</v>
+    <v>996211</v>
+    <v>658869</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -13031,17 +13031,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13263,9 +13263,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>700335.32000000007</v>
+        <v>714251.41</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13892,7 +13892,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.567410456732686</v>
+        <v>10.690473805110809</v>
       </c>
       <c r="K3" s="260" t="s">
         <v>444</v>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>693836.32000000007</v>
+        <v>707752.41</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.562863851780918</v>
+        <v>17.615582321093626</v>
       </c>
       <c r="K4" s="260" t="s">
         <v>445</v>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.729077459880621</v>
+        <v>16.790441009241029</v>
       </c>
       <c r="K5" s="260" t="s">
         <v>446</v>
@@ -13958,14 +13958,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.8</v>
+        <v>11.309799999999999</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-605.76042605489556</v>
+        <v>-617.79725522326919</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.079558397473312</v>
+        <v>14.121470098003947</v>
       </c>
       <c r="K6" s="261" t="s">
         <v>447</v>
@@ -13985,14 +13985,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.01</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.3187509575752323</v>
+        <v>1.3449553435159602</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.484509566408331</v>
+        <v>25.561804517667408</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -14009,14 +14009,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.02</v>
+        <v>0.26979999999999998</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.1560176630817362E-2</v>
+        <v>1.1334944372038412E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>16.884683946455176</v>
+        <v>16.955954350223362</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14033,14 +14033,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>9.2509999999999999E-4</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6508176450426913E-3</v>
+        <v>-1.6186540026607993E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.56050683423800152</v>
+        <v>0.53656133667633543</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.8479999999999998E-3</v>
+        <v>2.4438000000000001E-2</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.79259999999999997</v>
+        <v>0.78690000000000004</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>697289</v>
+        <v>658869</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>9.2798404055931365E-3</v>
+        <v>9.0990369903504974E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="I17" s="258">
         <f ca="1">DCF!C15</f>
-        <v>8.4921795094382302E-2</v>
+        <v>8.4249862994684455E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="I18" s="259">
         <f ca="1">Multiples!C54</f>
-        <v>8.8106999999999991E-2</v>
+        <v>8.7310499999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14293,7 +14293,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20125,6 +20125,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20132,12 +20138,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21197,16 +21197,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>700335.32000000007</v>
+        <v>714251.41</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.79259999999999997</v>
+        <v>0.78690000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.6655736475166084E-2</v>
+        <v>8.5111080360827637E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.91334426352483389</v>
+        <v>0.9148889196391724</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.8106999999999991E-2</v>
+        <v>8.7310499999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.4921795094382302E-2</v>
+        <v>8.4249862994684455E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>853662.77797955589</v>
+        <v>862590.47674973309</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21748,23 +21748,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13219.596425372247</v>
+        <v>13227.788883113239</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8755.3009980007737</v>
+        <v>8766.1560432858496</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21387.434141125133</v>
+        <v>21427.221495885453</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30047.686085008943</v>
+        <v>30122.240047129435</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36148.020834145675</v>
+        <v>36260.168134521278</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21783,7 +21783,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>567929.17073882709</v>
+        <v>575649.03290566697</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4921795094382302E-2</v>
+        <v>8.4249862994684455E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109558.03848365277</v>
+        <v>109803.57460393527</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>567929.17073882709</v>
+        <v>575649.03290566697</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>677487.20922247984</v>
+        <v>685452.60750960221</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>683986.20922247984</v>
+        <v>691951.60750960221</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21884,7 +21884,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.567410456732686</v>
+        <v>10.690473805110809</v>
       </c>
     </row>
   </sheetData>
@@ -22153,23 +22153,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13219.596425372247</v>
+        <v>13227.788883113239</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8755.3009980007737</v>
+        <v>8766.1560432858496</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21387.434141125133</v>
+        <v>21427.221495885453</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>30047.686085008943</v>
+        <v>30122.240047129435</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36148.020834145675</v>
+        <v>36260.168134521278</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22955,7 +22955,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4921795094382302E-2</v>
+        <v>8.4249862994684455E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1056864.9080208645</v>
+        <v>1060143.7748456921</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1130274.9256703716</v>
+        <v>1133687.1813151061</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1136773.9256703716</v>
+        <v>1140186.1813151061</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23035,7 +23035,7 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.562863851780918</v>
+        <v>17.615582321093626</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.8106999999999991E-2</v>
+        <v>8.7310499999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>16.729077459880621</v>
+        <v>16.790441009241029</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4921795094382302E-2</v>
+        <v>8.4249862994684455E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>831404.47918535047</v>
+        <v>833983.86709398939</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>904814.49683485762</v>
+        <v>907527.2735634034</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>911313.49683485762</v>
+        <v>914026.2735634034</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23198,7 +23198,7 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.079558397473312</v>
+        <v>14.121470098003947</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4921795094382302E-2</v>
+        <v>8.4249862994684455E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1569601.3485458384</v>
+        <v>1574470.9527411265</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1643011.3661953455</v>
+        <v>1648014.3592105405</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1649510.3661953455</v>
+        <v>1654513.3592105405</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23302,22 +23302,22 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.484509566408331</v>
+        <v>25.561804517667408</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.567410456732686</v>
+        <v>10.690473805110809</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.562863851780918</v>
+        <v>17.615582321093626</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23385,7 +23385,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>16.729077459880621</v>
+        <v>16.790441009241029</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.079558397473312</v>
+        <v>14.121470098003947</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.484509566408331</v>
+        <v>25.561804517667408</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>16.884683946455176</v>
+        <v>16.955954350223362</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.56050683423800152</v>
+        <v>0.53656133667633543</v>
       </c>
     </row>
   </sheetData>
@@ -23939,7 +23939,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.8106999999999991E-2</v>
+        <v>8.7310499999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24192,7 +24192,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>805637.45771296183</v>
+        <v>814062.90242715669</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24246,23 +24246,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10692.014901397444</v>
+        <v>10698.64096451066</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14289.897831463124</v>
+        <v>14307.614810938194</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19098.475069181339</v>
+        <v>19134.004240092851</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25525.147504206805</v>
+        <v>25588.480197272245</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>34114.407184418364</v>
+        <v>34220.245307263329</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24281,15 +24281,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>535978.63826038444</v>
+        <v>543264.19678585685</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="277" t="s">
+      <c r="B14" s="278" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="278"/>
+      <c r="C14" s="279"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24297,7 +24297,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.410619786229503</v>
+        <v>10.531684398606984</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24316,20 +24316,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="279" t="s">
+      <c r="E17" s="277" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="279"/>
-      <c r="G17" s="279"/>
-      <c r="H17" s="279"/>
-      <c r="I17" s="279"/>
+      <c r="F17" s="277"/>
+      <c r="G17" s="277"/>
+      <c r="H17" s="277"/>
+      <c r="I17" s="277"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="277" t="s">
+      <c r="B19" s="278" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="278"/>
+      <c r="C19" s="279"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4921795094382302E-2</v>
+        <v>8.4249862994684455E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24363,7 +24363,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>671608.22</v>
+        <v>684953.48499999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24390,15 +24390,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>665109.22</v>
+        <v>678454.48499999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="277" t="s">
+      <c r="B28" s="278" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="278"/>
+      <c r="C28" s="279"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24406,7 +24406,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>103719.94249066708</v>
+        <v>103948.98552007729</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>535978.63826038444</v>
+        <v>543264.19678585685</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24424,7 +24424,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>639698.58075105154</v>
+        <v>647213.18230593414</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24451,7 +24451,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>646197.58075105154</v>
+        <v>653712.18230593414</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24469,21 +24469,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.410619786229503</v>
+        <v>10.531684398606984</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31442,7 +31442,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32591,7 +32591,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-605.76042605489556</v>
+        <v>-617.79725522326919</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32628,7 +32628,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3187509575752323</v>
+        <v>1.3449553435159602</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32689,7 +32689,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.8061218606377287</v>
+        <v>1.8420106037095505</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>700335.32000000007</v>
+        <v>714251.41</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>693836.32000000007</v>
+        <v>707752.41</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32848,7 +32848,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.366376299003728</v>
+        <v>1.3937813439728395</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32885,7 +32885,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>55.334262700374836</v>
+        <v>56.444087247786911</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33020,7 +33020,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>86.50386857707511</v>
+        <v>88.222753211462461</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33057,7 +33057,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-115.36463046734394</v>
+        <v>-117.67846808887447</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33094,7 +33094,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.1560176630817362E-2</v>
+        <v>1.1334944372038412E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33131,7 +33131,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.6508176450426913E-3</v>
+        <v>-1.6186540026607993E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33745,7 +33745,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.2798404055931365E-3</v>
+        <v>9.0990369903504974E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35396,7 +35396,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35412,7 +35412,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>700335.32000000007</v>
+        <v>714251.41</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35432,7 +35432,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>693836.32000000007</v>
+        <v>707752.41</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35452,7 +35452,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-605.76042605489556</v>
+        <v>-617.79725522326919</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35472,7 +35472,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.3187509575752323</v>
+        <v>1.3449553435159602</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35492,7 +35492,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.8061218606377287</v>
+        <v>1.8420106037095505</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35512,7 +35512,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.366376299003728</v>
+        <v>1.3937813439728395</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35521,7 +35521,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>55.334262700374836</v>
+        <v>56.444087247786911</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6508176450426913E-3</v>
+        <v>-1.6186540026607993E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35773,7 +35773,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.1560176630817362E-2</v>
+        <v>1.1334944372038412E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35858,7 +35858,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>9.2798404055931365E-3</v>
+        <v>9.0990369903504974E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36037,7 +36037,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>10.82</v>
+        <v>11.035</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>700335.32000000007</v>
+        <v>714251.41</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36095,7 +36095,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>693836.32000000007</v>
+        <v>707752.41</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-605.76042605489556</v>
+        <v>-617.79725522326919</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36153,7 +36153,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.3187509575752323</v>
+        <v>1.3449553435159602</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36182,7 +36182,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.8061218606377287</v>
+        <v>1.8420106037095505</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.366376299003728</v>
+        <v>1.3937813439728395</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36240,7 +36240,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>55.334262700374836</v>
+        <v>56.444087247786911</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37013,7 +37013,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6508176450426913E-3</v>
+        <v>-1.6186540026607993E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37042,7 +37042,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.1560176630817362E-2</v>
+        <v>1.1334944372038412E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37365,7 +37365,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.2798404055931365E-3</v>
+        <v>9.0990369903504974E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37854,14 +37854,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="268" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="F3" s="268" t="s">
+      <c r="D3" s="269"/>
+      <c r="F3" s="270" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="267"/>
+      <c r="G3" s="269"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37928,19 +37928,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="269">
+      <c r="C7" s="266">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="270"/>
-      <c r="F7" s="269">
+      <c r="D7" s="267"/>
+      <c r="F7" s="266">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="270"/>
+      <c r="G7" s="267"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37967,19 +37967,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="269">
+      <c r="C9" s="266">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="270"/>
-      <c r="F9" s="269">
+      <c r="D9" s="267"/>
+      <c r="F9" s="266">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="270"/>
+      <c r="G9" s="267"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -38006,19 +38006,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="269">
+      <c r="C11" s="266">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="270"/>
-      <c r="F11" s="269">
+      <c r="D11" s="267"/>
+      <c r="F11" s="266">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="270"/>
+      <c r="G11" s="267"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -38045,19 +38045,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="269">
+      <c r="C13" s="266">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="270"/>
-      <c r="F13" s="269">
+      <c r="D13" s="267"/>
+      <c r="F13" s="266">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="270"/>
+      <c r="G13" s="267"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -38084,19 +38084,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="269">
+      <c r="C15" s="266">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="270"/>
-      <c r="F15" s="269">
+      <c r="D15" s="267"/>
+      <c r="F15" s="266">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="270"/>
+      <c r="G15" s="267"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -38123,19 +38123,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="269">
+      <c r="C17" s="266">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="270"/>
-      <c r="F17" s="269">
+      <c r="D17" s="267"/>
+      <c r="F17" s="266">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="270"/>
+      <c r="G17" s="267"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -38162,22 +38162,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="269">
+      <c r="C19" s="266">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="270"/>
-      <c r="F19" s="269">
+      <c r="D19" s="267"/>
+      <c r="F19" s="266">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="270"/>
+      <c r="G19" s="267"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -38204,22 +38204,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="269">
+      <c r="C21" s="266">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="270"/>
-      <c r="F21" s="269">
+      <c r="D21" s="267"/>
+      <c r="F21" s="266">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="270"/>
+      <c r="G21" s="267"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38268,22 +38268,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="269">
+      <c r="C25" s="266">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="270"/>
-      <c r="F25" s="269">
+      <c r="D25" s="267"/>
+      <c r="F25" s="266">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="270"/>
+      <c r="G25" s="267"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38311,22 +38311,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="269">
+      <c r="C27" s="266">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="F27" s="269">
+      <c r="D27" s="267"/>
+      <c r="F27" s="266">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="270"/>
+      <c r="G27" s="267"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38354,22 +38354,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="269">
+      <c r="C29" s="266">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="270"/>
-      <c r="F29" s="269">
+      <c r="D29" s="267"/>
+      <c r="F29" s="266">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="270"/>
+      <c r="G29" s="267"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38418,22 +38418,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="269">
+      <c r="C33" s="266">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="270"/>
-      <c r="F33" s="269">
+      <c r="D33" s="267"/>
+      <c r="F33" s="266">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="270"/>
+      <c r="G33" s="267"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38461,25 +38461,43 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="269">
+      <c r="C35" s="266">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="270"/>
-      <c r="F35" s="269">
+      <c r="D35" s="267"/>
+      <c r="F35" s="266">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="270"/>
+      <c r="G35" s="267"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38490,24 +38508,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E296D1-D11E-4744-82CC-47C6A26200B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D05091E-413A-7C43-9D43-8A3087733085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -164,7 +164,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -175,7 +175,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -185,19 +206,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="450">
   <si>
     <t>Ticker</t>
   </si>
@@ -1544,6 +1574,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2169,7 +2202,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="280">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2526,12 +2559,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2539,6 +2566,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2559,15 +2592,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12958,7 +12994,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12977,11 +13013,9 @@
     <v>Powered by Refinitiv</v>
     <v>24.07</v>
     <v>7.77</v>
-    <v>0.78690000000000004</v>
-    <v>0.40500000000000003</v>
-    <v>3.8100000000000002E-2</v>
-    <v>0.26979999999999998</v>
-    <v>2.4438000000000001E-2</v>
+    <v>0.78290000000000004</v>
+    <v>0.52</v>
+    <v>4.6098999999999994E-2</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12989,35 +13023,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>11.055</v>
+    <v>11.845000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46310.908268726562</v>
+    <v>46315.726398865627</v>
     <v>0</v>
-    <v>10.62</v>
-    <v>684952822</v>
+    <v>11.295</v>
+    <v>732437092</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.69</v>
-    <v>62.932899999999997</v>
-    <v>10.63</v>
-    <v>11.035</v>
-    <v>11.309799999999999</v>
+    <v>11.295</v>
+    <v>69.863799999999998</v>
+    <v>11.28</v>
+    <v>11.8</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>996211</v>
-    <v>658869</v>
+    <v>274172</v>
+    <v>687377</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13031,28 +13079,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>51.77</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13074,8 +13122,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13096,7 +13142,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13106,6 +13151,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13141,7 +13191,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13152,16 +13202,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13255,19 +13302,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13339,9 +13380,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13349,9 +13387,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13846,7 +13881,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13884,7 +13919,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>714251.41</v>
+        <v>763766.8</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13892,7 +13927,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.690473805110809</v>
+        <v>10.779963307751274</v>
       </c>
       <c r="K3" s="260" t="s">
         <v>444</v>
@@ -13911,7 +13946,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>707752.41</v>
+        <v>757267.8</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13919,7 +13954,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.615582321093626</v>
+        <v>17.653347927200912</v>
       </c>
       <c r="K4" s="260" t="s">
         <v>445</v>
@@ -13931,7 +13966,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13946,7 +13981,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.790441009241029</v>
+        <v>16.846143452819938</v>
       </c>
       <c r="K5" s="260" t="s">
         <v>446</v>
@@ -13956,16 +13991,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>11.309799999999999</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-617.79725522326919</v>
+        <v>-660.62597296190086</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13973,7 +14008,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.121470098003947</v>
+        <v>14.151493861261276</v>
       </c>
       <c r="K6" s="261" t="s">
         <v>447</v>
@@ -13985,14 +14020,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.40500000000000003</v>
+        <v>0.52</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.3449553435159602</v>
+        <v>1.4381942051190151</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -14000,23 +14035,23 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.561804517667408</v>
+        <v>25.617176428200224</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.26979999999999998</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.1334944372038412E-2</v>
+        <v>1.0600094164868124E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -14024,7 +14059,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>16.955954350223362</v>
+        <v>17.009624995446725</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14033,14 +14068,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.8100000000000002E-2</v>
+        <v>4.6098999999999994E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6186540026607993E-3</v>
+        <v>-1.5137158406238916E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -14048,16 +14083,16 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.53656133667633543</v>
+        <v>0.44149364368192573</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.4438000000000001E-2</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14112,7 +14147,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.78690000000000004</v>
+        <v>0.78290000000000004</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14121,10 +14156,10 @@
         <f>Statement!AC129</f>
         <v>-3.1491107997558164E-3</v>
       </c>
-      <c r="H13" s="184" t="s">
+      <c r="H13" s="282" t="s">
         <v>440</v>
       </c>
-      <c r="I13" s="213">
+      <c r="I13" s="280">
         <f>'Reverse DCF'!C17</f>
         <v>0.45</v>
       </c>
@@ -14135,7 +14170,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>658869</v>
+        <v>687377</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14144,6 +14179,13 @@
         <f>Statement!AC140</f>
         <v>-1.4540196296708597E-2</v>
       </c>
+      <c r="H14" s="186" t="s">
+        <v>449</v>
+      </c>
+      <c r="I14" s="281">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>10.619720879169423</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="185" t="s">
@@ -14151,7 +14193,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>9.0990369903504974E-3</v>
+        <v>8.5091417956370975E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14184,7 +14226,7 @@
       </c>
       <c r="I17" s="258">
         <f ca="1">DCF!C15</f>
-        <v>8.4249862994684455E-2</v>
+        <v>8.3770030039768115E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14206,7 +14248,7 @@
       </c>
       <c r="I18" s="259">
         <f ca="1">Multiples!C54</f>
-        <v>8.7310499999999999E-2</v>
+        <v>8.6590500000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14273,12 +14315,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14293,7 +14335,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20125,12 +20167,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20138,6 +20174,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21197,16 +21239,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21328,7 +21370,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21337,7 +21379,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>714251.41</v>
+        <v>763766.8</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21355,7 +21397,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21364,7 +21406,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.78690000000000004</v>
+        <v>0.78290000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21407,7 +21449,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.5111080360827637E-2</v>
+        <v>8.0034901895032207E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21416,7 +21458,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9148889196391724</v>
+        <v>0.91996509810496774</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21434,7 +21476,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.7310499999999999E-2</v>
+        <v>8.6590500000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21443,7 +21485,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.4249862994684455E-2</v>
+        <v>8.3770030039768115E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21694,7 +21736,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>862590.47674973309</v>
+        <v>869080.97608121228</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21748,23 +21790,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13227.788883113239</v>
+        <v>13233.645410652167</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8766.1560432858496</v>
+        <v>8773.9200921087231</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21427.221495885453</v>
+        <v>21455.694436072074</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30122.240047129435</v>
+        <v>30175.621280360043</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36260.168134521278</v>
+        <v>36340.509149774109</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21783,7 +21825,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>575649.03290566697</v>
+        <v>581265.51468854188</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21806,7 +21848,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4249862994684455E-2</v>
+        <v>8.3770030039768115E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21821,7 +21863,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109803.57460393527</v>
+        <v>109979.39036896711</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21830,7 +21872,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>575649.03290566697</v>
+        <v>581265.51468854188</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21839,7 +21881,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>685452.60750960221</v>
+        <v>691244.90505750896</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21866,7 +21908,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>691951.60750960221</v>
+        <v>697743.90505750896</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21884,7 +21926,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.690473805110809</v>
+        <v>10.779963307751274</v>
       </c>
     </row>
   </sheetData>
@@ -22153,23 +22195,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13227.788883113239</v>
+        <v>13233.645410652167</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8766.1560432858496</v>
+        <v>8773.9200921087231</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21427.221495885453</v>
+        <v>21455.694436072074</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>30122.240047129435</v>
+        <v>30175.621280360043</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36260.168134521278</v>
+        <v>36340.509149774109</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22955,7 +22997,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4249862994684455E-2</v>
+        <v>8.3770030039768115E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22981,7 +23023,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1060143.7748456921</v>
+        <v>1062492.7167168132</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22990,7 +23032,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1133687.1813151061</v>
+        <v>1136131.5979360063</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23017,7 +23059,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1140186.1813151061</v>
+        <v>1142630.5979360063</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23035,7 +23077,7 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.615582321093626</v>
+        <v>17.653347927200912</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23059,7 +23101,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.7310499999999999E-2</v>
+        <v>8.6590500000000001E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23094,7 +23136,7 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>16.790441009241029</v>
+        <v>16.846143452819938</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23118,7 +23160,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4249862994684455E-2</v>
+        <v>8.3770030039768115E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23144,7 +23186,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>833983.86709398939</v>
+        <v>835831.7104448044</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23153,7 +23195,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>907527.2735634034</v>
+        <v>909470.59166399739</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23180,7 +23222,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>914026.2735634034</v>
+        <v>915969.59166399739</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23198,7 +23240,7 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.121470098003947</v>
+        <v>14.151493861261276</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23222,7 +23264,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4249862994684455E-2</v>
+        <v>8.3770030039768115E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23248,7 +23290,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1574470.9527411265</v>
+        <v>1577959.4802724947</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23257,7 +23299,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1648014.3592105405</v>
+        <v>1651598.3614916878</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23284,7 +23326,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1654513.3592105405</v>
+        <v>1658097.3614916878</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23302,22 +23344,22 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.561804517667408</v>
+        <v>25.617176428200224</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23367,7 +23409,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.690473805110809</v>
+        <v>10.779963307751274</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23376,7 +23418,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.615582321093626</v>
+        <v>17.653347927200912</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23385,7 +23427,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>16.790441009241029</v>
+        <v>16.846143452819938</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23394,7 +23436,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.121470098003947</v>
+        <v>14.151493861261276</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23403,7 +23445,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.561804517667408</v>
+        <v>25.617176428200224</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23412,7 +23454,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>16.955954350223362</v>
+        <v>17.009624995446725</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23421,7 +23463,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23430,7 +23472,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.53656133667633543</v>
+        <v>0.44149364368192573</v>
       </c>
     </row>
   </sheetData>
@@ -23939,7 +23981,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.7310499999999999E-2</v>
+        <v>8.6590500000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24192,7 +24234,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>814062.90242715669</v>
+        <v>820188.25955362816</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24246,23 +24288,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10698.64096451066</v>
+        <v>10703.377726337705</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14307.614810938194</v>
+        <v>14320.286844082762</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19134.004240092851</v>
+        <v>19159.429905215289</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25588.480197272245</v>
+        <v>25633.826912101231</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>34220.245307263329</v>
+        <v>34296.066501472538</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24281,15 +24323,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>543264.19678585685</v>
+        <v>548564.70680171566</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="278" t="s">
+      <c r="B14" s="277" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="279"/>
+      <c r="C14" s="278"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24297,7 +24339,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24306,7 +24348,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.531684398606984</v>
+        <v>10.619720879169423</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24316,20 +24358,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="277" t="s">
+      <c r="E17" s="279" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="277"/>
-      <c r="G17" s="277"/>
-      <c r="H17" s="277"/>
-      <c r="I17" s="277"/>
+      <c r="F17" s="279"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="279"/>
+      <c r="I17" s="279"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="278" t="s">
+      <c r="B19" s="277" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="279"/>
+      <c r="C19" s="278"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24345,7 +24387,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.4249862994684455E-2</v>
+        <v>8.3770030039768115E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24363,7 +24405,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>684953.48499999999</v>
+        <v>732437.8</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24390,15 +24432,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>678454.48499999999</v>
+        <v>725938.8</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="278" t="s">
+      <c r="B28" s="277" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="279"/>
+      <c r="C28" s="278"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24406,7 +24448,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>103948.98552007729</v>
+        <v>104112.98788920953</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24415,7 +24457,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>543264.19678585685</v>
+        <v>548564.70680171566</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24424,7 +24466,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>647213.18230593414</v>
+        <v>652677.69469092519</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24451,7 +24493,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>653712.18230593414</v>
+        <v>659176.69469092519</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24469,21 +24511,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.531684398606984</v>
+        <v>10.619720879169423</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31442,7 +31484,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31513,7 +31555,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32591,7 +32633,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-617.79725522326919</v>
+        <v>-660.62597296190086</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32628,7 +32670,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3449553435159602</v>
+        <v>1.4381942051190151</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32689,7 +32731,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.8420106037095505</v>
+        <v>1.9697077592906838</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32750,7 +32792,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>714251.41</v>
+        <v>763766.8</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32811,7 +32853,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>707752.41</v>
+        <v>757267.8</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32848,7 +32890,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.3937813439728395</v>
+        <v>1.4912923179327011</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32885,7 +32927,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>56.444087247786911</v>
+        <v>60.392997846718245</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33020,7 +33062,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>88.222753211462461</v>
+        <v>94.338784584980246</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33057,7 +33099,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-117.67846808887447</v>
+        <v>-125.91142520734358</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33094,7 +33136,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.1334944372038412E-2</v>
+        <v>1.0600094164868124E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33131,7 +33173,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.6186540026607993E-3</v>
+        <v>-1.5137158406238916E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33745,7 +33787,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>9.0990369903504974E-3</v>
+        <v>8.5091417956370975E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35396,7 +35438,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35412,7 +35454,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>714251.41</v>
+        <v>763766.8</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35432,7 +35474,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>707752.41</v>
+        <v>757267.8</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35452,7 +35494,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-617.79725522326919</v>
+        <v>-660.62597296190086</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35472,7 +35514,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.3449553435159602</v>
+        <v>1.4381942051190151</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35492,7 +35534,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.8420106037095505</v>
+        <v>1.9697077592906838</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35512,7 +35554,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.3937813439728395</v>
+        <v>1.4912923179327011</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35521,7 +35563,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>56.444087247786911</v>
+        <v>60.392997846718245</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35757,7 +35799,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6186540026607993E-3</v>
+        <v>-1.5137158406238916E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35773,7 +35815,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.1334944372038412E-2</v>
+        <v>1.0600094164868124E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35858,7 +35900,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>9.0990369903504974E-3</v>
+        <v>8.5091417956370975E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36037,7 +36079,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>11.035</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36066,7 +36108,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>714251.41</v>
+        <v>763766.8</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36095,7 +36137,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>707752.41</v>
+        <v>757267.8</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36124,7 +36166,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-617.79725522326919</v>
+        <v>-660.62597296190086</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36153,7 +36195,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.3449553435159602</v>
+        <v>1.4381942051190151</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36182,7 +36224,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.8420106037095505</v>
+        <v>1.9697077592906838</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36211,7 +36253,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.3937813439728395</v>
+        <v>1.4912923179327011</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36240,7 +36282,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>56.444087247786911</v>
+        <v>60.392997846718245</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37013,7 +37055,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6186540026607993E-3</v>
+        <v>-1.5137158406238916E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37042,7 +37084,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.1334944372038412E-2</v>
+        <v>1.0600094164868124E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37365,7 +37407,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>9.0990369903504974E-3</v>
+        <v>8.5091417956370975E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37854,14 +37896,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="268" t="s">
+      <c r="C3" s="266" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="269"/>
-      <c r="F3" s="270" t="s">
+      <c r="D3" s="267"/>
+      <c r="F3" s="268" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="269"/>
+      <c r="G3" s="267"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37928,19 +37970,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="266">
+      <c r="C7" s="269">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="267"/>
-      <c r="F7" s="266">
+      <c r="D7" s="270"/>
+      <c r="F7" s="269">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="267"/>
+      <c r="G7" s="270"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37967,19 +38009,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="266">
+      <c r="C9" s="269">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="F9" s="266">
+      <c r="D9" s="270"/>
+      <c r="F9" s="269">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="267"/>
+      <c r="G9" s="270"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -38006,19 +38048,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="266">
+      <c r="C11" s="269">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="F11" s="266">
+      <c r="D11" s="270"/>
+      <c r="F11" s="269">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="267"/>
+      <c r="G11" s="270"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -38045,19 +38087,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="266">
+      <c r="C13" s="269">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="F13" s="266">
+      <c r="D13" s="270"/>
+      <c r="F13" s="269">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="267"/>
+      <c r="G13" s="270"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -38084,19 +38126,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="266">
+      <c r="C15" s="269">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="267"/>
-      <c r="F15" s="266">
+      <c r="D15" s="270"/>
+      <c r="F15" s="269">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="267"/>
+      <c r="G15" s="270"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -38123,19 +38165,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="266">
+      <c r="C17" s="269">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="F17" s="266">
+      <c r="D17" s="270"/>
+      <c r="F17" s="269">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="267"/>
+      <c r="G17" s="270"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -38162,22 +38204,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="266">
+      <c r="C19" s="269">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="267"/>
-      <c r="F19" s="266">
+      <c r="D19" s="270"/>
+      <c r="F19" s="269">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="267"/>
+      <c r="G19" s="270"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -38204,22 +38246,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="266">
+      <c r="C21" s="269">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="267"/>
-      <c r="F21" s="266">
+      <c r="D21" s="270"/>
+      <c r="F21" s="269">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="267"/>
+      <c r="G21" s="270"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38268,22 +38310,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="266">
+      <c r="C25" s="269">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="F25" s="266">
+      <c r="D25" s="270"/>
+      <c r="F25" s="269">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="267"/>
+      <c r="G25" s="270"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38311,22 +38353,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="266">
+      <c r="C27" s="269">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="267"/>
-      <c r="F27" s="266">
+      <c r="D27" s="270"/>
+      <c r="F27" s="269">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="267"/>
+      <c r="G27" s="270"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38354,22 +38396,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="266">
+      <c r="C29" s="269">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="267"/>
-      <c r="F29" s="266">
+      <c r="D29" s="270"/>
+      <c r="F29" s="269">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="267"/>
+      <c r="G29" s="270"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38418,22 +38460,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="266">
+      <c r="C33" s="269">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="F33" s="266">
+      <c r="D33" s="270"/>
+      <c r="F33" s="269">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="267"/>
+      <c r="G33" s="270"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38461,43 +38503,25 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="266">
+      <c r="C35" s="269">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="267"/>
-      <c r="F35" s="266">
+      <c r="D35" s="270"/>
+      <c r="F35" s="269">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="267"/>
+      <c r="G35" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38508,6 +38532,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D05091E-413A-7C43-9D43-8A3087733085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EEAFA4-7567-9340-AC60-CBD64688655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -164,7 +164,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -175,28 +175,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -206,21 +185,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2547,6 +2517,9 @@
     <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2601,9 +2574,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12994,7 +12964,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13013,9 +12983,11 @@
     <v>Powered by Refinitiv</v>
     <v>24.07</v>
     <v>7.77</v>
-    <v>0.78290000000000004</v>
-    <v>0.52</v>
-    <v>4.6098999999999994E-2</v>
+    <v>0.76980000000000004</v>
+    <v>-0.02</v>
+    <v>-1.572E-3</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -13023,49 +12995,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>11.845000000000001</v>
+    <v>12.7</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46315.726398865627</v>
+    <v>46318.937500022657</v>
     <v>0</v>
-    <v>11.295</v>
-    <v>732437092</v>
+    <v>12.350099999999999</v>
+    <v>788300938</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>11.295</v>
-    <v>69.863799999999998</v>
-    <v>11.28</v>
-    <v>11.8</v>
+    <v>12.55</v>
+    <v>75.192400000000006</v>
+    <v>12.72</v>
+    <v>12.7</v>
+    <v>12.7</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>274172</v>
-    <v>687377</v>
+    <v>696514</v>
+    <v>718903</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13079,28 +13037,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>6</v>
-    <v>50.9</v>
+    <v>3</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13122,6 +13080,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13142,6 +13102,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13151,11 +13112,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13191,7 +13147,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13202,13 +13158,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13302,13 +13261,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13380,6 +13345,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13387,6 +13355,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13890,18 +13861,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="262" t="s">
+      <c r="B2" s="265" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="263"/>
-      <c r="E2" s="262" t="s">
+      <c r="C2" s="266"/>
+      <c r="E2" s="265" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="263"/>
-      <c r="H2" s="262" t="s">
+      <c r="F2" s="266"/>
+      <c r="H2" s="265" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="263"/>
+      <c r="I2" s="266"/>
       <c r="K2" s="136" t="s">
         <v>443</v>
       </c>
@@ -13919,7 +13890,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>763766.8</v>
+        <v>822020.2</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13927,7 +13898,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>10.779963307751274</v>
+        <v>11.178900477094921</v>
       </c>
       <c r="K3" s="260" t="s">
         <v>444</v>
@@ -13946,7 +13917,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>757267.8</v>
+        <v>815521.2</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13954,7 +13925,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.653347927200912</v>
+        <v>17.816106600358328</v>
       </c>
       <c r="K4" s="260" t="s">
         <v>445</v>
@@ -13966,7 +13937,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13981,7 +13952,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.846143452819938</v>
+        <v>17.034958556683026</v>
       </c>
       <c r="K5" s="260" t="s">
         <v>446</v>
@@ -13991,16 +13962,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>12.7</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-660.62597296190086</v>
+        <v>-711.01269971323222</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -14008,7 +13979,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.151493861261276</v>
+        <v>14.280884958201142</v>
       </c>
       <c r="K6" s="261" t="s">
         <v>447</v>
@@ -14020,14 +13991,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.52</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.4381942051190151</v>
+        <v>1.54788698347555</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -14035,23 +14006,23 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.617176428200224</v>
+        <v>25.855818804529399</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.0600094164868124E-2</v>
+        <v>9.8489063894050301E-3</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -14059,7 +14030,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>17.009624995446725</v>
+        <v>17.233333879373362</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14068,14 +14039,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.6098999999999994E-2</v>
+        <v>-1.572E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.5137158406238916E-3</v>
+        <v>-1.4064446393198364E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -14083,16 +14054,16 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.44149364368192573</v>
+        <v>0.35695542357270571</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14147,7 +14118,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.78290000000000004</v>
+        <v>0.76980000000000004</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14156,10 +14127,10 @@
         <f>Statement!AC129</f>
         <v>-3.1491107997558164E-3</v>
       </c>
-      <c r="H13" s="282" t="s">
+      <c r="H13" s="264" t="s">
         <v>440</v>
       </c>
-      <c r="I13" s="280">
+      <c r="I13" s="262">
         <f>'Reverse DCF'!C17</f>
         <v>0.45</v>
       </c>
@@ -14170,7 +14141,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>687377</v>
+        <v>718903</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14182,9 +14153,9 @@
       <c r="H14" s="186" t="s">
         <v>449</v>
       </c>
-      <c r="I14" s="281">
+      <c r="I14" s="263">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>10.619720879169423</v>
+        <v>11.012184769358846</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14193,7 +14164,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>8.5091417956370975E-3</v>
+        <v>7.9061317471273828E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14204,16 +14175,16 @@
         <f>Statement!AC175</f>
         <v>0.10470267918995989</v>
       </c>
-      <c r="H16" s="262" t="s">
+      <c r="H16" s="265" t="s">
         <v>441</v>
       </c>
-      <c r="I16" s="263"/>
+      <c r="I16" s="266"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="264" t="s">
+      <c r="B17" s="267" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="264"/>
+      <c r="C17" s="267"/>
       <c r="E17" s="184" t="s">
         <v>308</v>
       </c>
@@ -14226,7 +14197,7 @@
       </c>
       <c r="I17" s="258">
         <f ca="1">DCF!C15</f>
-        <v>8.3770030039768115E-2</v>
+        <v>8.1716405592244246E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14248,7 +14219,7 @@
       </c>
       <c r="I18" s="259">
         <f ca="1">Multiples!C54</f>
-        <v>8.6590500000000001E-2</v>
+        <v>8.4170999999999996E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14299,14 +14270,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="264" t="s">
+      <c r="B25" s="267" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="264"/>
-      <c r="E25" s="262" t="s">
+      <c r="C25" s="267"/>
+      <c r="E25" s="265" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="263"/>
+      <c r="F25" s="266"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14315,12 +14286,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14335,7 +14306,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14683,36 +14654,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="265" t="s">
+      <c r="C2" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="265"/>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="265"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="265"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="265" t="s">
+      <c r="S2" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="T2" s="265"/>
-      <c r="U2" s="265"/>
-      <c r="V2" s="265"/>
-      <c r="W2" s="265"/>
-      <c r="X2" s="265"/>
-      <c r="Y2" s="265"/>
-      <c r="Z2" s="265"/>
-      <c r="AA2" s="265" t="s">
+      <c r="T2" s="268"/>
+      <c r="U2" s="268"/>
+      <c r="V2" s="268"/>
+      <c r="W2" s="268"/>
+      <c r="X2" s="268"/>
+      <c r="Y2" s="268"/>
+      <c r="Z2" s="268"/>
+      <c r="AA2" s="268" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" s="265"/>
-      <c r="AC2" s="265"/>
+      <c r="AB2" s="268"/>
+      <c r="AC2" s="268"/>
       <c r="AE2" s="86" t="s">
         <v>125</v>
       </c>
@@ -14723,32 +14694,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="274" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
+      <c r="D4" s="274"/>
+      <c r="E4" s="274"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="274"/>
+      <c r="K4" s="274"/>
+      <c r="L4" s="274"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="272" t="s">
+      <c r="S4" s="275" t="s">
         <v>126</v>
       </c>
-      <c r="T4" s="273"/>
-      <c r="U4" s="273"/>
-      <c r="V4" s="273"/>
-      <c r="W4" s="273"/>
-      <c r="X4" s="273"/>
-      <c r="Y4" s="273"/>
-      <c r="Z4" s="273"/>
-      <c r="AA4" s="273"/>
-      <c r="AB4" s="273"/>
-      <c r="AC4" s="273"/>
+      <c r="T4" s="276"/>
+      <c r="U4" s="276"/>
+      <c r="V4" s="276"/>
+      <c r="W4" s="276"/>
+      <c r="X4" s="276"/>
+      <c r="Y4" s="276"/>
+      <c r="Z4" s="276"/>
+      <c r="AA4" s="276"/>
+      <c r="AB4" s="276"/>
+      <c r="AC4" s="276"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15239,33 +15210,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="274" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="271"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="271"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="271"/>
-      <c r="L11" s="271"/>
+      <c r="D11" s="274"/>
+      <c r="E11" s="274"/>
+      <c r="F11" s="274"/>
+      <c r="G11" s="274"/>
+      <c r="H11" s="274"/>
+      <c r="I11" s="274"/>
+      <c r="J11" s="274"/>
+      <c r="K11" s="274"/>
+      <c r="L11" s="274"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="272" t="s">
+      <c r="S11" s="275" t="s">
         <v>132</v>
       </c>
-      <c r="T11" s="273"/>
-      <c r="U11" s="273"/>
-      <c r="V11" s="273"/>
-      <c r="W11" s="273"/>
-      <c r="X11" s="273"/>
-      <c r="Y11" s="273"/>
-      <c r="Z11" s="273"/>
-      <c r="AA11" s="273"/>
-      <c r="AB11" s="273"/>
-      <c r="AC11" s="273"/>
+      <c r="T11" s="276"/>
+      <c r="U11" s="276"/>
+      <c r="V11" s="276"/>
+      <c r="W11" s="276"/>
+      <c r="X11" s="276"/>
+      <c r="Y11" s="276"/>
+      <c r="Z11" s="276"/>
+      <c r="AA11" s="276"/>
+      <c r="AB11" s="276"/>
+      <c r="AC11" s="276"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15706,33 +15677,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="271" t="s">
+      <c r="C19" s="274" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="271"/>
-      <c r="E19" s="271"/>
-      <c r="F19" s="271"/>
-      <c r="G19" s="271"/>
-      <c r="H19" s="271"/>
-      <c r="I19" s="271"/>
-      <c r="J19" s="271"/>
-      <c r="K19" s="271"/>
-      <c r="L19" s="271"/>
+      <c r="D19" s="274"/>
+      <c r="E19" s="274"/>
+      <c r="F19" s="274"/>
+      <c r="G19" s="274"/>
+      <c r="H19" s="274"/>
+      <c r="I19" s="274"/>
+      <c r="J19" s="274"/>
+      <c r="K19" s="274"/>
+      <c r="L19" s="274"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="272" t="s">
+      <c r="S19" s="275" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="273"/>
-      <c r="U19" s="273"/>
-      <c r="V19" s="273"/>
-      <c r="W19" s="273"/>
-      <c r="X19" s="273"/>
-      <c r="Y19" s="273"/>
-      <c r="Z19" s="273"/>
-      <c r="AA19" s="273"/>
-      <c r="AB19" s="273"/>
-      <c r="AC19" s="273"/>
+      <c r="T19" s="276"/>
+      <c r="U19" s="276"/>
+      <c r="V19" s="276"/>
+      <c r="W19" s="276"/>
+      <c r="X19" s="276"/>
+      <c r="Y19" s="276"/>
+      <c r="Z19" s="276"/>
+      <c r="AA19" s="276"/>
+      <c r="AB19" s="276"/>
+      <c r="AC19" s="276"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16969,35 +16940,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="265" t="s">
+      <c r="C2" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="265"/>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="265"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="265"/>
-      <c r="P2" s="265" t="s">
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="P2" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="265"/>
-      <c r="R2" s="265"/>
-      <c r="S2" s="265"/>
-      <c r="T2" s="265"/>
-      <c r="U2" s="265"/>
-      <c r="V2" s="265"/>
-      <c r="W2" s="265"/>
-      <c r="X2" s="265" t="s">
+      <c r="Q2" s="268"/>
+      <c r="R2" s="268"/>
+      <c r="S2" s="268"/>
+      <c r="T2" s="268"/>
+      <c r="U2" s="268"/>
+      <c r="V2" s="268"/>
+      <c r="W2" s="268"/>
+      <c r="X2" s="268" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="265"/>
-      <c r="Z2" s="265"/>
+      <c r="Y2" s="268"/>
+      <c r="Z2" s="268"/>
       <c r="AB2" s="86" t="s">
         <v>125</v>
       </c>
@@ -17006,31 +16977,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="274" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
-      <c r="P4" s="273" t="s">
+      <c r="D4" s="274"/>
+      <c r="E4" s="274"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="274"/>
+      <c r="K4" s="274"/>
+      <c r="L4" s="274"/>
+      <c r="P4" s="276" t="s">
         <v>126</v>
       </c>
-      <c r="Q4" s="273"/>
-      <c r="R4" s="273"/>
-      <c r="S4" s="273"/>
-      <c r="T4" s="273"/>
-      <c r="U4" s="273"/>
-      <c r="V4" s="273"/>
-      <c r="W4" s="273"/>
-      <c r="X4" s="273"/>
-      <c r="Y4" s="273"/>
-      <c r="Z4" s="273"/>
+      <c r="Q4" s="276"/>
+      <c r="R4" s="276"/>
+      <c r="S4" s="276"/>
+      <c r="T4" s="276"/>
+      <c r="U4" s="276"/>
+      <c r="V4" s="276"/>
+      <c r="W4" s="276"/>
+      <c r="X4" s="276"/>
+      <c r="Y4" s="276"/>
+      <c r="Z4" s="276"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17225,32 +17196,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="271" t="s">
+      <c r="C9" s="274" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="271"/>
-      <c r="E9" s="271"/>
-      <c r="F9" s="271"/>
-      <c r="G9" s="271"/>
-      <c r="H9" s="271"/>
-      <c r="I9" s="271"/>
-      <c r="J9" s="271"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="271"/>
+      <c r="D9" s="274"/>
+      <c r="E9" s="274"/>
+      <c r="F9" s="274"/>
+      <c r="G9" s="274"/>
+      <c r="H9" s="274"/>
+      <c r="I9" s="274"/>
+      <c r="J9" s="274"/>
+      <c r="K9" s="274"/>
+      <c r="L9" s="274"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="273" t="s">
+      <c r="P9" s="276" t="s">
         <v>138</v>
       </c>
-      <c r="Q9" s="273"/>
-      <c r="R9" s="273"/>
-      <c r="S9" s="273"/>
-      <c r="T9" s="273"/>
-      <c r="U9" s="273"/>
-      <c r="V9" s="273"/>
-      <c r="W9" s="273"/>
-      <c r="X9" s="273"/>
-      <c r="Y9" s="273"/>
-      <c r="Z9" s="273"/>
+      <c r="Q9" s="276"/>
+      <c r="R9" s="276"/>
+      <c r="S9" s="276"/>
+      <c r="T9" s="276"/>
+      <c r="U9" s="276"/>
+      <c r="V9" s="276"/>
+      <c r="W9" s="276"/>
+      <c r="X9" s="276"/>
+      <c r="Y9" s="276"/>
+      <c r="Z9" s="276"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18008,31 +17979,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="271" t="s">
+      <c r="C20" s="274" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="271"/>
-      <c r="E20" s="271"/>
-      <c r="F20" s="271"/>
-      <c r="G20" s="271"/>
-      <c r="H20" s="271"/>
-      <c r="I20" s="271"/>
-      <c r="J20" s="271"/>
-      <c r="K20" s="271"/>
-      <c r="L20" s="271"/>
-      <c r="P20" s="273" t="s">
+      <c r="D20" s="274"/>
+      <c r="E20" s="274"/>
+      <c r="F20" s="274"/>
+      <c r="G20" s="274"/>
+      <c r="H20" s="274"/>
+      <c r="I20" s="274"/>
+      <c r="J20" s="274"/>
+      <c r="K20" s="274"/>
+      <c r="L20" s="274"/>
+      <c r="P20" s="276" t="s">
         <v>140</v>
       </c>
-      <c r="Q20" s="273"/>
-      <c r="R20" s="273"/>
-      <c r="S20" s="273"/>
-      <c r="T20" s="273"/>
-      <c r="U20" s="273"/>
-      <c r="V20" s="273"/>
-      <c r="W20" s="273"/>
-      <c r="X20" s="273"/>
-      <c r="Y20" s="273"/>
-      <c r="Z20" s="273"/>
+      <c r="Q20" s="276"/>
+      <c r="R20" s="276"/>
+      <c r="S20" s="276"/>
+      <c r="T20" s="276"/>
+      <c r="U20" s="276"/>
+      <c r="V20" s="276"/>
+      <c r="W20" s="276"/>
+      <c r="X20" s="276"/>
+      <c r="Y20" s="276"/>
+      <c r="Z20" s="276"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18756,60 +18727,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="265" t="s">
+      <c r="C3" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="E3" s="265"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275" t="s">
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="268"/>
+      <c r="G3" s="277"/>
+      <c r="H3" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="265"/>
-      <c r="J3" s="265"/>
-      <c r="K3" s="265"/>
-      <c r="L3" s="265"/>
-      <c r="P3" s="276"/>
-      <c r="Q3" s="276"/>
-      <c r="R3" s="276"/>
-      <c r="S3" s="276"/>
-      <c r="T3" s="276"/>
-      <c r="U3" s="276"/>
-      <c r="V3" s="276"/>
-      <c r="W3" s="276"/>
-      <c r="X3" s="276"/>
-      <c r="Y3" s="276"/>
-      <c r="Z3" s="276"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="268"/>
+      <c r="K3" s="268"/>
+      <c r="L3" s="268"/>
+      <c r="P3" s="279"/>
+      <c r="Q3" s="279"/>
+      <c r="R3" s="279"/>
+      <c r="S3" s="279"/>
+      <c r="T3" s="279"/>
+      <c r="U3" s="279"/>
+      <c r="V3" s="279"/>
+      <c r="W3" s="279"/>
+      <c r="X3" s="279"/>
+      <c r="Y3" s="279"/>
+      <c r="Z3" s="279"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="274" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="271"/>
-      <c r="E5" s="271"/>
-      <c r="F5" s="271"/>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
-      <c r="P5" s="276"/>
-      <c r="Q5" s="276"/>
-      <c r="R5" s="276"/>
-      <c r="S5" s="276"/>
-      <c r="T5" s="276"/>
-      <c r="U5" s="276"/>
-      <c r="V5" s="276"/>
-      <c r="W5" s="276"/>
-      <c r="X5" s="276"/>
-      <c r="Y5" s="276"/>
-      <c r="Z5" s="276"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="274"/>
+      <c r="G5" s="274"/>
+      <c r="H5" s="274"/>
+      <c r="I5" s="274"/>
+      <c r="J5" s="274"/>
+      <c r="K5" s="274"/>
+      <c r="L5" s="274"/>
+      <c r="P5" s="279"/>
+      <c r="Q5" s="279"/>
+      <c r="R5" s="279"/>
+      <c r="S5" s="279"/>
+      <c r="T5" s="279"/>
+      <c r="U5" s="279"/>
+      <c r="V5" s="279"/>
+      <c r="W5" s="279"/>
+      <c r="X5" s="279"/>
+      <c r="Y5" s="279"/>
+      <c r="Z5" s="279"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18995,30 +18966,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="274" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="271"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="271"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="271"/>
-      <c r="L11" s="271"/>
+      <c r="D11" s="274"/>
+      <c r="E11" s="274"/>
+      <c r="F11" s="274"/>
+      <c r="G11" s="274"/>
+      <c r="H11" s="274"/>
+      <c r="I11" s="274"/>
+      <c r="J11" s="274"/>
+      <c r="K11" s="274"/>
+      <c r="L11" s="274"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="276"/>
-      <c r="Q11" s="276"/>
-      <c r="R11" s="276"/>
-      <c r="S11" s="276"/>
-      <c r="T11" s="276"/>
-      <c r="U11" s="276"/>
-      <c r="V11" s="276"/>
-      <c r="W11" s="276"/>
-      <c r="X11" s="276"/>
-      <c r="Y11" s="276"/>
-      <c r="Z11" s="276"/>
+      <c r="P11" s="279"/>
+      <c r="Q11" s="279"/>
+      <c r="R11" s="279"/>
+      <c r="S11" s="279"/>
+      <c r="T11" s="279"/>
+      <c r="U11" s="279"/>
+      <c r="V11" s="279"/>
+      <c r="W11" s="279"/>
+      <c r="X11" s="279"/>
+      <c r="Y11" s="279"/>
+      <c r="Z11" s="279"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19260,18 +19231,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="271" t="s">
+      <c r="C18" s="274" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="271"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="271"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="271"/>
-      <c r="K18" s="271"/>
-      <c r="L18" s="271"/>
+      <c r="D18" s="274"/>
+      <c r="E18" s="274"/>
+      <c r="F18" s="274"/>
+      <c r="G18" s="274"/>
+      <c r="H18" s="274"/>
+      <c r="I18" s="274"/>
+      <c r="J18" s="274"/>
+      <c r="K18" s="274"/>
+      <c r="L18" s="274"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19484,23 +19455,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="276"/>
-      <c r="C25" s="276"/>
+      <c r="B25" s="279"/>
+      <c r="C25" s="279"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="271" t="s">
+      <c r="C26" s="274" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="271"/>
-      <c r="E26" s="271"/>
-      <c r="F26" s="271"/>
-      <c r="G26" s="271"/>
-      <c r="H26" s="271"/>
-      <c r="I26" s="271"/>
-      <c r="J26" s="271"/>
-      <c r="K26" s="271"/>
-      <c r="L26" s="271"/>
+      <c r="D26" s="274"/>
+      <c r="E26" s="274"/>
+      <c r="F26" s="274"/>
+      <c r="G26" s="274"/>
+      <c r="H26" s="274"/>
+      <c r="I26" s="274"/>
+      <c r="J26" s="274"/>
+      <c r="K26" s="274"/>
+      <c r="L26" s="274"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19692,18 +19663,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="271" t="s">
+      <c r="C33" s="274" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="271"/>
-      <c r="E33" s="271"/>
-      <c r="F33" s="271"/>
-      <c r="G33" s="271"/>
-      <c r="H33" s="271"/>
-      <c r="I33" s="271"/>
-      <c r="J33" s="271"/>
-      <c r="K33" s="271"/>
-      <c r="L33" s="271"/>
+      <c r="D33" s="274"/>
+      <c r="E33" s="274"/>
+      <c r="F33" s="274"/>
+      <c r="G33" s="274"/>
+      <c r="H33" s="274"/>
+      <c r="I33" s="274"/>
+      <c r="J33" s="274"/>
+      <c r="K33" s="274"/>
+      <c r="L33" s="274"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19887,18 +19858,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="271" t="s">
+      <c r="C40" s="274" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="271"/>
-      <c r="E40" s="271"/>
-      <c r="F40" s="271"/>
-      <c r="G40" s="271"/>
-      <c r="H40" s="271"/>
-      <c r="I40" s="271"/>
-      <c r="J40" s="271"/>
-      <c r="K40" s="271"/>
-      <c r="L40" s="271"/>
+      <c r="D40" s="274"/>
+      <c r="E40" s="274"/>
+      <c r="F40" s="274"/>
+      <c r="G40" s="274"/>
+      <c r="H40" s="274"/>
+      <c r="I40" s="274"/>
+      <c r="J40" s="274"/>
+      <c r="K40" s="274"/>
+      <c r="L40" s="274"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20217,60 +20188,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="265" t="s">
+      <c r="C2" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="265"/>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="265"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="265"/>
-      <c r="S2" s="276"/>
-      <c r="T2" s="276"/>
-      <c r="U2" s="276"/>
-      <c r="V2" s="276"/>
-      <c r="W2" s="276"/>
-      <c r="X2" s="276"/>
-      <c r="Y2" s="276"/>
-      <c r="Z2" s="276"/>
-      <c r="AA2" s="276"/>
-      <c r="AB2" s="276"/>
-      <c r="AC2" s="276"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="S2" s="279"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="279"/>
+      <c r="AB2" s="279"/>
+      <c r="AC2" s="279"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="274" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
-      <c r="S4" s="276"/>
-      <c r="T4" s="276"/>
-      <c r="U4" s="276"/>
-      <c r="V4" s="276"/>
-      <c r="W4" s="276"/>
-      <c r="X4" s="276"/>
-      <c r="Y4" s="276"/>
-      <c r="Z4" s="276"/>
-      <c r="AA4" s="276"/>
-      <c r="AB4" s="276"/>
-      <c r="AC4" s="276"/>
+      <c r="D4" s="274"/>
+      <c r="E4" s="274"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="274"/>
+      <c r="K4" s="274"/>
+      <c r="L4" s="274"/>
+      <c r="S4" s="279"/>
+      <c r="T4" s="279"/>
+      <c r="U4" s="279"/>
+      <c r="V4" s="279"/>
+      <c r="W4" s="279"/>
+      <c r="X4" s="279"/>
+      <c r="Y4" s="279"/>
+      <c r="Z4" s="279"/>
+      <c r="AA4" s="279"/>
+      <c r="AB4" s="279"/>
+      <c r="AC4" s="279"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20633,18 +20604,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="271" t="s">
+      <c r="C13" s="274" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="271"/>
-      <c r="E13" s="271"/>
-      <c r="F13" s="271"/>
-      <c r="G13" s="271"/>
-      <c r="H13" s="271"/>
-      <c r="I13" s="271"/>
-      <c r="J13" s="271"/>
-      <c r="K13" s="271"/>
-      <c r="L13" s="271"/>
+      <c r="D13" s="274"/>
+      <c r="E13" s="274"/>
+      <c r="F13" s="274"/>
+      <c r="G13" s="274"/>
+      <c r="H13" s="274"/>
+      <c r="I13" s="274"/>
+      <c r="J13" s="274"/>
+      <c r="K13" s="274"/>
+      <c r="L13" s="274"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20737,18 +20708,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="271" t="s">
+      <c r="C18" s="274" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="271"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="271"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="271"/>
-      <c r="K18" s="271"/>
-      <c r="L18" s="271"/>
+      <c r="D18" s="274"/>
+      <c r="E18" s="274"/>
+      <c r="F18" s="274"/>
+      <c r="G18" s="274"/>
+      <c r="H18" s="274"/>
+      <c r="I18" s="274"/>
+      <c r="J18" s="274"/>
+      <c r="K18" s="274"/>
+      <c r="L18" s="274"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20940,18 +20911,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="271" t="s">
+      <c r="C25" s="274" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="271"/>
-      <c r="E25" s="271"/>
-      <c r="F25" s="271"/>
-      <c r="G25" s="271"/>
-      <c r="H25" s="271"/>
-      <c r="I25" s="271"/>
-      <c r="J25" s="271"/>
-      <c r="K25" s="271"/>
-      <c r="L25" s="271"/>
+      <c r="D25" s="274"/>
+      <c r="E25" s="274"/>
+      <c r="F25" s="274"/>
+      <c r="G25" s="274"/>
+      <c r="H25" s="274"/>
+      <c r="I25" s="274"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="274"/>
+      <c r="L25" s="274"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21089,18 +21060,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="271" t="s">
+      <c r="C31" s="274" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="271"/>
-      <c r="E31" s="271"/>
-      <c r="F31" s="271"/>
-      <c r="G31" s="271"/>
-      <c r="H31" s="271"/>
-      <c r="I31" s="271"/>
-      <c r="J31" s="271"/>
-      <c r="K31" s="271"/>
-      <c r="L31" s="271"/>
+      <c r="D31" s="274"/>
+      <c r="E31" s="274"/>
+      <c r="F31" s="274"/>
+      <c r="G31" s="274"/>
+      <c r="H31" s="274"/>
+      <c r="I31" s="274"/>
+      <c r="J31" s="274"/>
+      <c r="K31" s="274"/>
+      <c r="L31" s="274"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21350,10 +21321,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="265" t="s">
+      <c r="B4" s="268" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="265"/>
+      <c r="C4" s="268"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21370,7 +21341,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21379,7 +21350,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>763766.8</v>
+        <v>822020.2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21397,7 +21368,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21406,7 +21377,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.78290000000000004</v>
+        <v>0.76980000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21438,10 +21409,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="265" t="s">
+      <c r="B15" s="268" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="265"/>
+      <c r="C15" s="268"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21449,7 +21420,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.0034901895032207E-2</v>
+        <v>7.478731323712709E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21458,7 +21429,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.91996509810496774</v>
+        <v>0.92521268676287294</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21476,7 +21447,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.6590500000000001E-2</v>
+        <v>8.4170999999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21485,7 +21456,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.3770030039768115E-2</v>
+        <v>8.1716405592244246E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21530,60 +21501,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="265" t="s">
+      <c r="C3" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="E3" s="265"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275" t="s">
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="268"/>
+      <c r="G3" s="277"/>
+      <c r="H3" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="265"/>
-      <c r="J3" s="265"/>
-      <c r="K3" s="265"/>
-      <c r="L3" s="265"/>
-      <c r="P3" s="276"/>
-      <c r="Q3" s="276"/>
-      <c r="R3" s="276"/>
-      <c r="S3" s="276"/>
-      <c r="T3" s="276"/>
-      <c r="U3" s="276"/>
-      <c r="V3" s="276"/>
-      <c r="W3" s="276"/>
-      <c r="X3" s="276"/>
-      <c r="Y3" s="276"/>
-      <c r="Z3" s="276"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="268"/>
+      <c r="K3" s="268"/>
+      <c r="L3" s="268"/>
+      <c r="P3" s="279"/>
+      <c r="Q3" s="279"/>
+      <c r="R3" s="279"/>
+      <c r="S3" s="279"/>
+      <c r="T3" s="279"/>
+      <c r="U3" s="279"/>
+      <c r="V3" s="279"/>
+      <c r="W3" s="279"/>
+      <c r="X3" s="279"/>
+      <c r="Y3" s="279"/>
+      <c r="Z3" s="279"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="274" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="271"/>
-      <c r="E5" s="271"/>
-      <c r="F5" s="271"/>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
-      <c r="P5" s="276"/>
-      <c r="Q5" s="276"/>
-      <c r="R5" s="276"/>
-      <c r="S5" s="276"/>
-      <c r="T5" s="276"/>
-      <c r="U5" s="276"/>
-      <c r="V5" s="276"/>
-      <c r="W5" s="276"/>
-      <c r="X5" s="276"/>
-      <c r="Y5" s="276"/>
-      <c r="Z5" s="276"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="274"/>
+      <c r="G5" s="274"/>
+      <c r="H5" s="274"/>
+      <c r="I5" s="274"/>
+      <c r="J5" s="274"/>
+      <c r="K5" s="274"/>
+      <c r="L5" s="274"/>
+      <c r="P5" s="279"/>
+      <c r="Q5" s="279"/>
+      <c r="R5" s="279"/>
+      <c r="S5" s="279"/>
+      <c r="T5" s="279"/>
+      <c r="U5" s="279"/>
+      <c r="V5" s="279"/>
+      <c r="W5" s="279"/>
+      <c r="X5" s="279"/>
+      <c r="Y5" s="279"/>
+      <c r="Z5" s="279"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21736,7 +21707,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>869080.97608121228</v>
+        <v>897999.80118502828</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21790,23 +21761,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13233.645410652167</v>
+        <v>13258.769313372582</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8773.9200921087231</v>
+        <v>8807.2660606026984</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21455.694436072074</v>
+        <v>21578.126643872361</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30175.621280360043</v>
+        <v>30405.42675929482</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36340.509149774109</v>
+        <v>36686.781349016725</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21825,14 +21796,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>581265.51468854188</v>
+        <v>606330.14215428662</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="265" t="s">
+      <c r="B13" s="268" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="265"/>
+      <c r="C13" s="268"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21848,14 +21819,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.3770030039768115E-2</v>
+        <v>8.1716405592244246E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="265" t="s">
+      <c r="B18" s="268" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="265"/>
+      <c r="C18" s="268"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21863,7 +21834,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>109979.39036896711</v>
+        <v>110736.37012615919</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21872,7 +21843,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>581265.51468854188</v>
+        <v>606330.14215428662</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21881,7 +21852,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>691244.90505750896</v>
+        <v>717066.51228044578</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21908,7 +21879,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>697743.90505750896</v>
+        <v>723565.51228044578</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21926,7 +21897,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>10.779963307751274</v>
+        <v>11.178900477094921</v>
       </c>
     </row>
   </sheetData>
@@ -21969,37 +21940,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="265" t="s">
+      <c r="C2" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="265"/>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="265"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="265"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="274" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
+      <c r="D4" s="274"/>
+      <c r="E4" s="274"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="274"/>
+      <c r="K4" s="274"/>
+      <c r="L4" s="274"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22195,23 +22166,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13233.645410652167</v>
+        <v>13258.769313372582</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8773.9200921087231</v>
+        <v>8807.2660606026984</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21455.694436072074</v>
+        <v>21578.126643872361</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>30175.621280360043</v>
+        <v>30405.42675929482</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36340.509149774109</v>
+        <v>36686.781349016725</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22219,18 +22190,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="274" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="271"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="271"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="271"/>
-      <c r="L11" s="271"/>
+      <c r="D11" s="274"/>
+      <c r="E11" s="274"/>
+      <c r="F11" s="274"/>
+      <c r="G11" s="274"/>
+      <c r="H11" s="274"/>
+      <c r="I11" s="274"/>
+      <c r="J11" s="274"/>
+      <c r="K11" s="274"/>
+      <c r="L11" s="274"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22424,18 +22395,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="271" t="s">
+      <c r="C17" s="274" t="s">
         <v>208</v>
       </c>
-      <c r="D17" s="271"/>
-      <c r="E17" s="271"/>
-      <c r="F17" s="271"/>
-      <c r="G17" s="271"/>
-      <c r="H17" s="271"/>
-      <c r="I17" s="271"/>
-      <c r="J17" s="271"/>
-      <c r="K17" s="271"/>
-      <c r="L17" s="271"/>
+      <c r="D17" s="274"/>
+      <c r="E17" s="274"/>
+      <c r="F17" s="274"/>
+      <c r="G17" s="274"/>
+      <c r="H17" s="274"/>
+      <c r="I17" s="274"/>
+      <c r="J17" s="274"/>
+      <c r="K17" s="274"/>
+      <c r="L17" s="274"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22569,18 +22540,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="271" t="s">
+      <c r="C22" s="274" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="271"/>
-      <c r="E22" s="271"/>
-      <c r="F22" s="271"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="271"/>
-      <c r="K22" s="271"/>
-      <c r="L22" s="271"/>
+      <c r="D22" s="274"/>
+      <c r="E22" s="274"/>
+      <c r="F22" s="274"/>
+      <c r="G22" s="274"/>
+      <c r="H22" s="274"/>
+      <c r="I22" s="274"/>
+      <c r="J22" s="274"/>
+      <c r="K22" s="274"/>
+      <c r="L22" s="274"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22664,18 +22635,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="271" t="s">
+      <c r="C27" s="274" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="271"/>
-      <c r="E27" s="271"/>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="271"/>
-      <c r="K27" s="271"/>
-      <c r="L27" s="271"/>
+      <c r="D27" s="274"/>
+      <c r="E27" s="274"/>
+      <c r="F27" s="274"/>
+      <c r="G27" s="274"/>
+      <c r="H27" s="274"/>
+      <c r="I27" s="274"/>
+      <c r="J27" s="274"/>
+      <c r="K27" s="274"/>
+      <c r="L27" s="274"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22976,10 +22947,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="265" t="s">
+      <c r="B39" s="268" t="s">
         <v>217</v>
       </c>
-      <c r="C39" s="265"/>
+      <c r="C39" s="268"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22997,7 +22968,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.3770030039768115E-2</v>
+        <v>8.1716405592244246E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23023,7 +22994,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1062492.7167168132</v>
+        <v>1072616.7270376505</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23032,7 +23003,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1136131.5979360063</v>
+        <v>1146666.3158147931</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23059,7 +23030,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1142630.5979360063</v>
+        <v>1153165.3158147931</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23077,14 +23048,14 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.653347927200912</v>
+        <v>17.816106600358328</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="265" t="s">
+      <c r="B52" s="268" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="265"/>
+      <c r="C52" s="268"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -23101,7 +23072,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.6590500000000001E-2</v>
+        <v>8.4170999999999996E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23136,14 +23107,14 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>16.846143452819938</v>
+        <v>17.034958556683026</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="265" t="s">
+      <c r="B60" s="268" t="s">
         <v>335</v>
       </c>
-      <c r="C60" s="265"/>
+      <c r="C60" s="268"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -23160,7 +23131,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.3770030039768115E-2</v>
+        <v>8.1716405592244246E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23186,7 +23157,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>835831.7104448044</v>
+        <v>843795.97102738463</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23195,7 +23166,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>909470.59166399739</v>
+        <v>917845.55980452709</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23222,7 +23193,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>915969.59166399739</v>
+        <v>924344.55980452709</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23240,14 +23211,14 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.151493861261276</v>
+        <v>14.280884958201142</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="265" t="s">
+      <c r="B73" s="268" t="s">
         <v>436</v>
       </c>
-      <c r="C73" s="265"/>
+      <c r="C73" s="268"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23264,7 +23235,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.3770030039768115E-2</v>
+        <v>8.1716405592244246E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23290,7 +23261,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1577959.4802724947</v>
+        <v>1592995.1391648273</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23299,7 +23270,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1651598.3614916878</v>
+        <v>1667044.7279419699</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23326,7 +23297,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1658097.3614916878</v>
+        <v>1673543.7279419699</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23344,7 +23315,7 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.617176428200224</v>
+        <v>25.855818804529399</v>
       </c>
     </row>
   </sheetData>
@@ -23397,10 +23368,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="265" t="s">
+      <c r="B4" s="268" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="265"/>
+      <c r="C4" s="268"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23409,7 +23380,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>10.779963307751274</v>
+        <v>11.178900477094921</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23418,7 +23389,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.653347927200912</v>
+        <v>17.816106600358328</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23427,7 +23398,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>16.846143452819938</v>
+        <v>17.034958556683026</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23436,7 +23407,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.151493861261276</v>
+        <v>14.280884958201142</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23445,7 +23416,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.617176428200224</v>
+        <v>25.855818804529399</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23454,7 +23425,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>17.009624995446725</v>
+        <v>17.233333879373362</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23463,7 +23434,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23472,7 +23443,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.44149364368192573</v>
+        <v>0.35695542357270571</v>
       </c>
     </row>
   </sheetData>
@@ -23567,37 +23538,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="265" t="s">
+      <c r="C2" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="265"/>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="265"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="265"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="274" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
+      <c r="D4" s="274"/>
+      <c r="E4" s="274"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="274"/>
+      <c r="K4" s="274"/>
+      <c r="L4" s="274"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23710,18 +23681,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="271" t="s">
+      <c r="C9" s="274" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="271"/>
-      <c r="E9" s="271"/>
-      <c r="F9" s="271"/>
-      <c r="G9" s="271"/>
-      <c r="H9" s="271"/>
-      <c r="I9" s="271"/>
-      <c r="J9" s="271"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="271"/>
+      <c r="D9" s="274"/>
+      <c r="E9" s="274"/>
+      <c r="F9" s="274"/>
+      <c r="G9" s="274"/>
+      <c r="H9" s="274"/>
+      <c r="I9" s="274"/>
+      <c r="J9" s="274"/>
+      <c r="K9" s="274"/>
+      <c r="L9" s="274"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23842,18 +23813,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="271" t="s">
+      <c r="C14" s="274" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="271"/>
-      <c r="E14" s="271"/>
-      <c r="F14" s="271"/>
-      <c r="G14" s="271"/>
-      <c r="H14" s="271"/>
-      <c r="I14" s="271"/>
-      <c r="J14" s="271"/>
-      <c r="K14" s="271"/>
-      <c r="L14" s="271"/>
+      <c r="D14" s="274"/>
+      <c r="E14" s="274"/>
+      <c r="F14" s="274"/>
+      <c r="G14" s="274"/>
+      <c r="H14" s="274"/>
+      <c r="I14" s="274"/>
+      <c r="J14" s="274"/>
+      <c r="K14" s="274"/>
+      <c r="L14" s="274"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23943,10 +23914,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="265" t="s">
+      <c r="B20" s="268" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="265"/>
+      <c r="C20" s="268"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23981,7 +23952,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.6590500000000001E-2</v>
+        <v>8.4170999999999996E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24047,60 +24018,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="265" t="s">
+      <c r="C3" s="268" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="E3" s="265"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275" t="s">
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="268"/>
+      <c r="G3" s="277"/>
+      <c r="H3" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="265"/>
-      <c r="J3" s="265"/>
-      <c r="K3" s="265"/>
-      <c r="L3" s="265"/>
-      <c r="P3" s="276"/>
-      <c r="Q3" s="276"/>
-      <c r="R3" s="276"/>
-      <c r="S3" s="276"/>
-      <c r="T3" s="276"/>
-      <c r="U3" s="276"/>
-      <c r="V3" s="276"/>
-      <c r="W3" s="276"/>
-      <c r="X3" s="276"/>
-      <c r="Y3" s="276"/>
-      <c r="Z3" s="276"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="268"/>
+      <c r="K3" s="268"/>
+      <c r="L3" s="268"/>
+      <c r="P3" s="279"/>
+      <c r="Q3" s="279"/>
+      <c r="R3" s="279"/>
+      <c r="S3" s="279"/>
+      <c r="T3" s="279"/>
+      <c r="U3" s="279"/>
+      <c r="V3" s="279"/>
+      <c r="W3" s="279"/>
+      <c r="X3" s="279"/>
+      <c r="Y3" s="279"/>
+      <c r="Z3" s="279"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="274" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="271"/>
-      <c r="E5" s="271"/>
-      <c r="F5" s="271"/>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
-      <c r="P5" s="276"/>
-      <c r="Q5" s="276"/>
-      <c r="R5" s="276"/>
-      <c r="S5" s="276"/>
-      <c r="T5" s="276"/>
-      <c r="U5" s="276"/>
-      <c r="V5" s="276"/>
-      <c r="W5" s="276"/>
-      <c r="X5" s="276"/>
-      <c r="Y5" s="276"/>
-      <c r="Z5" s="276"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="274"/>
+      <c r="G5" s="274"/>
+      <c r="H5" s="274"/>
+      <c r="I5" s="274"/>
+      <c r="J5" s="274"/>
+      <c r="K5" s="274"/>
+      <c r="L5" s="274"/>
+      <c r="P5" s="279"/>
+      <c r="Q5" s="279"/>
+      <c r="R5" s="279"/>
+      <c r="S5" s="279"/>
+      <c r="T5" s="279"/>
+      <c r="U5" s="279"/>
+      <c r="V5" s="279"/>
+      <c r="W5" s="279"/>
+      <c r="X5" s="279"/>
+      <c r="Y5" s="279"/>
+      <c r="Z5" s="279"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24234,7 +24205,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>820188.25955362816</v>
+        <v>847480.17075986101</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24288,23 +24259,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10703.377726337705</v>
+        <v>10723.697948954514</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14320.286844082762</v>
+        <v>14374.712212551407</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19159.429905215289</v>
+        <v>19268.758983818618</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25633.826912101231</v>
+        <v>25829.043899209319</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>34296.066501472538</v>
+        <v>34622.85813567588</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24323,15 +24294,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>548564.70680171566</v>
+        <v>572219.24963866326</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="277" t="s">
+      <c r="B14" s="280" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="278"/>
+      <c r="C14" s="281"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24339,7 +24310,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24348,7 +24319,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>10.619720879169423</v>
+        <v>11.012184769358846</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24358,20 +24329,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="279" t="s">
+      <c r="E17" s="282" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="279"/>
-      <c r="G17" s="279"/>
-      <c r="H17" s="279"/>
-      <c r="I17" s="279"/>
+      <c r="F17" s="282"/>
+      <c r="G17" s="282"/>
+      <c r="H17" s="282"/>
+      <c r="I17" s="282"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="277" t="s">
+      <c r="B19" s="280" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="278"/>
+      <c r="C19" s="281"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24387,7 +24358,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.3770030039768115E-2</v>
+        <v>8.1716405592244246E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24405,7 +24376,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>732437.8</v>
+        <v>788301.7</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24432,15 +24403,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>725938.8</v>
+        <v>781802.7</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="277" t="s">
+      <c r="B28" s="280" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="278"/>
+      <c r="C28" s="281"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24448,7 +24419,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>104112.98788920953</v>
+        <v>104819.07118020974</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24457,7 +24428,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>548564.70680171566</v>
+        <v>572219.24963866326</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24466,7 +24437,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>652677.69469092519</v>
+        <v>677038.32081887301</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24493,7 +24464,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>659176.69469092519</v>
+        <v>683537.32081887301</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24511,7 +24482,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>10.619720879169423</v>
+        <v>11.012184769358846</v>
       </c>
     </row>
   </sheetData>
@@ -31484,7 +31455,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31555,7 +31526,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32633,7 +32604,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-660.62597296190086</v>
+        <v>-711.01269971323222</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32670,7 +32641,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.4381942051190151</v>
+        <v>1.54788698347555</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32731,7 +32702,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.9697077592906838</v>
+        <v>2.1199397070331933</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32792,7 +32763,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>763766.8</v>
+        <v>822020.2</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32853,7 +32824,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>757267.8</v>
+        <v>815521.2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32890,7 +32861,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.4912923179327011</v>
+        <v>1.6060111108266557</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32927,7 +32898,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>60.392997846718245</v>
+        <v>65.038775021931571</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33062,7 +33033,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>94.338784584980246</v>
+        <v>101.53411561264822</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33099,7 +33070,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-125.91142520734358</v>
+        <v>-135.59725711142488</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33136,7 +33107,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>1.0600094164868124E-2</v>
+        <v>9.8489063894050301E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33173,7 +33144,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.5137158406238916E-3</v>
+        <v>-1.4064446393198364E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33787,7 +33758,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>8.5091417956370975E-3</v>
+        <v>7.9061317471273828E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35422,15 +35393,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="265" t="s">
+      <c r="B4" s="268" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="265"/>
-      <c r="E4" s="265" t="s">
+      <c r="C4" s="268"/>
+      <c r="E4" s="268" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35438,7 +35409,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35454,7 +35425,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>763766.8</v>
+        <v>822020.2</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35474,7 +35445,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>757267.8</v>
+        <v>815521.2</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35494,7 +35465,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-660.62597296190086</v>
+        <v>-711.01269971323222</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35514,7 +35485,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.4381942051190151</v>
+        <v>1.54788698347555</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35534,7 +35505,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.9697077592906838</v>
+        <v>2.1199397070331933</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35554,7 +35525,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.4912923179327011</v>
+        <v>1.6060111108266557</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35563,18 +35534,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>60.392997846718245</v>
+        <v>65.038775021931571</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="265" t="s">
+      <c r="B15" s="268" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="265"/>
-      <c r="E15" s="265" t="s">
+      <c r="C15" s="268"/>
+      <c r="E15" s="268" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="265"/>
+      <c r="F15" s="268"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35625,14 +35596,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="265" t="s">
+      <c r="B21" s="268" t="s">
         <v>257</v>
       </c>
-      <c r="C21" s="265"/>
-      <c r="E21" s="265" t="s">
+      <c r="C21" s="268"/>
+      <c r="E21" s="268" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="265"/>
+      <c r="F21" s="268"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35701,14 +35672,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="265" t="s">
+      <c r="B29" s="268" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="265"/>
-      <c r="E29" s="265" t="s">
+      <c r="C29" s="268"/>
+      <c r="E29" s="268" t="s">
         <v>268</v>
       </c>
-      <c r="F29" s="265"/>
+      <c r="F29" s="268"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35784,14 +35755,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="265" t="s">
+      <c r="B37" s="268" t="s">
         <v>280</v>
       </c>
-      <c r="C37" s="265"/>
-      <c r="E37" s="265" t="s">
+      <c r="C37" s="268"/>
+      <c r="E37" s="268" t="s">
         <v>283</v>
       </c>
-      <c r="F37" s="265"/>
+      <c r="F37" s="268"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35799,7 +35770,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.5137158406238916E-3</v>
+        <v>-1.4064446393198364E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35815,7 +35786,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>1.0600094164868124E-2</v>
+        <v>9.8489063894050301E-3</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35860,14 +35831,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="265" t="s">
+      <c r="B45" s="268" t="s">
         <v>291</v>
       </c>
-      <c r="C45" s="265"/>
-      <c r="E45" s="265" t="s">
+      <c r="C45" s="268"/>
+      <c r="E45" s="268" t="s">
         <v>297</v>
       </c>
-      <c r="F45" s="265"/>
+      <c r="F45" s="268"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35900,18 +35871,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>8.5091417956370975E-3</v>
+        <v>7.9061317471273828E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="265" t="s">
+      <c r="B51" s="268" t="s">
         <v>294</v>
       </c>
-      <c r="C51" s="265"/>
-      <c r="E51" s="265" t="s">
+      <c r="C51" s="268"/>
+      <c r="E51" s="268" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="265"/>
+      <c r="F51" s="268"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36079,7 +36050,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36108,7 +36079,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>763766.8</v>
+        <v>822020.2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36137,7 +36108,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>757267.8</v>
+        <v>815521.2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36166,7 +36137,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-660.62597296190086</v>
+        <v>-711.01269971323222</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36195,7 +36166,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.4381942051190151</v>
+        <v>1.54788698347555</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36224,7 +36195,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>1.9697077592906838</v>
+        <v>2.1199397070331933</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36253,7 +36224,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.4912923179327011</v>
+        <v>1.6060111108266557</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36282,7 +36253,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>60.392997846718245</v>
+        <v>65.038775021931571</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37055,7 +37026,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.5137158406238916E-3</v>
+        <v>-1.4064446393198364E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37084,7 +37055,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.0600094164868124E-2</v>
+        <v>9.8489063894050301E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37407,7 +37378,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>8.5091417956370975E-3</v>
+        <v>7.9061317471273828E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37896,14 +37867,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="269" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="F3" s="268" t="s">
+      <c r="D3" s="270"/>
+      <c r="F3" s="271" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="267"/>
+      <c r="G3" s="270"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37970,19 +37941,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="269">
+      <c r="C7" s="272">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="270"/>
-      <c r="F7" s="269">
+      <c r="D7" s="273"/>
+      <c r="F7" s="272">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="270"/>
+      <c r="G7" s="273"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -38009,19 +37980,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="269">
+      <c r="C9" s="272">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="270"/>
-      <c r="F9" s="269">
+      <c r="D9" s="273"/>
+      <c r="F9" s="272">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="270"/>
+      <c r="G9" s="273"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -38048,19 +38019,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="269">
+      <c r="C11" s="272">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="270"/>
-      <c r="F11" s="269">
+      <c r="D11" s="273"/>
+      <c r="F11" s="272">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="270"/>
+      <c r="G11" s="273"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -38087,19 +38058,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="269">
+      <c r="C13" s="272">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="270"/>
-      <c r="F13" s="269">
+      <c r="D13" s="273"/>
+      <c r="F13" s="272">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="270"/>
+      <c r="G13" s="273"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -38126,19 +38097,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="269">
+      <c r="C15" s="272">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="270"/>
-      <c r="F15" s="269">
+      <c r="D15" s="273"/>
+      <c r="F15" s="272">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="270"/>
+      <c r="G15" s="273"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -38165,19 +38136,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="269">
+      <c r="C17" s="272">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="270"/>
-      <c r="F17" s="269">
+      <c r="D17" s="273"/>
+      <c r="F17" s="272">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="270"/>
+      <c r="G17" s="273"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -38204,22 +38175,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="269">
+      <c r="C19" s="272">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="270"/>
-      <c r="F19" s="269">
+      <c r="D19" s="273"/>
+      <c r="F19" s="272">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="270"/>
+      <c r="G19" s="273"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -38246,22 +38217,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="269">
+      <c r="C21" s="272">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="270"/>
-      <c r="F21" s="269">
+      <c r="D21" s="273"/>
+      <c r="F21" s="272">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="270"/>
+      <c r="G21" s="273"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38310,22 +38281,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="269">
+      <c r="C25" s="272">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="270"/>
-      <c r="F25" s="269">
+      <c r="D25" s="273"/>
+      <c r="F25" s="272">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="270"/>
+      <c r="G25" s="273"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38353,22 +38324,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="269">
+      <c r="C27" s="272">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="F27" s="269">
+      <c r="D27" s="273"/>
+      <c r="F27" s="272">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="270"/>
+      <c r="G27" s="273"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38396,22 +38367,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="269">
+      <c r="C29" s="272">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="270"/>
-      <c r="F29" s="269">
+      <c r="D29" s="273"/>
+      <c r="F29" s="272">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="270"/>
+      <c r="G29" s="273"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38460,22 +38431,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="269">
+      <c r="C33" s="272">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="270"/>
-      <c r="F33" s="269">
+      <c r="D33" s="273"/>
+      <c r="F33" s="272">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="270"/>
+      <c r="G33" s="273"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38503,22 +38474,22 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="269">
+      <c r="C35" s="272">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="270"/>
-      <c r="F35" s="269">
+      <c r="D35" s="273"/>
+      <c r="F35" s="272">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="270"/>
+      <c r="G35" s="273"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EEAFA4-7567-9340-AC60-CBD64688655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928B0207-7412-C94E-8707-3695DA1792EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2532,6 +2532,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2539,12 +2545,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2565,14 +2565,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12981,13 +12981,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>24.07</v>
+    <v>23.865100000000002</v>
     <v>7.77</v>
-    <v>0.76980000000000004</v>
+    <v>0.75829999999999997</v>
+    <v>-0.09</v>
+    <v>-7.0869999999999995E-3</v>
     <v>-0.02</v>
-    <v>-1.572E-3</v>
-    <v>0</v>
-    <v>0</v>
+    <v>-1.586E-3</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12995,25 +12995,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>12.7</v>
+    <v>12.85</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46318.937500022657</v>
+    <v>46321.843751260938</v>
     <v>0</v>
-    <v>12.350099999999999</v>
-    <v>788300938</v>
+    <v>12.56</v>
+    <v>782714553</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>12.55</v>
-    <v>75.192400000000006</v>
-    <v>12.72</v>
+    <v>12.69</v>
+    <v>74.659599999999998</v>
     <v>12.7</v>
-    <v>12.7</v>
+    <v>12.61</v>
+    <v>12.59</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>696514</v>
-    <v>718903</v>
+    <v>574947</v>
+    <v>679066</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -13037,17 +13037,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>822020.2</v>
+        <v>816194.86</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>11.178900477094921</v>
+        <v>11.213353487232084</v>
       </c>
       <c r="K3" s="260" t="s">
         <v>444</v>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>815521.2</v>
+        <v>809695.86</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.816106600358328</v>
+        <v>17.829749171595605</v>
       </c>
       <c r="K4" s="260" t="s">
         <v>445</v>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>17.034958556683026</v>
+        <v>17.048123816270984</v>
       </c>
       <c r="K5" s="260" t="s">
         <v>446</v>
@@ -13964,14 +13964,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>12.7</v>
+        <v>12.59</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-711.01269971323222</v>
+        <v>-705.97402703809905</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.280884958201142</v>
+        <v>14.291730446868652</v>
       </c>
       <c r="K6" s="261" t="s">
         <v>447</v>
@@ -13991,14 +13991,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.54788698347555</v>
+        <v>1.5369177056398964</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.855818804529399</v>
+        <v>25.875822430644842</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -14015,14 +14015,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>9.8489063894050301E-3</v>
+        <v>9.9191999322318699E-3</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>17.233333879373362</v>
+        <v>17.251755870522434</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14039,14 +14039,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.572E-3</v>
+        <v>-7.0869999999999995E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.4064446393198364E-3</v>
+        <v>-1.4164827057384552E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.35695542357270571</v>
+        <v>0.36810117926426922</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-1.586E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="C11" s="209" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>24.07</v>
+        <v>23.865100000000002</v>
       </c>
       <c r="E11" s="186" t="s">
         <v>301</v>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.76980000000000004</v>
+        <v>0.75829999999999997</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14141,7 +14141,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>718903</v>
+        <v>679066</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="I14" s="263">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>11.012184769358846</v>
+        <v>11.046079044331362</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>7.9061317471273828E-3</v>
+        <v>7.9625593329514469E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="I17" s="258">
         <f ca="1">DCF!C15</f>
-        <v>8.1716405592244246E-2</v>
+        <v>8.1545315069608271E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="I18" s="259">
         <f ca="1">Multiples!C54</f>
-        <v>8.4170999999999996E-2</v>
+        <v>8.4003499999999995E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20138,6 +20138,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20145,12 +20151,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21210,16 +21210,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>822020.2</v>
+        <v>816194.86</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21368,7 +21368,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.76980000000000004</v>
+        <v>0.75829999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21420,7 +21420,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.478731323712709E-2</v>
+        <v>7.528090190612749E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21429,7 +21429,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92521268676287294</v>
+        <v>0.92471909809387254</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.4170999999999996E-2</v>
+        <v>8.4003499999999995E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.1716405592244246E-2</v>
+        <v>8.1545315069608271E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21707,7 +21707,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>897999.80118502828</v>
+        <v>900496.16106454108</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21761,23 +21761,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13258.769313372582</v>
+        <v>13260.866728746425</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8807.2660606026984</v>
+        <v>8810.0527379918021</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21578.126643872361</v>
+        <v>21588.368647481122</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30405.42675929482</v>
+        <v>30424.670760613342</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36686.781349016725</v>
+        <v>36715.808088225553</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21796,7 +21796,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>606330.14215428662</v>
+        <v>608496.75085152558</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21819,7 +21819,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1716405592244246E-2</v>
+        <v>8.1545315069608271E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>110736.37012615919</v>
+        <v>110799.76696305824</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>606330.14215428662</v>
+        <v>608496.75085152558</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21852,7 +21852,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>717066.51228044578</v>
+        <v>719296.51781458384</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21879,7 +21879,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>723565.51228044578</v>
+        <v>725795.51781458384</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>11.178900477094921</v>
+        <v>11.213353487232084</v>
       </c>
     </row>
   </sheetData>
@@ -22166,23 +22166,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13258.769313372582</v>
+        <v>13260.866728746425</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8807.2660606026984</v>
+        <v>8810.0527379918021</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21578.126643872361</v>
+        <v>21588.368647481122</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>30405.42675929482</v>
+        <v>30424.670760613342</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36686.781349016725</v>
+        <v>36715.808088225553</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22968,7 +22968,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1716405592244246E-2</v>
+        <v>8.1545315069608271E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1072616.7270376505</v>
+        <v>1073465.3860058645</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1146666.3158147931</v>
+        <v>1147549.3448806971</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1153165.3158147931</v>
+        <v>1154048.3448806971</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.816106600358328</v>
+        <v>17.829749171595605</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.4170999999999996E-2</v>
+        <v>8.4003499999999995E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>17.034958556683026</v>
+        <v>17.048123816270984</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23131,7 +23131,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1716405592244246E-2</v>
+        <v>8.1545315069608271E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23157,7 +23157,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>843795.97102738463</v>
+        <v>844463.58602918766</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>917845.55980452709</v>
+        <v>918547.54490402038</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>924344.55980452709</v>
+        <v>925046.54490402038</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.280884958201142</v>
+        <v>14.291730446868652</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23235,7 +23235,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1716405592244246E-2</v>
+        <v>8.1545315069608271E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23261,7 +23261,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1592995.1391648273</v>
+        <v>1594255.5237710855</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1667044.7279419699</v>
+        <v>1668339.4826459181</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1673543.7279419699</v>
+        <v>1674838.4826459181</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23315,22 +23315,22 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.855818804529399</v>
+        <v>25.875822430644842</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>11.178900477094921</v>
+        <v>11.213353487232084</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.816106600358328</v>
+        <v>17.829749171595605</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>17.034958556683026</v>
+        <v>17.048123816270984</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23407,7 +23407,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.280884958201142</v>
+        <v>14.291730446868652</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23416,7 +23416,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.855818804529399</v>
+        <v>25.875822430644842</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>17.233333879373362</v>
+        <v>17.251755870522434</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23434,7 +23434,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.35695542357270571</v>
+        <v>0.36810117926426922</v>
       </c>
     </row>
   </sheetData>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.4170999999999996E-2</v>
+        <v>8.4003499999999995E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24205,7 +24205,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>847480.17075986101</v>
+        <v>849836.09054311237</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24259,23 +24259,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10723.697948954514</v>
+        <v>10725.394339351766</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14374.712212551407</v>
+        <v>14379.260466824864</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19268.758983818618</v>
+        <v>19277.904851868505</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25829.043899209319</v>
+        <v>25845.391446599049</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>34622.85813567588</v>
+        <v>34650.251889960498</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24294,15 +24294,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>572219.24963866326</v>
+        <v>574263.96936608723</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="280" t="s">
+      <c r="B14" s="281" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="281"/>
+      <c r="C14" s="282"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>11.012184769358846</v>
+        <v>11.046079044331362</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24329,20 +24329,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="282" t="s">
+      <c r="E17" s="280" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="282"/>
-      <c r="G17" s="282"/>
-      <c r="H17" s="282"/>
-      <c r="I17" s="282"/>
+      <c r="F17" s="280"/>
+      <c r="G17" s="280"/>
+      <c r="H17" s="280"/>
+      <c r="I17" s="280"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="280" t="s">
+      <c r="B19" s="281" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="281"/>
+      <c r="C19" s="282"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24358,7 +24358,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1716405592244246E-2</v>
+        <v>8.1545315069608271E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>788301.7</v>
+        <v>782715.30999999994</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24403,15 +24403,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>781802.7</v>
+        <v>776216.30999999994</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="280" t="s">
+      <c r="B28" s="281" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="281"/>
+      <c r="C28" s="282"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24419,7 +24419,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>104819.07118020974</v>
+        <v>104878.20299460468</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24428,7 +24428,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>572219.24963866326</v>
+        <v>574263.96936608723</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>677038.32081887301</v>
+        <v>679142.17236069194</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>683537.32081887301</v>
+        <v>685641.17236069194</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24482,21 +24482,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>11.012184769358846</v>
+        <v>11.046079044331362</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31455,7 +31455,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32604,7 +32604,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-711.01269971323222</v>
+        <v>-705.97402703809905</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32641,7 +32641,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.54788698347555</v>
+        <v>1.5369177056398964</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32702,7 +32702,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>2.1199397070331933</v>
+        <v>2.1049165122589422</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32763,7 +32763,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>822020.2</v>
+        <v>816194.86</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32824,7 +32824,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>815521.2</v>
+        <v>809695.86</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32861,7 +32861,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.6060111108266557</v>
+        <v>1.5945392315372602</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32898,7 +32898,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>65.038775021931571</v>
+        <v>64.574197304410234</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33033,7 +33033,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>101.53411561264822</v>
+        <v>100.81458250988142</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33070,7 +33070,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-135.59725711142488</v>
+        <v>-134.62867392101677</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33107,7 +33107,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>9.8489063894050301E-3</v>
+        <v>9.9191999322318699E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33144,7 +33144,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.4064446393198364E-3</v>
+        <v>-1.4164827057384552E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33758,7 +33758,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>7.9061317471273828E-3</v>
+        <v>7.9625593329514469E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>822020.2</v>
+        <v>816194.86</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35445,7 +35445,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>815521.2</v>
+        <v>809695.86</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35465,7 +35465,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-711.01269971323222</v>
+        <v>-705.97402703809905</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35485,7 +35485,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.54788698347555</v>
+        <v>1.5369177056398964</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35505,7 +35505,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>2.1199397070331933</v>
+        <v>2.1049165122589422</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35525,7 +35525,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.6060111108266557</v>
+        <v>1.5945392315372602</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35534,7 +35534,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>65.038775021931571</v>
+        <v>64.574197304410234</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35770,7 +35770,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.4064446393198364E-3</v>
+        <v>-1.4164827057384552E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35786,7 +35786,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>9.8489063894050301E-3</v>
+        <v>9.9191999322318699E-3</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35871,7 +35871,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>7.9061317471273828E-3</v>
+        <v>7.9625593329514469E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36050,7 +36050,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>12.7</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36079,7 +36079,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>822020.2</v>
+        <v>816194.86</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>815521.2</v>
+        <v>809695.86</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36137,7 +36137,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-711.01269971323222</v>
+        <v>-705.97402703809905</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.54788698347555</v>
+        <v>1.5369177056398964</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36195,7 +36195,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>2.1199397070331933</v>
+        <v>2.1049165122589422</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36224,7 +36224,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.6060111108266557</v>
+        <v>1.5945392315372602</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36253,7 +36253,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>65.038775021931571</v>
+        <v>64.574197304410234</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37026,7 +37026,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.4064446393198364E-3</v>
+        <v>-1.4164827057384552E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>9.8489063894050301E-3</v>
+        <v>9.9191999322318699E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37378,7 +37378,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>7.9061317471273828E-3</v>
+        <v>7.9625593329514469E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37867,14 +37867,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="269" t="s">
+      <c r="C3" s="271" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="270"/>
-      <c r="F3" s="271" t="s">
+      <c r="D3" s="272"/>
+      <c r="F3" s="273" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="270"/>
+      <c r="G3" s="272"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37941,19 +37941,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="272">
+      <c r="C7" s="269">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="273"/>
-      <c r="F7" s="272">
+      <c r="D7" s="270"/>
+      <c r="F7" s="269">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="273"/>
+      <c r="G7" s="270"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37980,19 +37980,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="272">
+      <c r="C9" s="269">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="273"/>
-      <c r="F9" s="272">
+      <c r="D9" s="270"/>
+      <c r="F9" s="269">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="273"/>
+      <c r="G9" s="270"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -38019,19 +38019,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="272">
+      <c r="C11" s="269">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="273"/>
-      <c r="F11" s="272">
+      <c r="D11" s="270"/>
+      <c r="F11" s="269">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="273"/>
+      <c r="G11" s="270"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -38058,19 +38058,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="272">
+      <c r="C13" s="269">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="273"/>
-      <c r="F13" s="272">
+      <c r="D13" s="270"/>
+      <c r="F13" s="269">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="273"/>
+      <c r="G13" s="270"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -38097,19 +38097,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="272">
+      <c r="C15" s="269">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="273"/>
-      <c r="F15" s="272">
+      <c r="D15" s="270"/>
+      <c r="F15" s="269">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="273"/>
+      <c r="G15" s="270"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -38136,19 +38136,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="272">
+      <c r="C17" s="269">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="273"/>
-      <c r="F17" s="272">
+      <c r="D17" s="270"/>
+      <c r="F17" s="269">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="273"/>
+      <c r="G17" s="270"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -38175,22 +38175,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="272">
+      <c r="C19" s="269">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="273"/>
-      <c r="F19" s="272">
+      <c r="D19" s="270"/>
+      <c r="F19" s="269">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="273"/>
+      <c r="G19" s="270"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -38217,22 +38217,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="272">
+      <c r="C21" s="269">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="273"/>
-      <c r="F21" s="272">
+      <c r="D21" s="270"/>
+      <c r="F21" s="269">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="273"/>
+      <c r="G21" s="270"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38281,22 +38281,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="272">
+      <c r="C25" s="269">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="273"/>
-      <c r="F25" s="272">
+      <c r="D25" s="270"/>
+      <c r="F25" s="269">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="273"/>
+      <c r="G25" s="270"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38324,22 +38324,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="272">
+      <c r="C27" s="269">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="273"/>
-      <c r="F27" s="272">
+      <c r="D27" s="270"/>
+      <c r="F27" s="269">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="273"/>
+      <c r="G27" s="270"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38367,22 +38367,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="272">
+      <c r="C29" s="269">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="273"/>
-      <c r="F29" s="272">
+      <c r="D29" s="270"/>
+      <c r="F29" s="269">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="273"/>
+      <c r="G29" s="270"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38431,22 +38431,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="272">
+      <c r="C33" s="269">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="273"/>
-      <c r="F33" s="272">
+      <c r="D33" s="270"/>
+      <c r="F33" s="269">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="273"/>
+      <c r="G33" s="270"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38474,25 +38474,43 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="272">
+      <c r="C35" s="269">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="273"/>
-      <c r="F35" s="272">
+      <c r="D35" s="270"/>
+      <c r="F35" s="269">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="273"/>
+      <c r="G35" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38503,24 +38521,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928B0207-7412-C94E-8707-3695DA1792EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B94F1F0-3815-5647-B111-8EF166D41E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="454">
   <si>
     <t>Ticker</t>
   </si>
@@ -1547,6 +1547,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2532,12 +2544,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2545,6 +2551,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2565,14 +2577,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12983,11 +12995,11 @@
     <v>Powered by Refinitiv</v>
     <v>23.865100000000002</v>
     <v>7.77</v>
-    <v>0.75829999999999997</v>
-    <v>-0.09</v>
-    <v>-7.0869999999999995E-3</v>
-    <v>-0.02</v>
-    <v>-1.586E-3</v>
+    <v>0.7742</v>
+    <v>-0.32</v>
+    <v>-2.5377E-2</v>
+    <v>-0.24</v>
+    <v>-1.9528E-2</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12995,25 +13007,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>12.85</v>
+    <v>12.685</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46321.843751260938</v>
+    <v>46322.859079837501</v>
     <v>0</v>
-    <v>12.56</v>
-    <v>782714553</v>
+    <v>12.1745</v>
+    <v>762851852</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>12.69</v>
-    <v>74.659599999999998</v>
-    <v>12.7</v>
+    <v>12.46</v>
+    <v>72.764899999999997</v>
     <v>12.61</v>
-    <v>12.59</v>
+    <v>12.29</v>
+    <v>12.05</v>
     <v>62070940</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>574947</v>
-    <v>679066</v>
+    <v>646633</v>
+    <v>670458</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -13037,17 +13049,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13890,7 +13902,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>816194.86</v>
+        <v>795482.53999999992</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13898,7 +13910,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>11.213353487232084</v>
+        <v>11.096778138761671</v>
       </c>
       <c r="K3" s="260" t="s">
         <v>444</v>
@@ -13917,7 +13929,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>809695.86</v>
+        <v>788983.53999999992</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13925,7 +13937,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>17.829749171595605</v>
+        <v>17.78332872639329</v>
       </c>
       <c r="K4" s="260" t="s">
         <v>445</v>
@@ -13937,7 +13949,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>255</v>
@@ -13952,7 +13964,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>17.048123816270984</v>
+        <v>16.993538282962714</v>
       </c>
       <c r="K5" s="260" t="s">
         <v>446</v>
@@ -13964,14 +13976,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>12.59</v>
+        <v>12.05</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>249</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-705.97402703809905</v>
+        <v>-688.05874641540345</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13979,7 +13991,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>14.291730446868652</v>
+        <v>14.254827286655088</v>
       </c>
       <c r="K6" s="261" t="s">
         <v>447</v>
@@ -13991,14 +14003,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.09</v>
+        <v>-0.32</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>213</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>1.5369177056398964</v>
+        <v>1.4979158288909062</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -14006,7 +14018,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>25.875822430644842</v>
+        <v>25.807758015128989</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -14015,14 +14027,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>9.9191999322318699E-3</v>
+        <v>1.0177470394259062E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -14030,7 +14042,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>17.251755870522434</v>
+        <v>17.187246089980352</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14039,14 +14051,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-7.0869999999999995E-3</v>
+        <v>-2.5377E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>300</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-1.4164827057384552E-3</v>
+        <v>-1.4533642733410839E-3</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -14054,7 +14066,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.36810117926426922</v>
+        <v>0.39847405125958935</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14063,7 +14075,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.586E-3</v>
+        <v>-1.9528E-2</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>305</v>
@@ -14118,7 +14130,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.75829999999999997</v>
+        <v>0.7742</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>114</v>
@@ -14141,7 +14153,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>679066</v>
+        <v>670458</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>115</v>
@@ -14155,7 +14167,7 @@
       </c>
       <c r="I14" s="263">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>11.046079044331362</v>
+        <v>10.931394429506236</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14164,7 +14176,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>7.9625593329514469E-3</v>
+        <v>8.1698839046800455E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14197,7 +14209,7 @@
       </c>
       <c r="I17" s="258">
         <f ca="1">DCF!C15</f>
-        <v>8.1545315069608271E-2</v>
+        <v>8.2128128342820614E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14219,7 +14231,7 @@
       </c>
       <c r="I18" s="259">
         <f ca="1">Multiples!C54</f>
-        <v>8.4003499999999995E-2</v>
+        <v>8.4698999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14291,7 +14303,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14306,7 +14318,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20138,12 +20150,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20151,6 +20157,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21210,16 +21222,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21341,7 +21353,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21350,7 +21362,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>816194.86</v>
+        <v>795482.53999999992</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21368,7 +21380,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21377,7 +21389,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.75829999999999997</v>
+        <v>0.7742</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21420,7 +21432,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.528090190612749E-2</v>
+        <v>7.7089917454177814E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21429,7 +21441,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92471909809387254</v>
+        <v>0.92291008254582219</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21447,7 +21459,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.4003499999999995E-2</v>
+        <v>8.4698999999999997E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21456,7 +21468,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.1545315069608271E-2</v>
+        <v>8.2128128342820614E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21707,7 +21719,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>900496.16106454108</v>
+        <v>892048.76164749719</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21761,23 +21773,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>13260.866728746425</v>
+        <v>13253.724682493874</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8810.0527379918021</v>
+        <v>8800.5654456155607</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>21588.368647481122</v>
+        <v>21553.506197462295</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>30424.670760613342</v>
+        <v>30359.179137053623</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>36715.808088225553</v>
+        <v>36617.042412757037</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21796,7 +21808,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>608496.75085152558</v>
+        <v>601167.04393410543</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21819,7 +21831,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1545315069608271E-2</v>
+        <v>8.2128128342820614E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21834,7 +21846,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>110799.76696305824</v>
+        <v>110584.01787538239</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21843,7 +21855,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>608496.75085152558</v>
+        <v>601167.04393410543</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21852,7 +21864,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>719296.51781458384</v>
+        <v>711751.06180948787</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21879,7 +21891,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>725795.51781458384</v>
+        <v>718250.06180948787</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21897,7 +21909,7 @@
       </c>
       <c r="C26" s="257">
         <f ca="1">C24/C25</f>
-        <v>11.213353487232084</v>
+        <v>11.096778138761671</v>
       </c>
     </row>
   </sheetData>
@@ -22166,23 +22178,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>13260.866728746425</v>
+        <v>13253.724682493874</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>8810.0527379918021</v>
+        <v>8800.5654456155607</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>21588.368647481122</v>
+        <v>21553.506197462295</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>30424.670760613342</v>
+        <v>30359.179137053623</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>36715.808088225553</v>
+        <v>36617.042412757037</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22968,7 +22980,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1545315069608271E-2</v>
+        <v>8.2128128342820614E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22994,7 +23006,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1073465.3860058645</v>
+        <v>1070577.7596819068</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23003,7 +23015,7 @@
       </c>
       <c r="C45" s="112">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1147549.3448806971</v>
+        <v>1144544.7351445321</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23030,7 +23042,7 @@
       </c>
       <c r="C48" s="112">
         <f ca="1">C45+C46-C47</f>
-        <v>1154048.3448806971</v>
+        <v>1151043.7351445321</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23048,7 +23060,7 @@
       </c>
       <c r="C50" s="257">
         <f ca="1">C48/C49</f>
-        <v>17.829749171595605</v>
+        <v>17.78332872639329</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23072,7 +23084,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.4003499999999995E-2</v>
+        <v>8.4698999999999997E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23107,7 +23119,7 @@
       </c>
       <c r="C58" s="257">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>17.048123816270984</v>
+        <v>16.993538282962714</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23131,7 +23143,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1545315069608271E-2</v>
+        <v>8.2128128342820614E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23157,7 +23169,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>844463.58602918766</v>
+        <v>842191.97549341188</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23166,7 +23178,7 @@
       </c>
       <c r="C66" s="112">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>918547.54490402038</v>
+        <v>916158.95095603727</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23193,7 +23205,7 @@
       </c>
       <c r="C69" s="112">
         <f ca="1">C66+C67-C68</f>
-        <v>925046.54490402038</v>
+        <v>922657.95095603727</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23211,7 +23223,7 @@
       </c>
       <c r="C71" s="257">
         <f ca="1">C69/C70</f>
-        <v>14.291730446868652</v>
+        <v>14.254827286655088</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23235,7 +23247,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1545315069608271E-2</v>
+        <v>8.2128128342820614E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23261,7 +23273,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>1594255.5237710855</v>
+        <v>1589966.9698246138</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23270,7 +23282,7 @@
       </c>
       <c r="C79" s="112">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>1668339.4826459181</v>
+        <v>1663933.945287239</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23297,7 +23309,7 @@
       </c>
       <c r="C82" s="112">
         <f ca="1">C79+C80-C81</f>
-        <v>1674838.4826459181</v>
+        <v>1670432.945287239</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23315,22 +23327,22 @@
       </c>
       <c r="C84" s="257">
         <f ca="1">C82/C83</f>
-        <v>25.875822430644842</v>
+        <v>25.807758015128989</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23380,7 +23392,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>11.213353487232084</v>
+        <v>11.096778138761671</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23389,7 +23401,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>17.829749171595605</v>
+        <v>17.78332872639329</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23398,7 +23410,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>17.048123816270984</v>
+        <v>16.993538282962714</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23407,7 +23419,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>14.291730446868652</v>
+        <v>14.254827286655088</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23416,7 +23428,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>25.875822430644842</v>
+        <v>25.807758015128989</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23425,7 +23437,7 @@
       </c>
       <c r="C10" s="257">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>17.251755870522434</v>
+        <v>17.187246089980352</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23434,7 +23446,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23443,7 +23455,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.36810117926426922</v>
+        <v>0.39847405125958935</v>
       </c>
     </row>
   </sheetData>
@@ -23952,7 +23964,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>8.4003499999999995E-2</v>
+        <v>8.4698999999999997E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24205,7 +24217,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>849836.09054311237</v>
+        <v>841863.9245237147</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24259,23 +24271,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>10725.394339351766</v>
+        <v>10719.61784947253</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>14379.260466824864</v>
+        <v>14363.775854841258</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>19277.904851868505</v>
+        <v>19246.773504922363</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>25845.391446599049</v>
+        <v>25789.757101015086</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>34650.251889960498</v>
+        <v>34557.042569200275</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24294,15 +24306,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>574263.96936608723</v>
+        <v>567346.61675443</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="281" t="s">
+      <c r="B14" s="280" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="282"/>
+      <c r="C14" s="281"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24310,7 +24322,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24319,7 +24331,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>11.046079044331362</v>
+        <v>10.931394429506236</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24329,20 +24341,20 @@
       <c r="C17" s="160">
         <v>0.45</v>
       </c>
-      <c r="E17" s="280" t="s">
+      <c r="E17" s="282" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="280"/>
-      <c r="G17" s="280"/>
-      <c r="H17" s="280"/>
-      <c r="I17" s="280"/>
+      <c r="F17" s="282"/>
+      <c r="G17" s="282"/>
+      <c r="H17" s="282"/>
+      <c r="I17" s="282"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="281" t="s">
+      <c r="B19" s="280" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="282"/>
+      <c r="C19" s="281"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24358,7 +24370,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.1545315069608271E-2</v>
+        <v>8.2128128342820614E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24376,7 +24388,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>782715.30999999994</v>
+        <v>762852.59</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24403,15 +24415,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>776216.30999999994</v>
+        <v>756353.59</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="281" t="s">
+      <c r="B28" s="280" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="282"/>
+      <c r="C28" s="281"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24419,7 +24431,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>104878.20299460468</v>
+        <v>104676.96687945152</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24428,7 +24440,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>574263.96936608723</v>
+        <v>567346.61675443</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24437,7 +24449,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>679142.17236069194</v>
+        <v>672023.58363388153</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24464,7 +24476,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>685641.17236069194</v>
+        <v>678522.58363388153</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24482,21 +24494,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>11.046079044331362</v>
+        <v>10.931394429506236</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31455,7 +31467,7 @@
       </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31526,7 +31538,7 @@
       </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32604,7 +32616,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-705.97402703809905</v>
+        <v>-688.05874641540345</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32641,7 +32653,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.5369177056398964</v>
+        <v>1.4979158288909062</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32702,7 +32714,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>2.1049165122589422</v>
+        <v>2.0515007086171613</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32763,7 +32775,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>816194.86</v>
+        <v>795482.53999999992</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32824,7 +32836,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>809695.86</v>
+        <v>788983.53999999992</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32861,7 +32873,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>1.5945392315372602</v>
+        <v>1.5537503273971873</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32898,7 +32910,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC14</f>
-        <v>64.574197304410234</v>
+        <v>62.922365419889935</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33033,7 +33045,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="150">AC153/AC157</f>
-        <v>100.81458250988142</v>
+        <v>98.256242588932793</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33070,7 +33082,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="150"/>
-        <v>-134.62867392101677</v>
+        <v>-131.1848225773434</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33107,7 +33119,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="153">AC157/AC153</f>
-        <v>9.9191999322318699E-3</v>
+        <v>1.0177470394259062E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33144,7 +33156,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-1.4164827057384552E-3</v>
+        <v>-1.4533642733410839E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33758,7 +33770,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>7.9625593329514469E-3</v>
+        <v>8.1698839046800455E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35376,7 +35388,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -35409,7 +35421,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35425,7 +35437,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>816194.86</v>
+        <v>795482.53999999992</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35445,7 +35457,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>809695.86</v>
+        <v>788983.53999999992</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35465,7 +35477,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-705.97402703809905</v>
+        <v>-688.05874641540345</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>255</v>
@@ -35485,7 +35497,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.5369177056398964</v>
+        <v>1.4979158288909062</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>256</v>
@@ -35505,7 +35517,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>2.1049165122589422</v>
+        <v>2.0515007086171613</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35525,7 +35537,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.5945392315372602</v>
+        <v>1.5537503273971873</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35534,7 +35546,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>64.574197304410234</v>
+        <v>62.922365419889935</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35770,7 +35782,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.4164827057384552E-3</v>
+        <v>-1.4533642733410839E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>282</v>
@@ -35786,7 +35798,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>9.9191999322318699E-3</v>
+        <v>1.0177470394259062E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>284</v>
@@ -35871,7 +35883,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>7.9625593329514469E-3</v>
+        <v>8.1698839046800455E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35925,8 +35937,51 @@
         <v>0.64278593560555031</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="268" t="s">
+        <v>450</v>
+      </c>
+      <c r="C57" s="268"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" s="174">
+        <f ca="1">Statement!AC159</f>
+        <v>98.256242588932793</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C59" s="174">
+        <f ca="1">Statement!AC160</f>
+        <v>-131.1848225773434</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="C60" s="175">
+        <f>Statement!AC166</f>
+        <v>-1.1843979332907461E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="C61" s="175">
+        <f>Statement!AC167</f>
+        <v>1.5943504538266578E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -35951,7 +36006,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I94"/>
+  <dimension ref="B1:I100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -36050,7 +36105,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC120</f>
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36079,7 +36134,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>816194.86</v>
+        <v>795482.53999999992</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36108,7 +36163,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>809695.86</v>
+        <v>788983.53999999992</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36137,7 +36192,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-705.97402703809905</v>
+        <v>-688.05874641540345</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36166,7 +36221,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>1.5369177056398964</v>
+        <v>1.4979158288909062</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36195,7 +36250,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>2.1049165122589422</v>
+        <v>2.0515007086171613</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36224,7 +36279,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>1.5945392315372602</v>
+        <v>1.5537503273971873</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36253,7 +36308,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>64.574197304410234</v>
+        <v>62.922365419889935</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37026,7 +37081,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-1.4164827057384552E-3</v>
+        <v>-1.4533642733410839E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37055,7 +37110,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>9.9191999322318699E-3</v>
+        <v>1.0177470394259062E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37378,7 +37433,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>7.9625593329514469E-3</v>
+        <v>8.1698839046800455E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37715,101 +37770,136 @@
       </c>
       <c r="I85" s="197"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C88" s="174">
+        <f>Statement!M159</f>
+        <v>-10.428876668619713</v>
+      </c>
+      <c r="D88" s="174">
+        <f>Statement!N159</f>
+        <v>-11.027449586238799</v>
+      </c>
+      <c r="E88" s="174">
+        <f>Statement!O159</f>
+        <v>-11.186718130267725</v>
+      </c>
+      <c r="F88" s="174">
+        <f>Statement!P159</f>
+        <v>-29.04398207317281</v>
+      </c>
+      <c r="G88" s="174">
+        <f>Statement!Q159</f>
+        <v>-64.413515151515142</v>
+      </c>
+      <c r="I88" s="174">
+        <f ca="1">Statement!AC159</f>
+        <v>98.256242588932793</v>
+      </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
-        <f>Statement!B193</f>
-        <v>Subscription and related services</v>
-      </c>
-      <c r="C89" s="175">
-        <f>Statement!M193</f>
-        <v>1</v>
-      </c>
-      <c r="D89" s="175">
-        <f>Statement!N193</f>
-        <v>0.35032560671733987</v>
-      </c>
-      <c r="E89" s="175">
-        <f>Statement!O193</f>
-        <v>0.28269819732506302</v>
-      </c>
-      <c r="F89" s="175">
-        <f>Statement!P193</f>
-        <v>0.18783094368819361</v>
-      </c>
-      <c r="G89" s="175">
-        <f>Statement!Q193</f>
-        <v>0.11679303852221261</v>
-      </c>
-      <c r="I89" s="197"/>
+      <c r="B89" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C89" s="174">
+        <f>Statement!M160</f>
+        <v>-8.1218035626781511</v>
+      </c>
+      <c r="D89" s="174">
+        <f>Statement!N160</f>
+        <v>-9.7187264564592724</v>
+      </c>
+      <c r="E89" s="174">
+        <f>Statement!O160</f>
+        <v>-10.229925893244395</v>
+      </c>
+      <c r="F89" s="174">
+        <f>Statement!P160</f>
+        <v>-26.916931225634531</v>
+      </c>
+      <c r="G89" s="174">
+        <f>Statement!Q160</f>
+        <v>-63.453625238165024</v>
+      </c>
+      <c r="I89" s="174">
+        <f ca="1">Statement!AC160</f>
+        <v>-131.1848225773434</v>
+      </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
-        <f>Statement!B194</f>
-        <v>Payment solutions</v>
+      <c r="B90" s="20" t="s">
+        <v>451</v>
       </c>
       <c r="C90" s="175">
-        <f>Statement!M194</f>
-        <v>1</v>
+        <f>Statement!M166</f>
+        <v>-0.67949613802741604</v>
       </c>
       <c r="D90" s="175">
-        <f>Statement!N194</f>
-        <v>0.20194475544853607</v>
+        <f>Statement!N166</f>
+        <v>-0.6454487202306789</v>
       </c>
       <c r="E90" s="175">
-        <f>Statement!O194</f>
-        <v>0.20725296039199673</v>
+        <f>Statement!O166</f>
+        <v>-0.37531960516307933</v>
       </c>
       <c r="F90" s="175">
-        <f>Statement!P194</f>
-        <v>7.5362012472254519E-2</v>
+        <f>Statement!P166</f>
+        <v>-0.14480971289597988</v>
       </c>
       <c r="G90" s="175">
-        <f>Statement!Q194</f>
-        <v>0.19381757420876744</v>
-      </c>
-      <c r="I90" s="197"/>
+        <f>Statement!Q166</f>
+        <v>-2.8394206300159597E-2</v>
+      </c>
+      <c r="I90" s="175">
+        <f>Statement!AC166</f>
+        <v>-1.1843979332907461E-2</v>
+      </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="str">
-        <f>Statement!B195</f>
-        <v>Network solutions</v>
+      <c r="B91" s="20" t="s">
+        <v>452</v>
       </c>
       <c r="C91" s="175">
-        <f>Statement!M195</f>
-        <v>1</v>
+        <f>Statement!M167</f>
+        <v>-0.66433900944037738</v>
       </c>
       <c r="D91" s="175">
-        <f>Statement!N195</f>
-        <v>0.40079591759015959</v>
+        <f>Statement!N167</f>
+        <v>-0.62333487593891279</v>
       </c>
       <c r="E91" s="175">
-        <f>Statement!O195</f>
-        <v>0.30837196025391822</v>
+        <f>Statement!O167</f>
+        <v>-0.36230244822466523</v>
       </c>
       <c r="F91" s="175">
-        <f>Statement!P195</f>
-        <v>0.26295284302826927</v>
+        <f>Statement!P167</f>
+        <v>-0.13978366558443878</v>
       </c>
       <c r="G91" s="175">
-        <f>Statement!Q195</f>
-        <v>0.14895979862293626</v>
-      </c>
-      <c r="I91" s="197"/>
+        <f>Statement!Q167</f>
+        <v>-2.7122854984799966E-2</v>
+      </c>
+      <c r="I91" s="175">
+        <f>Statement!AC167</f>
+        <v>1.5943504538266578E-2</v>
+      </c>
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>324</v>
+        <v>453</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -37843,6 +37933,98 @@
         <v>0</v>
       </c>
       <c r="I94" s="197"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
+        <f>Statement!B193</f>
+        <v>Subscription and related services</v>
+      </c>
+      <c r="C98" s="175">
+        <f>Statement!M193</f>
+        <v>1</v>
+      </c>
+      <c r="D98" s="175">
+        <f>Statement!N193</f>
+        <v>0.35032560671733987</v>
+      </c>
+      <c r="E98" s="175">
+        <f>Statement!O193</f>
+        <v>0.28269819732506302</v>
+      </c>
+      <c r="F98" s="175">
+        <f>Statement!P193</f>
+        <v>0.18783094368819361</v>
+      </c>
+      <c r="G98" s="175">
+        <f>Statement!Q193</f>
+        <v>0.11679303852221261</v>
+      </c>
+      <c r="I98" s="197"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
+        <f>Statement!B194</f>
+        <v>Payment solutions</v>
+      </c>
+      <c r="C99" s="175">
+        <f>Statement!M194</f>
+        <v>1</v>
+      </c>
+      <c r="D99" s="175">
+        <f>Statement!N194</f>
+        <v>0.20194475544853607</v>
+      </c>
+      <c r="E99" s="175">
+        <f>Statement!O194</f>
+        <v>0.20725296039199673</v>
+      </c>
+      <c r="F99" s="175">
+        <f>Statement!P194</f>
+        <v>7.5362012472254519E-2</v>
+      </c>
+      <c r="G99" s="175">
+        <f>Statement!Q194</f>
+        <v>0.19381757420876744</v>
+      </c>
+      <c r="I99" s="197"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="str">
+        <f>Statement!B195</f>
+        <v>Network solutions</v>
+      </c>
+      <c r="C100" s="175">
+        <f>Statement!M195</f>
+        <v>1</v>
+      </c>
+      <c r="D100" s="175">
+        <f>Statement!N195</f>
+        <v>0.40079591759015959</v>
+      </c>
+      <c r="E100" s="175">
+        <f>Statement!O195</f>
+        <v>0.30837196025391822</v>
+      </c>
+      <c r="F100" s="175">
+        <f>Statement!P195</f>
+        <v>0.26295284302826927</v>
+      </c>
+      <c r="G100" s="175">
+        <f>Statement!Q195</f>
+        <v>0.14895979862293626</v>
+      </c>
+      <c r="I100" s="197"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -37867,14 +38049,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="271" t="s">
+      <c r="C3" s="269" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="272"/>
-      <c r="F3" s="273" t="s">
+      <c r="D3" s="270"/>
+      <c r="F3" s="271" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="272"/>
+      <c r="G3" s="270"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37941,19 +38123,19 @@
       <c r="B7" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="269">
+      <c r="C7" s="272">
         <f>Statement!AA91</f>
         <v>-1.128040630847367E-2</v>
       </c>
-      <c r="D7" s="270"/>
-      <c r="F7" s="269">
+      <c r="D7" s="273"/>
+      <c r="F7" s="272">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.10407232100976505</v>
       </c>
-      <c r="G7" s="270"/>
+      <c r="G7" s="273"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -37980,19 +38162,19 @@
       <c r="B9" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="269">
+      <c r="C9" s="272">
         <f>Statement!AA92</f>
         <v>-3.438408639867079E-3</v>
       </c>
-      <c r="D9" s="270"/>
-      <c r="F9" s="269">
+      <c r="D9" s="273"/>
+      <c r="F9" s="272">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14728620387343588</v>
       </c>
-      <c r="G9" s="270"/>
+      <c r="G9" s="273"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -38019,19 +38201,19 @@
       <c r="B11" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="269">
+      <c r="C11" s="272">
         <f>Statement!AA93</f>
         <v>-1.5159644296297988E-2</v>
       </c>
-      <c r="D11" s="270"/>
-      <c r="F11" s="269">
+      <c r="D11" s="273"/>
+      <c r="F11" s="272">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3641068153842285E-2</v>
       </c>
-      <c r="G11" s="270"/>
+      <c r="G11" s="273"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -38058,19 +38240,19 @@
       <c r="B13" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="269">
+      <c r="C13" s="272">
         <f>Statement!AA99</f>
         <v>-2.704942363825261E-2</v>
       </c>
-      <c r="D13" s="270"/>
-      <c r="F13" s="269">
+      <c r="D13" s="273"/>
+      <c r="F13" s="272">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.0275760900383378E-2</v>
       </c>
-      <c r="G13" s="270"/>
+      <c r="G13" s="273"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -38097,19 +38279,19 @@
       <c r="B15" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="269">
+      <c r="C15" s="272">
         <f>Statement!AA100</f>
         <v>0.12727811527633723</v>
       </c>
-      <c r="D15" s="270"/>
-      <c r="F15" s="269">
+      <c r="D15" s="273"/>
+      <c r="F15" s="272">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.0484406104844064</v>
       </c>
-      <c r="G15" s="270"/>
+      <c r="G15" s="273"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -38136,19 +38318,19 @@
       <c r="B17" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="269">
+      <c r="C17" s="272">
         <f>Statement!AA102</f>
         <v>-0.35268309146135673</v>
       </c>
-      <c r="D17" s="270"/>
-      <c r="F17" s="269">
+      <c r="D17" s="273"/>
+      <c r="F17" s="272">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9327217125382263</v>
       </c>
-      <c r="G17" s="270"/>
+      <c r="G17" s="273"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -38175,22 +38357,22 @@
       <c r="B19" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="269">
+      <c r="C19" s="272">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>6.8019535468480524E-3</v>
       </c>
-      <c r="D19" s="270"/>
-      <c r="F19" s="269">
+      <c r="D19" s="273"/>
+      <c r="F19" s="272">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.2596050967804688E-2</v>
       </c>
-      <c r="G19" s="270"/>
+      <c r="G19" s="273"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -38217,22 +38399,22 @@
       <c r="B21" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="269">
+      <c r="C21" s="272">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.40000000000000008</v>
       </c>
-      <c r="D21" s="270"/>
-      <c r="F21" s="269">
+      <c r="D21" s="273"/>
+      <c r="F21" s="272">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G21" s="270"/>
+      <c r="G21" s="273"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38281,22 +38463,22 @@
       <c r="B25" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="269">
+      <c r="C25" s="272">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-4.9316211756226169E-4</v>
       </c>
-      <c r="D25" s="270"/>
-      <c r="F25" s="269">
+      <c r="D25" s="273"/>
+      <c r="F25" s="272">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-1.8751629362034932E-2</v>
       </c>
-      <c r="G25" s="270"/>
+      <c r="G25" s="273"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38324,22 +38506,22 @@
       <c r="B27" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="269">
+      <c r="C27" s="272">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-8.2306096659593236E-2</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="F27" s="269">
+      <c r="D27" s="273"/>
+      <c r="F27" s="272">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.35562834601296139</v>
       </c>
-      <c r="G27" s="270"/>
+      <c r="G27" s="273"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38367,22 +38549,22 @@
       <c r="B29" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="269">
+      <c r="C29" s="272">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.5164998759407821E-2</v>
       </c>
-      <c r="D29" s="270"/>
-      <c r="F29" s="269">
+      <c r="D29" s="273"/>
+      <c r="F29" s="272">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8535593413156616E-2</v>
       </c>
-      <c r="G29" s="270"/>
+      <c r="G29" s="273"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38431,22 +38613,22 @@
       <c r="B33" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="269">
+      <c r="C33" s="272">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>7.6465590484282074E-3</v>
       </c>
-      <c r="D33" s="270"/>
-      <c r="F33" s="269">
+      <c r="D33" s="273"/>
+      <c r="F33" s="272">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.2010297738974707E-2</v>
       </c>
-      <c r="G33" s="270"/>
+      <c r="G33" s="273"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="235" t="str">
@@ -38474,43 +38656,25 @@
       <c r="B35" s="206" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="269">
+      <c r="C35" s="272">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-8.0779526242585314E-3</v>
       </c>
-      <c r="D35" s="270"/>
-      <c r="F35" s="269">
+      <c r="D35" s="273"/>
+      <c r="F35" s="272">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-7.604627494945404E-2</v>
       </c>
-      <c r="G35" s="270"/>
+      <c r="G35" s="273"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38521,6 +38685,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
